--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$292</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q293"/>
+  <dimension ref="A1:Q292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22408,17 +22408,17 @@
       </c>
       <c r="C254" s="6" t="inlineStr">
         <is>
-          <t>2 chambres meublé, secteur Place Valois (Hochelaga), près métro Joliette</t>
+          <t>6½ (3 chambres), rez-de-chaussée avec cour et stationnement - 27e Avenue (Rosemont, près métro D'Iberville)</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>2117A, Rue Nicolet, Montréal</t>
+          <t>6749, 27e Avenue, Montréal</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
@@ -22433,7 +22433,7 @@
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I254" s="5" t="inlineStr">
@@ -22443,17 +22443,17 @@
       </c>
       <c r="J254" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L254" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M254" s="5" t="inlineStr">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="N254" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/21083818</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/20987825</t>
         </is>
       </c>
       <c r="O254" s="5" t="inlineStr">
@@ -22473,12 +22473,12 @@
       </c>
       <c r="P254" s="6" t="inlineStr">
         <is>
-          <t>Meublé et équipé (laveuse-sécheuse, frigo, cuisinière, lave-vaisselle inclus), internet inclus, secteur Place Valois, Walk Score 97, disponible 7 jours après acceptation, superficie et balcon non précisés</t>
+          <t>7 pièces, rez-de-chaussée de triplex avec sous-sol, cour et stationnement inclus, animaux permis sur analyse, disponible 1er juillet 2026, métro Fabre aussi accessible (~5 min)</t>
         </is>
       </c>
       <c r="Q254" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15AD50DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6C9AB9DDDDDDDDDDC&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -22495,22 +22495,22 @@
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>6½ (3 chambres), rez-de-chaussée avec cour et stationnement - 27e Avenue (Rosemont, près métro D'Iberville)</t>
+          <t>5½ semi-meublé, 3 grandes chambres - rue Saint-Hubert (Villeray, près métro Jarry)</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>6749, 27e Avenue, Montréal</t>
+          <t>7635, Rue Saint-Hubert, Montréal</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -22530,17 +22530,17 @@
       </c>
       <c r="J255" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K255" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M255" s="5" t="inlineStr">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="N255" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/20987825</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25817021</t>
         </is>
       </c>
       <c r="O255" s="5" t="inlineStr">
@@ -22560,19 +22560,19 @@
       </c>
       <c r="P255" s="6" t="inlineStr">
         <is>
-          <t>7 pièces, rez-de-chaussée de triplex avec sous-sol, cour et stationnement inclus, animaux permis sur analyse, disponible 1er juillet 2026, métro Fabre aussi accessible (~5 min)</t>
+          <t>Semi-meublé, animaux acceptés sous conditions, disponible 1er juillet 2026, à ~11 min du métro Jarry (proche de la limite de 12 min) ; à ne pas confondre avec le 7639 rue Saint-Hubert déjà répertorié (adresse voisine, annonce distincte)</t>
         </is>
       </c>
       <c r="Q255" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6C9AB9DDDDDDDDDDC&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD627F1DDDDDDDDDD2&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
@@ -22582,22 +22582,22 @@
       </c>
       <c r="C256" s="6" t="inlineStr">
         <is>
-          <t>5½ semi-meublé, 3 grandes chambres - rue Saint-Hubert (Villeray, près métro Jarry)</t>
+          <t>4 chambres meublé, Plateau-Mont-Royal (Marketplace)</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>7635, Rue Saint-Hubert, Montréal</t>
+          <t>3681, avenue Coloniale, Montréal (H2X 2Y7)</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -22607,7 +22607,7 @@
       </c>
       <c r="H256" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I256" s="5" t="inlineStr">
@@ -22617,7 +22617,7 @@
       </c>
       <c r="J256" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Mont-Royal ou Sherbrooke (à vérifier)</t>
         </is>
       </c>
       <c r="K256" s="5" t="inlineStr">
@@ -22627,17 +22627,17 @@
       </c>
       <c r="L256" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M256" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N256" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25817021</t>
+          <t>https://www.facebook.com/marketplace/item/1578661203923320</t>
         </is>
       </c>
       <c r="O256" s="5" t="inlineStr">
@@ -22647,19 +22647,19 @@
       </c>
       <c r="P256" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions, disponible 1er juillet 2026, à ~11 min du métro Jarry (proche de la limite de 12 min) ; à ne pas confondre avec le 7639 rue Saint-Hubert déjà répertorié (adresse voisine, annonce distincte)</t>
+          <t>Meublé, orienté étudiants, bail 1 an, dispo maintenant. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q256" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD627F1DDDDDDDDDD2&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/746058480_2385279625296639_1965210297754561149_n.jpg?stp=c93.0.895.895a_dst-jpg_tt6&amp;cstp=mx895x895&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=ngElLDKbnLQQ7kNvwHndFuc&amp;_nc_oc=AdpOYEcvWwImdnqaiYyy1pwfVcV2sab1mFRQ5KYGa5FE_CkYORsBa8yvv6PCL2lbQ7E&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EorVHkPe0HNRZxtO75C5fg&amp;_nc_ss=7f2a8&amp;oh=00_AQBlE2b8WT_3jlX6ddiFysYujtaCjsMiZRfF96JJT7pp3g&amp;oe=6A60805A</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
@@ -22669,17 +22669,17 @@
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>4 chambres meublé, Plateau-Mont-Royal (Marketplace)</t>
+          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>3681, avenue Coloniale, Montréal (H2X 2Y7)</t>
+          <t>2121 Avenue Papineau, app. 106, Montréal</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
@@ -22694,59 +22694,59 @@
       </c>
       <c r="H257" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I257" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J257" s="5" t="inlineStr">
+        <is>
+          <t>Papineau</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L257" s="5" t="inlineStr">
+        <is>
+          <t>11 (estimé)</t>
+        </is>
+      </c>
+      <c r="M257" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N257" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
+        </is>
+      </c>
+      <c r="O257" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I257" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J257" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal ou Sherbrooke (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K257" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L257" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M257" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N257" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1578661203923320</t>
-        </is>
-      </c>
-      <c r="O257" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P257" s="6" t="inlineStr">
         <is>
-          <t>Meublé, orienté étudiants, bail 1 an, dispo maintenant. Lien Facebook (connexion requise)</t>
+          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q257" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/746058480_2385279625296639_1965210297754561149_n.jpg?stp=c93.0.895.895a_dst-jpg_tt6&amp;cstp=mx895x895&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=ngElLDKbnLQQ7kNvwHndFuc&amp;_nc_oc=AdpOYEcvWwImdnqaiYyy1pwfVcV2sab1mFRQ5KYGa5FE_CkYORsBa8yvv6PCL2lbQ7E&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EorVHkPe0HNRZxtO75C5fg&amp;_nc_ss=7f2a8&amp;oh=00_AQBlE2b8WT_3jlX6ddiFysYujtaCjsMiZRfF96JJT7pp3g&amp;oe=6A60805A</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
@@ -22756,22 +22756,22 @@
       </c>
       <c r="C258" s="6" t="inlineStr">
         <is>
-          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
+          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>2121 Avenue Papineau, app. 106, Montréal</t>
+          <t>3855 rue St-André (H2L 3V9)</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -22781,7 +22781,7 @@
       </c>
       <c r="H258" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I258" s="5" t="inlineStr">
@@ -22791,17 +22791,17 @@
       </c>
       <c r="J258" s="5" t="inlineStr">
         <is>
-          <t>Papineau</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K258" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L258" s="5" t="inlineStr">
         <is>
-          <t>11 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M258" s="5" t="inlineStr">
@@ -22811,7 +22811,7 @@
       </c>
       <c r="N258" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
+          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
         </is>
       </c>
       <c r="O258" s="5" t="inlineStr">
@@ -22821,19 +22821,19 @@
       </c>
       <c r="P258" s="6" t="inlineStr">
         <is>
-          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
+          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q258" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
@@ -22843,7 +22843,7 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
@@ -22853,12 +22853,12 @@
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>3855 rue St-André (H2L 3V9)</t>
+          <t>4275 Rue de Bordeaux, Montréal</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -22868,59 +22868,59 @@
       </c>
       <c r="H259" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I259" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J259" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L259" s="5" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M259" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N259" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+        </is>
+      </c>
+      <c r="O259" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I259" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J259" s="5" t="inlineStr">
-        <is>
-          <t>Sherbrooke</t>
-        </is>
-      </c>
-      <c r="K259" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L259" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M259" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N259" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
-        </is>
-      </c>
-      <c r="O259" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P259" s="6" t="inlineStr">
         <is>
-          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
         </is>
       </c>
       <c r="Q259" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B260" s="5" t="inlineStr">
@@ -22930,7 +22930,7 @@
       </c>
       <c r="C260" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
@@ -22940,12 +22940,12 @@
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -22965,7 +22965,7 @@
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M260" s="5" t="inlineStr">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N260" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
         </is>
       </c>
       <c r="O260" s="5" t="inlineStr">
@@ -22995,19 +22995,19 @@
       </c>
       <c r="P260" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
         </is>
       </c>
       <c r="Q260" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
@@ -23017,7 +23017,7 @@
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
@@ -23027,12 +23027,12 @@
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>62 rue Rachel Est, Montréal</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="J261" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K261" s="5" t="inlineStr">
@@ -23062,7 +23062,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M261" s="5" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="N261" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
         </is>
       </c>
       <c r="O261" s="5" t="inlineStr">
@@ -23082,19 +23082,19 @@
       </c>
       <c r="P261" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
         </is>
       </c>
       <c r="Q261" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
@@ -23104,22 +23104,22 @@
       </c>
       <c r="C262" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>5½ rénové - Rosemont, 3 chambres + bureau (Marketplace)</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>n/d (secteur Rosemont, Montréal)</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -23129,59 +23129,59 @@
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
+          <t>3 (selon titre, à confirmer)</t>
+        </is>
+      </c>
+      <c r="I262" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J262" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L262" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M262" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N262" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1905640337262053</t>
+        </is>
+      </c>
+      <c r="O262" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I262" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J262" s="5" t="inlineStr">
-        <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K262" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L262" s="5" t="inlineStr">
-        <is>
-          <t>8 (estimé)</t>
-        </is>
-      </c>
-      <c r="M262" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N262" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
-        </is>
-      </c>
-      <c r="O262" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P262" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>Annonce titre seulement (« 5 1/2 rénové - Rosemont - 3 chambres + bureau »), aucune adresse ni description détaillée disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q262" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/787761292_1065504692896878_4836055761486525916_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=MOCJ79afpPoQ7kNvwHB1OUw&amp;_nc_oc=Adr_kZR22WI-TaE-t3PMKjYftS_SVUX2bAUlPv8Qz_8bghKNDkoSXa2JK6t9RqxndLc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=wgjL71BuqJilZmCDsgzwAw&amp;_nc_ss=7f289&amp;oh=00_AQIu4EnP-eitSmW9cB7PzqKfHZ07AHdQlQEc8LQQHjmjMA&amp;oe=6A9DD845</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
@@ -23191,7 +23191,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové - Rosemont, 3 chambres + bureau (Marketplace)</t>
+          <t>Logement 5 1/2 rénové, 3 chambres + bureau - Rosemont (Marketplace)</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Rosemont, Montréal)</t>
+          <t>n/d (secteur Rosemont-La Petite-Patrie, Montréal)</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>3 (selon titre, à confirmer)</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="I263" s="5" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="N263" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1905640337262053</t>
+          <t>https://www.facebook.com/marketplace/item/1613584236892605</t>
         </is>
       </c>
       <c r="O263" s="5" t="inlineStr">
@@ -23256,19 +23256,19 @@
       </c>
       <c r="P263" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (« 5 1/2 rénové - Rosemont - 3 chambres + bureau »), aucune adresse ni description détaillée disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Annonce titre seulement (« Logement 5 1/2 rénové Rosemont - 3 chambres + bureau »), aucune adresse ni description détaillée disponible via le scraper. Nombre de chambres selon le titre (3 + bureau). Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q263" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/787761292_1065504692896878_4836055761486525916_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=MOCJ79afpPoQ7kNvwHB1OUw&amp;_nc_oc=Adr_kZR22WI-TaE-t3PMKjYftS_SVUX2bAUlPv8Qz_8bghKNDkoSXa2JK6t9RqxndLc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=wgjL71BuqJilZmCDsgzwAw&amp;_nc_ss=7f289&amp;oh=00_AQIu4EnP-eitSmW9cB7PzqKfHZ07AHdQlQEc8LQQHjmjMA&amp;oe=6A9DD845</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/789845450_1602489944997832_5213134105176151966_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xzqo9iyYcAkQ7kNvwHRvmWj&amp;_nc_oc=Adp04UM8mMS7TYZztbruBwtONw22BOWfpCFSRMezlhO7JaSrV4L2CIIxMvRmLg4IrzQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=iDnTU3IQw0eGZCC-IJSGrw&amp;_nc_ss=7f2a8&amp;oh=00_AQKWwqFPn5wiyRr8UhOqIiE2fW-83zbjH04dhSzspmsjgw&amp;oe=6A9A671F</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
@@ -23278,7 +23278,7 @@
       </c>
       <c r="C264" s="6" t="inlineStr">
         <is>
-          <t>Logement 5 1/2 rénové, 3 chambres + bureau - Rosemont (Marketplace)</t>
+          <t>4½ rénové (2 chambres), semi-meublé - Plaza St-Hubert (Rosemont), près du métro Beaubien</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
@@ -23288,12 +23288,12 @@
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Rosemont-La Petite-Patrie, Montréal)</t>
+          <t>6617, Rue Saint-Hubert, app. 201, Montréal</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -23303,7 +23303,7 @@
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I264" s="5" t="inlineStr">
@@ -23313,27 +23313,27 @@
       </c>
       <c r="J264" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K264" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L264" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M264" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N264" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1613584236892605</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/26894928</t>
         </is>
       </c>
       <c r="O264" s="5" t="inlineStr">
@@ -23343,12 +23343,12 @@
       </c>
       <c r="P264" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (« Logement 5 1/2 rénové Rosemont - 3 chambres + bureau »), aucune adresse ni description détaillée disponible via le scraper. Nombre de chambres selon le titre (3 + bureau). Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Entièrement rénové (finitions contemporaines), semi-meublé, climatisation et internet inclus, animaux acceptés sous conditions, disponible 2 jours après acceptation, en plein Plaza St-Hubert, proche marché Jean-Talon et Petite Italie, Walk Score 97. Balcon et superficie non précisés.</t>
         </is>
       </c>
       <c r="Q264" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/789845450_1602489944997832_5213134105176151966_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xzqo9iyYcAkQ7kNvwHRvmWj&amp;_nc_oc=Adp04UM8mMS7TYZztbruBwtONw22BOWfpCFSRMezlhO7JaSrV4L2CIIxMvRmLg4IrzQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=iDnTU3IQw0eGZCC-IJSGrw&amp;_nc_ss=7f2a8&amp;oh=00_AQKWwqFPn5wiyRr8UhOqIiE2fW-83zbjH04dhSzspmsjgw&amp;oe=6A9A671F</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4631F1DDDDDDDDDDC&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové (2 chambres), semi-meublé - Plaza St-Hubert (Rosemont), près du métro Beaubien</t>
+          <t>4½ (2 chambres) - secteur résidentiel calme, 23e Avenue (Rosemont)</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
@@ -23375,12 +23375,12 @@
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>6617, Rue Saint-Hubert, app. 201, Montréal</t>
+          <t>6001, 23e Avenue, app. 3, Montréal</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -23400,7 +23400,7 @@
       </c>
       <c r="J265" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Beaubien ou Rosemont (estimé)</t>
         </is>
       </c>
       <c r="K265" s="5" t="inlineStr">
@@ -23410,7 +23410,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M265" s="5" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="N265" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/26894928</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/22497736</t>
         </is>
       </c>
       <c r="O265" s="5" t="inlineStr">
@@ -23430,12 +23430,12 @@
       </c>
       <c r="P265" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové (finitions contemporaines), semi-meublé, climatisation et internet inclus, animaux acceptés sous conditions, disponible 2 jours après acceptation, en plein Plaza St-Hubert, proche marché Jean-Talon et Petite Italie, Walk Score 97. Balcon et superficie non précisés.</t>
+          <t>Bien aménagé, lumineux, finitions soignées, secteur résidentiel paisible près parcs/commerces/écoles, disponible 5 jours après acceptation, Walk Score 85. Balcon, animaux et chauffage non précisés dans l'annonce.</t>
         </is>
       </c>
       <c r="Q265" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4631F1DDDDDDDDDDC&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4AE812DDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -23452,22 +23452,22 @@
       </c>
       <c r="C266" s="6" t="inlineStr">
         <is>
-          <t>4½ (2 chambres) - secteur résidentiel calme, 23e Avenue (Rosemont)</t>
+          <t>4½ (2 chambres) - rue De La Roche (Plateau)</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>6001, 23e Avenue, app. 3, Montréal</t>
+          <t>4417, Rue De La Roche, app. 4, Montréal</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="J266" s="5" t="inlineStr">
         <is>
-          <t>Beaubien ou Rosemont (estimé)</t>
+          <t>Mont-Royal (estimé)</t>
         </is>
       </c>
       <c r="K266" s="5" t="inlineStr">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="L266" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M266" s="5" t="inlineStr">
@@ -23507,7 +23507,7 @@
       </c>
       <c r="N266" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/22497736</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/14734354</t>
         </is>
       </c>
       <c r="O266" s="5" t="inlineStr">
@@ -23517,19 +23517,19 @@
       </c>
       <c r="P266" s="6" t="inlineStr">
         <is>
-          <t>Bien aménagé, lumineux, finitions soignées, secteur résidentiel paisible près parcs/commerces/écoles, disponible 5 jours après acceptation, Walk Score 85. Balcon, animaux et chauffage non précisés dans l'annonce.</t>
+          <t>Peu de détails dans l'annonce (balcon, superficie, animaux et chauffage non précisés), disponible 24 août 2026, Walk Score 99, secteur à confirmer avant de contacter.</t>
         </is>
       </c>
       <c r="Q266" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4AE812DDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2DDB74DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>4½ (2 chambres) - rue De La Roche (Plateau)</t>
+          <t>2 chambres rénové, près de la rue Mont-Royal et du métro Mont-Royal (Marketplace)</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>4417, Rue De La Roche, app. 4, Montréal</t>
+          <t>4408, Avenue de l'Hôtel-de-Ville, Montréal</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -23574,7 +23574,7 @@
       </c>
       <c r="J267" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal (estimé)</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K267" s="5" t="inlineStr">
@@ -23584,17 +23584,17 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M267" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N267" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/14734354</t>
+          <t>https://www.facebook.com/marketplace/item/3643447005808131</t>
         </is>
       </c>
       <c r="O267" s="5" t="inlineStr">
@@ -23604,19 +23604,19 @@
       </c>
       <c r="P267" s="6" t="inlineStr">
         <is>
-          <t>Peu de détails dans l'annonce (balcon, superficie, animaux et chauffage non précisés), disponible 24 août 2026, Walk Score 99, secteur à confirmer avant de contacter.</t>
+          <t>Nouvellement rénové, meublé (table, chaises, canapé, lits), climatisation incluse, isolation phonique/thermique complète, plafonds hauts, animaux acceptés. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q267" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2DDB74DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/769082955_1572138077922196_3928924517892675151_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=5lbjrhSykR4Q7kNvwGXZEsS&amp;_nc_oc=AdosPHcT82UDB5JXJB3hFRrzA2ywy8Iz4eDC9_v14IG5fPngcGQrop8r6fkrAZcfxOg&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=hnqIHFjbxMu6V7YVFERN2g&amp;_nc_ss=7f2a8&amp;oh=00_AQFUCFiOoITnnQEKag8_p25qfElq9MW43hMXPo8TnhpJ_g&amp;oe=6A91378D</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -23626,22 +23626,22 @@
       </c>
       <c r="C268" s="6" t="inlineStr">
         <is>
-          <t>2 chambres rénové, près de la rue Mont-Royal et du métro Mont-Royal (Marketplace)</t>
+          <t>Appartement 5½ (Hochelaga) - infos limitées, à vérifier via Facebook Marketplace</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>4408, Avenue de l'Hôtel-de-Ville, Montréal</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -23651,7 +23651,7 @@
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I268" s="5" t="inlineStr">
@@ -23661,17 +23661,17 @@
       </c>
       <c r="J268" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>n/d (secteur Hochelaga)</t>
         </is>
       </c>
       <c r="K268" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L268" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M268" s="5" t="inlineStr">
@@ -23681,7 +23681,7 @@
       </c>
       <c r="N268" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/3643447005808131</t>
+          <t>https://www.facebook.com/marketplace/item/1020807880801669</t>
         </is>
       </c>
       <c r="O268" s="5" t="inlineStr">
@@ -23691,19 +23691,19 @@
       </c>
       <c r="P268" s="6" t="inlineStr">
         <is>
-          <t>Nouvellement rénové, meublé (table, chaises, canapé, lits), climatisation incluse, isolation phonique/thermique complète, plafonds hauts, animaux acceptés. Lien Facebook (connexion requise)</t>
+          <t>Fiche Marketplace très peu détaillée (titre et prix seulement, pas de description ni superficie). Chambres estimées à 3 d'après le type 5½. Le lien exige une connexion Facebook pour voir les détails complets.</t>
         </is>
       </c>
       <c r="Q268" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/769082955_1572138077922196_3928924517892675151_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=5lbjrhSykR4Q7kNvwGXZEsS&amp;_nc_oc=AdosPHcT82UDB5JXJB3hFRrzA2ywy8Iz4eDC9_v14IG5fPngcGQrop8r6fkrAZcfxOg&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=hnqIHFjbxMu6V7YVFERN2g&amp;_nc_ss=7f2a8&amp;oh=00_AQFUCFiOoITnnQEKag8_p25qfElq9MW43hMXPo8TnhpJ_g&amp;oe=6A91378D</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/740733947_28734879242768603_2405899251014488449_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q9ViAyeDpUAQ7kNvwFF85BL&amp;_nc_oc=Adr4Bry90yP1945bAQ7iQ52U9LuxXUfcltCcAJNNZMjNUaTJQ7tsFLsd_jtuJfl42Ps&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=rTvNKBKykO1Kn418ORNEfA&amp;_nc_ss=7f2a8&amp;oh=00_AQHwScRvAsPs8uZWD-UEV1uK_8325MQziNdaYa1h63-U7A&amp;oe=6A8FDC27</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
@@ -23713,22 +23713,22 @@
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>Appartement 5½ (Hochelaga) - infos limitées, à vérifier via Facebook Marketplace</t>
+          <t>Appartement 2 chambres + bureau, quartier central Plateau, à ~11 min du métro Sherbrooke (Marketplace)</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>3984 Rue de Bullion, Montréal, QC H2W 2E4</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -23738,59 +23738,59 @@
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I269" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J269" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L269" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M269" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N269" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1528694045314689</t>
+        </is>
+      </c>
+      <c r="O269" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I269" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J269" s="5" t="inlineStr">
-        <is>
-          <t>n/d (secteur Hochelaga)</t>
-        </is>
-      </c>
-      <c r="K269" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L269" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M269" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N269" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1020807880801669</t>
-        </is>
-      </c>
-      <c r="O269" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="P269" s="6" t="inlineStr">
         <is>
-          <t>Fiche Marketplace très peu détaillée (titre et prix seulement, pas de description ni superficie). Chambres estimées à 3 d'après le type 5½. Le lien exige une connexion Facebook pour voir les détails complets.</t>
+          <t>Deux chambres fermees + un espace de bureau, electromenagers inclus, bail 1 an, disponible maintenant, quartier central (Walk Score 100, Bike Score 98). Superficie non indiquee. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q269" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/740733947_28734879242768603_2405899251014488449_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q9ViAyeDpUAQ7kNvwFF85BL&amp;_nc_oc=Adr4Bry90yP1945bAQ7iQ52U9LuxXUfcltCcAJNNZMjNUaTJQ7tsFLsd_jtuJfl42Ps&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=rTvNKBKykO1Kn418ORNEfA&amp;_nc_ss=7f2a8&amp;oh=00_AQHwScRvAsPs8uZWD-UEV1uK_8325MQziNdaYa1h63-U7A&amp;oe=6A8FDC27</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/722994642_10164255701674834_4384640404152492239_n.jpg?stp=c342.0.1365.1365a_dst-jpg_tt6&amp;cstp=mx1365x1365&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=P20jq1k6qjIQ7kNvwF35WB_&amp;_nc_oc=AdrWOhKe-TO43O_pi7-zm4f94i1vfAPIWDFFxE3h49ZzbSfBqp_EeJowVqfsNEyEzmY&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=-RRMTc1fIutY57-pjw9YmQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHvo5JUjbFeFE0mNam3RiJtgV0tjwf8rAM1aebC8RWpDQ&amp;oe=6A8E14C9</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
@@ -23800,22 +23800,22 @@
       </c>
       <c r="C270" s="6" t="inlineStr">
         <is>
-          <t>Appartement 2 chambres + bureau, quartier central Plateau, à ~11 min du métro Sherbrooke (Marketplace)</t>
+          <t>5½ rénové (2 chambres), garde-robes walk-in - secteur Villeray, à 5 min du métro Jarry</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>3984 Rue de Bullion, Montréal, QC H2W 2E4</t>
+          <t>n/d (Montréal, QC H2R 2P3)</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -23830,12 +23830,12 @@
       </c>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J270" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K270" s="5" t="inlineStr">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="L270" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M270" s="5" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="N270" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1528694045314689</t>
+          <t>https://www.facebook.com/marketplace/item/1318066247058264</t>
         </is>
       </c>
       <c r="O270" s="5" t="inlineStr">
@@ -23865,19 +23865,19 @@
       </c>
       <c r="P270" s="6" t="inlineStr">
         <is>
-          <t>Deux chambres fermees + un espace de bureau, electromenagers inclus, bail 1 an, disponible maintenant, quartier central (Walk Score 100, Bike Score 98). Superficie non indiquee. Lien Facebook (connexion requise).</t>
+          <t>Entièrement rénové (cuisine avec îlot, planchers refaits), chambre principale avec walk-in, 2e chambre avec grand garde-robe, thermopompe, porte-patio vers cour arrière (pas de balcon), à distance de marche du métro Jarry et du marché Jean-Talon, références demandées, aucun animal, disponible 1er oct. 2026, bail 1 an. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q270" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/722994642_10164255701674834_4384640404152492239_n.jpg?stp=c342.0.1365.1365a_dst-jpg_tt6&amp;cstp=mx1365x1365&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=P20jq1k6qjIQ7kNvwF35WB_&amp;_nc_oc=AdrWOhKe-TO43O_pi7-zm4f94i1vfAPIWDFFxE3h49ZzbSfBqp_EeJowVqfsNEyEzmY&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=-RRMTc1fIutY57-pjw9YmQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHvo5JUjbFeFE0mNam3RiJtgV0tjwf8rAM1aebC8RWpDQ&amp;oe=6A8E14C9</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/730304009_10243338752987620_3251931066748678009_n.jpg?stp=c341.0.1367.1367a_dst-jpg_tt6&amp;cstp=mx1367x1367&amp;ctp=s565x565&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=T1M2AeYt3WkQ7kNvwEbtDR9&amp;_nc_oc=AdqdPqtbLbupPJRjBJ9G6l5MxrQhR9IhCxSGNw-xvzoSzkXhl2b7yw4yEMa1hIVXQLo&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=gi1y626B7giI3AkvJxbp7A&amp;_nc_ss=7f2a8&amp;oh=00_AQHDh36TzcRlsSalStNzCi2WPYfPNl7gzA_gMGdg3e-VhQ&amp;oe=6A8B7951</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
@@ -23887,22 +23887,22 @@
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (2 chambres), garde-robes walk-in - secteur Villeray, à 5 min du métro Jarry</t>
+          <t>5 1/2 (2 chambres) avec bureau, 2e étage - rue Saint-Viateur Ouest (Mile-End/Plateau)</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2R 2P3)</t>
+          <t>229, Rue Saint-Viateur Ouest, app. 3, Montréal</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -23917,12 +23917,12 @@
       </c>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J271" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Rosemont (estimé)</t>
         </is>
       </c>
       <c r="K271" s="5" t="inlineStr">
@@ -23932,17 +23932,17 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M271" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N271" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1318066247058264</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/12176453</t>
         </is>
       </c>
       <c r="O271" s="5" t="inlineStr">
@@ -23952,19 +23952,19 @@
       </c>
       <c r="P271" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové (cuisine avec îlot, planchers refaits), chambre principale avec walk-in, 2e chambre avec grand garde-robe, thermopompe, porte-patio vers cour arrière (pas de balcon), à distance de marche du métro Jarry et du marché Jean-Talon, références demandées, aucun animal, disponible 1er oct. 2026, bail 1 an. Lien Facebook (connexion requise).</t>
+          <t>Salle a manger, bureau, semi-meuble (frigo et cuisiniere inclus), locataire paie chauffage et electricite, animaux et fumeurs non acceptes, disponible 5 jours apres acceptation, secteur Mile-End/Plateau, Walk Score 100</t>
         </is>
       </c>
       <c r="Q271" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/730304009_10243338752987620_3251931066748678009_n.jpg?stp=c341.0.1367.1367a_dst-jpg_tt6&amp;cstp=mx1367x1367&amp;ctp=s565x565&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=T1M2AeYt3WkQ7kNvwEbtDR9&amp;_nc_oc=AdqdPqtbLbupPJRjBJ9G6l5MxrQhR9IhCxSGNw-xvzoSzkXhl2b7yw4yEMa1hIVXQLo&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=gi1y626B7giI3AkvJxbp7A&amp;_nc_ss=7f2a8&amp;oh=00_AQHDh36TzcRlsSalStNzCi2WPYfPNl7gzA_gMGdg3e-VhQ&amp;oe=6A8B7951</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4189D5DDDDDDDDDDB&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
@@ -23974,22 +23974,22 @@
       </c>
       <c r="C272" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 (2 chambres) avec bureau, 2e étage - rue Saint-Viateur Ouest (Mile-End/Plateau)</t>
+          <t>Logement 6 1/2 à louer dans Villeray (Marketplace)</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>229, Rue Saint-Viateur Ouest, app. 3, Montréal</t>
+          <t>n/d (secteur Villeray, Montréal)</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
@@ -24009,27 +24009,27 @@
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>Rosemont (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M272" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N272" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/12176453</t>
+          <t>https://www.facebook.com/marketplace/item/1020450404083699</t>
         </is>
       </c>
       <c r="O272" s="5" t="inlineStr">
@@ -24039,19 +24039,19 @@
       </c>
       <c r="P272" s="6" t="inlineStr">
         <is>
-          <t>Salle a manger, bureau, semi-meuble (frigo et cuisiniere inclus), locataire paie chauffage et electricite, animaux et fumeurs non acceptes, disponible 5 jours apres acceptation, secteur Mile-End/Plateau, Walk Score 100</t>
+          <t>Annonce titre seulement (« Logement a loué 6 1/2 dans villeray »), aucune description ni adresse disponible via le scraper. Nombre de chambres estimé à 3 selon la nomenclature standard d'un 6½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q272" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4189D5DDDDDDDDDDB&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/763805631_1503784241770162_4967544372375745805_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=101&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=jGqmb0NgpJoQ7kNvwFH3YjO&amp;_nc_oc=AdoY1EsSNcq7zLnPmamdgZYnFxscFtqiBT5k0ZKtBAzp-lkY2KX7KLoaQ55MsEJFKcc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=Jh4pE02jeamMrq9aD_orfQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHVB3CnZ5QJ3Jhj2o-a6Li1sE8vgz3c5ABW_l7p_nT4sA&amp;oe=6A790FD8</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
@@ -24061,22 +24061,22 @@
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>Logement 6 1/2 à louer dans Villeray (Marketplace)</t>
+          <t>2 chambres - rue De Lanaudière (Rosemont), à 6 min du métro Jean-Talon</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Villeray, Montréal)</t>
+          <t>6583, Rue De Lanaudière, Montréal</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -24086,7 +24086,7 @@
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I273" s="5" t="inlineStr">
@@ -24096,27 +24096,27 @@
       </c>
       <c r="J273" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K273" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M273" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N273" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1020450404083699</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/20257676</t>
         </is>
       </c>
       <c r="O273" s="5" t="inlineStr">
@@ -24126,12 +24126,12 @@
       </c>
       <c r="P273" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (« Logement a loué 6 1/2 dans villeray »), aucune description ni adresse disponible via le scraper. Nombre de chambres estimé à 3 selon la nomenclature standard d'un 6½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Chauffage central inclus + 5 électroménagers, quintuplex de 1932, disponible 1er sept. 2026, Walk Score 94</t>
         </is>
       </c>
       <c r="Q273" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/763805631_1503784241770162_4967544372375745805_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=101&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=jGqmb0NgpJoQ7kNvwFH3YjO&amp;_nc_oc=AdoY1EsSNcq7zLnPmamdgZYnFxscFtqiBT5k0ZKtBAzp-lkY2KX7KLoaQ55MsEJFKcc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=Jh4pE02jeamMrq9aD_orfQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHVB3CnZ5QJ3Jhj2o-a6Li1sE8vgz3c5ABW_l7p_nT4sA&amp;oe=6A790FD8</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15EA61DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -24148,22 +24148,22 @@
       </c>
       <c r="C274" s="6" t="inlineStr">
         <is>
-          <t>2 chambres - rue De Lanaudière (Rosemont), à 6 min du métro Jean-Talon</t>
+          <t>2 chambres avec cour privée - rue Demers (Plateau), près du métro Laurier</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>6583, Rue De Lanaudière, Montréal</t>
+          <t>170, Rue Demers, Montréal</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -24178,22 +24178,22 @@
       </c>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J274" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K274" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L274" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8-10 (estimé)</t>
         </is>
       </c>
       <c r="M274" s="5" t="inlineStr">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="N274" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/20257676</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/15892581</t>
         </is>
       </c>
       <c r="O274" s="5" t="inlineStr">
@@ -24213,19 +24213,19 @@
       </c>
       <c r="P274" s="6" t="inlineStr">
         <is>
-          <t>Chauffage central inclus + 5 électroménagers, quintuplex de 1932, disponible 1er sept. 2026, Walk Score 94</t>
+          <t>Thermopompe murale incluse, meublé, cour privée (pas de balcon), animaux non acceptés, secteur Mile End, Walk Score 99</t>
         </is>
       </c>
       <c r="Q274" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15EA61DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADFCE64DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
@@ -24235,7 +24235,7 @@
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>2 chambres avec cour privée - rue Demers (Plateau), près du métro Laurier</t>
+          <t>Spacieux 4½ rénové, 2 chambres - avenue Henri-Julien (Plateau), à 2 min du métro Laurier</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
@@ -24245,12 +24245,12 @@
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>170, Rue Demers, Montréal</t>
+          <t>5010, Avenue Henri-Julien, Montréal</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -24265,7 +24265,7 @@
       </c>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J275" s="5" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>8-10 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M275" s="5" t="inlineStr">
@@ -24290,7 +24290,7 @@
       </c>
       <c r="N275" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/15892581</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/13104221</t>
         </is>
       </c>
       <c r="O275" s="5" t="inlineStr">
@@ -24300,12 +24300,12 @@
       </c>
       <c r="P275" s="6" t="inlineStr">
         <is>
-          <t>Thermopompe murale incluse, meublé, cour privée (pas de balcon), animaux non acceptés, secteur Mile End, Walk Score 99</t>
+          <t>Cuisine et salle de bain rénovées, hauts plafonds, immeuble de 1910, chats acceptés, disponible 7 jours après acceptation, Walk Score 99</t>
         </is>
       </c>
       <c r="Q275" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADFCE64DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA41C20BDDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -24322,7 +24322,7 @@
       </c>
       <c r="C276" s="6" t="inlineStr">
         <is>
-          <t>Spacieux 4½ rénové, 2 chambres - avenue Henri-Julien (Plateau), à 2 min du métro Laurier</t>
+          <t>4½ avec cour arrière privée - rue Rivard (Plateau), à quelques pas du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
@@ -24332,7 +24332,7 @@
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>5010, Avenue Henri-Julien, Montréal</t>
+          <t>4452, Rue Rivard, Montréal</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
@@ -24352,12 +24352,12 @@
       </c>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J276" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K276" s="5" t="inlineStr">
@@ -24367,7 +24367,7 @@
       </c>
       <c r="L276" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="M276" s="5" t="inlineStr">
@@ -24377,7 +24377,7 @@
       </c>
       <c r="N276" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/13104221</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/14560801</t>
         </is>
       </c>
       <c r="O276" s="5" t="inlineStr">
@@ -24387,19 +24387,19 @@
       </c>
       <c r="P276" s="6" t="inlineStr">
         <is>
-          <t>Cuisine et salle de bain rénovées, hauts plafonds, immeuble de 1910, chats acceptés, disponible 7 jours après acceptation, Walk Score 99</t>
+          <t>Cour arrière privée, lumineux et bien entretenu, Walk Score 100, animaux acceptés sous conditions, disponible 1er août 2026</t>
         </is>
       </c>
       <c r="Q276" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA41C20BDDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA44883FDDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
@@ -24409,22 +24409,22 @@
       </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
-          <t>4½ avec cour arrière privée - rue Rivard (Plateau), à quelques pas du métro Mont-Royal</t>
+          <t>Grand 6 1/2, 2 chambres - rue Jean-Talon Est (Rosemont, près marché Jean-Talon)</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>4452, Rue Rivard, Montréal</t>
+          <t>274, Rue Jean-Talon Est, app. 302, Montréal</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -24439,22 +24439,22 @@
       </c>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J277" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K277" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M277" s="5" t="inlineStr">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="N277" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/14560801</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/14545078</t>
         </is>
       </c>
       <c r="O277" s="5" t="inlineStr">
@@ -24474,19 +24474,19 @@
       </c>
       <c r="P277" s="6" t="inlineStr">
         <is>
-          <t>Cour arrière privée, lumineux et bien entretenu, Walk Score 100, animaux acceptés sous conditions, disponible 1er août 2026</t>
+          <t>6 pièces au total, concept ouvert, comptoirs de quartz, walk score 100, dispo 1er juillet 2026, près du marché Jean-Talon, superficie non précisée</t>
         </is>
       </c>
       <c r="Q277" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA44883FDDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE4013DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
@@ -24496,7 +24496,7 @@
       </c>
       <c r="C278" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2, 2 chambres - rue Jean-Talon Est (Rosemont, près marché Jean-Talon)</t>
+          <t>Cession de bail 7½, Rosemont-La Petite-Patrie (Marketplace)</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
@@ -24506,12 +24506,12 @@
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>274, Rue Jean-Talon Est, app. 302, Montréal</t>
+          <t>n/d (Montréal, QC H2G 1T5)</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I278" s="5" t="inlineStr">
@@ -24531,27 +24531,27 @@
       </c>
       <c r="J278" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K278" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L278" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M278" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N278" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/14545078</t>
+          <t>https://www.facebook.com/marketplace/item/1375157431101110</t>
         </is>
       </c>
       <c r="O278" s="5" t="inlineStr">
@@ -24561,12 +24561,12 @@
       </c>
       <c r="P278" s="6" t="inlineStr">
         <is>
-          <t>6 pièces au total, concept ouvert, comptoirs de quartz, walk score 100, dispo 1er juillet 2026, près du marché Jean-Talon, superficie non précisée</t>
+          <t>Cession de bail. Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q278" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE4013DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702670571_1710902896599779_1133264177050399379_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=akFqSvK3rfAQ7kNvwG-Cqey&amp;_nc_oc=Adrp5N9Rg13Pf-obfNZqB1ZqwyOcgjJji8vk0ggvRJiA9uCo-xDJXuQAit6O7YIGPW0&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQBG56r36JKH2gkm4Baddcm0ylaFria-4p9Il0vYABnyMg&amp;oe=6A607060</t>
         </is>
       </c>
     </row>
@@ -24583,22 +24583,22 @@
       </c>
       <c r="C279" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail 7½, Rosemont-La Petite-Patrie (Marketplace)</t>
+          <t>Condo 2 chambres semi-meublé, stationnement intérieur - rue Villeray, à 9 min du métro Fabre</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 1T5)</t>
+          <t>1414 Rue Villeray, app. 105, Montréal</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -24608,59 +24608,59 @@
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I279" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J279" s="5" t="inlineStr">
+        <is>
+          <t>Fabre</t>
+        </is>
+      </c>
+      <c r="K279" s="5" t="inlineStr">
+        <is>
+          <t>bleue</t>
+        </is>
+      </c>
+      <c r="L279" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M279" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N279" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/25583093</t>
+        </is>
+      </c>
+      <c r="O279" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I279" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J279" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K279" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L279" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M279" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N279" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1375157431101110</t>
-        </is>
-      </c>
-      <c r="O279" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="P279" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail. Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
+          <t>Immeuble de 2011 (30 unités), RDC, plancher chauffant salle de bain, stationnement intérieur avec borne de recharge, casier de rangement, buanderie commune, terrasse sur le toit, Walk Score 94, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q279" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702670571_1710902896599779_1133264177050399379_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=akFqSvK3rfAQ7kNvwG-Cqey&amp;_nc_oc=Adrp5N9Rg13Pf-obfNZqB1ZqwyOcgjJji8vk0ggvRJiA9uCo-xDJXuQAit6O7YIGPW0&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQBG56r36JKH2gkm4Baddcm0ylaFria-4p9Il0vYABnyMg&amp;oe=6A607060</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD77D67DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -24670,22 +24670,22 @@
       </c>
       <c r="C280" s="6" t="inlineStr">
         <is>
-          <t>Condo 2 chambres semi-meublé, stationnement intérieur - rue Villeray, à 9 min du métro Fabre</t>
+          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>1414 Rue Villeray, app. 105, Montréal</t>
+          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -24705,17 +24705,17 @@
       </c>
       <c r="J280" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K280" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L280" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M280" s="5" t="inlineStr">
@@ -24725,7 +24725,7 @@
       </c>
       <c r="N280" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/25583093</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
         </is>
       </c>
       <c r="O280" s="5" t="inlineStr">
@@ -24735,12 +24735,12 @@
       </c>
       <c r="P280" s="6" t="inlineStr">
         <is>
-          <t>Immeuble de 2011 (30 unités), RDC, plancher chauffant salle de bain, stationnement intérieur avec borne de recharge, casier de rangement, buanderie commune, terrasse sur le toit, Walk Score 94, dispo 1er juillet 2026</t>
+          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
         </is>
       </c>
       <c r="Q280" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD77D67DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -24757,22 +24757,22 @@
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
+          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
+          <t>6391 Avenue Henri-Julien, Montréal</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -24792,17 +24792,17 @@
       </c>
       <c r="J281" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jean-Talon (à vérifier)</t>
         </is>
       </c>
       <c r="K281" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M281" s="5" t="inlineStr">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="N281" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
         </is>
       </c>
       <c r="O281" s="5" t="inlineStr">
@@ -24822,19 +24822,19 @@
       </c>
       <c r="P281" s="6" t="inlineStr">
         <is>
-          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
+          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
         </is>
       </c>
       <c r="Q281" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -24844,22 +24844,22 @@
       </c>
       <c r="C282" s="6" t="inlineStr">
         <is>
-          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
+          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>6391 Avenue Henri-Julien, Montréal</t>
+          <t>Rue Beaubien (Montréal, QC)</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -24879,27 +24879,27 @@
       </c>
       <c r="J282" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon (à vérifier)</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K282" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L282" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M282" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N282" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
+          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
         </is>
       </c>
       <c r="O282" s="5" t="inlineStr">
@@ -24909,19 +24909,19 @@
       </c>
       <c r="P282" s="6" t="inlineStr">
         <is>
-          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
+          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q282" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -24931,22 +24931,22 @@
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
+          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>Rue Beaubien (Montréal, QC)</t>
+          <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="H283" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I283" s="5" t="inlineStr">
@@ -24966,27 +24966,27 @@
       </c>
       <c r="J283" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K283" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M283" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N283" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
       <c r="O283" s="5" t="inlineStr">
@@ -24996,19 +24996,19 @@
       </c>
       <c r="P283" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
       <c r="Q283" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -25018,22 +25018,22 @@
       </c>
       <c r="C284" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
+          <t>5½ au Plateau-Mont-Royal (Marketplace)</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>1889 Rue des Carrières, Montréal</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="H284" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I284" s="5" t="inlineStr">
@@ -25068,34 +25068,34 @@
       </c>
       <c r="M284" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N284" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
+          <t>https://www.facebook.com/marketplace/item/2124372061520309</t>
         </is>
       </c>
       <c r="O284" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P284" s="6" t="inlineStr">
         <is>
-          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
+          <t>Annonce titre seulement, description non disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q284" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/790150151_2283077578925626_1749367086388284890_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=ijxRbFhYaKgQ7kNvwENuJLs&amp;_nc_oc=AdqRCM7MaQD28AUVRdjZcBzo8BdTIquAZ9ZXEJ_CuW49MLQJ8m_tT8IYK6EBtN-I4h8&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=21kqsDFTPPlqY_va03ORdw&amp;_nc_ss=7f2a8&amp;oh=00_AQLzxnd4o8SoM-y6_91RzKmvUUM3My8GuhXTwpSztagGmg&amp;oe=6A9C7E28</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
@@ -25105,7 +25105,7 @@
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
-          <t>5½ au Plateau-Mont-Royal (Marketplace)</t>
+          <t>5½ meublé, Plateau-Mont-Royal (Marketplace), disponible 10 juin, bail minimum 1 an</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -25130,59 +25130,59 @@
       </c>
       <c r="H285" s="5" t="inlineStr">
         <is>
+          <t>2 (estimé)</t>
+        </is>
+      </c>
+      <c r="I285" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J285" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K285" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L285" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M285" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N285" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2129210164276639</t>
+        </is>
+      </c>
+      <c r="O285" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I285" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J285" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K285" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L285" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M285" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N285" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/2124372061520309</t>
-        </is>
-      </c>
-      <c r="O285" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="P285" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Annonce titre seulement (meublé, deux prix affichés selon la durée du bail : 2100$ et 2500$), aucune adresse ni description détaillée disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q285" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/790150151_2283077578925626_1749367086388284890_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=ijxRbFhYaKgQ7kNvwENuJLs&amp;_nc_oc=AdqRCM7MaQD28AUVRdjZcBzo8BdTIquAZ9ZXEJ_CuW49MLQJ8m_tT8IYK6EBtN-I4h8&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=21kqsDFTPPlqY_va03ORdw&amp;_nc_ss=7f2a8&amp;oh=00_AQLzxnd4o8SoM-y6_91RzKmvUUM3My8GuhXTwpSztagGmg&amp;oe=6A9C7E28</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/598654016_1589371882248064_7696909030407170199_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=N7m7nUpE6yMQ7kNvwEavU5f&amp;_nc_oc=AdoffqWsvOkDQufR2l4pvvs8I99wUIXqF-oRgpMOgZIXjIPtOiBQxSSfc9hbuhLkhtM&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=XHazkfFuptT2M_pPSTeS4Q&amp;_nc_ss=7f2a8&amp;oh=00_AQFmBd7yIIHbAZt0cYChuyEoJmxi7lgNayPM_0n-aenWnQ&amp;oe=6A9664A6</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -25192,22 +25192,22 @@
       </c>
       <c r="C286" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé, Plateau-Mont-Royal (Marketplace), disponible 10 juin, bail minimum 1 an</t>
+          <t>5 1/2 in Hochelaga (Marketplace)</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>n/d (secteur Hochelaga-Maisonneuve, Montréal)</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="N286" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2129210164276639</t>
+          <t>https://www.facebook.com/marketplace/item/2583777198803688</t>
         </is>
       </c>
       <c r="O286" s="5" t="inlineStr">
@@ -25257,19 +25257,19 @@
       </c>
       <c r="P286" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (meublé, deux prix affichés selon la durée du bail : 2100$ et 2500$), aucune adresse ni description détaillée disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Annonce titre seulement (« 5 1/2 in Hochelaga »), aucune description ni adresse disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q286" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/598654016_1589371882248064_7696909030407170199_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=N7m7nUpE6yMQ7kNvwEavU5f&amp;_nc_oc=AdoffqWsvOkDQufR2l4pvvs8I99wUIXqF-oRgpMOgZIXjIPtOiBQxSSfc9hbuhLkhtM&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=XHazkfFuptT2M_pPSTeS4Q&amp;_nc_ss=7f2a8&amp;oh=00_AQFmBd7yIIHbAZt0cYChuyEoJmxi7lgNayPM_0n-aenWnQ&amp;oe=6A9664A6</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/764987455_1048157270911968_5209086800819479873_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=8fuDHfd2FxAQ7kNvwGWBzmX&amp;_nc_oc=AdrF-5lGt6Z8Q_hcNZtBCxKNzLwKQK14kM3UBQyfvjLyXZs14CcB6FEbpaYw4bSMoBQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=CInYmIZz43q5AWNfaqlZcQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHVVF-2wulz0t4MIMCVRVAytHTtSomrEGuVuullI6JrYA&amp;oe=6A790A2B</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -25279,22 +25279,22 @@
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 in Hochelaga (Marketplace)</t>
+          <t>Appartement 5 1/2, Plateau-Mont-Royal (Marketplace)</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Hochelaga-Maisonneuve, Montréal)</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>2 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I287" s="5" t="inlineStr">
@@ -25334,7 +25334,7 @@
       </c>
       <c r="N287" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2583777198803688</t>
+          <t>https://www.facebook.com/marketplace/item/1552904606229687</t>
         </is>
       </c>
       <c r="O287" s="5" t="inlineStr">
@@ -25344,19 +25344,19 @@
       </c>
       <c r="P287" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (« 5 1/2 in Hochelaga »), aucune description ni adresse disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
         </is>
       </c>
       <c r="Q287" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/764987455_1048157270911968_5209086800819479873_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=8fuDHfd2FxAQ7kNvwGWBzmX&amp;_nc_oc=AdrF-5lGt6Z8Q_hcNZtBCxKNzLwKQK14kM3UBQyfvjLyXZs14CcB6FEbpaYw4bSMoBQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=CInYmIZz43q5AWNfaqlZcQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHVVF-2wulz0t4MIMCVRVAytHTtSomrEGuVuullI6JrYA&amp;oe=6A790A2B</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/720906013_1532570941905242_5666371068595538123_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YEDvMBzBavUQ7kNvwEkVbXh&amp;_nc_oc=AdqtpC8qtzZHEdxPx9e94VcYtRcN6s4rYqZkBbexWTpuWv5UghDk5D0a0ySf9p9btAk&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=TJJlLcUljG48fNVcDPZJaA&amp;_nc_ss=7f2a8&amp;oh=00_AQBrJbOYbvchb0Tq-5jSsFppBFkZ2xgQOdjHrsx0FadLHQ&amp;oe=6A632614</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -25366,22 +25366,22 @@
       </c>
       <c r="C288" s="6" t="inlineStr">
         <is>
-          <t>Appartement 5 1/2, Plateau-Mont-Royal (Marketplace)</t>
+          <t>Beau 5½ à Nouveau Rosemont (Marketplace)</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>n/d (secteur Nouveau-Rosemont, Montréal)</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="N288" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1552904606229687</t>
+          <t>https://www.facebook.com/marketplace/item/771126382598215</t>
         </is>
       </c>
       <c r="O288" s="5" t="inlineStr">
@@ -25431,19 +25431,19 @@
       </c>
       <c r="P288" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
+          <t>Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q288" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/720906013_1532570941905242_5666371068595538123_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YEDvMBzBavUQ7kNvwEkVbXh&amp;_nc_oc=AdqtpC8qtzZHEdxPx9e94VcYtRcN6s4rYqZkBbexWTpuWv5UghDk5D0a0ySf9p9btAk&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=TJJlLcUljG48fNVcDPZJaA&amp;_nc_ss=7f2a8&amp;oh=00_AQBrJbOYbvchb0Tq-5jSsFppBFkZ2xgQOdjHrsx0FadLHQ&amp;oe=6A632614</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/674573089_942123441857660_1258864760862245194_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=-PqFDWdPNa8Q7kNvwG9FoYC&amp;_nc_oc=Adqy82S_lfHjbp4dkLyXqO9W2nrNBD-zKhYTIwlodmCwj46lhM9QhEG2rupuBRJOPVI&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQDV5R2cb2f6avoKzX1khDbQ_SvUKiySFkJsux9T10Rmdg&amp;oe=6A6059BA</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
@@ -25453,7 +25453,7 @@
       </c>
       <c r="C289" s="6" t="inlineStr">
         <is>
-          <t>Beau 5½ à Nouveau Rosemont (Marketplace)</t>
+          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -25463,12 +25463,12 @@
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Nouveau-Rosemont, Montréal)</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="N289" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/771126382598215</t>
+          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
         </is>
       </c>
       <c r="O289" s="5" t="inlineStr">
@@ -25518,12 +25518,12 @@
       </c>
       <c r="P289" s="6" t="inlineStr">
         <is>
-          <t>Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
+          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
         </is>
       </c>
       <c r="Q289" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/674573089_942123441857660_1258864760862245194_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=-PqFDWdPNa8Q7kNvwG9FoYC&amp;_nc_oc=Adqy82S_lfHjbp4dkLyXqO9W2nrNBD-zKhYTIwlodmCwj46lhM9QhEG2rupuBRJOPVI&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQDV5R2cb2f6avoKzX1khDbQ_SvUKiySFkJsux9T10Rmdg&amp;oe=6A6059BA</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
         </is>
       </c>
     </row>
@@ -25540,7 +25540,7 @@
       </c>
       <c r="C290" s="6" t="inlineStr">
         <is>
-          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
+          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
@@ -25550,7 +25550,7 @@
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
@@ -25575,12 +25575,12 @@
       </c>
       <c r="J290" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Pie-IX (mentionné dans le titre)</t>
         </is>
       </c>
       <c r="K290" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L290" s="5" t="inlineStr">
@@ -25595,7 +25595,7 @@
       </c>
       <c r="N290" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
+          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
         </is>
       </c>
       <c r="O290" s="5" t="inlineStr">
@@ -25605,12 +25605,12 @@
       </c>
       <c r="P290" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
+          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q290" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
         </is>
       </c>
     </row>
@@ -25627,22 +25627,22 @@
       </c>
       <c r="C291" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
+          <t>Location 4 et demi Plateau, pet friendly</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -25662,12 +25662,12 @@
       </c>
       <c r="J291" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX (mentionné dans le titre)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K291" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L291" s="5" t="inlineStr">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="N291" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
+          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
         </is>
       </c>
       <c r="O291" s="5" t="inlineStr">
@@ -25692,12 +25692,12 @@
       </c>
       <c r="P291" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
+          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q291" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
         </is>
       </c>
     </row>
@@ -25714,12 +25714,12 @@
       </c>
       <c r="C292" s="6" t="inlineStr">
         <is>
-          <t>Location 4 et demi Plateau, pet friendly</t>
+          <t>5 1/2 Rosemont avec cour privée</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -25769,7 +25769,7 @@
       </c>
       <c r="N292" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
+          <t>https://www.facebook.com/marketplace/item/1493110625829174</t>
         </is>
       </c>
       <c r="O292" s="5" t="inlineStr">
@@ -25779,104 +25779,17 @@
       </c>
       <c r="P292" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
+          <t>Annonce titre seulement, description non disponible via le scraper ; cour privée mentionnée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q292" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C293" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 Rosemont avec cour privée</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E293" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC)</t>
-        </is>
-      </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H293" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I293" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J293" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K293" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L293" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M293" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N293" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1493110625829174</t>
-        </is>
-      </c>
-      <c r="O293" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P293" s="6" t="inlineStr">
-        <is>
-          <t>Annonce titre seulement, description non disponible via le scraper ; cour privée mentionnée. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q293" s="5" t="inlineStr">
-        <is>
           <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730530074_1035539099460685_3801485303896565628_n.jpg?stp=c313.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=_9b7saLCWEUQ7kNvwHrw_2v&amp;_nc_oc=AdoqEj5UFxI4lgfrZP0kbf8mdi_MJO6fIO-zv3fvQ5DsX656NtR6Rf8AiVxw-oho-l4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQDqhmwAH6WdMqAuOtshO7wqRdBG7RkedN25_yaUpz5ikg&amp;oe=6A5EB662</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q293"/>
+  <autoFilter ref="A1:Q292"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -26169,7 +26082,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N290" r:id="rId289"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N291" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N292" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N293" r:id="rId292"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$292</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$291</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q292"/>
+  <dimension ref="A1:Q291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18752,7 +18752,7 @@
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B212" s="5" t="inlineStr">
@@ -18762,27 +18762,27 @@
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>5½ de 1000 pi², 2 chambres, grande cour privée - Plateau (rue Parthenais), 5 min du métro Mont-Royal</t>
+          <t>4½ meublé avec balcon refait à neuf - entre les métros Jarry et Jean-Talon (Villeray)</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>4242, Rue Parthenais, Montréal, QC H2H 2G3</t>
+          <t>Secteur Villeray, entre métro Jarry et Jean-Talon, Montréal</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H212" s="5" t="inlineStr">
@@ -18792,12 +18792,12 @@
       </c>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J212" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Jarry ou Jean-Talon (à vérifier)</t>
         </is>
       </c>
       <c r="K212" s="5" t="inlineStr">
@@ -18807,32 +18807,32 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M212" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N212" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1200370795499483</t>
+        </is>
+      </c>
+      <c r="O212" s="5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M212" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N212" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-2-ch-plateau-est-cour-privee-stationnement-tout-equipe/1737761531</t>
-        </is>
-      </c>
-      <c r="O212" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P212" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, très grande cour arrière privée (pas de balcon mentionné), 2 places de stationnement en sus, laveuse/sécheuse et lave-vaisselle inclus, chauffage et eau chaude inclus, animaux à discuter, disponible immédiatement</t>
+          <t>Appartement meublé (2 lits queen, meubles inclus), balcon refait à neuf à l'arrière, à 5 min à pied du parc Jarry et 10 min du marché Jean-Talon, 2e étage d'un duplex, lien exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q212" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/b0/b0fe6894-b114-43bf-8514-ba73e88eb136?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719951504_1525424678988571_3029279822230004988_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=1GvmU2MuoZYQ7kNvwGQoY7P&amp;_nc_oc=AdoTdsiH2zz9uO5Fd_ygBkJLJi0OpX-UJyx11ydhdL0cY2WAinKXNKxj7G3DpqNMvvc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=I01Huqn8cRYQWCF5daV0fw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrBcwEvZHdYqd9spbMH4nzFS0cAnJtwO-FuyEAgUC8XQ&amp;oe=6A683EFF</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>4½ meublé avec balcon refait à neuf - entre les métros Jarry et Jean-Talon (Villeray)</t>
+          <t>2 chambres, 950 pi² au rez-de-chaussée - rue Jarry Est (Villeray), à 1-2 coins de rue du métro Jarry</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>Secteur Villeray, entre métro Jarry et Jean-Talon, Montréal</t>
+          <t>659, Rue Jarry Est, app. 4, Montréal</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -18879,12 +18879,12 @@
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
-          <t>Jarry ou Jean-Talon (à vérifier)</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K213" s="5" t="inlineStr">
@@ -18894,17 +18894,17 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>2 (estimé)</t>
         </is>
       </c>
       <c r="M213" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N213" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1200370795499483</t>
+          <t>https://www.zumper.com/apartment-buildings/p1626378/659-rue-jarry-e-parc-jarry-montreal-qc</t>
         </is>
       </c>
       <c r="O213" s="5" t="inlineStr">
@@ -18914,12 +18914,12 @@
       </c>
       <c r="P213" s="6" t="inlineStr">
         <is>
-          <t>Appartement meublé (2 lits queen, meubles inclus), balcon refait à neuf à l'arrière, à 5 min à pied du parc Jarry et 10 min du marché Jean-Talon, 2e étage d'un duplex, lien exige une connexion Facebook</t>
+          <t>Entièrement rénové, nouveaux électroménagers, chauffage au gaz, climatiseur mural, laveuse-sécheuse dans l'unité, animaux acceptés, hydro en sus</t>
         </is>
       </c>
       <c r="Q213" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719951504_1525424678988571_3029279822230004988_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=1GvmU2MuoZYQ7kNvwGQoY7P&amp;_nc_oc=AdoTdsiH2zz9uO5Fd_ygBkJLJi0OpX-UJyx11ydhdL0cY2WAinKXNKxj7G3DpqNMvvc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=I01Huqn8cRYQWCF5daV0fw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrBcwEvZHdYqd9spbMH4nzFS0cAnJtwO-FuyEAgUC8XQ&amp;oe=6A683EFF</t>
+          <t>https://img.zumpercdn.com/903928655/1280x960?auto=format</t>
         </is>
       </c>
     </row>
@@ -18936,7 +18936,7 @@
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>2 chambres, 950 pi² au rez-de-chaussée - rue Jarry Est (Villeray), à 1-2 coins de rue du métro Jarry</t>
+          <t>2 chambres, 954 pi² - rue Guizot Ouest (Villeray), près du parc Jarry</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
@@ -18946,17 +18946,17 @@
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>659, Rue Jarry Est, app. 4, Montréal</t>
+          <t>5, Rue Guizot Ouest, app. 202, Montréal</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>954</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -18981,17 +18981,17 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2 (estimé)</t>
+          <t>8-10 (estimé)</t>
         </is>
       </c>
       <c r="M214" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N214" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/apartment-buildings/p1626378/659-rue-jarry-e-parc-jarry-montreal-qc</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/13280662</t>
         </is>
       </c>
       <c r="O214" s="5" t="inlineStr">
@@ -19001,19 +19001,19 @@
       </c>
       <c r="P214" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, nouveaux électroménagers, chauffage au gaz, climatiseur mural, laveuse-sécheuse dans l'unité, animaux acceptés, hydro en sus</t>
+          <t>Eau chaude et internet inclus, immeuble neuf (2022), adjacent au parc Jarry, Walk Score 95</t>
         </is>
       </c>
       <c r="Q214" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/903928655/1280x960?auto=format</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4D9F96DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
@@ -19023,32 +19023,32 @@
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>2 chambres, 954 pi² - rue Guizot Ouest (Villeray), près du parc Jarry</t>
+          <t>Grand 3 chambres - Place Victor-Bourgeau (Rosemont), à 7 min du métro Pie-IX</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>5, Rue Guizot Ouest, app. 202, Montréal</t>
+          <t>3827, Place Victor-Bourgeau, app. 2e étage, Montréal</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H215" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I215" s="5" t="inlineStr">
@@ -19058,17 +19058,17 @@
       </c>
       <c r="J215" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K215" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>8-10 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M215" s="5" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="N215" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/13280662</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10515269</t>
         </is>
       </c>
       <c r="O215" s="5" t="inlineStr">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="P215" s="6" t="inlineStr">
         <is>
-          <t>Eau chaude et internet inclus, immeuble neuf (2022), adjacent au parc Jarry, Walk Score 95</t>
+          <t>Walk Score 92, quartier calme et verdoyant, immeuble de 1950, disponible 1er juin 2026</t>
         </is>
       </c>
       <c r="Q215" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4D9F96DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE61F41BDDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -19110,22 +19110,22 @@
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>Grand 3 chambres - Place Victor-Bourgeau (Rosemont), à 7 min du métro Pie-IX</t>
+          <t>2 chambres avec terrasse privée - rue Boyer (Villeray), à 5 min du métro Jean-Talon</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>3827, Place Victor-Bourgeau, app. 2e étage, Montréal</t>
+          <t>7236, Rue Boyer, Montréal</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -19135,27 +19135,27 @@
       </c>
       <c r="H216" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J216" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K216" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M216" s="5" t="inlineStr">
@@ -19165,7 +19165,7 @@
       </c>
       <c r="N216" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10515269</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25783192</t>
         </is>
       </c>
       <c r="O216" s="5" t="inlineStr">
@@ -19175,19 +19175,19 @@
       </c>
       <c r="P216" s="6" t="inlineStr">
         <is>
-          <t>Walk Score 92, quartier calme et verdoyant, immeuble de 1950, disponible 1er juin 2026</t>
+          <t>Terrasse privée spacieuse, exposition sud-ouest, 2e étage, salle de bain rénovée, animaux non acceptés, semi-meublé, disponible 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q216" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE61F41BDDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD1568EDDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
@@ -19197,22 +19197,22 @@
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>2 chambres avec terrasse privée - rue Boyer (Villeray), à 5 min du métro Jean-Talon</t>
+          <t>Maison de ville 3 chambres, 30 sec. du métro Joliette (Marketplace)</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>7236, Rue Boyer, Montréal</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -19222,52 +19222,52 @@
       </c>
       <c r="H217" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J217" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K217" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
+          <t>1 (estimé)</t>
+        </is>
+      </c>
+      <c r="M217" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N217" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/937512682223269</t>
+        </is>
+      </c>
+      <c r="O217" s="5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M217" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N217" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25783192</t>
-        </is>
-      </c>
-      <c r="O217" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P217" s="6" t="inlineStr">
         <is>
-          <t>Terrasse privée spacieuse, exposition sud-ouest, 2e étage, salle de bain rénovée, animaux non acceptés, semi-meublé, disponible 1er juillet 2026</t>
+          <t>Maison de ville sur 2 étages, construction 2022, bien insonorisée/isolée, à ~70 m (232 pi) du métro Joliette (ligne verte), 5 min à pied du Stade olympique et du parc Maisonneuve, 5 électroménagers inclus + climatiseur, chats acceptés (pas de chien). Prix promotionnel (1 mois gratuit, 11 paiements de 2495$, prix effectif affiché 2286$/mois). Superficie non précisée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q217" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD1568EDDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/695533556_26680042614991015_3858715915734079399_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=KTZncwxQFmoQ7kNvwHfwwo5&amp;_nc_oc=Ado4CpQxclhHJOhRwML4zuwnarUD2KC8ZJod-1TQhIMQwe3qlDVkd7pZXkkMCjB6AGA&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=ye39ADDWTO92n3hVi4vUhw&amp;_nc_ss=7f2a8&amp;oh=00_AQB29QcdgQcUH0a5p0mMoQC4dDWKsB094Cm8Yu8nBhoFpA&amp;oe=6A65B2CE</t>
         </is>
       </c>
     </row>
@@ -19284,47 +19284,47 @@
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>Maison de ville 3 chambres, 30 sec. du métro Joliette (Marketplace)</t>
+          <t>4½ rénové, terrasse commune sur le toit - avenue Papineau (Villeray, près métro Fabre)</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>7145, Avenue Papineau, app. 209, Montréal</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>966</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non (terrasse commune sur le toit)</t>
         </is>
       </c>
       <c r="J218" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Fabre (à vérifier)</t>
         </is>
       </c>
       <c r="K218" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L218" s="5" t="inlineStr">
@@ -19334,12 +19334,12 @@
       </c>
       <c r="M218" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N218" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/937512682223269</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25866247</t>
         </is>
       </c>
       <c r="O218" s="5" t="inlineStr">
@@ -19349,19 +19349,19 @@
       </c>
       <c r="P218" s="6" t="inlineStr">
         <is>
-          <t>Maison de ville sur 2 étages, construction 2022, bien insonorisée/isolée, à ~70 m (232 pi) du métro Joliette (ligne verte), 5 min à pied du Stade olympique et du parc Maisonneuve, 5 électroménagers inclus + climatiseur, chats acceptés (pas de chien). Prix promotionnel (1 mois gratuit, 11 paiements de 2495$, prix effectif affiché 2286$/mois). Superficie non précisée. Lien Facebook (connexion requise)</t>
+          <t>966 pi², 2 salles de bain, ascenseur, insonorisation béton, stationnement garage optionnel (100$/mois), disponible 1er juillet 2026, distance au métro Fabre à vérifier (adresse sur avenue Papineau, assez éloignée du tracé habituel de la station)</t>
         </is>
       </c>
       <c r="Q218" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/695533556_26680042614991015_3858715915734079399_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=KTZncwxQFmoQ7kNvwHfwwo5&amp;_nc_oc=Ado4CpQxclhHJOhRwML4zuwnarUD2KC8ZJod-1TQhIMQwe3qlDVkd7pZXkkMCjB6AGA&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=ye39ADDWTO92n3hVi4vUhw&amp;_nc_ss=7f2a8&amp;oh=00_AQB29QcdgQcUH0a5p0mMoQC4dDWKsB094Cm8Yu8nBhoFpA&amp;oe=6A65B2CE</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA112268DDDDDDDDDDA&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
@@ -19371,52 +19371,52 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, terrasse commune sur le toit - avenue Papineau (Villeray, près métro Fabre)</t>
+          <t>5 1/2, 3 chambres fermées - rue Ontario Est (Hochelaga-Maisonneuve, près métro Préfontaine)</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>7145, Avenue Papineau, app. 209, Montréal</t>
+          <t>3547, Rue Ontario Est, Montréal</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>non (terrasse commune sur le toit)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J219" s="5" t="inlineStr">
         <is>
-          <t>Fabre (à vérifier)</t>
+          <t>Préfontaine (estimé)</t>
         </is>
       </c>
       <c r="K219" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>1 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M219" s="5" t="inlineStr">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="N219" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25866247</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-mercier-hochelaga-maisonneuve/10439922</t>
         </is>
       </c>
       <c r="O219" s="5" t="inlineStr">
@@ -19436,19 +19436,19 @@
       </c>
       <c r="P219" s="6" t="inlineStr">
         <is>
-          <t>966 pi², 2 salles de bain, ascenseur, insonorisation béton, stationnement garage optionnel (100$/mois), disponible 1er juillet 2026, distance au métro Fabre à vérifier (adresse sur avenue Papineau, assez éloignée du tracé habituel de la station)</t>
+          <t>construit en 1957, walk score 98, dispo 1er juillet 2026, superficie non précisée, distance au métro estimée à partir de l'adresse</t>
         </is>
       </c>
       <c r="Q219" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA112268DDDDDDDDDDA&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6AB5B6DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
@@ -19458,22 +19458,22 @@
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres fermées - rue Ontario Est (Hochelaga-Maisonneuve, près métro Préfontaine)</t>
+          <t>4½ à céder – Villeray, 2 chambres fermées, balcon (Marketplace)</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>3547, Rue Ontario Est, Montréal</t>
+          <t>n/d (secteur Villeray, près métro Castelnau)</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -19483,37 +19483,37 @@
       </c>
       <c r="H220" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J220" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine (estimé)</t>
+          <t>Castelnau</t>
         </is>
       </c>
       <c r="K220" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M220" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N220" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-mercier-hochelaga-maisonneuve/10439922</t>
+          <t>https://www.facebook.com/marketplace/item/2227879828059640</t>
         </is>
       </c>
       <c r="O220" s="5" t="inlineStr">
@@ -19523,19 +19523,19 @@
       </c>
       <c r="P220" s="6" t="inlineStr">
         <is>
-          <t>construit en 1957, walk score 98, dispo 1er juillet 2026, superficie non précisée, distance au métro estimée à partir de l'adresse</t>
+          <t>Condo moderne 2e étage, stationnement intérieur, tous électros inclus (lave-vaisselle, laveuse-sécheuse), animaux acceptés, dispo 1er sept 2026, à 2 min de la station Castelnau et de la gare Parc, à moins de 5 min de la Petite Italie et du marché Jean-Talon. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q220" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6AB5B6DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/751071826_10164875789774427_3752394249248914976_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=Knb577I_QIQQ7kNvwHRURl7&amp;_nc_oc=AdpbxRYFmapFBEQPrC-_hmjYxOXo72tZ-p3CMQU5NBPUrVItHwHBTrgtLoc6wHMBtWo&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=l5CS9zZsCO7-lUvHOJjbjg&amp;_nc_ss=7f2a8&amp;oh=00_AQAA-uj7lhihOErymRJc0BP7_KKrvcik23WWAhRADb1gcQ&amp;oe=6A62F372</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>4½ à céder – Villeray, 2 chambres fermées, balcon (Marketplace)</t>
+          <t>4½ rénové 2024, balcon privé, dernier étage - rue Foucher (Villeray), près métro Jarry</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
@@ -19555,12 +19555,12 @@
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Villeray, près métro Castelnau)</t>
+          <t>8325B Rue Foucher, Montréal</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="J221" s="5" t="inlineStr">
         <is>
-          <t>Castelnau</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K221" s="5" t="inlineStr">
@@ -19590,17 +19590,17 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M221" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N221" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2227879828059640</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/20638950</t>
         </is>
       </c>
       <c r="O221" s="5" t="inlineStr">
@@ -19610,19 +19610,19 @@
       </c>
       <c r="P221" s="6" t="inlineStr">
         <is>
-          <t>Condo moderne 2e étage, stationnement intérieur, tous électros inclus (lave-vaisselle, laveuse-sécheuse), animaux acceptés, dispo 1er sept 2026, à 2 min de la station Castelnau et de la gare Parc, à moins de 5 min de la Petite Italie et du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>Dernier étage sans voisin au-dessus, puits de lumière, chats acceptés, proche pharmacie/dépanneur/restos, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q221" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/751071826_10164875789774427_3752394249248914976_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=Knb577I_QIQQ7kNvwHRURl7&amp;_nc_oc=AdpbxRYFmapFBEQPrC-_hmjYxOXo72tZ-p3CMQU5NBPUrVItHwHBTrgtLoc6wHMBtWo&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=l5CS9zZsCO7-lUvHOJjbjg&amp;_nc_ss=7f2a8&amp;oh=00_AQAA-uj7lhihOErymRJc0BP7_KKrvcik23WWAhRADb1gcQ&amp;oe=6A62F372</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1701B6DDDDDDDDDD0&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
@@ -19632,22 +19632,22 @@
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové 2024, balcon privé, dernier étage - rue Foucher (Villeray), près métro Jarry</t>
+          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>8325B Rue Foucher, Montréal</t>
+          <t>6904 Rue Hutchison, Montréal</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -19667,7 +19667,7 @@
       </c>
       <c r="J222" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Parc ou Acadie</t>
         </is>
       </c>
       <c r="K222" s="5" t="inlineStr">
@@ -19677,17 +19677,17 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M222" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N222" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/20638950</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
         </is>
       </c>
       <c r="O222" s="5" t="inlineStr">
@@ -19697,12 +19697,12 @@
       </c>
       <c r="P222" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage sans voisin au-dessus, puits de lumière, chats acceptés, proche pharmacie/dépanneur/restos, dispo 1er juillet 2026</t>
+          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
         </is>
       </c>
       <c r="Q222" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1701B6DDDDDDDDDD0&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
         </is>
       </c>
     </row>
@@ -19719,22 +19719,22 @@
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
+          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>6904 Rue Hutchison, Montréal</t>
+          <t>3514 Avenue De Lorimier, Montréal</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="J223" s="5" t="inlineStr">
         <is>
-          <t>Parc ou Acadie</t>
+          <t>Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K223" s="5" t="inlineStr">
@@ -19764,39 +19764,39 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
+          <t>12 (estimé)</t>
+        </is>
+      </c>
+      <c r="M223" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N223" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
+        </is>
+      </c>
+      <c r="O223" s="5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M223" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N223" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
-        </is>
-      </c>
-      <c r="O223" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P223" s="6" t="inlineStr">
         <is>
-          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
+          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
         </is>
       </c>
       <c r="Q223" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
@@ -19806,22 +19806,22 @@
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
+          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>3514 Avenue De Lorimier, Montréal</t>
+          <t>Secteur station Papineau (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -19831,37 +19831,37 @@
       </c>
       <c r="H224" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J224" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal (à vérifier)</t>
+          <t>Papineau</t>
         </is>
       </c>
       <c r="K224" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M224" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N224" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
+          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
         </is>
       </c>
       <c r="O224" s="5" t="inlineStr">
@@ -19871,12 +19871,12 @@
       </c>
       <c r="P224" s="6" t="inlineStr">
         <is>
-          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
+          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q224" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
         </is>
       </c>
     </row>
@@ -19893,22 +19893,22 @@
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
+          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>Secteur station Papineau (adresse exacte n/d)</t>
+          <t>1478 rue Dézéry</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="H225" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I225" s="5" t="inlineStr">
@@ -19928,7 +19928,7 @@
       </c>
       <c r="J225" s="5" t="inlineStr">
         <is>
-          <t>Papineau</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K225" s="5" t="inlineStr">
@@ -19938,32 +19938,32 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M225" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N225" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
+        </is>
+      </c>
+      <c r="O225" s="5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M225" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N225" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
-        </is>
-      </c>
-      <c r="O225" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P225" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q225" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
         </is>
       </c>
     </row>
@@ -19980,32 +19980,32 @@
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
+          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>1478 rue Dézéry</t>
+          <t>Rue Drolet entre St-Zotique et Bélanger</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I226" s="5" t="inlineStr">
@@ -20015,12 +20015,12 @@
       </c>
       <c r="J226" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K226" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L226" s="5" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="N226" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
+          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
         </is>
       </c>
       <c r="O226" s="5" t="inlineStr">
@@ -20045,19 +20045,19 @@
       </c>
       <c r="P226" s="6" t="inlineStr">
         <is>
-          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q226" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
@@ -20067,32 +20067,32 @@
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>Rue Drolet entre St-Zotique et Bélanger</t>
+          <t>5472 1ere Avenue, Montréal</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>995</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I227" s="5" t="inlineStr">
@@ -20102,27 +20102,27 @@
       </c>
       <c r="J227" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K227" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M227" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N227" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
         </is>
       </c>
       <c r="O227" s="5" t="inlineStr">
@@ -20132,19 +20132,19 @@
       </c>
       <c r="P227" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
         </is>
       </c>
       <c r="Q227" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B228" s="5" t="inlineStr">
@@ -20154,27 +20154,27 @@
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>5½ (3 chambres), quartier historique - rue Saint-Urbain (Plateau-Mont-Royal), à ~10 min du métro Laurier</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>4267, Rue Saint-Urbain, app. 5, Montréal</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H228" s="5" t="inlineStr">
@@ -20189,49 +20189,49 @@
       </c>
       <c r="J228" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K228" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M228" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N228" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/26740585</t>
         </is>
       </c>
       <c r="O228" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P228" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+          <t>Immeuble de 1914, Walk Score 100 (quartier très commerçant/piéton), chats acceptés (chiens non acceptés), disponible depuis le 4 août 2026, superficie et balcon non précisés dans l'annonce.</t>
         </is>
       </c>
       <c r="Q228" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4B5060DDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
@@ -20241,22 +20241,22 @@
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres), quartier historique - rue Saint-Urbain (Plateau-Mont-Royal), à ~10 min du métro Laurier</t>
+          <t>6 pièces, 3 chambres - boulevard Rosemont (Rosemont), à 6 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>4267, Rue Saint-Urbain, app. 5, Montréal</t>
+          <t>2112, Boulevard Rosemont, app. 1, Montréal</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="J229" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K229" s="5" t="inlineStr">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M229" s="5" t="inlineStr">
@@ -20296,7 +20296,7 @@
       </c>
       <c r="N229" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/26740585</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/27141902</t>
         </is>
       </c>
       <c r="O229" s="5" t="inlineStr">
@@ -20306,12 +20306,12 @@
       </c>
       <c r="P229" s="6" t="inlineStr">
         <is>
-          <t>Immeuble de 1914, Walk Score 100 (quartier très commerçant/piéton), chats acceptés (chiens non acceptés), disponible depuis le 4 août 2026, superficie et balcon non précisés dans l'annonce.</t>
+          <t>Concept ouvert, 3 chambres au sous-sol, salle de bain complète, rangement abondant, au coeur de Rosemont près des commerces/cafés/restos et du parc du Père-Marquette, Walk Score 97, libre 5 jours après acceptation. Balcon non mentionné, superficie non précisée.</t>
         </is>
       </c>
       <c r="Q229" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4B5060DDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4F19FEDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -20328,22 +20328,22 @@
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
-          <t>6 pièces, 3 chambres - boulevard Rosemont (Rosemont), à 6 min du métro Rosemont</t>
+          <t>5½ rénové (3 chambres), près métro Place-Saint-Henri - Saint-Henri (Marketplace)</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Saint-Henri (Sud-Ouest)</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>2112, Boulevard Rosemont, app. 1, Montréal</t>
+          <t>n/d (secteur Place-Saint-Henri, Montréal)</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -20363,7 +20363,7 @@
       </c>
       <c r="J230" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Place-Saint-Henri</t>
         </is>
       </c>
       <c r="K230" s="5" t="inlineStr">
@@ -20373,17 +20373,17 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M230" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N230" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/27141902</t>
+          <t>https://www.facebook.com/marketplace/item/976925808446839</t>
         </is>
       </c>
       <c r="O230" s="5" t="inlineStr">
@@ -20393,19 +20393,15 @@
       </c>
       <c r="P230" s="6" t="inlineStr">
         <is>
-          <t>Concept ouvert, 3 chambres au sous-sol, salle de bain complète, rangement abondant, au coeur de Rosemont près des commerces/cafés/restos et du parc du Père-Marquette, Walk Score 97, libre 5 jours après acceptation. Balcon non mentionné, superficie non précisée.</t>
-        </is>
-      </c>
-      <c r="Q230" s="5" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4F19FEDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
+          <t>Cuisine équipée (frigo, cuisinière, lave-vaisselle, laveuse-sécheuse inclus), eau chaude incluse, climatisation, chauffage électrique, stationnement garage, à distance de marche du métro Place-Saint-Henri (Walk Score 98, Transit Score 84), proche écoles/parcs/restaurants, disponible maintenant. Balcon non mentionné. Lien Facebook (connexion requise).</t>
+        </is>
+      </c>
+      <c r="Q230" s="5" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
@@ -20415,22 +20411,22 @@
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), près métro Place-Saint-Henri - Saint-Henri (Marketplace)</t>
+          <t>8½, 5 chambres, à 3 min du métro Sherbrooke (Marketplace)</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Saint-Henri (Sud-Ouest)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Place-Saint-Henri, Montréal)</t>
+          <t>n/d (secteur Saint-Denis / Sherbrooke, Montréal)</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -20440,29 +20436,29 @@
       </c>
       <c r="H231" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I231" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J231" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L231" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I231" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J231" s="5" t="inlineStr">
-        <is>
-          <t>Place-Saint-Henri</t>
-        </is>
-      </c>
-      <c r="K231" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L231" s="5" t="inlineStr">
-        <is>
-          <t>5 (estimé)</t>
-        </is>
-      </c>
       <c r="M231" s="5" t="inlineStr">
         <is>
           <t>Marketplace</t>
@@ -20470,7 +20466,7 @@
       </c>
       <c r="N231" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/976925808446839</t>
+          <t>https://www.facebook.com/marketplace/item/1295097232428646</t>
         </is>
       </c>
       <c r="O231" s="5" t="inlineStr">
@@ -20480,10 +20476,14 @@
       </c>
       <c r="P231" s="6" t="inlineStr">
         <is>
-          <t>Cuisine équipée (frigo, cuisinière, lave-vaisselle, laveuse-sécheuse inclus), eau chaude incluse, climatisation, chauffage électrique, stationnement garage, à distance de marche du métro Place-Saint-Henri (Walk Score 98, Transit Score 84), proche écoles/parcs/restaurants, disponible maintenant. Balcon non mentionné. Lien Facebook (connexion requise).</t>
-        </is>
-      </c>
-      <c r="Q231" s="5" t="inlineStr"/>
+          <t>Disponible dès maintenant. Cuisine, salon, salle de bain, laveuse/sécheuse et poêle/frigo inclus. Walk Score 100. Superficie non précisée. Lien Facebook (connexion requise).</t>
+        </is>
+      </c>
+      <c r="Q231" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/773052468_122209107038545443_8124178759229006599_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=8W3VLy_Ym_kQ7kNvwFIJaYd&amp;_nc_oc=Adp9nhRnmxNKKFcbiAiLVBQJQQHZuDhec66NEgGslkc442E2vBxEcqbXAhgsPemgoqQ&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=MShXopbQP3LpJJAaNRSMHA&amp;_nc_ss=7f2a8&amp;oh=00_AQK6hcw9O9E27JmIaA9ZhO2shHRn5FuWRwhlcU3O_od5jQ&amp;oe=6A9C8812</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -20498,22 +20498,22 @@
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>8½, 5 chambres, à 3 min du métro Sherbrooke (Marketplace)</t>
+          <t>4½ rénové, 2 chambres, balcon privé, près du parc Lafontaine (Marketplace)</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Village, bordure Plateau-Mont-Royal)</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Saint-Denis / Sherbrooke, Montréal)</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -20523,27 +20523,27 @@
       </c>
       <c r="H232" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J232" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K232" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M232" s="5" t="inlineStr">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="N232" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1295097232428646</t>
+          <t>https://www.facebook.com/marketplace/item/1500903075380300</t>
         </is>
       </c>
       <c r="O232" s="5" t="inlineStr">
@@ -20563,19 +20563,19 @@
       </c>
       <c r="P232" s="6" t="inlineStr">
         <is>
-          <t>Disponible dès maintenant. Cuisine, salon, salle de bain, laveuse/sécheuse et poêle/frigo inclus. Walk Score 100. Superficie non précisée. Lien Facebook (connexion requise).</t>
+          <t>Disponible maintenant. Électros inclus (frigo, four, lave-vaisselle), laveuse/sécheuse dans la salle de bain, balcon privé. À distance de marche du parc Lafontaine, rue Sainte-Catherine, Village, Plateau et Vieux-Port ; proche de 3 stations de métro (non nommées) et du REM. Stationnement extérieur optionnel 155$/mois. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q232" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/773052468_122209107038545443_8124178759229006599_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=8W3VLy_Ym_kQ7kNvwFIJaYd&amp;_nc_oc=Adp9nhRnmxNKKFcbiAiLVBQJQQHZuDhec66NEgGslkc442E2vBxEcqbXAhgsPemgoqQ&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=MShXopbQP3LpJJAaNRSMHA&amp;_nc_ss=7f2a8&amp;oh=00_AQK6hcw9O9E27JmIaA9ZhO2shHRn5FuWRwhlcU3O_od5jQ&amp;oe=6A9C8812</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/645223637_25975322942095889_2760400941040486007_n.jpg?stp=c0.169.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=UqU8shEBO-gQ7kNvwEcCfAB&amp;_nc_oc=AdrqOIuPIMAdt12BVyA2qGTqmtL60QbUVYNttUp5ybmsHwUnjnjXptke1Nf-nOzJNZA&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=aAA0kX9E3mYumnJWwqsfMA&amp;_nc_ss=7f2a8&amp;oh=00_AQLy8u9GSPwMv6YCqb841eKa7q6nPkFs4URMeC2pz_vCyg&amp;oe=6A9C8B11</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
@@ -20585,22 +20585,22 @@
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres, balcon privé, près du parc Lafontaine (Marketplace)</t>
+          <t>Grand 5½ (3 chambres) - rue Jean-Talon Est, Villeray, à 1 min du métro Fabre</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Village, bordure Plateau-Mont-Royal)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>1557, Rue Jean-Talon Est, Montréal</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -20610,37 +20610,37 @@
       </c>
       <c r="H233" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J233" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K233" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M233" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N233" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1500903075380300</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/9236151</t>
         </is>
       </c>
       <c r="O233" s="5" t="inlineStr">
@@ -20650,19 +20650,19 @@
       </c>
       <c r="P233" s="6" t="inlineStr">
         <is>
-          <t>Disponible maintenant. Électros inclus (frigo, four, lave-vaisselle), laveuse/sécheuse dans la salle de bain, balcon privé. À distance de marche du parc Lafontaine, rue Sainte-Catherine, Village, Plateau et Vieux-Port ; proche de 3 stations de métro (non nommées) et du REM. Stationnement extérieur optionnel 155$/mois. Lien Facebook (connexion requise).</t>
+          <t>Construit en 1953, climatisation centrale, cuisinière/réfrigérateur/laveuse/sécheuse inclus, disponible 1er juin 2026, Walk Score 96, à une minute du métro Fabre</t>
         </is>
       </c>
       <c r="Q233" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/645223637_25975322942095889_2760400941040486007_n.jpg?stp=c0.169.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=UqU8shEBO-gQ7kNvwEcCfAB&amp;_nc_oc=AdrqOIuPIMAdt12BVyA2qGTqmtL60QbUVYNttUp5ybmsHwUnjnjXptke1Nf-nOzJNZA&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=aAA0kX9E3mYumnJWwqsfMA&amp;_nc_ss=7f2a8&amp;oh=00_AQLy8u9GSPwMv6YCqb841eKa7q6nPkFs4URMeC2pz_vCyg&amp;oe=6A9C8B11</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD28DD7DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B234" s="5" t="inlineStr">
@@ -20672,22 +20672,22 @@
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ (3 chambres) - rue Jean-Talon Est, Villeray, à 1 min du métro Fabre</t>
+          <t>2 chambres, unite 201 - rue Davidson (Hochelaga, secteur Prefontaine/Joliette), a 4 min du metro Joliette</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>1557, Rue Jean-Talon Est, Montréal</t>
+          <t>2591, Rue Davidson, app. 201, Montreal, QC H1W 2Z3</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -20697,7 +20697,7 @@
       </c>
       <c r="H234" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I234" s="5" t="inlineStr">
@@ -20707,27 +20707,27 @@
       </c>
       <c r="J234" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K234" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M234" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N234" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/9236151</t>
+          <t>https://www.zumper.com/apartment-buildings/p1346142/2591-davidson-prefontaine-montreal-qc</t>
         </is>
       </c>
       <c r="O234" s="5" t="inlineStr">
@@ -20737,19 +20737,19 @@
       </c>
       <c r="P234" s="6" t="inlineStr">
         <is>
-          <t>Construit en 1953, climatisation centrale, cuisinière/réfrigérateur/laveuse/sécheuse inclus, disponible 1er juin 2026, Walk Score 96, à une minute du métro Fabre</t>
+          <t>petits animaux acceptes; laveuse-secheuse a l'unite, lave-vaisselle; meme immeuble que d'autres unites deja suivies (app. 102 a 2095$)</t>
         </is>
       </c>
       <c r="Q234" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD28DD7DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://img.zumpercdn.com/917687687/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
@@ -20759,27 +20759,27 @@
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>2 chambres, unite 201 - rue Davidson (Hochelaga, secteur Prefontaine/Joliette), a 4 min du metro Joliette</t>
+          <t>Condo / Appartement a louer - 4355, Rue Marquette</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>2591, Rue Davidson, app. 201, Montreal, QC H1W 2Z3</t>
+          <t>4355, Rue Marquette, Montreal (Le Plateau-Mont-Royal)</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>995</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -20794,49 +20794,49 @@
       </c>
       <c r="J235" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K235" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M235" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N235" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/28692748</t>
+        </is>
+      </c>
+      <c r="O235" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M235" s="5" t="inlineStr">
-        <is>
-          <t>Zumper</t>
-        </is>
-      </c>
-      <c r="N235" s="7" t="inlineStr">
-        <is>
-          <t>https://www.zumper.com/apartment-buildings/p1346142/2591-davidson-prefontaine-montreal-qc</t>
-        </is>
-      </c>
-      <c r="O235" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P235" s="6" t="inlineStr">
         <is>
-          <t>petits animaux acceptes; laveuse-secheuse a l'unite, lave-vaisselle; meme immeuble que d'autres unites deja suivies (app. 102 a 2095$)</t>
+          <t>Disponible le 1er septembre 2026. Superficie 995 pi2, 2 chambres. Aucune mention de balcon dans la description. Distance approximative de 12 min a pied de la station Mont-Royal (ligne orange).</t>
         </is>
       </c>
       <c r="Q235" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/917687687/1280x960?auto=format</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA461E36DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B236" s="5" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>Condo / Appartement a louer - 4355, Rue Marquette</t>
+          <t>3½ chambres à louer, Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
@@ -20856,22 +20856,22 @@
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>4355, Rue Marquette, Montreal (Le Plateau-Mont-Royal)</t>
+          <t>3910, Avenue Henri-Julien, apt. 1, Montréal</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I236" s="5" t="inlineStr">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="J236" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K236" s="5" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M236" s="5" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="N236" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/28692748</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-le-plateau-mont-royal/19149920</t>
         </is>
       </c>
       <c r="O236" s="5" t="inlineStr">
@@ -20911,12 +20911,12 @@
       </c>
       <c r="P236" s="6" t="inlineStr">
         <is>
-          <t>Disponible le 1er septembre 2026. Superficie 995 pi2, 2 chambres. Aucune mention de balcon dans la description. Distance approximative de 12 min a pied de la station Mont-Royal (ligne orange).</t>
+          <t>Courtier immobilier (L'Expert Immobilier P.M.), libre 1er août, pas d'info chauffage/animaux/balcon dans l'annonce.</t>
         </is>
       </c>
       <c r="Q236" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA461E36DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA408B52DDDDDDDDDD0&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -20933,22 +20933,22 @@
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>3½ chambres à louer, Plateau-Mont-Royal</t>
+          <t>Grand 5½ au niveau de la rue (en rénovation) - Villeray</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>3910, Avenue Henri-Julien, apt. 1, Montréal</t>
+          <t>8329, Rue St-Denis, Montréal</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="J237" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K237" s="5" t="inlineStr">
@@ -20978,17 +20978,17 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M237" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N237" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-le-plateau-mont-royal/19149920</t>
+          <t>https://www.facebook.com/marketplace/item/1045734174887528</t>
         </is>
       </c>
       <c r="O237" s="5" t="inlineStr">
@@ -20998,19 +20998,19 @@
       </c>
       <c r="P237" s="6" t="inlineStr">
         <is>
-          <t>Courtier immobilier (L'Expert Immobilier P.M.), libre 1er août, pas d'info chauffage/animaux/balcon dans l'annonce.</t>
+          <t>Logement actuellement en rénovation (livré rafraîchi), chauffage inclus, entrée indépendante. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q237" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA408B52DDDDDDDDDD0&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/777851665_1392285162836899_2586773633785074076_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=bbqkjXEOooUQ7kNvwGCLjF3&amp;_nc_oc=AdqcFQl6IK4Vq6ghSY5Gwq2lHYbKp-DdU9d1587_dNK-lvUnNr1YatumMq7j0GnExkY&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=xz3GAY07JF78DVneStR9iQ&amp;_nc_ss=7f2a8&amp;oh=00_AQGYpPqDbvxzZHJaxQpQuKilNWHE6U_FE7M9qHH5BdSoTw&amp;oe=6A949B24</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B238" s="5" t="inlineStr">
@@ -21020,22 +21020,22 @@
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ au niveau de la rue (en rénovation) - Villeray</t>
+          <t>5 1/2 Apartment à côté du métro Laurier (Marketplace)</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>8329, Rue St-Denis, Montréal</t>
+          <t>n/d (secteur métro Laurier, Montréal)</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H238" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="I238" s="5" t="inlineStr">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="J238" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Laurier (estimé du titre)</t>
         </is>
       </c>
       <c r="K238" s="5" t="inlineStr">
@@ -21065,7 +21065,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M238" s="5" t="inlineStr">
@@ -21075,7 +21075,7 @@
       </c>
       <c r="N238" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1045734174887528</t>
+          <t>https://www.facebook.com/marketplace/item/1494146445585365</t>
         </is>
       </c>
       <c r="O238" s="5" t="inlineStr">
@@ -21085,19 +21085,19 @@
       </c>
       <c r="P238" s="6" t="inlineStr">
         <is>
-          <t>Logement actuellement en rénovation (livré rafraîchi), chauffage inclus, entrée indépendante. Lien Facebook (connexion requise).</t>
+          <t>Annonce titre seulement (« 5 1/2 Apartment à côté du métro laurier »), aucune description disponible via le scraper ; quartier et proximité métro estimés à partir du titre, à confirmer. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q238" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/777851665_1392285162836899_2586773633785074076_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=bbqkjXEOooUQ7kNvwGCLjF3&amp;_nc_oc=AdqcFQl6IK4Vq6ghSY5Gwq2lHYbKp-DdU9d1587_dNK-lvUnNr1YatumMq7j0GnExkY&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=xz3GAY07JF78DVneStR9iQ&amp;_nc_ss=7f2a8&amp;oh=00_AQGYpPqDbvxzZHJaxQpQuKilNWHE6U_FE7M9qHH5BdSoTw&amp;oe=6A949B24</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/699126897_1973485496863353_2557441085218132183_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=1TfRKggdwDcQ7kNvwEurKS5&amp;_nc_oc=AdoR-cEqyxjiGQ0UmeNWANwJPUjdZDGYcYoZbroFxLyW1VqV4CZrGQZ3Dx9LatXKOdo&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=V_1P3sgeyFFynjrs9YnECA&amp;_nc_ss=7f2a8&amp;oh=00_AQFKi9JtscuC3zLGzRNAS8-wnmDcB7WEfSrc3K0HAzOrbA&amp;oe=6A911748</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
@@ -21107,22 +21107,22 @@
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Apartment à côté du métro Laurier (Marketplace)</t>
+          <t>5½ semi-meublé (3 chambres), immeuble Cogir - rue Jarry Est (Villeray), à quelques pas du métro Jarry</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur métro Laurier, Montréal)</t>
+          <t>2660, Rue Jarry Est, Montréal, QC</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="H239" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I239" s="5" t="inlineStr">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="J239" s="5" t="inlineStr">
         <is>
-          <t>Laurier (estimé du titre)</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K239" s="5" t="inlineStr">
@@ -21152,17 +21152,17 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M239" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N239" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1494146445585365</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-2660-rue-jarry-e-1129566</t>
         </is>
       </c>
       <c r="O239" s="5" t="inlineStr">
@@ -21172,19 +21172,19 @@
       </c>
       <c r="P239" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (« 5 1/2 Apartment à côté du métro laurier »), aucune description disponible via le scraper ; quartier et proximité métro estimés à partir du titre, à confirmer. Lien Facebook (connexion requise)</t>
+          <t>Immeuble Cogir (69 unités), semi-meublé, 5 électroménagers inclus, chauffage/eau chaude/internet inclus, climatisation murale, stationnement intérieur en option, promotion 1 mois gratuit sous conditions, superficie non précisée.</t>
         </is>
       </c>
       <c r="Q239" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/699126897_1973485496863353_2557441085218132183_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=1TfRKggdwDcQ7kNvwEurKS5&amp;_nc_oc=AdoR-cEqyxjiGQ0UmeNWANwJPUjdZDGYcYoZbroFxLyW1VqV4CZrGQZ3Dx9LatXKOdo&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=V_1P3sgeyFFynjrs9YnECA&amp;_nc_ss=7f2a8&amp;oh=00_AQFKi9JtscuC3zLGzRNAS8-wnmDcB7WEfSrc3K0HAzOrbA&amp;oe=6A911748</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1129566/5-1-2-villeray-st-michel-parc-extension-1600-15601049.jpg</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
@@ -21194,7 +21194,7 @@
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>5½ semi-meublé (3 chambres), immeuble Cogir - rue Jarry Est (Villeray), à quelques pas du métro Jarry</t>
+          <t>5 1/2 spacieux (3 chambres) - rue Everett (Villeray), à 2 min du métro Jean-Talon</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
@@ -21204,12 +21204,12 @@
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>2660, Rue Jarry Est, Montréal, QC</t>
+          <t>2709, Rue Everett, Montréal, QC</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K240" s="5" t="inlineStr">
@@ -21239,17 +21239,17 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M240" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N240" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-2660-rue-jarry-e-1129566</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/12317886</t>
         </is>
       </c>
       <c r="O240" s="5" t="inlineStr">
@@ -21259,19 +21259,19 @@
       </c>
       <c r="P240" s="6" t="inlineStr">
         <is>
-          <t>Immeuble Cogir (69 unités), semi-meublé, 5 électroménagers inclus, chauffage/eau chaude/internet inclus, climatisation murale, stationnement intérieur en option, promotion 1 mois gratuit sous conditions, superficie non précisée.</t>
+          <t>Rez-de-chaussée avec sous-sol aménagé récemment rénové (2 chambres au sous-sol + bureau), 5 pièces, disponible 1er juin 2026, Walk Score 91.</t>
         </is>
       </c>
       <c r="Q240" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1129566/5-1-2-villeray-st-michel-parc-extension-1600-15601049.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADEAC93DDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
@@ -21281,22 +21281,22 @@
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 spacieux (3 chambres) - rue Everett (Villeray), à 2 min du métro Jean-Talon</t>
+          <t>5½ semi-meublé (3 chambres) - rue Saint-Hubert (Rosemont), à 5 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>2709, Rue Everett, Montréal, QC</t>
+          <t>5912, Rue Saint-Hubert, Montréal, QC</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="J241" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K241" s="5" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M241" s="5" t="inlineStr">
@@ -21336,7 +21336,7 @@
       </c>
       <c r="N241" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/12317886</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/25204133</t>
         </is>
       </c>
       <c r="O241" s="5" t="inlineStr">
@@ -21346,12 +21346,12 @@
       </c>
       <c r="P241" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée avec sous-sol aménagé récemment rénové (2 chambres au sous-sol + bureau), 5 pièces, disponible 1er juin 2026, Walk Score 91.</t>
+          <t>Semi-meublé, immeuble de 1989, 1 salle de bain + salle d'eau, animaux non acceptés, disponible 3 jours après acceptation de la promesse de location, Walk Score 97. Superficie non précisée mais 10 pièces au total (spacieux).</t>
         </is>
       </c>
       <c r="Q241" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADEAC93DDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15BA0BDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>5½ semi-meublé (3 chambres) - rue Saint-Hubert (Rosemont), à 5 min du métro Rosemont</t>
+          <t>5½ (3 chambres) - rue Bélanger (Rosemont/Villeray), à 5 min du métro D'Iberville</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
@@ -21378,12 +21378,12 @@
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>5912, Rue Saint-Hubert, Montréal, QC</t>
+          <t>2468, Rue Bélanger, Montréal, QC</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -21403,12 +21403,12 @@
       </c>
       <c r="J242" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K242" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L242" s="5" t="inlineStr">
@@ -21423,7 +21423,7 @@
       </c>
       <c r="N242" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/25204133</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/12923755</t>
         </is>
       </c>
       <c r="O242" s="5" t="inlineStr">
@@ -21433,19 +21433,19 @@
       </c>
       <c r="P242" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, immeuble de 1989, 1 salle de bain + salle d'eau, animaux non acceptés, disponible 3 jours après acceptation de la promesse de location, Walk Score 97. Superficie non précisée mais 10 pièces au total (spacieux).</t>
+          <t>Animaux non acceptés, disponible 10 jours après acceptation de la promesse de location, courtier RE/MAX, Walk Score 96. Superficie non précisée mais 6 pièces/3 chambres (spacieux).</t>
         </is>
       </c>
       <c r="Q242" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15BA0BDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA409A74DDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
@@ -21455,22 +21455,22 @@
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres) - rue Bélanger (Rosemont/Villeray), à 5 min du métro D'Iberville</t>
+          <t>4 chambres, tout pres du metro Sherbrooke - avenue de Lorimier (Plateau, pres Parc Lafontaine) (Marketplace)</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>2468, Rue Bélanger, Montréal, QC</t>
+          <t>2319, Avenue de Lorimier, Montreal, QC H2K 3X4</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="H243" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I243" s="5" t="inlineStr">
@@ -21490,27 +21490,27 @@
       </c>
       <c r="J243" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K243" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>8 (estime)</t>
         </is>
       </c>
       <c r="M243" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N243" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/12923755</t>
+          <t>https://www.facebook.com/marketplace/item/1440128458152716</t>
         </is>
       </c>
       <c r="O243" s="5" t="inlineStr">
@@ -21520,19 +21520,15 @@
       </c>
       <c r="P243" s="6" t="inlineStr">
         <is>
-          <t>Animaux non acceptés, disponible 10 jours après acceptation de la promesse de location, courtier RE/MAX, Walk Score 96. Superficie non précisée mais 6 pièces/3 chambres (spacieux).</t>
-        </is>
-      </c>
-      <c r="Q243" s="5" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA409A74DDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
+          <t>1 seule salle de bain, climatisation, 4 electromenagers inclus, stationnement exterieur, tout pres du Parc Lafontaine ; le metro Sherbrooke a une entree a l'angle Cherrier/de Lorimier a quelques centaines de metres (non confirme directement par l'annonce). Disponible maintenant, bail 1 an. Lien Facebook (connexion requise).</t>
+        </is>
+      </c>
+      <c r="Q243" s="5" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B244" s="5" t="inlineStr">
@@ -21542,22 +21538,22 @@
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>4 chambres, tout pres du metro Sherbrooke - avenue de Lorimier (Plateau, pres Parc Lafontaine) (Marketplace)</t>
+          <t>5½ (3 chambres) - rue Bélanger, Rosemont/La Petite-Patrie, à 5 min du métro D'Iberville</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>2319, Avenue de Lorimier, Montreal, QC H2K 3X4</t>
+          <t>2470, Rue Bélanger, Montréal, QC</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -21567,55 +21563,59 @@
       </c>
       <c r="H244" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I244" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J244" s="5" t="inlineStr">
+        <is>
+          <t>D'Iberville</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="inlineStr">
+        <is>
+          <t>bleue</t>
+        </is>
+      </c>
+      <c r="L244" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M244" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N244" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9637205</t>
+        </is>
+      </c>
+      <c r="O244" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I244" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J244" s="5" t="inlineStr">
-        <is>
-          <t>Sherbrooke</t>
-        </is>
-      </c>
-      <c r="K244" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L244" s="5" t="inlineStr">
-        <is>
-          <t>8 (estime)</t>
-        </is>
-      </c>
-      <c r="M244" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N244" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1440128458152716</t>
-        </is>
-      </c>
-      <c r="O244" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P244" s="6" t="inlineStr">
         <is>
-          <t>1 seule salle de bain, climatisation, 4 electromenagers inclus, stationnement exterieur, tout pres du Parc Lafontaine ; le metro Sherbrooke a une entree a l'angle Cherrier/de Lorimier a quelques centaines de metres (non confirme directement par l'annonce). Disponible maintenant, bail 1 an. Lien Facebook (connexion requise).</t>
-        </is>
-      </c>
-      <c r="Q244" s="5" t="inlineStr"/>
+          <t>Logement de 6 pièces avec 3 chambres fermées (plus spacieux qu'un 5½), superficie non précisée par la fiche, animaux non acceptés, non-fumeurs, disponible 30 jours après acceptation de la promesse de location.</t>
+        </is>
+      </c>
+      <c r="Q244" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA409F9BDDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
@@ -21625,22 +21625,22 @@
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres) - rue Bélanger, Rosemont/La Petite-Patrie, à 5 min du métro D'Iberville</t>
+          <t>Cession de bail - Spacieux 3 chambres - 113 avenue Laurier Est (Plateau), à 7 min du métro Laurier</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>2470, Rue Bélanger, Montréal, QC</t>
+          <t>113, Avenue Laurier Est, Montréal</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -21660,27 +21660,27 @@
       </c>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K245" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M245" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N245" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9637205</t>
+          <t>https://www.facebook.com/marketplace/item/1334820052136089</t>
         </is>
       </c>
       <c r="O245" s="5" t="inlineStr">
@@ -21690,19 +21690,19 @@
       </c>
       <c r="P245" s="6" t="inlineStr">
         <is>
-          <t>Logement de 6 pièces avec 3 chambres fermées (plus spacieux qu'un 5½), superficie non précisée par la fiche, animaux non acceptés, non-fumeurs, disponible 30 jours après acceptation de la promesse de location.</t>
+          <t>Climatisation incluse, frigo et cuisiniere inclus, chats acceptes, disponible maintenant, promotion en cours. Lien Facebook (connexion requise) pour plus de details</t>
         </is>
       </c>
       <c r="Q245" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA409F9BDDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/756222412_1017386767836725_5739541558876083891_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=1k4qbrVFJKQQ7kNvwEj3yoN&amp;_nc_oc=AdpZYMJs7KK_vqKo_VnUSsID23B9yvH_t4K83jTVnEv2yoUM-9bYw0EumtA8a9aBZU8&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=scQ6-RimtwNLLPrNy_sIVQ&amp;_nc_ss=7f2a8&amp;oh=00_AQGT30nwKt0hgdXqXg5fPPqpy_Q8L3RL9rOuQbnnpdioVg&amp;oe=6A7E5515</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
@@ -21712,22 +21712,22 @@
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail - Spacieux 3 chambres - 113 avenue Laurier Est (Plateau), à 7 min du métro Laurier</t>
+          <t>3 grandes chambres, entièrement rénové - Villeray</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray-Saint-Michel-Parc-Extension</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>113, Avenue Laurier Est, Montréal</t>
+          <t>7635, Rue Saint-Hubert, Montréal</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="J246" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K246" s="5" t="inlineStr">
@@ -21757,17 +21757,17 @@
       </c>
       <c r="L246" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M246" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N246" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1334820052136089</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25817021</t>
         </is>
       </c>
       <c r="O246" s="5" t="inlineStr">
@@ -21777,19 +21777,19 @@
       </c>
       <c r="P246" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, frigo et cuisiniere inclus, chats acceptes, disponible maintenant, promotion en cours. Lien Facebook (connexion requise) pour plus de details</t>
+          <t>Moderne et entièrement rénové, aire ouverte et abondante lumière naturelle, animaux acceptés sous conditions, non-fumeur, stationnement en location (1-100$/mois), quartier dynamique de Villeray, balcon non mentionné dans l'annonce, disponible dès maintenant</t>
         </is>
       </c>
       <c r="Q246" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/756222412_1017386767836725_5739541558876083891_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=1k4qbrVFJKQQ7kNvwEj3yoN&amp;_nc_oc=AdpZYMJs7KK_vqKo_VnUSsID23B9yvH_t4K83jTVnEv2yoUM-9bYw0EumtA8a9aBZU8&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=scQ6-RimtwNLLPrNy_sIVQ&amp;_nc_ss=7f2a8&amp;oh=00_AQGT30nwKt0hgdXqXg5fPPqpy_Q8L3RL9rOuQbnnpdioVg&amp;oe=6A7E5515</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD627F1DDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
@@ -21799,22 +21799,22 @@
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>3 grandes chambres, entièrement rénové - Villeray</t>
+          <t>Grand condo 3 chambres, secteur Côte-des-Neiges-NDG, à 6 min du métro Plamondon</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension</t>
+          <t>Notre-Dame-de-Grâce</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>7635, Rue Saint-Hubert, Montréal</t>
+          <t>n/d (2180 Avenue Van Horne, Montréal)</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="J247" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Plamondon</t>
         </is>
       </c>
       <c r="K247" s="5" t="inlineStr">
@@ -21844,17 +21844,17 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M247" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N247" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25817021</t>
+          <t>https://www.facebook.com/marketplace/item/2155493188182731</t>
         </is>
       </c>
       <c r="O247" s="5" t="inlineStr">
@@ -21864,12 +21864,12 @@
       </c>
       <c r="P247" s="6" t="inlineStr">
         <is>
-          <t>Moderne et entièrement rénové, aire ouverte et abondante lumière naturelle, animaux acceptés sous conditions, non-fumeur, stationnement en location (1-100$/mois), quartier dynamique de Villeray, balcon non mentionné dans l'annonce, disponible dès maintenant</t>
+          <t>Grand 5 1/2 spacieux et lumineux, 3 chambres fermees, entierement renove, chauffage et eau chaude inclus, a 10 min de marche de l'UdM/Poly/HEC/Sainte-Justine. Le lien Marketplace exige une connexion Facebook.</t>
         </is>
       </c>
       <c r="Q247" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD627F1DDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/481156679_664529416364719_2168568913754087784_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=vw8p3HHsu2cQ7kNvwE2NDyr&amp;_nc_oc=Ado0sgW1rFkUtz5Yp3CUfMzXbfTR62iocR7B2m5qNcRpWflXhNRclxjPXV7x2lLUP20&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=HILoInAtu5S7lebdsQuqmg&amp;_nc_ss=7f2a8&amp;oh=00_AQDznoRo6raDcHjdnSNLqlDP69toAEwdOrt-D6F5nudkPw&amp;oe=6A703993</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="C248" s="6" t="inlineStr">
         <is>
-          <t>Grand condo 3 chambres, secteur Côte-des-Neiges-NDG, à 6 min du métro Plamondon</t>
+          <t>3 chambres fermées, secteur NDG, à ~10 min du métro Vendôme</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
@@ -21896,12 +21896,12 @@
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>n/d (2180 Avenue Van Horne, Montréal)</t>
+          <t>n/d (Avenue d'Oxford, Montréal, QC H4A 2Y2)</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="J248" s="5" t="inlineStr">
         <is>
-          <t>Plamondon</t>
+          <t>Vendôme</t>
         </is>
       </c>
       <c r="K248" s="5" t="inlineStr">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="L248" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M248" s="5" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="N248" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2155493188182731</t>
+          <t>https://www.facebook.com/marketplace/item/1010816048507614</t>
         </is>
       </c>
       <c r="O248" s="5" t="inlineStr">
@@ -21951,19 +21951,19 @@
       </c>
       <c r="P248" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 spacieux et lumineux, 3 chambres fermees, entierement renove, chauffage et eau chaude inclus, a 10 min de marche de l'UdM/Poly/HEC/Sainte-Justine. Le lien Marketplace exige une connexion Facebook.</t>
+          <t>Petite salle de lavage, acces a la cour, beaucoup de petits commerces (epicerie, Dollarama) a proximite, ligne d'autobus 105 et 420 express pres, grand parc et voie cyclable sur Maisonneuve. Le lien Marketplace exige une connexion Facebook.</t>
         </is>
       </c>
       <c r="Q248" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/481156679_664529416364719_2168568913754087784_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=vw8p3HHsu2cQ7kNvwE2NDyr&amp;_nc_oc=Ado0sgW1rFkUtz5Yp3CUfMzXbfTR62iocR7B2m5qNcRpWflXhNRclxjPXV7x2lLUP20&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=HILoInAtu5S7lebdsQuqmg&amp;_nc_ss=7f2a8&amp;oh=00_AQDznoRo6raDcHjdnSNLqlDP69toAEwdOrt-D6F5nudkPw&amp;oe=6A703993</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/758964283_27986895444278763_3549468274452706154_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=wCa1Hke9Y3QQ7kNvwEPYiqS&amp;_nc_oc=AdrMi2qF5GGrSnUUDf0cKq7CMi6xor3aP9htP7DtSInOcqEtKHrPFafre50VqkvnGns&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=HILoInAtu5S7lebdsQuqmg&amp;_nc_ss=7f2a8&amp;oh=00_AQBUMAz4arOsqNOrUKT6EXx0Op5x1JwDM045l9BlsN0QRw&amp;oe=6A70432A</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
@@ -21973,22 +21973,22 @@
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées, secteur NDG, à ~10 min du métro Vendôme</t>
+          <t>Appartement rénové (semi sous-sol), 3 chambres - avenue De Gaspé (Villeray/Petite Italie, près métro De Castelnau)</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Notre-Dame-de-Grâce</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>n/d (Avenue d'Oxford, Montréal, QC H4A 2Y2)</t>
+          <t>6695, Avenue De Gaspé, app. 1, Montréal</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -22008,27 +22008,27 @@
       </c>
       <c r="J249" s="5" t="inlineStr">
         <is>
-          <t>Vendôme</t>
+          <t>De Castelnau</t>
         </is>
       </c>
       <c r="K249" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9 (estimé, incertain)</t>
         </is>
       </c>
       <c r="M249" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N249" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1010816048507614</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/15505756</t>
         </is>
       </c>
       <c r="O249" s="5" t="inlineStr">
@@ -22038,19 +22038,19 @@
       </c>
       <c r="P249" s="6" t="inlineStr">
         <is>
-          <t>Petite salle de lavage, acces a la cour, beaucoup de petits commerces (epicerie, Dollarama) a proximite, ligne d'autobus 105 et 420 express pres, grand parc et voie cyclable sur Maisonneuve. Le lien Marketplace exige une connexion Facebook.</t>
+          <t>Unité en semi sous-sol (moins de lumière naturelle), coin Saint-Zotique/De Gaspé, cuisine équipée, laveuse-sécheuse incluses, non-fumeurs, disponible immédiatement ou 5 jours après acceptation. Walk Score 99. Superficie et balcon non précisés, distance métro estimée non confirmée.</t>
         </is>
       </c>
       <c r="Q249" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/758964283_27986895444278763_3549468274452706154_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=wCa1Hke9Y3QQ7kNvwEPYiqS&amp;_nc_oc=AdrMi2qF5GGrSnUUDf0cKq7CMi6xor3aP9htP7DtSInOcqEtKHrPFafre50VqkvnGns&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=HILoInAtu5S7lebdsQuqmg&amp;_nc_ss=7f2a8&amp;oh=00_AQBUMAz4arOsqNOrUKT6EXx0Op5x1JwDM045l9BlsN0QRw&amp;oe=6A70432A</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA416127DDDDDDDDDD0&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
@@ -22060,22 +22060,22 @@
       </c>
       <c r="C250" s="6" t="inlineStr">
         <is>
-          <t>Appartement rénové (semi sous-sol), 3 chambres - avenue De Gaspé (Villeray/Petite Italie, près métro De Castelnau)</t>
+          <t>3 chambres - rue Saint-Dominique (Plateau), à 8 min du métro Sherbrooke/Saint-Laurent</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>6695, Avenue De Gaspé, app. 1, Montréal</t>
+          <t>3554, Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -22095,17 +22095,17 @@
       </c>
       <c r="J250" s="5" t="inlineStr">
         <is>
-          <t>De Castelnau</t>
+          <t>Sherbrooke ou Saint-Laurent</t>
         </is>
       </c>
       <c r="K250" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L250" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé, incertain)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M250" s="5" t="inlineStr">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="N250" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/15505756</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/17619217</t>
         </is>
       </c>
       <c r="O250" s="5" t="inlineStr">
@@ -22125,12 +22125,12 @@
       </c>
       <c r="P250" s="6" t="inlineStr">
         <is>
-          <t>Unité en semi sous-sol (moins de lumière naturelle), coin Saint-Zotique/De Gaspé, cuisine équipée, laveuse-sécheuse incluses, non-fumeurs, disponible immédiatement ou 5 jours après acceptation. Walk Score 99. Superficie et balcon non précisés, distance métro estimée non confirmée.</t>
+          <t>Immeuble construit en 1915, stationnement ruelle 200$/mois en sus, disponible 7 jours après acceptation, Walk Score 100</t>
         </is>
       </c>
       <c r="Q250" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA416127DDDDDDDDDD0&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE31D9FDDDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -22147,7 +22147,7 @@
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>3 chambres - rue Saint-Dominique (Plateau), à 8 min du métro Sherbrooke/Saint-Laurent</t>
+          <t>2 chambres, rez-de-chaussée avec cour partagée - rue De Bullion (Plateau/Mile-End), à 5 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
@@ -22157,12 +22157,12 @@
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>3554, Rue Saint-Dominique, Montréal</t>
+          <t>4632, Rue De Bullion, Montréal</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -22172,27 +22172,27 @@
       </c>
       <c r="H251" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J251" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Saint-Laurent</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K251" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M251" s="5" t="inlineStr">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="N251" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/17619217</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/16426752</t>
         </is>
       </c>
       <c r="O251" s="5" t="inlineStr">
@@ -22212,19 +22212,19 @@
       </c>
       <c r="P251" s="6" t="inlineStr">
         <is>
-          <t>Immeuble construit en 1915, stationnement ruelle 200$/mois en sus, disponible 7 jours après acceptation, Walk Score 100</t>
+          <t>Semi-meublé, cour partagée (pas de balcon), animaux acceptés sous conditions, disponible 1er sept. 2026, Walk Score 100</t>
         </is>
       </c>
       <c r="Q251" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE31D9FDDDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA131C84DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
@@ -22234,22 +22234,22 @@
       </c>
       <c r="C252" s="6" t="inlineStr">
         <is>
-          <t>2 chambres, rez-de-chaussée avec cour partagée - rue De Bullion (Plateau/Mile-End), à 5 min du métro Mont-Royal</t>
+          <t>3 chambres + bureau avec cour privée - rue Drolet (Villeray, près Jean-Talon/De Castelnau)</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>4632, Rue De Bullion, Montréal</t>
+          <t>7372, Rue Drolet, Montréal</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
@@ -22269,17 +22269,17 @@
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>De Castelnau</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M252" s="5" t="inlineStr">
@@ -22289,7 +22289,7 @@
       </c>
       <c r="N252" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/16426752</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/23857701</t>
         </is>
       </c>
       <c r="O252" s="5" t="inlineStr">
@@ -22299,19 +22299,19 @@
       </c>
       <c r="P252" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, cour partagée (pas de balcon), animaux acceptés sous conditions, disponible 1er sept. 2026, Walk Score 100</t>
+          <t>Rez-de-chaussée avec cour privée (pas de balcon), immeuble de 1923, proche Marché Jean-Talon et Petite Italie, Walk Score 98, non-fumeur, animaux non acceptés, disponible 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q252" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA131C84DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD115E0DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
@@ -22321,22 +22321,22 @@
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>3 chambres + bureau avec cour privée - rue Drolet (Villeray, près Jean-Talon/De Castelnau)</t>
+          <t>6½ (3 chambres), rez-de-chaussée avec cour et stationnement - 27e Avenue (Rosemont, près métro D'Iberville)</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>7372, Rue Drolet, Montréal</t>
+          <t>6749, 27e Avenue, Montréal</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -22351,12 +22351,12 @@
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>De Castelnau</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K253" s="5" t="inlineStr">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M253" s="5" t="inlineStr">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="N253" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/23857701</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/20987825</t>
         </is>
       </c>
       <c r="O253" s="5" t="inlineStr">
@@ -22386,12 +22386,12 @@
       </c>
       <c r="P253" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée avec cour privée (pas de balcon), immeuble de 1923, proche Marché Jean-Talon et Petite Italie, Walk Score 98, non-fumeur, animaux non acceptés, disponible 1er juillet 2026</t>
+          <t>7 pièces, rez-de-chaussée de triplex avec sous-sol, cour et stationnement inclus, animaux permis sur analyse, disponible 1er juillet 2026, métro Fabre aussi accessible (~5 min)</t>
         </is>
       </c>
       <c r="Q253" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD115E0DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6C9AB9DDDDDDDDDDC&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -22408,22 +22408,22 @@
       </c>
       <c r="C254" s="6" t="inlineStr">
         <is>
-          <t>6½ (3 chambres), rez-de-chaussée avec cour et stationnement - 27e Avenue (Rosemont, près métro D'Iberville)</t>
+          <t>5½ semi-meublé, 3 grandes chambres - rue Saint-Hubert (Villeray, près métro Jarry)</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>6749, 27e Avenue, Montréal</t>
+          <t>7635, Rue Saint-Hubert, Montréal</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -22443,17 +22443,17 @@
       </c>
       <c r="J254" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L254" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M254" s="5" t="inlineStr">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="N254" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/20987825</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25817021</t>
         </is>
       </c>
       <c r="O254" s="5" t="inlineStr">
@@ -22473,19 +22473,19 @@
       </c>
       <c r="P254" s="6" t="inlineStr">
         <is>
-          <t>7 pièces, rez-de-chaussée de triplex avec sous-sol, cour et stationnement inclus, animaux permis sur analyse, disponible 1er juillet 2026, métro Fabre aussi accessible (~5 min)</t>
+          <t>Semi-meublé, animaux acceptés sous conditions, disponible 1er juillet 2026, à ~11 min du métro Jarry (proche de la limite de 12 min) ; à ne pas confondre avec le 7639 rue Saint-Hubert déjà répertorié (adresse voisine, annonce distincte)</t>
         </is>
       </c>
       <c r="Q254" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6C9AB9DDDDDDDDDDC&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD627F1DDDDDDDDDD2&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
@@ -22495,22 +22495,22 @@
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>5½ semi-meublé, 3 grandes chambres - rue Saint-Hubert (Villeray, près métro Jarry)</t>
+          <t>4 chambres meublé, Plateau-Mont-Royal (Marketplace)</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>7635, Rue Saint-Hubert, Montréal</t>
+          <t>3681, avenue Coloniale, Montréal (H2X 2Y7)</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="H255" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I255" s="5" t="inlineStr">
@@ -22530,7 +22530,7 @@
       </c>
       <c r="J255" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Mont-Royal ou Sherbrooke (à vérifier)</t>
         </is>
       </c>
       <c r="K255" s="5" t="inlineStr">
@@ -22540,17 +22540,17 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M255" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N255" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/25817021</t>
+          <t>https://www.facebook.com/marketplace/item/1578661203923320</t>
         </is>
       </c>
       <c r="O255" s="5" t="inlineStr">
@@ -22560,19 +22560,19 @@
       </c>
       <c r="P255" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions, disponible 1er juillet 2026, à ~11 min du métro Jarry (proche de la limite de 12 min) ; à ne pas confondre avec le 7639 rue Saint-Hubert déjà répertorié (adresse voisine, annonce distincte)</t>
+          <t>Meublé, orienté étudiants, bail 1 an, dispo maintenant. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q255" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD627F1DDDDDDDDDD2&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/746058480_2385279625296639_1965210297754561149_n.jpg?stp=c93.0.895.895a_dst-jpg_tt6&amp;cstp=mx895x895&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=ngElLDKbnLQQ7kNvwHndFuc&amp;_nc_oc=AdpOYEcvWwImdnqaiYyy1pwfVcV2sab1mFRQ5KYGa5FE_CkYORsBa8yvv6PCL2lbQ7E&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EorVHkPe0HNRZxtO75C5fg&amp;_nc_ss=7f2a8&amp;oh=00_AQBlE2b8WT_3jlX6ddiFysYujtaCjsMiZRfF96JJT7pp3g&amp;oe=6A60805A</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
@@ -22582,17 +22582,17 @@
       </c>
       <c r="C256" s="6" t="inlineStr">
         <is>
-          <t>4 chambres meublé, Plateau-Mont-Royal (Marketplace)</t>
+          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>3681, avenue Coloniale, Montréal (H2X 2Y7)</t>
+          <t>2121 Avenue Papineau, app. 106, Montréal</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
@@ -22607,59 +22607,59 @@
       </c>
       <c r="H256" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I256" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J256" s="5" t="inlineStr">
+        <is>
+          <t>Papineau</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L256" s="5" t="inlineStr">
+        <is>
+          <t>11 (estimé)</t>
+        </is>
+      </c>
+      <c r="M256" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N256" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
+        </is>
+      </c>
+      <c r="O256" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I256" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J256" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal ou Sherbrooke (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K256" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L256" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M256" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N256" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1578661203923320</t>
-        </is>
-      </c>
-      <c r="O256" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P256" s="6" t="inlineStr">
         <is>
-          <t>Meublé, orienté étudiants, bail 1 an, dispo maintenant. Lien Facebook (connexion requise)</t>
+          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q256" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/746058480_2385279625296639_1965210297754561149_n.jpg?stp=c93.0.895.895a_dst-jpg_tt6&amp;cstp=mx895x895&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=ngElLDKbnLQQ7kNvwHndFuc&amp;_nc_oc=AdpOYEcvWwImdnqaiYyy1pwfVcV2sab1mFRQ5KYGa5FE_CkYORsBa8yvv6PCL2lbQ7E&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EorVHkPe0HNRZxtO75C5fg&amp;_nc_ss=7f2a8&amp;oh=00_AQBlE2b8WT_3jlX6ddiFysYujtaCjsMiZRfF96JJT7pp3g&amp;oe=6A60805A</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
@@ -22669,22 +22669,22 @@
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
+          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>2121 Avenue Papineau, app. 106, Montréal</t>
+          <t>3855 rue St-André (H2L 3V9)</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="H257" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I257" s="5" t="inlineStr">
@@ -22704,17 +22704,17 @@
       </c>
       <c r="J257" s="5" t="inlineStr">
         <is>
-          <t>Papineau</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K257" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>11 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M257" s="5" t="inlineStr">
@@ -22724,7 +22724,7 @@
       </c>
       <c r="N257" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
+          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
         </is>
       </c>
       <c r="O257" s="5" t="inlineStr">
@@ -22734,19 +22734,19 @@
       </c>
       <c r="P257" s="6" t="inlineStr">
         <is>
-          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
+          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q257" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="C258" s="6" t="inlineStr">
         <is>
-          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
@@ -22766,12 +22766,12 @@
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>3855 rue St-André (H2L 3V9)</t>
+          <t>4275 Rue de Bordeaux, Montréal</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -22781,59 +22781,59 @@
       </c>
       <c r="H258" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I258" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J258" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L258" s="5" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M258" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N258" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+        </is>
+      </c>
+      <c r="O258" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I258" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J258" s="5" t="inlineStr">
-        <is>
-          <t>Sherbrooke</t>
-        </is>
-      </c>
-      <c r="K258" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L258" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M258" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N258" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
-        </is>
-      </c>
-      <c r="O258" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P258" s="6" t="inlineStr">
         <is>
-          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
         </is>
       </c>
       <c r="Q258" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
@@ -22843,7 +22843,7 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
@@ -22853,12 +22853,12 @@
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -22878,7 +22878,7 @@
       </c>
       <c r="J259" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
         </is>
       </c>
       <c r="K259" s="5" t="inlineStr">
@@ -22888,7 +22888,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M259" s="5" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="N259" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
         </is>
       </c>
       <c r="O259" s="5" t="inlineStr">
@@ -22908,19 +22908,19 @@
       </c>
       <c r="P259" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
         </is>
       </c>
       <c r="Q259" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B260" s="5" t="inlineStr">
@@ -22930,7 +22930,7 @@
       </c>
       <c r="C260" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
@@ -22940,12 +22940,12 @@
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>62 rue Rachel Est, Montréal</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -22965,7 +22965,7 @@
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M260" s="5" t="inlineStr">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N260" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
         </is>
       </c>
       <c r="O260" s="5" t="inlineStr">
@@ -22995,19 +22995,19 @@
       </c>
       <c r="P260" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
         </is>
       </c>
       <c r="Q260" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
@@ -23017,22 +23017,22 @@
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>5½ rénové - Rosemont, 3 chambres + bureau (Marketplace)</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>n/d (secteur Rosemont, Montréal)</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -23042,59 +23042,59 @@
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
+          <t>3 (selon titre, à confirmer)</t>
+        </is>
+      </c>
+      <c r="I261" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J261" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L261" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M261" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N261" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1905640337262053</t>
+        </is>
+      </c>
+      <c r="O261" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I261" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J261" s="5" t="inlineStr">
-        <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K261" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L261" s="5" t="inlineStr">
-        <is>
-          <t>8 (estimé)</t>
-        </is>
-      </c>
-      <c r="M261" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N261" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
-        </is>
-      </c>
-      <c r="O261" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P261" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>Annonce titre seulement (« 5 1/2 rénové - Rosemont - 3 chambres + bureau »), aucune adresse ni description détaillée disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q261" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/787761292_1065504692896878_4836055761486525916_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=MOCJ79afpPoQ7kNvwHB1OUw&amp;_nc_oc=Adr_kZR22WI-TaE-t3PMKjYftS_SVUX2bAUlPv8Qz_8bghKNDkoSXa2JK6t9RqxndLc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=wgjL71BuqJilZmCDsgzwAw&amp;_nc_ss=7f289&amp;oh=00_AQIu4EnP-eitSmW9cB7PzqKfHZ07AHdQlQEc8LQQHjmjMA&amp;oe=6A9DD845</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
@@ -23104,7 +23104,7 @@
       </c>
       <c r="C262" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové - Rosemont, 3 chambres + bureau (Marketplace)</t>
+          <t>Logement 5 1/2 rénové, 3 chambres + bureau - Rosemont (Marketplace)</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Rosemont, Montréal)</t>
+          <t>n/d (secteur Rosemont-La Petite-Patrie, Montréal)</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
@@ -23129,7 +23129,7 @@
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>3 (selon titre, à confirmer)</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="I262" s="5" t="inlineStr">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="N262" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1905640337262053</t>
+          <t>https://www.facebook.com/marketplace/item/1613584236892605</t>
         </is>
       </c>
       <c r="O262" s="5" t="inlineStr">
@@ -23169,19 +23169,19 @@
       </c>
       <c r="P262" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (« 5 1/2 rénové - Rosemont - 3 chambres + bureau »), aucune adresse ni description détaillée disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Annonce titre seulement (« Logement 5 1/2 rénové Rosemont - 3 chambres + bureau »), aucune adresse ni description détaillée disponible via le scraper. Nombre de chambres selon le titre (3 + bureau). Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q262" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/787761292_1065504692896878_4836055761486525916_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=MOCJ79afpPoQ7kNvwHB1OUw&amp;_nc_oc=Adr_kZR22WI-TaE-t3PMKjYftS_SVUX2bAUlPv8Qz_8bghKNDkoSXa2JK6t9RqxndLc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=wgjL71BuqJilZmCDsgzwAw&amp;_nc_ss=7f289&amp;oh=00_AQIu4EnP-eitSmW9cB7PzqKfHZ07AHdQlQEc8LQQHjmjMA&amp;oe=6A9DD845</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/789845450_1602489944997832_5213134105176151966_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xzqo9iyYcAkQ7kNvwHRvmWj&amp;_nc_oc=Adp04UM8mMS7TYZztbruBwtONw22BOWfpCFSRMezlhO7JaSrV4L2CIIxMvRmLg4IrzQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=iDnTU3IQw0eGZCC-IJSGrw&amp;_nc_ss=7f2a8&amp;oh=00_AQKWwqFPn5wiyRr8UhOqIiE2fW-83zbjH04dhSzspmsjgw&amp;oe=6A9A671F</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
@@ -23191,7 +23191,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>Logement 5 1/2 rénové, 3 chambres + bureau - Rosemont (Marketplace)</t>
+          <t>4½ rénové (2 chambres), semi-meublé - Plaza St-Hubert (Rosemont), près du métro Beaubien</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
@@ -23201,12 +23201,12 @@
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Rosemont-La Petite-Patrie, Montréal)</t>
+          <t>6617, Rue Saint-Hubert, app. 201, Montréal</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I263" s="5" t="inlineStr">
@@ -23226,27 +23226,27 @@
       </c>
       <c r="J263" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K263" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M263" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N263" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1613584236892605</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/26894928</t>
         </is>
       </c>
       <c r="O263" s="5" t="inlineStr">
@@ -23256,12 +23256,12 @@
       </c>
       <c r="P263" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (« Logement 5 1/2 rénové Rosemont - 3 chambres + bureau »), aucune adresse ni description détaillée disponible via le scraper. Nombre de chambres selon le titre (3 + bureau). Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Entièrement rénové (finitions contemporaines), semi-meublé, climatisation et internet inclus, animaux acceptés sous conditions, disponible 2 jours après acceptation, en plein Plaza St-Hubert, proche marché Jean-Talon et Petite Italie, Walk Score 97. Balcon et superficie non précisés.</t>
         </is>
       </c>
       <c r="Q263" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/789845450_1602489944997832_5213134105176151966_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xzqo9iyYcAkQ7kNvwHRvmWj&amp;_nc_oc=Adp04UM8mMS7TYZztbruBwtONw22BOWfpCFSRMezlhO7JaSrV4L2CIIxMvRmLg4IrzQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=iDnTU3IQw0eGZCC-IJSGrw&amp;_nc_ss=7f2a8&amp;oh=00_AQKWwqFPn5wiyRr8UhOqIiE2fW-83zbjH04dhSzspmsjgw&amp;oe=6A9A671F</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4631F1DDDDDDDDDDC&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -23278,7 +23278,7 @@
       </c>
       <c r="C264" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové (2 chambres), semi-meublé - Plaza St-Hubert (Rosemont), près du métro Beaubien</t>
+          <t>4½ (2 chambres) - secteur résidentiel calme, 23e Avenue (Rosemont)</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
@@ -23288,12 +23288,12 @@
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>6617, Rue Saint-Hubert, app. 201, Montréal</t>
+          <t>6001, 23e Avenue, app. 3, Montréal</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -23313,7 +23313,7 @@
       </c>
       <c r="J264" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Beaubien ou Rosemont (estimé)</t>
         </is>
       </c>
       <c r="K264" s="5" t="inlineStr">
@@ -23323,7 +23323,7 @@
       </c>
       <c r="L264" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M264" s="5" t="inlineStr">
@@ -23333,7 +23333,7 @@
       </c>
       <c r="N264" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/26894928</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/22497736</t>
         </is>
       </c>
       <c r="O264" s="5" t="inlineStr">
@@ -23343,12 +23343,12 @@
       </c>
       <c r="P264" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové (finitions contemporaines), semi-meublé, climatisation et internet inclus, animaux acceptés sous conditions, disponible 2 jours après acceptation, en plein Plaza St-Hubert, proche marché Jean-Talon et Petite Italie, Walk Score 97. Balcon et superficie non précisés.</t>
+          <t>Bien aménagé, lumineux, finitions soignées, secteur résidentiel paisible près parcs/commerces/écoles, disponible 5 jours après acceptation, Walk Score 85. Balcon, animaux et chauffage non précisés dans l'annonce.</t>
         </is>
       </c>
       <c r="Q264" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4631F1DDDDDDDDDDC&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4AE812DDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -23365,22 +23365,22 @@
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>4½ (2 chambres) - secteur résidentiel calme, 23e Avenue (Rosemont)</t>
+          <t>4½ (2 chambres) - rue De La Roche (Plateau)</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>6001, 23e Avenue, app. 3, Montréal</t>
+          <t>4417, Rue De La Roche, app. 4, Montréal</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -23400,7 +23400,7 @@
       </c>
       <c r="J265" s="5" t="inlineStr">
         <is>
-          <t>Beaubien ou Rosemont (estimé)</t>
+          <t>Mont-Royal (estimé)</t>
         </is>
       </c>
       <c r="K265" s="5" t="inlineStr">
@@ -23410,7 +23410,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M265" s="5" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="N265" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/22497736</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/14734354</t>
         </is>
       </c>
       <c r="O265" s="5" t="inlineStr">
@@ -23430,19 +23430,19 @@
       </c>
       <c r="P265" s="6" t="inlineStr">
         <is>
-          <t>Bien aménagé, lumineux, finitions soignées, secteur résidentiel paisible près parcs/commerces/écoles, disponible 5 jours après acceptation, Walk Score 85. Balcon, animaux et chauffage non précisés dans l'annonce.</t>
+          <t>Peu de détails dans l'annonce (balcon, superficie, animaux et chauffage non précisés), disponible 24 août 2026, Walk Score 99, secteur à confirmer avant de contacter.</t>
         </is>
       </c>
       <c r="Q265" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4AE812DDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2DDB74DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="C266" s="6" t="inlineStr">
         <is>
-          <t>4½ (2 chambres) - rue De La Roche (Plateau)</t>
+          <t>2 chambres rénové, près de la rue Mont-Royal et du métro Mont-Royal (Marketplace)</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
@@ -23462,12 +23462,12 @@
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>4417, Rue De La Roche, app. 4, Montréal</t>
+          <t>4408, Avenue de l'Hôtel-de-Ville, Montréal</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="J266" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal (estimé)</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K266" s="5" t="inlineStr">
@@ -23497,17 +23497,17 @@
       </c>
       <c r="L266" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M266" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N266" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/14734354</t>
+          <t>https://www.facebook.com/marketplace/item/3643447005808131</t>
         </is>
       </c>
       <c r="O266" s="5" t="inlineStr">
@@ -23517,19 +23517,19 @@
       </c>
       <c r="P266" s="6" t="inlineStr">
         <is>
-          <t>Peu de détails dans l'annonce (balcon, superficie, animaux et chauffage non précisés), disponible 24 août 2026, Walk Score 99, secteur à confirmer avant de contacter.</t>
+          <t>Nouvellement rénové, meublé (table, chaises, canapé, lits), climatisation incluse, isolation phonique/thermique complète, plafonds hauts, animaux acceptés. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q266" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2DDB74DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/769082955_1572138077922196_3928924517892675151_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=5lbjrhSykR4Q7kNvwGXZEsS&amp;_nc_oc=AdosPHcT82UDB5JXJB3hFRrzA2ywy8Iz4eDC9_v14IG5fPngcGQrop8r6fkrAZcfxOg&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=hnqIHFjbxMu6V7YVFERN2g&amp;_nc_ss=7f2a8&amp;oh=00_AQFUCFiOoITnnQEKag8_p25qfElq9MW43hMXPo8TnhpJ_g&amp;oe=6A91378D</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
@@ -23539,22 +23539,22 @@
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>2 chambres rénové, près de la rue Mont-Royal et du métro Mont-Royal (Marketplace)</t>
+          <t>Appartement 5½ (Hochelaga) - infos limitées, à vérifier via Facebook Marketplace</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>4408, Avenue de l'Hôtel-de-Ville, Montréal</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I267" s="5" t="inlineStr">
@@ -23574,17 +23574,17 @@
       </c>
       <c r="J267" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>n/d (secteur Hochelaga)</t>
         </is>
       </c>
       <c r="K267" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M267" s="5" t="inlineStr">
@@ -23594,7 +23594,7 @@
       </c>
       <c r="N267" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/3643447005808131</t>
+          <t>https://www.facebook.com/marketplace/item/1020807880801669</t>
         </is>
       </c>
       <c r="O267" s="5" t="inlineStr">
@@ -23604,19 +23604,19 @@
       </c>
       <c r="P267" s="6" t="inlineStr">
         <is>
-          <t>Nouvellement rénové, meublé (table, chaises, canapé, lits), climatisation incluse, isolation phonique/thermique complète, plafonds hauts, animaux acceptés. Lien Facebook (connexion requise)</t>
+          <t>Fiche Marketplace très peu détaillée (titre et prix seulement, pas de description ni superficie). Chambres estimées à 3 d'après le type 5½. Le lien exige une connexion Facebook pour voir les détails complets.</t>
         </is>
       </c>
       <c r="Q267" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/769082955_1572138077922196_3928924517892675151_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=5lbjrhSykR4Q7kNvwGXZEsS&amp;_nc_oc=AdosPHcT82UDB5JXJB3hFRrzA2ywy8Iz4eDC9_v14IG5fPngcGQrop8r6fkrAZcfxOg&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=hnqIHFjbxMu6V7YVFERN2g&amp;_nc_ss=7f2a8&amp;oh=00_AQFUCFiOoITnnQEKag8_p25qfElq9MW43hMXPo8TnhpJ_g&amp;oe=6A91378D</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/740733947_28734879242768603_2405899251014488449_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q9ViAyeDpUAQ7kNvwFF85BL&amp;_nc_oc=Adr4Bry90yP1945bAQ7iQ52U9LuxXUfcltCcAJNNZMjNUaTJQ7tsFLsd_jtuJfl42Ps&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=rTvNKBKykO1Kn418ORNEfA&amp;_nc_ss=7f2a8&amp;oh=00_AQHwScRvAsPs8uZWD-UEV1uK_8325MQziNdaYa1h63-U7A&amp;oe=6A8FDC27</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -23626,22 +23626,22 @@
       </c>
       <c r="C268" s="6" t="inlineStr">
         <is>
-          <t>Appartement 5½ (Hochelaga) - infos limitées, à vérifier via Facebook Marketplace</t>
+          <t>Appartement 2 chambres + bureau, quartier central Plateau, à ~11 min du métro Sherbrooke (Marketplace)</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>3984 Rue de Bullion, Montréal, QC H2W 2E4</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -23651,59 +23651,59 @@
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I268" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J268" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K268" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L268" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M268" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N268" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1528694045314689</t>
+        </is>
+      </c>
+      <c r="O268" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I268" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J268" s="5" t="inlineStr">
-        <is>
-          <t>n/d (secteur Hochelaga)</t>
-        </is>
-      </c>
-      <c r="K268" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L268" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M268" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N268" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1020807880801669</t>
-        </is>
-      </c>
-      <c r="O268" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="P268" s="6" t="inlineStr">
         <is>
-          <t>Fiche Marketplace très peu détaillée (titre et prix seulement, pas de description ni superficie). Chambres estimées à 3 d'après le type 5½. Le lien exige une connexion Facebook pour voir les détails complets.</t>
+          <t>Deux chambres fermees + un espace de bureau, electromenagers inclus, bail 1 an, disponible maintenant, quartier central (Walk Score 100, Bike Score 98). Superficie non indiquee. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q268" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/740733947_28734879242768603_2405899251014488449_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q9ViAyeDpUAQ7kNvwFF85BL&amp;_nc_oc=Adr4Bry90yP1945bAQ7iQ52U9LuxXUfcltCcAJNNZMjNUaTJQ7tsFLsd_jtuJfl42Ps&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=rTvNKBKykO1Kn418ORNEfA&amp;_nc_ss=7f2a8&amp;oh=00_AQHwScRvAsPs8uZWD-UEV1uK_8325MQziNdaYa1h63-U7A&amp;oe=6A8FDC27</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/722994642_10164255701674834_4384640404152492239_n.jpg?stp=c342.0.1365.1365a_dst-jpg_tt6&amp;cstp=mx1365x1365&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=P20jq1k6qjIQ7kNvwF35WB_&amp;_nc_oc=AdrWOhKe-TO43O_pi7-zm4f94i1vfAPIWDFFxE3h49ZzbSfBqp_EeJowVqfsNEyEzmY&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=-RRMTc1fIutY57-pjw9YmQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHvo5JUjbFeFE0mNam3RiJtgV0tjwf8rAM1aebC8RWpDQ&amp;oe=6A8E14C9</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
@@ -23713,22 +23713,22 @@
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>Appartement 2 chambres + bureau, quartier central Plateau, à ~11 min du métro Sherbrooke (Marketplace)</t>
+          <t>5½ rénové (2 chambres), garde-robes walk-in - secteur Villeray, à 5 min du métro Jarry</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>3984 Rue de Bullion, Montréal, QC H2W 2E4</t>
+          <t>n/d (Montréal, QC H2R 2P3)</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -23743,12 +23743,12 @@
       </c>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J269" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K269" s="5" t="inlineStr">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M269" s="5" t="inlineStr">
@@ -23768,7 +23768,7 @@
       </c>
       <c r="N269" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1528694045314689</t>
+          <t>https://www.facebook.com/marketplace/item/1318066247058264</t>
         </is>
       </c>
       <c r="O269" s="5" t="inlineStr">
@@ -23778,19 +23778,19 @@
       </c>
       <c r="P269" s="6" t="inlineStr">
         <is>
-          <t>Deux chambres fermees + un espace de bureau, electromenagers inclus, bail 1 an, disponible maintenant, quartier central (Walk Score 100, Bike Score 98). Superficie non indiquee. Lien Facebook (connexion requise).</t>
+          <t>Entièrement rénové (cuisine avec îlot, planchers refaits), chambre principale avec walk-in, 2e chambre avec grand garde-robe, thermopompe, porte-patio vers cour arrière (pas de balcon), à distance de marche du métro Jarry et du marché Jean-Talon, références demandées, aucun animal, disponible 1er oct. 2026, bail 1 an. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q269" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/722994642_10164255701674834_4384640404152492239_n.jpg?stp=c342.0.1365.1365a_dst-jpg_tt6&amp;cstp=mx1365x1365&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=P20jq1k6qjIQ7kNvwF35WB_&amp;_nc_oc=AdrWOhKe-TO43O_pi7-zm4f94i1vfAPIWDFFxE3h49ZzbSfBqp_EeJowVqfsNEyEzmY&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=-RRMTc1fIutY57-pjw9YmQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHvo5JUjbFeFE0mNam3RiJtgV0tjwf8rAM1aebC8RWpDQ&amp;oe=6A8E14C9</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/730304009_10243338752987620_3251931066748678009_n.jpg?stp=c341.0.1367.1367a_dst-jpg_tt6&amp;cstp=mx1367x1367&amp;ctp=s565x565&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=T1M2AeYt3WkQ7kNvwEbtDR9&amp;_nc_oc=AdqdPqtbLbupPJRjBJ9G6l5MxrQhR9IhCxSGNw-xvzoSzkXhl2b7yw4yEMa1hIVXQLo&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=gi1y626B7giI3AkvJxbp7A&amp;_nc_ss=7f2a8&amp;oh=00_AQHDh36TzcRlsSalStNzCi2WPYfPNl7gzA_gMGdg3e-VhQ&amp;oe=6A8B7951</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
@@ -23800,22 +23800,22 @@
       </c>
       <c r="C270" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (2 chambres), garde-robes walk-in - secteur Villeray, à 5 min du métro Jarry</t>
+          <t>5 1/2 (2 chambres) avec bureau, 2e étage - rue Saint-Viateur Ouest (Mile-End/Plateau)</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2R 2P3)</t>
+          <t>229, Rue Saint-Viateur Ouest, app. 3, Montréal</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -23830,12 +23830,12 @@
       </c>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J270" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Rosemont (estimé)</t>
         </is>
       </c>
       <c r="K270" s="5" t="inlineStr">
@@ -23845,17 +23845,17 @@
       </c>
       <c r="L270" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M270" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N270" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1318066247058264</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/12176453</t>
         </is>
       </c>
       <c r="O270" s="5" t="inlineStr">
@@ -23865,19 +23865,19 @@
       </c>
       <c r="P270" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové (cuisine avec îlot, planchers refaits), chambre principale avec walk-in, 2e chambre avec grand garde-robe, thermopompe, porte-patio vers cour arrière (pas de balcon), à distance de marche du métro Jarry et du marché Jean-Talon, références demandées, aucun animal, disponible 1er oct. 2026, bail 1 an. Lien Facebook (connexion requise).</t>
+          <t>Salle a manger, bureau, semi-meuble (frigo et cuisiniere inclus), locataire paie chauffage et electricite, animaux et fumeurs non acceptes, disponible 5 jours apres acceptation, secteur Mile-End/Plateau, Walk Score 100</t>
         </is>
       </c>
       <c r="Q270" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/730304009_10243338752987620_3251931066748678009_n.jpg?stp=c341.0.1367.1367a_dst-jpg_tt6&amp;cstp=mx1367x1367&amp;ctp=s565x565&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=T1M2AeYt3WkQ7kNvwEbtDR9&amp;_nc_oc=AdqdPqtbLbupPJRjBJ9G6l5MxrQhR9IhCxSGNw-xvzoSzkXhl2b7yw4yEMa1hIVXQLo&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=gi1y626B7giI3AkvJxbp7A&amp;_nc_ss=7f2a8&amp;oh=00_AQHDh36TzcRlsSalStNzCi2WPYfPNl7gzA_gMGdg3e-VhQ&amp;oe=6A8B7951</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4189D5DDDDDDDDDDB&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
@@ -23887,22 +23887,22 @@
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 (2 chambres) avec bureau, 2e étage - rue Saint-Viateur Ouest (Mile-End/Plateau)</t>
+          <t>Logement 6 1/2 à louer dans Villeray (Marketplace)</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>229, Rue Saint-Viateur Ouest, app. 3, Montréal</t>
+          <t>n/d (secteur Villeray, Montréal)</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="I271" s="5" t="inlineStr">
@@ -23922,27 +23922,27 @@
       </c>
       <c r="J271" s="5" t="inlineStr">
         <is>
-          <t>Rosemont (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K271" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M271" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N271" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/12176453</t>
+          <t>https://www.facebook.com/marketplace/item/1020450404083699</t>
         </is>
       </c>
       <c r="O271" s="5" t="inlineStr">
@@ -23952,19 +23952,19 @@
       </c>
       <c r="P271" s="6" t="inlineStr">
         <is>
-          <t>Salle a manger, bureau, semi-meuble (frigo et cuisiniere inclus), locataire paie chauffage et electricite, animaux et fumeurs non acceptes, disponible 5 jours apres acceptation, secteur Mile-End/Plateau, Walk Score 100</t>
+          <t>Annonce titre seulement (« Logement a loué 6 1/2 dans villeray »), aucune description ni adresse disponible via le scraper. Nombre de chambres estimé à 3 selon la nomenclature standard d'un 6½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q271" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA4189D5DDDDDDDDDDB&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/763805631_1503784241770162_4967544372375745805_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=101&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=jGqmb0NgpJoQ7kNvwFH3YjO&amp;_nc_oc=AdoY1EsSNcq7zLnPmamdgZYnFxscFtqiBT5k0ZKtBAzp-lkY2KX7KLoaQ55MsEJFKcc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=Jh4pE02jeamMrq9aD_orfQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHVB3CnZ5QJ3Jhj2o-a6Li1sE8vgz3c5ABW_l7p_nT4sA&amp;oe=6A790FD8</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
@@ -23974,22 +23974,22 @@
       </c>
       <c r="C272" s="6" t="inlineStr">
         <is>
-          <t>Logement 6 1/2 à louer dans Villeray (Marketplace)</t>
+          <t>2 chambres - rue De Lanaudière (Rosemont), à 6 min du métro Jean-Talon</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Villeray, Montréal)</t>
+          <t>6583, Rue De Lanaudière, Montréal</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
@@ -24009,27 +24009,27 @@
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M272" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N272" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1020450404083699</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/20257676</t>
         </is>
       </c>
       <c r="O272" s="5" t="inlineStr">
@@ -24039,12 +24039,12 @@
       </c>
       <c r="P272" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (« Logement a loué 6 1/2 dans villeray »), aucune description ni adresse disponible via le scraper. Nombre de chambres estimé à 3 selon la nomenclature standard d'un 6½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Chauffage central inclus + 5 électroménagers, quintuplex de 1932, disponible 1er sept. 2026, Walk Score 94</t>
         </is>
       </c>
       <c r="Q272" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/763805631_1503784241770162_4967544372375745805_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=101&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=jGqmb0NgpJoQ7kNvwFH3YjO&amp;_nc_oc=AdoY1EsSNcq7zLnPmamdgZYnFxscFtqiBT5k0ZKtBAzp-lkY2KX7KLoaQ55MsEJFKcc&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=Jh4pE02jeamMrq9aD_orfQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHVB3CnZ5QJ3Jhj2o-a6Li1sE8vgz3c5ABW_l7p_nT4sA&amp;oe=6A790FD8</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15EA61DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -24061,22 +24061,22 @@
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>2 chambres - rue De Lanaudière (Rosemont), à 6 min du métro Jean-Talon</t>
+          <t>2 chambres avec cour privée - rue Demers (Plateau), près du métro Laurier</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>6583, Rue De Lanaudière, Montréal</t>
+          <t>170, Rue Demers, Montréal</t>
         </is>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -24091,22 +24091,22 @@
       </c>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J273" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K273" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8-10 (estimé)</t>
         </is>
       </c>
       <c r="M273" s="5" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="N273" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/20257676</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/15892581</t>
         </is>
       </c>
       <c r="O273" s="5" t="inlineStr">
@@ -24126,19 +24126,19 @@
       </c>
       <c r="P273" s="6" t="inlineStr">
         <is>
-          <t>Chauffage central inclus + 5 électroménagers, quintuplex de 1932, disponible 1er sept. 2026, Walk Score 94</t>
+          <t>Thermopompe murale incluse, meublé, cour privée (pas de balcon), animaux non acceptés, secteur Mile End, Walk Score 99</t>
         </is>
       </c>
       <c r="Q273" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15EA61DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADFCE64DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
@@ -24148,7 +24148,7 @@
       </c>
       <c r="C274" s="6" t="inlineStr">
         <is>
-          <t>2 chambres avec cour privée - rue Demers (Plateau), près du métro Laurier</t>
+          <t>Spacieux 4½ rénové, 2 chambres - avenue Henri-Julien (Plateau), à 2 min du métro Laurier</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
@@ -24158,12 +24158,12 @@
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>170, Rue Demers, Montréal</t>
+          <t>5010, Avenue Henri-Julien, Montréal</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -24178,7 +24178,7 @@
       </c>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J274" s="5" t="inlineStr">
@@ -24193,7 +24193,7 @@
       </c>
       <c r="L274" s="5" t="inlineStr">
         <is>
-          <t>8-10 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M274" s="5" t="inlineStr">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="N274" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/15892581</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/13104221</t>
         </is>
       </c>
       <c r="O274" s="5" t="inlineStr">
@@ -24213,12 +24213,12 @@
       </c>
       <c r="P274" s="6" t="inlineStr">
         <is>
-          <t>Thermopompe murale incluse, meublé, cour privée (pas de balcon), animaux non acceptés, secteur Mile End, Walk Score 99</t>
+          <t>Cuisine et salle de bain rénovées, hauts plafonds, immeuble de 1910, chats acceptés, disponible 7 jours après acceptation, Walk Score 99</t>
         </is>
       </c>
       <c r="Q274" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADFCE64DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA41C20BDDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>Spacieux 4½ rénové, 2 chambres - avenue Henri-Julien (Plateau), à 2 min du métro Laurier</t>
+          <t>4½ avec cour arrière privée - rue Rivard (Plateau), à quelques pas du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
@@ -24245,7 +24245,7 @@
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>5010, Avenue Henri-Julien, Montréal</t>
+          <t>4452, Rue Rivard, Montréal</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
@@ -24265,12 +24265,12 @@
       </c>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J275" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K275" s="5" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="M275" s="5" t="inlineStr">
@@ -24290,7 +24290,7 @@
       </c>
       <c r="N275" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/13104221</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/14560801</t>
         </is>
       </c>
       <c r="O275" s="5" t="inlineStr">
@@ -24300,19 +24300,19 @@
       </c>
       <c r="P275" s="6" t="inlineStr">
         <is>
-          <t>Cuisine et salle de bain rénovées, hauts plafonds, immeuble de 1910, chats acceptés, disponible 7 jours après acceptation, Walk Score 99</t>
+          <t>Cour arrière privée, lumineux et bien entretenu, Walk Score 100, animaux acceptés sous conditions, disponible 1er août 2026</t>
         </is>
       </c>
       <c r="Q275" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA41C20BDDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA44883FDDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
@@ -24322,22 +24322,22 @@
       </c>
       <c r="C276" s="6" t="inlineStr">
         <is>
-          <t>4½ avec cour arrière privée - rue Rivard (Plateau), à quelques pas du métro Mont-Royal</t>
+          <t>Grand 6 1/2, 2 chambres - rue Jean-Talon Est (Rosemont, près marché Jean-Talon)</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>4452, Rue Rivard, Montréal</t>
+          <t>274, Rue Jean-Talon Est, app. 302, Montréal</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -24352,22 +24352,22 @@
       </c>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J276" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K276" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L276" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M276" s="5" t="inlineStr">
@@ -24377,7 +24377,7 @@
       </c>
       <c r="N276" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/14560801</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/14545078</t>
         </is>
       </c>
       <c r="O276" s="5" t="inlineStr">
@@ -24387,19 +24387,19 @@
       </c>
       <c r="P276" s="6" t="inlineStr">
         <is>
-          <t>Cour arrière privée, lumineux et bien entretenu, Walk Score 100, animaux acceptés sous conditions, disponible 1er août 2026</t>
+          <t>6 pièces au total, concept ouvert, comptoirs de quartz, walk score 100, dispo 1er juillet 2026, près du marché Jean-Talon, superficie non précisée</t>
         </is>
       </c>
       <c r="Q276" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA44883FDDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE4013DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
@@ -24409,7 +24409,7 @@
       </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2, 2 chambres - rue Jean-Talon Est (Rosemont, près marché Jean-Talon)</t>
+          <t>Cession de bail 7½, Rosemont-La Petite-Patrie (Marketplace)</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
@@ -24419,12 +24419,12 @@
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>274, Rue Jean-Talon Est, app. 302, Montréal</t>
+          <t>n/d (Montréal, QC H2G 1T5)</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -24434,7 +24434,7 @@
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I277" s="5" t="inlineStr">
@@ -24444,27 +24444,27 @@
       </c>
       <c r="J277" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K277" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M277" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N277" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/14545078</t>
+          <t>https://www.facebook.com/marketplace/item/1375157431101110</t>
         </is>
       </c>
       <c r="O277" s="5" t="inlineStr">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="P277" s="6" t="inlineStr">
         <is>
-          <t>6 pièces au total, concept ouvert, comptoirs de quartz, walk score 100, dispo 1er juillet 2026, près du marché Jean-Talon, superficie non précisée</t>
+          <t>Cession de bail. Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q277" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE4013DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702670571_1710902896599779_1133264177050399379_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=akFqSvK3rfAQ7kNvwG-Cqey&amp;_nc_oc=Adrp5N9Rg13Pf-obfNZqB1ZqwyOcgjJji8vk0ggvRJiA9uCo-xDJXuQAit6O7YIGPW0&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQBG56r36JKH2gkm4Baddcm0ylaFria-4p9Il0vYABnyMg&amp;oe=6A607060</t>
         </is>
       </c>
     </row>
@@ -24496,22 +24496,22 @@
       </c>
       <c r="C278" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail 7½, Rosemont-La Petite-Patrie (Marketplace)</t>
+          <t>Condo 2 chambres semi-meublé, stationnement intérieur - rue Villeray, à 9 min du métro Fabre</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 1T5)</t>
+          <t>1414 Rue Villeray, app. 105, Montréal</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -24521,59 +24521,59 @@
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I278" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J278" s="5" t="inlineStr">
+        <is>
+          <t>Fabre</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="inlineStr">
+        <is>
+          <t>bleue</t>
+        </is>
+      </c>
+      <c r="L278" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M278" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N278" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/25583093</t>
+        </is>
+      </c>
+      <c r="O278" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I278" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J278" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K278" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L278" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M278" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N278" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1375157431101110</t>
-        </is>
-      </c>
-      <c r="O278" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="P278" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail. Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
+          <t>Immeuble de 2011 (30 unités), RDC, plancher chauffant salle de bain, stationnement intérieur avec borne de recharge, casier de rangement, buanderie commune, terrasse sur le toit, Walk Score 94, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q278" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702670571_1710902896599779_1133264177050399379_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=akFqSvK3rfAQ7kNvwG-Cqey&amp;_nc_oc=Adrp5N9Rg13Pf-obfNZqB1ZqwyOcgjJji8vk0ggvRJiA9uCo-xDJXuQAit6O7YIGPW0&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQBG56r36JKH2gkm4Baddcm0ylaFria-4p9Il0vYABnyMg&amp;oe=6A607060</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD77D67DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -24583,22 +24583,22 @@
       </c>
       <c r="C279" s="6" t="inlineStr">
         <is>
-          <t>Condo 2 chambres semi-meublé, stationnement intérieur - rue Villeray, à 9 min du métro Fabre</t>
+          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>1414 Rue Villeray, app. 105, Montréal</t>
+          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
         </is>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -24618,17 +24618,17 @@
       </c>
       <c r="J279" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K279" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M279" s="5" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="N279" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/25583093</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
         </is>
       </c>
       <c r="O279" s="5" t="inlineStr">
@@ -24648,12 +24648,12 @@
       </c>
       <c r="P279" s="6" t="inlineStr">
         <is>
-          <t>Immeuble de 2011 (30 unités), RDC, plancher chauffant salle de bain, stationnement intérieur avec borne de recharge, casier de rangement, buanderie commune, terrasse sur le toit, Walk Score 94, dispo 1er juillet 2026</t>
+          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
         </is>
       </c>
       <c r="Q279" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD77D67DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -24670,22 +24670,22 @@
       </c>
       <c r="C280" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
+          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
+          <t>6391 Avenue Henri-Julien, Montréal</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -24705,17 +24705,17 @@
       </c>
       <c r="J280" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jean-Talon (à vérifier)</t>
         </is>
       </c>
       <c r="K280" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L280" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M280" s="5" t="inlineStr">
@@ -24725,7 +24725,7 @@
       </c>
       <c r="N280" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
         </is>
       </c>
       <c r="O280" s="5" t="inlineStr">
@@ -24735,19 +24735,19 @@
       </c>
       <c r="P280" s="6" t="inlineStr">
         <is>
-          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
+          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
         </is>
       </c>
       <c r="Q280" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
@@ -24757,22 +24757,22 @@
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
-          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
+          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>6391 Avenue Henri-Julien, Montréal</t>
+          <t>Rue Beaubien (Montréal, QC)</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -24792,27 +24792,27 @@
       </c>
       <c r="J281" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon (à vérifier)</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K281" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M281" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N281" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
+          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
         </is>
       </c>
       <c r="O281" s="5" t="inlineStr">
@@ -24822,19 +24822,19 @@
       </c>
       <c r="P281" s="6" t="inlineStr">
         <is>
-          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
+          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q281" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -24844,22 +24844,22 @@
       </c>
       <c r="C282" s="6" t="inlineStr">
         <is>
-          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
+          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>Rue Beaubien (Montréal, QC)</t>
+          <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -24869,7 +24869,7 @@
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I282" s="5" t="inlineStr">
@@ -24879,27 +24879,27 @@
       </c>
       <c r="J282" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K282" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L282" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M282" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N282" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
       <c r="O282" s="5" t="inlineStr">
@@ -24909,19 +24909,19 @@
       </c>
       <c r="P282" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
       <c r="Q282" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -24931,22 +24931,22 @@
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
+          <t>5½ au Plateau-Mont-Royal (Marketplace)</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>1889 Rue des Carrières, Montréal</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="H283" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I283" s="5" t="inlineStr">
@@ -24981,34 +24981,34 @@
       </c>
       <c r="M283" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N283" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
+          <t>https://www.facebook.com/marketplace/item/2124372061520309</t>
         </is>
       </c>
       <c r="O283" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P283" s="6" t="inlineStr">
         <is>
-          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
+          <t>Annonce titre seulement, description non disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q283" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/790150151_2283077578925626_1749367086388284890_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=ijxRbFhYaKgQ7kNvwENuJLs&amp;_nc_oc=AdqRCM7MaQD28AUVRdjZcBzo8BdTIquAZ9ZXEJ_CuW49MLQJ8m_tT8IYK6EBtN-I4h8&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=21kqsDFTPPlqY_va03ORdw&amp;_nc_ss=7f2a8&amp;oh=00_AQLzxnd4o8SoM-y6_91RzKmvUUM3My8GuhXTwpSztagGmg&amp;oe=6A9C7E28</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C284" s="6" t="inlineStr">
         <is>
-          <t>5½ au Plateau-Mont-Royal (Marketplace)</t>
+          <t>5½ meublé, Plateau-Mont-Royal (Marketplace), disponible 10 juin, bail minimum 1 an</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -25043,59 +25043,59 @@
       </c>
       <c r="H284" s="5" t="inlineStr">
         <is>
+          <t>2 (estimé)</t>
+        </is>
+      </c>
+      <c r="I284" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J284" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L284" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M284" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N284" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2129210164276639</t>
+        </is>
+      </c>
+      <c r="O284" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I284" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J284" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K284" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L284" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M284" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N284" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/2124372061520309</t>
-        </is>
-      </c>
-      <c r="O284" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="P284" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Annonce titre seulement (meublé, deux prix affichés selon la durée du bail : 2100$ et 2500$), aucune adresse ni description détaillée disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q284" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/790150151_2283077578925626_1749367086388284890_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=ijxRbFhYaKgQ7kNvwENuJLs&amp;_nc_oc=AdqRCM7MaQD28AUVRdjZcBzo8BdTIquAZ9ZXEJ_CuW49MLQJ8m_tT8IYK6EBtN-I4h8&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=21kqsDFTPPlqY_va03ORdw&amp;_nc_ss=7f2a8&amp;oh=00_AQLzxnd4o8SoM-y6_91RzKmvUUM3My8GuhXTwpSztagGmg&amp;oe=6A9C7E28</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/598654016_1589371882248064_7696909030407170199_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=N7m7nUpE6yMQ7kNvwEavU5f&amp;_nc_oc=AdoffqWsvOkDQufR2l4pvvs8I99wUIXqF-oRgpMOgZIXjIPtOiBQxSSfc9hbuhLkhtM&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=XHazkfFuptT2M_pPSTeS4Q&amp;_nc_ss=7f2a8&amp;oh=00_AQFmBd7yIIHbAZt0cYChuyEoJmxi7lgNayPM_0n-aenWnQ&amp;oe=6A9664A6</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
@@ -25105,22 +25105,22 @@
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé, Plateau-Mont-Royal (Marketplace), disponible 10 juin, bail minimum 1 an</t>
+          <t>5 1/2 in Hochelaga (Marketplace)</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>n/d (secteur Hochelaga-Maisonneuve, Montréal)</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="N285" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2129210164276639</t>
+          <t>https://www.facebook.com/marketplace/item/2583777198803688</t>
         </is>
       </c>
       <c r="O285" s="5" t="inlineStr">
@@ -25170,19 +25170,19 @@
       </c>
       <c r="P285" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (meublé, deux prix affichés selon la durée du bail : 2100$ et 2500$), aucune adresse ni description détaillée disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Annonce titre seulement (« 5 1/2 in Hochelaga »), aucune description ni adresse disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
         </is>
       </c>
       <c r="Q285" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/598654016_1589371882248064_7696909030407170199_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=N7m7nUpE6yMQ7kNvwEavU5f&amp;_nc_oc=AdoffqWsvOkDQufR2l4pvvs8I99wUIXqF-oRgpMOgZIXjIPtOiBQxSSfc9hbuhLkhtM&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=XHazkfFuptT2M_pPSTeS4Q&amp;_nc_ss=7f2a8&amp;oh=00_AQFmBd7yIIHbAZt0cYChuyEoJmxi7lgNayPM_0n-aenWnQ&amp;oe=6A9664A6</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/764987455_1048157270911968_5209086800819479873_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=8fuDHfd2FxAQ7kNvwGWBzmX&amp;_nc_oc=AdrF-5lGt6Z8Q_hcNZtBCxKNzLwKQK14kM3UBQyfvjLyXZs14CcB6FEbpaYw4bSMoBQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=CInYmIZz43q5AWNfaqlZcQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHVVF-2wulz0t4MIMCVRVAytHTtSomrEGuVuullI6JrYA&amp;oe=6A790A2B</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -25192,22 +25192,22 @@
       </c>
       <c r="C286" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 in Hochelaga (Marketplace)</t>
+          <t>Appartement 5 1/2, Plateau-Mont-Royal (Marketplace)</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Hochelaga-Maisonneuve, Montréal)</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="H286" s="5" t="inlineStr">
         <is>
-          <t>2 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I286" s="5" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="N286" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2583777198803688</t>
+          <t>https://www.facebook.com/marketplace/item/1552904606229687</t>
         </is>
       </c>
       <c r="O286" s="5" t="inlineStr">
@@ -25257,19 +25257,19 @@
       </c>
       <c r="P286" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (« 5 1/2 in Hochelaga »), aucune description ni adresse disponible via le scraper. Nombre de chambres estimé à 2 selon la nomenclature standard d'un 5½, à confirmer. Lien Facebook (connexion requise) pour plus de détails.</t>
+          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
         </is>
       </c>
       <c r="Q286" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/764987455_1048157270911968_5209086800819479873_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=8fuDHfd2FxAQ7kNvwGWBzmX&amp;_nc_oc=AdrF-5lGt6Z8Q_hcNZtBCxKNzLwKQK14kM3UBQyfvjLyXZs14CcB6FEbpaYw4bSMoBQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=CInYmIZz43q5AWNfaqlZcQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHVVF-2wulz0t4MIMCVRVAytHTtSomrEGuVuullI6JrYA&amp;oe=6A790A2B</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/720906013_1532570941905242_5666371068595538123_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YEDvMBzBavUQ7kNvwEkVbXh&amp;_nc_oc=AdqtpC8qtzZHEdxPx9e94VcYtRcN6s4rYqZkBbexWTpuWv5UghDk5D0a0ySf9p9btAk&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=TJJlLcUljG48fNVcDPZJaA&amp;_nc_ss=7f2a8&amp;oh=00_AQBrJbOYbvchb0Tq-5jSsFppBFkZ2xgQOdjHrsx0FadLHQ&amp;oe=6A632614</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -25279,22 +25279,22 @@
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>Appartement 5 1/2, Plateau-Mont-Royal (Marketplace)</t>
+          <t>Beau 5½ à Nouveau Rosemont (Marketplace)</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>n/d (secteur Nouveau-Rosemont, Montréal)</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -25334,7 +25334,7 @@
       </c>
       <c r="N287" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1552904606229687</t>
+          <t>https://www.facebook.com/marketplace/item/771126382598215</t>
         </is>
       </c>
       <c r="O287" s="5" t="inlineStr">
@@ -25344,19 +25344,19 @@
       </c>
       <c r="P287" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
+          <t>Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q287" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/720906013_1532570941905242_5666371068595538123_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YEDvMBzBavUQ7kNvwEkVbXh&amp;_nc_oc=AdqtpC8qtzZHEdxPx9e94VcYtRcN6s4rYqZkBbexWTpuWv5UghDk5D0a0ySf9p9btAk&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=TJJlLcUljG48fNVcDPZJaA&amp;_nc_ss=7f2a8&amp;oh=00_AQBrJbOYbvchb0Tq-5jSsFppBFkZ2xgQOdjHrsx0FadLHQ&amp;oe=6A632614</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/674573089_942123441857660_1258864760862245194_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=-PqFDWdPNa8Q7kNvwG9FoYC&amp;_nc_oc=Adqy82S_lfHjbp4dkLyXqO9W2nrNBD-zKhYTIwlodmCwj46lhM9QhEG2rupuBRJOPVI&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQDV5R2cb2f6avoKzX1khDbQ_SvUKiySFkJsux9T10Rmdg&amp;oe=6A6059BA</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="C288" s="6" t="inlineStr">
         <is>
-          <t>Beau 5½ à Nouveau Rosemont (Marketplace)</t>
+          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -25376,12 +25376,12 @@
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Nouveau-Rosemont, Montréal)</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -25421,7 +25421,7 @@
       </c>
       <c r="N288" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/771126382598215</t>
+          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
         </is>
       </c>
       <c r="O288" s="5" t="inlineStr">
@@ -25431,12 +25431,12 @@
       </c>
       <c r="P288" s="6" t="inlineStr">
         <is>
-          <t>Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
+          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
         </is>
       </c>
       <c r="Q288" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/674573089_942123441857660_1258864760862245194_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=-PqFDWdPNa8Q7kNvwG9FoYC&amp;_nc_oc=Adqy82S_lfHjbp4dkLyXqO9W2nrNBD-zKhYTIwlodmCwj46lhM9QhEG2rupuBRJOPVI&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQDV5R2cb2f6avoKzX1khDbQ_SvUKiySFkJsux9T10Rmdg&amp;oe=6A6059BA</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
         </is>
       </c>
     </row>
@@ -25453,7 +25453,7 @@
       </c>
       <c r="C289" s="6" t="inlineStr">
         <is>
-          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
+          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
@@ -25488,12 +25488,12 @@
       </c>
       <c r="J289" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Pie-IX (mentionné dans le titre)</t>
         </is>
       </c>
       <c r="K289" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L289" s="5" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="N289" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
+          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
         </is>
       </c>
       <c r="O289" s="5" t="inlineStr">
@@ -25518,12 +25518,12 @@
       </c>
       <c r="P289" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
+          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q289" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
         </is>
       </c>
     </row>
@@ -25540,22 +25540,22 @@
       </c>
       <c r="C290" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
+          <t>Location 4 et demi Plateau, pet friendly</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -25575,12 +25575,12 @@
       </c>
       <c r="J290" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX (mentionné dans le titre)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K290" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L290" s="5" t="inlineStr">
@@ -25595,7 +25595,7 @@
       </c>
       <c r="N290" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
+          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
         </is>
       </c>
       <c r="O290" s="5" t="inlineStr">
@@ -25605,12 +25605,12 @@
       </c>
       <c r="P290" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
+          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q290" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
         </is>
       </c>
     </row>
@@ -25627,12 +25627,12 @@
       </c>
       <c r="C291" s="6" t="inlineStr">
         <is>
-          <t>Location 4 et demi Plateau, pet friendly</t>
+          <t>5 1/2 Rosemont avec cour privée</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
@@ -25642,7 +25642,7 @@
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="N291" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
+          <t>https://www.facebook.com/marketplace/item/1493110625829174</t>
         </is>
       </c>
       <c r="O291" s="5" t="inlineStr">
@@ -25692,104 +25692,17 @@
       </c>
       <c r="P291" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
+          <t>Annonce titre seulement, description non disponible via le scraper ; cour privée mentionnée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q291" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B292" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C292" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 Rosemont avec cour privée</t>
-        </is>
-      </c>
-      <c r="D292" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E292" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC)</t>
-        </is>
-      </c>
-      <c r="F292" s="5" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="G292" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H292" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I292" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J292" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K292" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L292" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M292" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N292" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1493110625829174</t>
-        </is>
-      </c>
-      <c r="O292" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P292" s="6" t="inlineStr">
-        <is>
-          <t>Annonce titre seulement, description non disponible via le scraper ; cour privée mentionnée. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q292" s="5" t="inlineStr">
-        <is>
           <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730530074_1035539099460685_3801485303896565628_n.jpg?stp=c313.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=_9b7saLCWEUQ7kNvwHrw_2v&amp;_nc_oc=AdoqEj5UFxI4lgfrZP0kbf8mdi_MJO6fIO-zv3fvQ5DsX656NtR6Rf8AiVxw-oho-l4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQDqhmwAH6WdMqAuOtshO7wqRdBG7RkedN25_yaUpz5ikg&amp;oe=6A5EB662</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q292"/>
+  <autoFilter ref="A1:Q291"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -26081,7 +25994,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N289" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N290" r:id="rId289"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N291" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N292" r:id="rId291"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -576,27 +576,27 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1000 pi², 2 balcons, à moins de 5 min du métro Jean-Talon - face au marché Jean-Talon</t>
+          <t>Grand 5½ (3 chambres), 1700 pi², balcon, garage inclus - avenue Laurier Est (Plateau), cession de bail</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>192 Rue Jean-Talon E., Montréal</t>
+          <t>Avenue Laurier Est, Montréal, QC H2L 3M7</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -611,45 +611,49 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12 (estimé, à vérifier)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Logis Québec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l362224</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/location-appartement-5-1-2-1700pi2-garage-inclus-plateau/1743833147</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Complètement rénové, A/C mural, lave-vaisselle inclus, stationnement (permis et parcomètre) inclus, chauffage/eau chaude/électricité non inclus, animaux non admis, disponible octobre 2026, immeuble semi-commercial de 5 logements, Petite-Italie.</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+          <t>Cession de bail, libre 1er déc.; chauffage au gaz; garage, lave-vaisselle, laveuse-sécheuse; distance au métro à vérifier (Laurier ou Papineau)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/88/88e3586c-3218-4aa4-b913-57f910f11d5e?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -659,164 +663,164 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>5½ (3 chambres), balcon, à 4 min du métro Joliette - Hochelaga-Maisonneuve</t>
+          <t>5½ (3 chambres), balcon - avenue des Érables (Plateau-Mont-Royal), près du métro Laurier</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>4849, Avenue des Érables, Montréal, QC H2H 2E3</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Laurier</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>12 (estimé)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-a-louer-au-plateau-montreal/1743820976</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Libre 28 sept.; électricité à la charge du locataire; frigo/électros non fournis; superficie annoncée illisible (11 100 pi²) donc n/d</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/6c/6c156b9e-812a-436a-8591-69983f02c2cf?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>3 chambres tout inclus (meublé), grande terrasse, chauffage/wifi/gaz inclus - Hochelaga-Maisonneuve, à 2 min du métro Joliette</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
           <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H1W 1G6)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Promenade Ontario, Montréal, QC H1W 1R9</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Joliette</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-5-1-2-a-4-minutes-du-metro-joliette/1743857169</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>3e étage, grande pièce commune ouverte et lumineuse, laveuse-sécheuse incluse, animaux acceptés, disponible 1er nov. 2026, bail 1 an. Superficie non précisée.</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/df/df00680a-ce8f-4364-8e45-a7ee1cb23499?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>4½ (2 chambres), 980 pi², terrasse/cour - Plateau, à quelques pas du métro Laurier</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H2J 2T4)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>980</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Laurier</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5 (estimé)</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-a-louer-dans-le-plateau-a-quelques-pas-du-metro-laurier/1743478226</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Rez-de-chaussée, meublé, accès cour arrière avec terrasse, 5 électroménagers inclus (lave-vaisselle, laveuse-sécheuse), chats permis, non-fumeur, disponible 1er oct. 2026, bail 1 an, références exigées.</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/6e/6ed2e853-548e-4e65-bd61-886cfbe5dd9f?rule=kijijica-960-jpg</t>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-chambres-tout-inclus-metro-joliette-grande-terrasse/1743152669</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>Meublé, entièrement équipé (literie, vaisselle), 2 salles de bain (1 en suite), terrasse arrière 20x11 pi, foyer au gaz naturel, laveuse-sécheuse, climatisation, tout inclus (chauffage au gaz, wifi), animaux limités, disponible 8 sept. 2026, bail 1 an, caution 1 mois, aucune garderie/entreprise/Airbnb permise, stationnement non inclus (propriétaire occupant).</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/8a/8afd6234-0152-42ae-b101-221bb3a5c8e0?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -833,17 +837,17 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>3 chambres tout inclus (meublé), grande terrasse, chauffage/wifi/gaz inclus - Hochelaga-Maisonneuve, à 2 min du métro Joliette</t>
+          <t>7½ rénové (3 chambres fermées), 1250 pi², balcon - Plateau/Petite-Italie, à 3 min du métro Beaubien</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Promenade Ontario, Montréal, QC H1W 1R9</t>
+          <t>6386 Rue Saint-Denis, Montréal, QC</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -853,7 +857,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -868,7 +872,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -878,7 +882,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -888,7 +892,7 @@
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-chambres-tout-inclus-metro-joliette-grande-terrasse/1743152669</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/71-2-3-chambres-a-coucher-au-metro-beaubien/1743449291</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
@@ -898,12 +902,12 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>Meublé, entièrement équipé (literie, vaisselle), 2 salles de bain (1 en suite), terrasse arrière 20x11 pi, foyer au gaz naturel, laveuse-sécheuse, climatisation, tout inclus (chauffage au gaz, wifi), animaux limités, disponible 8 sept. 2026, bail 1 an, caution 1 mois, aucune garderie/entreprise/Airbnb permise, stationnement non inclus (propriétaire occupant).</t>
+          <t>2e étage d'un 7½, 1,5 salle de bain, cuisine/salon/1 chambre orientés sud, laveuse-sécheuse à l'unité, électroménagers en option (four, frigo, lave-vaisselle), non-fumeur, animaux non admis, disponible 1er oct. 2026 (ou avant sur entente), visites sur rendez-vous, à la jonction Mile End/Petite-Italie/Marché Jean-Talon/Plateau, piste cyclable REV devant l'immeuble. Prix à la limite du budget (2400$).</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/8a/8afd6234-0152-42ae-b101-221bb3a5c8e0?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5f/5f745d2f-85f0-4942-aa0d-33017f3ef21b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -920,7 +924,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>7½ rénové (3 chambres fermées), 1250 pi², balcon - Plateau/Petite-Italie, à 3 min du métro Beaubien</t>
+          <t>5½ rénové (3 chambres fermées), 1250 pi², balcon, chauffé et eau chaude inclus - Plateau (secteur Saint-Louis), face au parc Jeanne-Mance</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -930,12 +934,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>6386 Rue Saint-Denis, Montréal, QC</t>
+          <t>n/d (Montréal, QC H2W 2N4)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -955,7 +959,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -975,7 +979,7 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/71-2-3-chambres-a-coucher-au-metro-beaubien/1743449291</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-emplacement-parfait/1736891738</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
@@ -985,12 +989,12 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>2e étage d'un 7½, 1,5 salle de bain, cuisine/salon/1 chambre orientés sud, laveuse-sécheuse à l'unité, électroménagers en option (four, frigo, lave-vaisselle), non-fumeur, animaux non admis, disponible 1er oct. 2026 (ou avant sur entente), visites sur rendez-vous, à la jonction Mile End/Petite-Italie/Marché Jean-Talon/Plateau, piste cyclable REV devant l'immeuble. Prix à la limite du budget (2400$).</t>
+          <t>Prix promotionnel 1re année (2245$/mois), prix régulier 2645$/mois par la suite - à vérifier au renouvellement. Duplex/triplex, entrée privée, face au parc Jeanne-Mance et vue sur le Mont-Royal, laveuse-sécheuse et lave-vaisselle inclus, frigo/congélateur inclus, chauffage et eau chaude inclus, animaux acceptés, fumeur extérieur seulement, disponible 1er oct. 2026, bail 1 an. Walk Score 10, Transit Score 10. Station non précisée par l'annonce, Sherbrooke (ligne verte) estimée à ~12 min.</t>
         </is>
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5f/5f745d2f-85f0-4942-aa0d-33017f3ef21b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/58/58ff440f-a1b5-47e0-ad60-2ce9c09ef345?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1011,32 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres fermées), 1250 pi², balcon, chauffé et eau chaude inclus - Plateau (secteur Saint-Louis), face au parc Jeanne-Mance</t>
+          <t>Grand 6½ rénové (4 chambres fermées), 1200 pi², balcon et grande cour - Hochelaga-Maisonneuve, à 6 min du métro Joliette</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2W 2N4)</t>
+          <t>n/d (Montréal, QC H1W 1C7)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1042,7 +1046,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1052,7 +1056,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
@@ -1062,7 +1066,7 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-emplacement-parfait/1736891738</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-renove-4-chambres-homa/1743249113</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
@@ -1072,19 +1076,19 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>Prix promotionnel 1re année (2245$/mois), prix régulier 2645$/mois par la suite - à vérifier au renouvellement. Duplex/triplex, entrée privée, face au parc Jeanne-Mance et vue sur le Mont-Royal, laveuse-sécheuse et lave-vaisselle inclus, frigo/congélateur inclus, chauffage et eau chaude inclus, animaux acceptés, fumeur extérieur seulement, disponible 1er oct. 2026, bail 1 an. Walk Score 10, Transit Score 10. Station non précisée par l'annonce, Sherbrooke (ligne verte) estimée à ~12 min.</t>
+          <t>Entièrement rénové, cuisine et salon séparés, laveuse-sécheuse (branchements), frigo/congélateur inclus, grande cour arrière, stationnement disponible, animaux acceptés, hydro non inclus, non-fumeur (extérieur permis), disponible 9 sept. 2026, bail 1 an.</t>
         </is>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/58/58ff440f-a1b5-47e0-ad60-2ce9c09ef345?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/95/957701f8-3728-48b2-8c06-e6ce352b8efb?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1094,32 +1098,32 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Grand 6½ rénové (4 chambres fermées), 1200 pi², balcon et grande cour - Hochelaga-Maisonneuve, à 6 min du métro Joliette</t>
+          <t>5½ sur deux étages, 3 chambres, 2 balcons - rue Napoléon (Plateau), à ~8-9 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 1C7)</t>
+          <t>106, Rue Napoléon, Montréal</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1129,7 +1133,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1139,17 +1143,17 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8-9 (estimé)</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>logisquebec</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-renove-4-chambres-homa/1743249113</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l358813</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
@@ -1159,19 +1163,15 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, cuisine et salon séparés, laveuse-sécheuse (branchements), frigo/congélateur inclus, grande cour arrière, stationnement disponible, animaux acceptés, hydro non inclus, non-fumeur (extérieur permis), disponible 9 sept. 2026, bail 1 an.</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/95/957701f8-3728-48b2-8c06-e6ce352b8efb?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ sur deux étages, 2 balcons, secteur Plateau proche métro Sherbrooke (ligne verte, ~676 m).</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>5½ sur deux étages, 3 chambres, 2 balcons - rue Napoléon (Plateau), à ~8-9 min du métro Sherbrooke</t>
+          <t>5½ rénové (3 chambres), 1100 pi², grand balcon arrière privé - rue La Fontaine (Hochelaga), à 5 min du métro Pie-IX</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>106, Rue Napoléon, Montréal</t>
+          <t>4602, Rue La Fontaine, Montréal, QC</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>8-9 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>logisquebec</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l358813</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22900247</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
@@ -1246,10 +1246,14 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>5½ sur deux étages, 2 balcons, secteur Plateau proche métro Sherbrooke (ligne verte, ~676 m).</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr"/>
+          <t>Entièrement rénové, thermopompe, cuisine et salle de bain refaites, 1 mois gratuit en promotion, animaux à discuter, disponible immédiatement, Walk Score 94.</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F87A3DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1264,22 +1268,22 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1100 pi², grand balcon arrière privé - rue La Fontaine (Hochelaga), à 5 min du métro Pie-IX</t>
+          <t>5½ rénové (3 chambres), 1100 pi², balcon - rue de Bullion (Plateau), à 11 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>4602, Rue La Fontaine, Montréal, QC</t>
+          <t>3984, Rue de Bullion, Montréal, QC H2W 2E4</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1299,7 +1303,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1309,17 +1313,17 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22900247</t>
+          <t>https://www.zumper.com/address/3984-rue-de-bullion-montreal-qc-h2w-2e4-can</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -1329,19 +1333,19 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, thermopompe, cuisine et salle de bain refaites, 1 mois gratuit en promotion, animaux à discuter, disponible immédiatement, Walk Score 94.</t>
+          <t>Plafonds de 9,5 pieds, plancher de bois franc récemment repeint, laveuse-sécheuse et électroménagers inclus, animaux acceptés, électricité/chauffage/eau non inclus, bail 1 an, à 3 rues du boul. Saint-Laurent.</t>
         </is>
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F87A3DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://img.zumpercdn.com/895146226/1280x960?dpr=1&amp;fit=crop&amp;h=542&amp;q=76&amp;w=991</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1351,27 +1355,27 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1100 pi², balcon - rue de Bullion (Plateau), à 11 min du métro Sherbrooke</t>
+          <t>5½ rénové, 3 chambres, près métro Pie-IX (Rosemont)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>3984, Rue de Bullion, Montréal, QC H2W 2E4</t>
+          <t>4419, Avenue Charlemagne, Montréal</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1386,7 +1390,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1396,17 +1400,17 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/address/3984-rue-de-bullion-montreal-qc-h2w-2e4-can</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l355773</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -1416,19 +1420,15 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Plafonds de 9,5 pieds, plancher de bois franc récemment repeint, laveuse-sécheuse et électroménagers inclus, animaux acceptés, électricité/chauffage/eau non inclus, bail 1 an, à 3 rues du boul. Saint-Laurent.</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>https://img.zumpercdn.com/895146226/1280x960?dpr=1&amp;fit=crop&amp;h=542&amp;q=76&amp;w=991</t>
-        </is>
-      </c>
+          <t>Récemment rénové, non meublé, proche du Parc Maisonneuve et du Jardin botanique, disponible 1er juillet 2026.</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1438,27 +1438,27 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 3 chambres, près métro Pie-IX (Rosemont)</t>
+          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>4419, Avenue Charlemagne, Montréal</t>
+          <t>Près du parc Lalancette (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1483,35 +1483,39 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>LogisQuébec</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l355773</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Récemment rénové, non meublé, proche du Parc Maisonneuve et du Jardin botanique, disponible 1er juillet 2026.</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr"/>
+          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1521,27 +1525,27 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
+          <t>5½ (3 chambres fermées), 920 pi², balcon - secteur Ateliers Angus (Rosemont), à 10 min du métro Préfontaine</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Près du parc Lalancette (adresse exacte n/d)</t>
+          <t>n/d (secteur Ateliers Angus, Montréal, QC H1X 2H3)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1556,7 +1560,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1566,39 +1570,39 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-a-louer-3-chambres-shop-angus-montreal/1743567611</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
+          <t>Plancher bois sur dalle béton avec isolation phonique, climatisation, locker disponible, animaux limités, libre 4 octobre, quartier vivant proche commerces et parcs.</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c2/c2ddd2a9-e29a-4342-bd11-8edefeef5b45?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1608,27 +1612,27 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres fermées), 920 pi², balcon - secteur Ateliers Angus (Rosemont), à 10 min du métro Préfontaine</t>
+          <t>5½ rénové (3 chambres fermées), 1000 pi², balcon - Plateau (Saint-Dominique), à ~5 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Ateliers Angus, Montréal, QC H1X 2H3)</t>
+          <t>3477 Rue Saint-Dominique, Montréal, QC H2X 2X5</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1643,7 +1647,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1653,7 +1657,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
@@ -1663,7 +1667,7 @@
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-a-louer-3-chambres-shop-angus-montreal/1743567611</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1743638566</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -1673,12 +1677,12 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Plancher bois sur dalle béton avec isolation phonique, climatisation, locker disponible, animaux limités, libre 4 octobre, quartier vivant proche commerces et parcs.</t>
+          <t>Disponible 1er juillet 2026, laveuse-sécheuse à l'unité, frigo et four inclus, climatisation, eau incluse, animaux limités (conditions), fumeur extérieur seulement, bail 1 an, en plein cœur du Plateau près commerces/restos/parcs. Walk Score/Transit Score élevés.</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c2/c2ddd2a9-e29a-4342-bd11-8edefeef5b45?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/df/df2e37ba-37c2-4005-aeda-298880ae36fb?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1695,32 +1699,32 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres fermées), 1000 pi², balcon - Plateau (Saint-Dominique), à ~5 min du métro Sherbrooke</t>
+          <t>Grand 6½ rénové (4 chambres fermées), 1500 pi², 2 étages, terrasse - Villeray, à 5 min du métro Fabre</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>3477 Rue Saint-Dominique, Montréal, QC H2X 2X5</t>
+          <t>7403 Rue de Bordeaux, Montréal, QC H2E 2M6</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1730,17 +1734,17 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1750,7 +1754,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1743638566</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-4-chambres-2-etages-stationnement-inclus/1743520116</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -1760,12 +1764,12 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Disponible 1er juillet 2026, laveuse-sécheuse à l'unité, frigo et four inclus, climatisation, eau incluse, animaux limités (conditions), fumeur extérieur seulement, bail 1 an, en plein cœur du Plateau près commerces/restos/parcs. Walk Score/Transit Score élevés.</t>
+          <t>Logement sur 2 étages, grandes pièces lumineuses, buanderie incluse, accès patio extérieur, stationnement intérieur en option (+100$/mois, sinon 2050$ sans parking), non chauffé/non éclairé, animaux acceptés, vérification de crédit requise, bail 1 an, disponible immédiatement (mention aussi du 15 sept. 2026). Note : métro Fabre est sur la ligne bleue, pas la ligne verte.</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/df/df2e37ba-37c2-4005-aeda-298880ae36fb?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/85/85133349-63d7-4d10-a907-3ad77380a0e8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1782,32 +1786,32 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Grand 6½ rénové (4 chambres fermées), 1500 pi², 2 étages, terrasse - Villeray, à 5 min du métro Fabre</t>
+          <t>5½ semi-meublé rénové (3 chambres), 950 pi², balcon - Rosemont, près Promenade Masson</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>7403 Rue de Bordeaux, Montréal, QC H2E 2M6</t>
+          <t>n/d (Montréal, QC H1Y 1S9)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1817,17 +1821,17 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
@@ -1837,7 +1841,7 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-4-chambres-2-etages-stationnement-inclus/1743520116</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rosemont-5-1-2-appartement-semi-meuble/1741831701</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -1847,19 +1851,19 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Logement sur 2 étages, grandes pièces lumineuses, buanderie incluse, accès patio extérieur, stationnement intérieur en option (+100$/mois, sinon 2050$ sans parking), non chauffé/non éclairé, animaux acceptés, vérification de crédit requise, bail 1 an, disponible immédiatement (mention aussi du 15 sept. 2026). Note : métro Fabre est sur la ligne bleue, pas la ligne verte.</t>
+          <t>3e étage, entièrement rénové en 2026, semi-meublé, 4 électroménagers inclus (frigo, laveuse-sécheuse), non-fumeur, animaux non admis, disponible 16 août 2026, bail 1 an, à une rue de la Promenade Masson. Walk Score 10, Transit Score 8. Station la plus proche non précisée par l'annonce, Beaubien (ligne verte) estimée à ~12 min de marche.</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/85/85133349-63d7-4d10-a907-3ad77380a0e8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2d/2dc02de9-9511-4f1f-9ce6-8431e747f9a6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1869,27 +1873,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>5½ semi-meublé rénové (3 chambres), 950 pi², balcon - Rosemont, près Promenade Masson</t>
+          <t>Grand 5½ (3 chambres), 1200 pi², 2 balcons - Villeray/Rosemont, à 10 min du métro Fabre</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1S9)</t>
+          <t>n/d (Montréal, QC H2E 2C8)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1904,17 +1908,17 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1924,7 +1928,7 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rosemont-5-1-2-appartement-semi-meuble/1741831701</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1743217472</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -1934,19 +1938,19 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>3e étage, entièrement rénové en 2026, semi-meublé, 4 électroménagers inclus (frigo, laveuse-sécheuse), non-fumeur, animaux non admis, disponible 16 août 2026, bail 1 an, à une rue de la Promenade Masson. Walk Score 10, Transit Score 8. Station la plus proche non précisée par l'annonce, Beaubien (ligne verte) estimée à ~12 min de marche.</t>
+          <t>Immeuble sécurisé avec concierge 24h, climatisation incluse, accès laveuse-sécheuse, animaux limités (chats seulement), chauffage non inclus, disponible 12 sept. 2026, bail 1 an. Walk Score 8/10, Transit Score 9/10.</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2d/2dc02de9-9511-4f1f-9ce6-8431e747f9a6?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/ba98470a-66af-4439-89d7-a03111a24476?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1956,22 +1960,22 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ (3 chambres), 1200 pi², 2 balcons - Villeray/Rosemont, à 10 min du métro Fabre</t>
+          <t>4½ rénové (4 chambres, 1200 pi²), immense balcon/cour privée - rue Gauthier (Plateau-Mont-Royal), à 4 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2E 2C8)</t>
+          <t>2184, Rue Gauthier, Montréal, QC</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1981,7 +1985,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1991,7 +1995,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -2001,7 +2005,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -2011,7 +2015,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1743217472</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rare-plateau-mont-royal-4-bedroom-2-bathrooms/1741923928</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -2021,12 +2025,12 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Immeuble sécurisé avec concierge 24h, climatisation incluse, accès laveuse-sécheuse, animaux limités (chats seulement), chauffage non inclus, disponible 12 sept. 2026, bail 1 an. Walk Score 8/10, Transit Score 9/10.</t>
+          <t>4 chambres fermées (possibilité d'une 5e), immense balcon/cour arrière privée, rue tranquille et bordée d'arbres, Walk Score 8/10 et Transit Score 9/10, animaux limités, disponible depuis le 12 août 2026, loyer négociable (annoncé à 2400$).</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/ba98470a-66af-4439-89d7-a03111a24476?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5a/5a4363b1-d8e4-4594-925f-b068d89b32a4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2047,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové (4 chambres, 1200 pi²), immense balcon/cour privée - rue Gauthier (Plateau-Mont-Royal), à 4 min du métro Mont-Royal</t>
+          <t>5½ (3 chambres + pièce double), 1450 pi², 2 balcons - avenue du Mont-Royal Est (Plateau-Mont-Royal), à ~12 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2053,22 +2057,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>2184, Rue Gauthier, Montréal, QC</t>
+          <t>2226, Avenue du Mont-Royal E, Montréal, QC H2H 1K4</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2088,7 +2092,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -2098,7 +2102,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rare-plateau-mont-royal-4-bedroom-2-bathrooms/1741923928</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-mont-royal-:-61-2-renove-2200-mois/1741874223</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2108,19 +2112,19 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>4 chambres fermées (possibilité d'une 5e), immense balcon/cour arrière privée, rue tranquille et bordée d'arbres, Walk Score 8/10 et Transit Score 9/10, animaux limités, disponible depuis le 12 août 2026, loyer négociable (annoncé à 2400$).</t>
+          <t>3 chambres dont une double, 2 balcons, Walk Score 8/10, la plupart des commerces de proximité accessibles à pied en quelques minutes, animaux limités, disponible depuis le 11 août 2026. Distance exacte au métro Mont-Royal non précisée par l'annonce, estimée à partir de l'adresse (secteur assez à l'est sur Mont-Royal, à valider).</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5a/5a4363b1-d8e4-4594-925f-b068d89b32a4?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2f/2f12e2b7-b740-4324-b3c5-273398885b1a?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2130,7 +2134,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres + pièce double), 1450 pi², 2 balcons - avenue du Mont-Royal Est (Plateau-Mont-Royal), à ~12 min du métro Mont-Royal</t>
+          <t>Grand 5 1/2 Plateau-Mont-Royal, près du parc Laurier</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2140,17 +2144,17 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2226, Avenue du Mont-Royal E, Montréal, QC H2H 1K4</t>
+          <t>5483, Rue Cartier, Montréal</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2165,17 +2169,17 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -2185,7 +2189,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-mont-royal-:-61-2-renove-2200-mois/1741874223</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-plateau-disponible-des-maintenant/1742926253</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2195,12 +2199,12 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>3 chambres dont une double, 2 balcons, Walk Score 8/10, la plupart des commerces de proximité accessibles à pied en quelques minutes, animaux limités, disponible depuis le 11 août 2026. Distance exacte au métro Mont-Royal non précisée par l'annonce, estimée à partir de l'adresse (secteur assez à l'est sur Mont-Royal, à valider).</t>
+          <t>Libre immédiatement, 3 balcons (avant, arrière, latéral), remise et BBQ inclus, bail 1 an, animaux acceptés sous conditions, station BIXI à 2 min</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2f/2f12e2b7-b740-4324-b3c5-273398885b1a?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a1/a156df4e-a074-4098-9f9f-fa7b1b73bbed?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2217,27 +2221,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 Plateau-Mont-Royal, près du parc Laurier</t>
+          <t>5½ rénové, 1200 pi², 3 chambres, balcon - rue Villeray, à ~10 min du métro De Castelnau</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>5483, Rue Cartier, Montréal</t>
+          <t>3007, Rue Villeray, Montréal</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2252,27 +2256,27 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>De Castelnau</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-plateau-disponible-des-maintenant/1742926253</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/16587333</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -2282,19 +2286,19 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Libre immédiatement, 3 balcons (avant, arrière, latéral), remise et BBQ inclus, bail 1 an, animaux acceptés sous conditions, station BIXI à 2 min</t>
+          <t>Climatisation incluse, cour clôturée, balcon neuf, Walk Score 92, disponible 5 jours après acceptation. Chauffage/animaux/meublé non précisés.</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a1/a156df4e-a074-4098-9f9f-fa7b1b73bbed?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2CC3A0DDDDDDDDDD2&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2304,27 +2308,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 1200 pi², 3 chambres, balcon - rue Villeray, à ~10 min du métro De Castelnau</t>
+          <t>5 1/2 rénové, 3 chambres, grande cour privée - rue Cuvillier (Hochelaga), à 5 min du métro Joliette</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>3007, Rue Villeray, Montréal</t>
+          <t>Rue Cuvillier, Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2339,27 +2343,27 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>De Castelnau</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/16587333</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-in-hochelaga-internet-included-pet-friendly/1742899363</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2369,19 +2373,19 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, cour clôturée, balcon neuf, Walk Score 92, disponible 5 jours après acceptation. Chauffage/animaux/meublé non précisés.</t>
+          <t>Internet et électroménagers inclus (frigo, cuisinière, lave-vaisselle, laveuse-sécheuse), immense cour privée, chauffé à l'eau chaude incluse, animaux acceptés (chiens et chats), disponible 1er septembre 2026, bail 1 an.</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2CC3A0DDDDDDDDDD2&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/dc/dc0af1fd-4be5-4589-b759-26be54d04e13?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2391,7 +2395,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 3 chambres, grande cour privée - rue Cuvillier (Hochelaga), à 5 min du métro Joliette</t>
+          <t>Grand 6½ rénové à 2 pas du métro Pie-IX (ligne verte)</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2401,17 +2405,17 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Rue Cuvillier, Montréal, QC H1W 3A8</t>
+          <t>n/d (Montréal, QC H1W 3S5)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2426,7 +2430,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -2446,7 +2450,7 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-in-hochelaga-internet-included-pet-friendly/1742899363</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-renove-a-2-pas-du-metro-pie-ix-ligne-verte/1742650298</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2456,19 +2460,19 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Internet et électroménagers inclus (frigo, cuisinière, lave-vaisselle, laveuse-sécheuse), immense cour privée, chauffé à l'eau chaude incluse, animaux acceptés (chiens et chats), disponible 1er septembre 2026, bail 1 an.</t>
+          <t>3e et dernier étage d'un triplex, thermopompe neuve (chauffage et climatisation inclus), eau incluse, 1 chat stérilisé accepté sous conditions, non-fumeur, aucun stationnement, disponible 1er septembre 2026, à 10 min de la Promenade Ontario.</t>
         </is>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/dc/dc0af1fd-4be5-4589-b759-26be54d04e13?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f4/f45db41c-6dff-4465-9306-2786cd9a6d0a?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2478,32 +2482,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Grand 6½ rénové à 2 pas du métro Pie-IX (ligne verte)</t>
+          <t>2 chambres rénové + bureau, 1233 pi², 2 balcons privés (vue rue et cour) - rue Beaudry (Plateau/Village), à 5 min des métros Beaudry et Sherbrooke (Marketplace)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3S5)</t>
+          <t>2096, Rue Beaudry, Montréal, QC H2L 3G3</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2513,7 +2517,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaudry</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -2528,12 +2532,12 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-renove-a-2-pas-du-metro-pie-ix-ligne-verte/1742650298</t>
+          <t>https://www.facebook.com/marketplace/item/1013235751248159</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2543,19 +2547,19 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>3e et dernier étage d'un triplex, thermopompe neuve (chauffage et climatisation inclus), eau incluse, 1 chat stérilisé accepté sous conditions, non-fumeur, aucun stationnement, disponible 1er septembre 2026, à 10 min de la Promenade Ontario.</t>
+          <t>Triplex historique (1910), 3e étage, planchers de bois franc, cuisine électros inox, salle de bain avec plancher chauffant, 2 balcons privés, BBQ permis, non meublé, pas d'animaux, à deux pas du Parc Lafontaine et des rues St-Denis/Mont-Royal. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f4/f45db41c-6dff-4465-9306-2786cd9a6d0a?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/708034371_1980439032561863_4399292961270502724_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=seOsuJ82OCgQ7kNvwHJQAF_&amp;_nc_oc=AdpIcN9dvrhSjH3cUUKe-1NoCXjdRPWkLEJHM1iRX0uSNM82UoGBmceDQc6ivHVJc0o&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=23FdRsoQlpiB5o1uD2RUxQ&amp;_nc_ss=7f2a8&amp;oh=00_AQE_v7UCx6SSbwxfLxWa52ow8tBnENPnwu6_KHRlOAjZ_w&amp;oe=6A91F461</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2565,27 +2569,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>2 chambres rénové + bureau, 1233 pi², 2 balcons privés (vue rue et cour) - rue Beaudry (Plateau/Village), à 5 min des métros Beaudry et Sherbrooke (Marketplace)</t>
+          <t>5½ rénové (2 chambres), 1160 pi², 2 terrasses, stationnement inclus - rue Bossuet (Hochelaga), à ~10-12 min des métros Préfontaine/Joliette</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2096, Rue Beaudry, Montréal, QC H2L 3G3</t>
+          <t>2502, Rue Bossuet, app. 305, Montréal, QC</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2595,12 +2599,12 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (2 terrasses)</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Beaudry</t>
+          <t>Préfontaine ou Joliette (à confirmer)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -2610,17 +2614,17 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10-12 (estimé)</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1013235751248159</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22273952</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2630,12 +2634,12 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Triplex historique (1910), 3e étage, planchers de bois franc, cuisine électros inox, salle de bain avec plancher chauffant, 2 balcons privés, BBQ permis, non meublé, pas d'animaux, à deux pas du Parc Lafontaine et des rues St-Denis/Mont-Royal. Lien Facebook (connexion requise).</t>
+          <t>Dernier étage (construction 2004), meublé et équipé, 1 place de stationnement garage incluse, animaux non acceptés, non-fumeur, Walk Score 84, disponible 5 jours après acceptation du bail, jusqu'en mai 2027.</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/708034371_1980439032561863_4399292961270502724_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=seOsuJ82OCgQ7kNvwHJQAF_&amp;_nc_oc=AdpIcN9dvrhSjH3cUUKe-1NoCXjdRPWkLEJHM1iRX0uSNM82UoGBmceDQc6ivHVJc0o&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=23FdRsoQlpiB5o1uD2RUxQ&amp;_nc_ss=7f2a8&amp;oh=00_AQE_v7UCx6SSbwxfLxWa52ow8tBnENPnwu6_KHRlOAjZ_w&amp;oe=6A91F461</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1D8268DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -2652,62 +2656,62 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (2 chambres), 1160 pi², 2 terrasses, stationnement inclus - rue Bossuet (Hochelaga), à ~10-12 min des métros Préfontaine/Joliette</t>
+          <t>5½ meublé, 3 chambres fermées, 1200 pi², terrasse arrière - rue Saint-Dominique (Mile-End/Plateau), à 10 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal (Mile-End)</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2502, Rue Bossuet, app. 305, Montréal, QC</t>
+          <t>5561, Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>oui (2 terrasses)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine ou Joliette (à confirmer)</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>10-12 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22273952</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5561-rue-saint-dominique-1139770</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2717,12 +2721,12 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage (construction 2004), meublé et équipé, 1 place de stationnement garage incluse, animaux non acceptés, non-fumeur, Walk Score 84, disponible 5 jours après acceptation du bail, jusqu'en mai 2027.</t>
+          <t>Entièrement meublé et équipé (peut être loué non meublé), rez-de-chaussée, belle salle de bain avec laveuse-sécheuse, grand espace ouvert salon/salle à manger avec mur de brique, petite terrasse arrière, WiFi inclus, situé entre Mile-End et Plateau, disponible immédiatement</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1D8268DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139770/5-1-2-plateau-mont-royal-1600-15844601.jpg</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2743,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé, 3 chambres fermées, 1200 pi², terrasse arrière - rue Saint-Dominique (Mile-End/Plateau), à 10 min du métro Rosemont</t>
+          <t>5½, 3 chambres fermées, 1100 pi², accès terrasse - rue Saint-Dominique (Mile-End/Plateau), à 10 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2749,7 +2753,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>5561, Rue Saint-Dominique, Montréal</t>
+          <t>5571, Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2759,7 +2763,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2794,7 +2798,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5561-rue-saint-dominique-1139770</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5571-rue-saint-dominique-1139764</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2804,19 +2808,19 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>Entièrement meublé et équipé (peut être loué non meublé), rez-de-chaussée, belle salle de bain avec laveuse-sécheuse, grand espace ouvert salon/salle à manger avec mur de brique, petite terrasse arrière, WiFi inclus, situé entre Mile-End et Plateau, disponible immédiatement</t>
+          <t>Rez-de-chaussée, 3 chambres lumineuses avec rangement, accès à une petite terrasse pour BBQ + rangement, à quelques pas du boulevard Saint-Laurent, coeur du Mile-End, tous électros inclus, disponible immédiatement</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139770/5-1-2-plateau-mont-royal-1600-15844601.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139764/plateau-mont-royal-1600-15844509.jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2826,22 +2830,22 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>5½, 3 chambres fermées, 1100 pi², accès terrasse - rue Saint-Dominique (Mile-End/Plateau), à 10 min du métro Rosemont</t>
+          <t>5½ meublé (2 chambres + bureau), terrasse privée + balcon - rue Rachel Est (Plateau) (Marketplace)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal (Mile-End)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>5571, Rue Saint-Dominique, Montréal</t>
+          <t>1952, Rue Rachel Est, Montréal (H2H 1P7)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2851,7 +2855,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2861,12 +2865,12 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Papineau (à vérifier)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2876,12 +2880,12 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5571-rue-saint-dominique-1139764</t>
+          <t>https://www.facebook.com/marketplace/item/2292527024853183</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
@@ -2891,12 +2895,12 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, 3 chambres lumineuses avec rangement, accès à une petite terrasse pour BBQ + rangement, à quelques pas du boulevard Saint-Laurent, coeur du Mile-End, tous électros inclus, disponible immédiatement</t>
+          <t>Meublé tout inclus (chauffage, électricité, internet), dernier étage, 2 chambres fermées dont une avec balcon privé, terrasse privée additionnelle, disponible 1er oct. 2026, animaux refusés, près du Parc La Fontaine et des commerces du Plateau. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139764/plateau-mont-royal-1600-15844509.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/761611239_1396606412369389_589761538047184410_n.jpg?stp=c106.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=ByqmxtV-qr8Q7kNvwHv7fu1&amp;_nc_oc=Adqs88FQ5PCbjl9_ccROEdYgjrDJgwYGaQdpr82zVt8nSiGqfRrTTxeuF3rWdT2I8lQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=GNvZuYTYNEtOQRxhL_vEyQ&amp;_nc_ss=7f2a8&amp;oh=00_AQEV1OaYCcEikcQP70OW1e4Cl8IrZ927IG4qBoDioL_qlg&amp;oe=6A8A9DFD</t>
         </is>
       </c>
     </row>
@@ -2913,22 +2917,22 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé (2 chambres + bureau), terrasse privée + balcon - rue Rachel Est (Plateau) (Marketplace)</t>
+          <t>5 1/2 meuble (3 chambres), petite terrasse arriere - rue Saint-Dominique (Mile-End/Plateau), a 6 min du metro Rosemont</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>1952, Rue Rachel Est, Montréal (H2H 1P7)</t>
+          <t>5561, Rue Saint-Dominique, Montréal, QC</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2938,7 +2942,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2948,27 +2952,27 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Papineau (à vérifier)</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>logisquebec</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2292527024853183</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357976</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
@@ -2978,14 +2982,10 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Meublé tout inclus (chauffage, électricité, internet), dernier étage, 2 chambres fermées dont une avec balcon privé, terrasse privée additionnelle, disponible 1er oct. 2026, animaux refusés, près du Parc La Fontaine et des commerces du Plateau. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/761611239_1396606412369389_589761538047184410_n.jpg?stp=c106.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=ByqmxtV-qr8Q7kNvwHv7fu1&amp;_nc_oc=Adqs88FQ5PCbjl9_ccROEdYgjrDJgwYGaQdpr82zVt8nSiGqfRrTTxeuF3rWdT2I8lQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=GNvZuYTYNEtOQRxhL_vEyQ&amp;_nc_ss=7f2a8&amp;oh=00_AQEV1OaYCcEikcQP70OW1e4Cl8IrZ927IG4qBoDioL_qlg&amp;oe=6A8A9DFD</t>
-        </is>
-      </c>
+          <t>Rez-de-chaussee, entierement meuble et equipe (louable non meuble), WiFi inclus, disponible immediatement, superficie annoncee jusqu'a 1200 pi2, chauffage non precise.</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3000,27 +3000,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meuble (3 chambres), petite terrasse arriere - rue Saint-Dominique (Mile-End/Plateau), a 6 min du metro Rosemont</t>
+          <t>Beau 5 1/2 meuble tout inclus (3 chambres), 2 balcons - secteur Hochelaga, a 5 min du metro Pie-IX</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>5561, Rue Saint-Dominique, Montréal, QC</t>
+          <t>n/d (Montréal, QC H1V 2L3)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -3030,32 +3030,32 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>logisquebec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357976</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-5-1-2-meuble-tout-inclus-metro-pie-ix/1742159498</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
@@ -3065,15 +3065,19 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussee, entierement meuble et equipe (louable non meuble), WiFi inclus, disponible immediatement, superficie annoncee jusqu'a 1200 pi2, chauffage non precise.</t>
-        </is>
-      </c>
-      <c r="Q30" s="5" t="inlineStr"/>
+          <t>Meuble, tout inclus (chauffage, hydro, eau chaude, internet, Netflix), climatisation, laveuse-secheuse et lave-vaisselle inclus, 2e etage, aucun animal, bail mensuel (min. 6 mois), disponible 1er octobre 2026.</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/25/256b45e3-2764-4740-872a-00527fcbff0f?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3083,22 +3087,22 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Beau 5 1/2 meuble tout inclus (3 chambres), 2 balcons - secteur Hochelaga, a 5 min du metro Pie-IX</t>
+          <t>5½ rénové (3 chambres), 1000 pi², balcon arrière - rue Saint-Dominique (Plateau-Mont-Royal), à 10 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2L3)</t>
+          <t>3477, Rue Saint-Dominique, Montréal, QC</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3113,12 +3117,12 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -3128,17 +3132,17 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-5-1-2-meuble-tout-inclus-metro-pie-ix/1742159498</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-3477-rue-saint-dominique-1130024</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
@@ -3148,19 +3152,19 @@
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Meuble, tout inclus (chauffage, hydro, eau chaude, internet, Netflix), climatisation, laveuse-secheuse et lave-vaisselle inclus, 2e etage, aucun animal, bail mensuel (min. 6 mois), disponible 1er octobre 2026.</t>
+          <t>2e étage, électroménagers inclus (four, frigo, laveuse-sécheuse), à distance de marche du boul. Saint-Laurent, bars/restaurants/parcs, disponible 19 août 2026, politique animaux non précisée.</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/25/256b45e3-2764-4740-872a-00527fcbff0f?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130024/plateau-mont-royal-600-15608538.jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3170,27 +3174,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1000 pi², balcon arrière - rue Saint-Dominique (Plateau-Mont-Royal), à 10 min du métro Sherbrooke</t>
+          <t>5½ rénové, petite terrasse - rue Saint-Dominique (Plateau, limite Mile-End)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>3477, Rue Saint-Dominique, Montréal, QC</t>
+          <t>5571 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -3200,32 +3204,32 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (terrasse + rangement)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Logis Québec</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-3477-rue-saint-dominique-1130024</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357647</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
@@ -3235,19 +3239,15 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>2e étage, électroménagers inclus (four, frigo, laveuse-sécheuse), à distance de marche du boul. Saint-Laurent, bars/restaurants/parcs, disponible 19 août 2026, politique animaux non précisée.</t>
-        </is>
-      </c>
-      <c r="Q32" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130024/plateau-mont-royal-600-15608538.jpg</t>
-        </is>
-      </c>
+          <t>Disponible immédiatement. Même immeuble déjà repéré au 5561/5571 à 2075$ précédemment; nouvelle fiche à prix réduit.</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3257,27 +3257,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, petite terrasse - rue Saint-Dominique (Plateau, limite Mile-End)</t>
+          <t>5½ (3 chambres, 1250 pi²) avec balcon, plancher flottant neuf - rue Léonard-De Vinci, Villeray/Saint-Michel, à 11 min du métro Saint-Michel</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
+          <t>Saint-Michel/Villeray</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>5571 Rue Saint-Dominique, Montréal</t>
+          <t>rue Léonard-De Vinci, entre 17e et 18e avenue, Montréal, QC H2A 2N9</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -3287,32 +3287,32 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>oui (terrasse + rangement)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Logis Québec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357647</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-dans-villeray-a-louer-pour-septembre/1741798163</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
@@ -3322,10 +3322,14 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>Disponible immédiatement. Même immeuble déjà repéré au 5561/5571 à 2075$ précédemment; nouvelle fiche à prix réduit.</t>
-        </is>
-      </c>
-      <c r="Q33" s="5" t="inlineStr"/>
+          <t>2e étage, plancher flottant neuf, aucun animal, non-fumeur, bail 1 an, disponible 1er septembre 2026.</t>
+        </is>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5df5accb-8187-4cb7-a711-ee6ae12ae898?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3340,27 +3344,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres, 1250 pi²) avec balcon, plancher flottant neuf - rue Léonard-De Vinci, Villeray/Saint-Michel, à 11 min du métro Saint-Michel</t>
+          <t>5½ (3 chambres, 1100 pi²) meublé, mur de brique - rue Saint-Dominique, Plateau-Mont-Royal (limite Mile-End), à 6 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel/Villeray</t>
+          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>rue Léonard-De Vinci, entre 17e et 18e avenue, Montréal, QC H2A 2N9</t>
+          <t>5561 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -3375,27 +3379,27 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Logisquebec</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-dans-villeray-a-louer-pour-septembre/1741798163</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357139</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3405,12 +3409,12 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>2e étage, plancher flottant neuf, aucun animal, non-fumeur, bail 1 an, disponible 1er septembre 2026.</t>
+          <t>Meublé et équipé, wifi inclus, disponible immédiatement, mur de brique apparent, salon/salle à manger ouvert.</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5df5accb-8187-4cb7-a711-ee6ae12ae898?rule=kijijica-960-jpg</t>
+          <t>https://i.logisquebec.com/i-a-louer/112098/357139/img_5778_jpg_6a7b438a91d83.jpg</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3431,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres, 1100 pi²) meublé, mur de brique - rue Saint-Dominique, Plateau-Mont-Royal (limite Mile-End), à 6 min du métro Rosemont</t>
+          <t>5½ (3 chambres, 1100 pi²) rez-de-chaussée avec terrasse - rue Saint-Dominique, Plateau-Mont-Royal (limite Mile-End), à 6 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -3437,7 +3441,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>5561 Rue Saint-Dominique, Montréal</t>
+          <t>5571 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -3482,7 +3486,7 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357139</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357134</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
@@ -3492,19 +3496,19 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>Meublé et équipé, wifi inclus, disponible immédiatement, mur de brique apparent, salon/salle à manger ouvert.</t>
+          <t>Rez-de-chaussée, accès à une petite terrasse (BBQ + rangement), tous électroménagers inclus, disponible immédiatement. Unité voisine de celle du 5561 Saint-Dominique (même secteur).</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://i.logisquebec.com/i-a-louer/112098/357139/img_5778_jpg_6a7b438a91d83.jpg</t>
+          <t>https://i.logisquebec.com/i-a-louer/112098/357134/758427288_10174783720475263_3825985666760897901_n_jpg_6a7b3e3cb1ac5.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -3514,32 +3518,32 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres, 1100 pi²) rez-de-chaussée avec terrasse - rue Saint-Dominique, Plateau-Mont-Royal (limite Mile-End), à 6 min du métro Rosemont</t>
+          <t>Penthouse 2 étages (2 chambres, 1372-1400 pi²) avec 2 balcons - boul. Pie-IX, Hochelaga-Maisonneuve, à 10 min du métro Pie-IX</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>5571 Rue Saint-Dominique, Montréal</t>
+          <t>1859, Boulevard Pie-IX, Montréal, QC H1V 2C7</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -3549,27 +3553,27 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Logisquebec</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357134</t>
+          <t>https://www.zumper.com/listings/773677p/2-bedroom-maisonneuve-montreal-qc</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
@@ -3579,19 +3583,19 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, accès à une petite terrasse (BBQ + rangement), tous électroménagers inclus, disponible immédiatement. Unité voisine de celle du 5561 Saint-Dominique (même secteur).</t>
+          <t>Penthouse d'angle sur deux étages (1372 à 1400 pi² selon la fiche), 2 balcons privés dont un sur cour, non meublé, laveuse-sécheuse et lave-vaisselle inclus, stationnement inclus, aucun animal, chauffage/eau/électricité/internet non inclus, secteur Maisonneuve (pas Mercier), à la limite ouest de Pie-IX autorisée.</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://i.logisquebec.com/i-a-louer/112098/357134/758427288_10174783720475263_3825985666760897901_n_jpg_6a7b3e3cb1ac5.jpg</t>
+          <t>https://img.zumpercdn.com/491722127/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3601,32 +3605,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Penthouse 2 étages (2 chambres, 1372-1400 pi²) avec 2 balcons - boul. Pie-IX, Hochelaga-Maisonneuve, à 10 min du métro Pie-IX</t>
+          <t>Grand 7½ (4 chambres, 1500 pi²) avec 2 balcons + terrasse privée - avenue Ogilvy, à 5 min du métro Parc</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>1859, Boulevard Pie-IX, Montréal, QC H1V 2C7</t>
+          <t>826, Avenue Ogilvy, Montréal, QC</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3636,27 +3640,27 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Parc</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/listings/773677p/2-bedroom-maisonneuve-montreal-qc</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/10316417</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
@@ -3666,19 +3670,19 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Penthouse d'angle sur deux étages (1372 à 1400 pi² selon la fiche), 2 balcons privés dont un sur cour, non meublé, laveuse-sécheuse et lave-vaisselle inclus, stationnement inclus, aucun animal, chauffage/eau/électricité/internet non inclus, secteur Maisonneuve (pas Mercier), à la limite ouest de Pie-IX autorisée.</t>
+          <t>3e étage, immeuble rénové, 2 balcons + grande terrasse privée arrière (~500 pi²), chauffage électrique, électroménagers inclus (frigo, cuisinière, laveuse-sécheuse), stationnement rue, libre 1er juillet 2026.</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/491722127/1280x960?auto=format</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA10B2ACDDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -3688,32 +3692,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Grand 7½ (4 chambres, 1500 pi²) avec 2 balcons + terrasse privée - avenue Ogilvy, à 5 min du métro Parc</t>
+          <t>Superbe 5½ (3 chambres), 1000 pi², balcon et terrasse arrière - Petite-Patrie, entre métro Jean-Talon et Beaubien</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>826, Avenue Ogilvy, Montréal, QC</t>
+          <t>n/d (Montréal, QC H2S 1G2)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -3723,27 +3727,27 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/10316417</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/1-950-superbe-5-1-2-petite-patrie/1741530066</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -3753,12 +3757,12 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>3e étage, immeuble rénové, 2 balcons + grande terrasse privée arrière (~500 pi²), chauffage électrique, électroménagers inclus (frigo, cuisinière, laveuse-sécheuse), stationnement rue, libre 1er juillet 2026.</t>
+          <t>Balcon + terrasse arrière, disponible 15 août 2026, animaux non acceptés, bail 1 an, visites sur rendez-vous.</t>
         </is>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA10B2ACDDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/57/57790a33-97f1-45eb-8680-1ff904a428ec?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
@@ -3775,22 +3779,22 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Superbe 5½ (3 chambres), 1000 pi², balcon et terrasse arrière - Petite-Patrie, entre métro Jean-Talon et Beaubien</t>
+          <t>5½ rénové (3 chambres), 1000 pi², grand balcon arrière privé - avenue Aird (Hochelaga), à 6 min du métro Pie-IX</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2S 1G2)</t>
+          <t>1692, Avenue Aird, Montréal, QC</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -3810,7 +3814,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -3820,17 +3824,17 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/1-950-superbe-5-1-2-petite-patrie/1741530066</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22918210</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
@@ -3840,12 +3844,12 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>Balcon + terrasse arrière, disponible 15 août 2026, animaux non acceptés, bail 1 an, visites sur rendez-vous.</t>
+          <t>Entièrement rénové, thermopompe incluse, 1 mois gratuit en promotion, animaux à discuter, disponible immédiatement, Walk Score 94.</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/57/57790a33-97f1-45eb-8680-1ff904a428ec?rule=kijijica-640-webp</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE581B7BDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -3862,22 +3866,22 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1000 pi², grand balcon arrière privé - avenue Aird (Hochelaga), à 6 min du métro Pie-IX</t>
+          <t>5½ entièrement rénové (3 chambres), 1000 pi², balcon - rue de la Visitation (Centre-Sud), à 2 min du métro Beaudry</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Ville-Marie (Sainte-Marie/Centre-Sud)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>1692, Avenue Aird, Montréal, QC</t>
+          <t>1576, Rue de la Visitation, Montréal, QC H2L 3C1</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -3897,7 +3901,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaudry</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -3907,17 +3911,17 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22918210</t>
+          <t>https://www.zumper.com/apartment-buildings/p1126251/1568-1576-rue-de-la-visitation-sainte-marie-montreal-qc</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
@@ -3927,19 +3931,19 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, thermopompe incluse, 1 mois gratuit en promotion, animaux à discuter, disponible immédiatement, Walk Score 94.</t>
+          <t>3 chambres fermées avec garde-robe et fenêtre, plancher de bois franc, laveuse-sécheuse, frigo et cuisinière inclus, chauffage électrique (~85$/mois), disponibilité 1er juillet/août/septembre selon l'unité.</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE581B7BDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://img.zumpercdn.com/829563647/1280x960?dpr=1&amp;fit=crop&amp;h=542&amp;q=76&amp;w=991</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3949,17 +3953,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>5½ entièrement rénové (3 chambres), 1000 pi², balcon - rue de la Visitation (Centre-Sud), à 2 min du métro Beaudry</t>
+          <t>Grand 5½ (3 chambres), 1400 pi², 2 balcons (avant/arrière) - secteur Parc-Jarry (Villeray), près métro Jean-Talon</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Sainte-Marie/Centre-Sud)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>1576, Rue de la Visitation, Montréal, QC H2L 3C1</t>
+          <t>n/d (secteur Parc-Jarry, Montréal, QC H2R 2E9)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3969,7 +3973,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -3984,17 +3988,17 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Beaudry</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>n/d (courte marche selon l'annonce)</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -4004,7 +4008,7 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/apartment-buildings/p1126251/1568-1576-rue-de-la-visitation-sainte-marie-montreal-qc</t>
+          <t>https://www.zumper.com/apartments-for-rent/9730117p/3-bedroom-parc-jarry-montreal-qc</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
@@ -4014,19 +4018,19 @@
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées avec garde-robe et fenêtre, plancher de bois franc, laveuse-sécheuse, frigo et cuisinière inclus, chauffage électrique (~85$/mois), disponibilité 1er juillet/août/septembre selon l'unité.</t>
+          <t>Chats acceptés (chiens refusés), proche marché Jean-Talon et Petite Italie ; la date de disponibilité affichée par la fiche (avril/mai) semble périmée, à valider auprès du proprio avant de contacter.</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/829563647/1280x960?dpr=1&amp;fit=crop&amp;h=542&amp;q=76&amp;w=991</t>
+          <t>https://img.zumpercdn.com/404533906/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4036,27 +4040,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ (3 chambres), 1400 pi², 2 balcons (avant/arrière) - secteur Parc-Jarry (Villeray), près métro Jean-Talon</t>
+          <t>Spacieux 5½ (3 chambres, 2 salles de bain), garage - 20e Avenue (Rosemont, secteur Saint-Michel)</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie (secteur Saint-Michel)</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Parc-Jarry, Montréal, QC H2R 2E9)</t>
+          <t>6940, 20e Avenue, app. 201, Montréal</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -4071,27 +4075,27 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>n/d (courte marche selon l'annonce)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/apartments-for-rent/9730117p/3-bedroom-parc-jarry-montreal-qc</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/17444358</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
@@ -4101,19 +4105,19 @@
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>Chats acceptés (chiens refusés), proche marché Jean-Talon et Petite Italie ; la date de disponibilité affichée par la fiche (avril/mai) semble périmée, à valider auprès du proprio avant de contacter.</t>
+          <t>Construit en 2016, cuisine ouverte équipée, garage intérieur + casier (150$/mois en sus), aucun animal ni fumeur accepté, disponible 10 jours après acceptation de la promesse de location.</t>
         </is>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/404533906/1280x960?auto=format</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE9F5F13DDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -4123,27 +4127,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Spacieux 5½ (3 chambres, 2 salles de bain), garage - 20e Avenue (Rosemont, secteur Saint-Michel)</t>
+          <t>Grand logement 5½ sur deux niveaux, 3 chambres (2 au sous-sol), terrasse privée, +1300 pi² - rue Villeray</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie (secteur Saint-Michel)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>6940, 20e Avenue, app. 201, Montréal</t>
+          <t>1180, Rue Villeray, Montréal, QC</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -4158,17 +4162,17 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Jarry (estimé)</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>n/d (estimé, non précisé par l'annonce)</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -4178,7 +4182,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/17444358</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/28201368</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -4188,19 +4192,19 @@
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>Construit en 2016, cuisine ouverte équipée, garage intérieur + casier (150$/mois en sus), aucun animal ni fumeur accepté, disponible 10 jours après acceptation de la promesse de location.</t>
+          <t>Sur deux niveaux, 2 chambres au sous-sol, 2 salles de bain, terrasse privée accessible depuis le salon, climatisation, chats acceptés (chiens refusés), disponible 1er juillet 2026, vérification de crédit exigée. Walk Score 97. Distance exacte au métro non précisée par l'annonce.</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE9F5F13DDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA12F7C2DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4210,32 +4214,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Grand logement 5½ sur deux niveaux, 3 chambres (2 au sous-sol), terrasse privée, +1300 pi² - rue Villeray</t>
+          <t>5½ rénové, 2 chambres fermées, 1129 pi², balcons avant/arrière - rue Cartier (Plateau-Mont-Royal, près métro Laurier)</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>1180, Rue Villeray, Montréal, QC</t>
+          <t>5228, Rue Cartier, Montréal</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -4245,17 +4249,17 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Jarry (estimé)</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>n/d (estimé, non précisé par l'annonce)</t>
+          <t>10 (estimé, à vérifier)</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -4265,7 +4269,7 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/28201368</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/27220680</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
@@ -4275,12 +4279,12 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Sur deux niveaux, 2 chambres au sous-sol, 2 salles de bain, terrasse privée accessible depuis le salon, climatisation, chats acceptés (chiens refusés), disponible 1er juillet 2026, vérification de crédit exigée. Walk Score 97. Distance exacte au métro non précisée par l'annonce.</t>
+          <t>2e étage d'un triplex de 1910, planchers de bois franc, salle de bain rénovée, une chambre avec grand lit double, coin lavage en cuisine, rue Cartier paisible, proche cafés/restos/parcs, animaux acceptés sous conditions, non-fumeur, dispo 1er juillet 2026, Walk Score 97 (distance exacte au métro Laurier non précisée par l'annonce)</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA12F7C2DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADBB74ADDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -4297,42 +4301,42 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 2 chambres fermées, 1129 pi², balcons avant/arrière - rue Cartier (Plateau-Mont-Royal, près métro Laurier)</t>
+          <t>7½ rénové, 3 chambres, terrasse arrière - Village, près métros Beaudry/Papineau</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Village/Centre-Sud)</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>5228, Rue Cartier, Montréal</t>
+          <t>n/d (Rue Sainte-Catherine Est, secteur Village, Montréal)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (terrasse arrière)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Beaudry ou Papineau</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -4342,17 +4346,17 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé, à vérifier)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/27220680</t>
+          <t>https://www.facebook.com/marketplace/item/1667192434430051</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
@@ -4362,19 +4366,19 @@
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>2e étage d'un triplex de 1910, planchers de bois franc, salle de bain rénovée, une chambre avec grand lit double, coin lavage en cuisine, rue Cartier paisible, proche cafés/restos/parcs, animaux acceptés sous conditions, non-fumeur, dispo 1er juillet 2026, Walk Score 97 (distance exacte au métro Laurier non précisée par l'annonce)</t>
+          <t>Terrasse arrière, planchers bois franc, boiserie style centenaire, climatisation murale, près pont Jacques-Cartier et nombreux restos/cafés, lien exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADBB74ADDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/692069772_26712358195041265_6975725434404613474_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=K4QVlYLlbQQQ7kNvwE0KbUC&amp;_nc_oc=Adrk3RVHHBi5OgoT14PLqzSx6d01I7y8L2T47es6h11qi8YHvRoE9bE1E0Q_zayt4sA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=AakSf6B1WC1yfj4w57lVGA&amp;_nc_ss=7f2a8&amp;oh=00_AQCYGPel-1aXi7quArIAJzfowcbz2xzXa35Ilq-Fz-dWhw&amp;oe=6A6A7855</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4384,42 +4388,42 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>7½ rénové, 3 chambres, terrasse arrière - Village, près métros Beaudry/Papineau</t>
+          <t>Grand 5½ de 1240 pi² avec 2 balcons privés - rue de la Visitation (Centre-Sud), à 2 min du métro Beaudry</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Village/Centre-Sud)</t>
+          <t>Centre-Sud</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>n/d (Rue Sainte-Catherine Est, secteur Village, Montréal)</t>
+          <t>1433, Rue de la Visitation, Montréal</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>oui (terrasse arrière)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Beaudry ou Papineau</t>
+          <t>Beaudry</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -4429,7 +4433,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
@@ -4439,7 +4443,7 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1667192434430051</t>
+          <t>https://www.facebook.com/marketplace/item/1675910780361896</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
@@ -4449,12 +4453,12 @@
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>Terrasse arrière, planchers bois franc, boiserie style centenaire, climatisation murale, près pont Jacques-Cartier et nombreux restos/cafés, lien exige une connexion Facebook</t>
+          <t>2 chambres fermées + 1 chambre ouverte, grande cuisine moderne avec îlot central, salle de bain rénovée avec espace laveuse/sécheuse, lien exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/692069772_26712358195041265_6975725434404613474_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=K4QVlYLlbQQQ7kNvwE0KbUC&amp;_nc_oc=Adrk3RVHHBi5OgoT14PLqzSx6d01I7y8L2T47es6h11qi8YHvRoE9bE1E0Q_zayt4sA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=AakSf6B1WC1yfj4w57lVGA&amp;_nc_ss=7f2a8&amp;oh=00_AQCYGPel-1aXi7quArIAJzfowcbz2xzXa35Ilq-Fz-dWhw&amp;oe=6A6A7855</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/747978141_10167419432889256_7838070296744630358_n.jpg?stp=c273.0.652.652a_dst-jpg_tt6&amp;cstp=mx652x652&amp;ctp=s565x565&amp;_nc_cat=102&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=1BHIBLZMut0Q7kNvwGcjJKY&amp;_nc_oc=AdqL6QD8fVTD7q3J4l5WBnexTjWzHzx5_JFODaqPJQYjJbX5CNPnTI7QmCUqQifrkxQ&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=I01Huqn8cRYQWCF5daV0fw&amp;_nc_ss=7f2a8&amp;oh=00_AQCmBZgaUJOgbf9TtDkOp05R878cvx5VZPmstj6q8E25Kg&amp;oe=6A686D2B</t>
         </is>
       </c>
     </row>
@@ -4471,32 +4475,32 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ de 1240 pi² avec 2 balcons privés - rue de la Visitation (Centre-Sud), à 2 min du métro Beaudry</t>
+          <t>Grand 5 1/2, 3 chambres - avenue St-Germain (Hochelaga), à 10 min du métro Préfontaine</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Centre-Sud</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>1433, Rue de la Visitation, Montréal</t>
+          <t>1921 Rue St-Germain, Montréal (H1W 2T5)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -4506,7 +4510,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Beaudry</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -4516,17 +4520,17 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1675910780361896</t>
+          <t>https://www.zumper.com/listings/20844079p/3-bedroom-hochelaga-montreal-qc</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
@@ -4536,12 +4540,12 @@
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées + 1 chambre ouverte, grande cuisine moderne avec îlot central, salle de bain rénovée avec espace laveuse/sécheuse, lien exige une connexion Facebook</t>
+          <t>Entièrement rénové, concept ouvert, climatisation, laveuse-sécheuse et lave-vaisselle inclus, grand balcon arrière, animaux acceptés, hydro en sus, disponible 1er oct. 2026 ; attention, la page affichait aussi 2495$ ailleurs sur l'annonce, à valider avant de contacter</t>
         </is>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/747978141_10167419432889256_7838070296744630358_n.jpg?stp=c273.0.652.652a_dst-jpg_tt6&amp;cstp=mx652x652&amp;ctp=s565x565&amp;_nc_cat=102&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=1BHIBLZMut0Q7kNvwGcjJKY&amp;_nc_oc=AdqL6QD8fVTD7q3J4l5WBnexTjWzHzx5_JFODaqPJQYjJbX5CNPnTI7QmCUqQifrkxQ&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=I01Huqn8cRYQWCF5daV0fw&amp;_nc_ss=7f2a8&amp;oh=00_AQCmBZgaUJOgbf9TtDkOp05R878cvx5VZPmstj6q8E25Kg&amp;oe=6A686D2B</t>
+          <t>https://img.zumpercdn.com/676603053/1280x960?auto=format</t>
         </is>
       </c>
     </row>
@@ -4558,27 +4562,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres - avenue St-Germain (Hochelaga), à 10 min du métro Préfontaine</t>
+          <t>Grand 6 1/2, 3 chambres avec cour - Parc-Jarry (Villeray), à 4 min du métro Jarry</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>1921 Rue St-Germain, Montréal (H1W 2T5)</t>
+          <t>Secteur Parc-Jarry (H2R 2E9), Montréal</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -4593,17 +4597,17 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
@@ -4613,7 +4617,7 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/listings/20844079p/3-bedroom-hochelaga-montreal-qc</t>
+          <t>https://www.zumper.com/apartments-for-rent/14724140p/3-bedroom-parc-jarry-montreal-qc</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
@@ -4623,19 +4627,19 @@
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, concept ouvert, climatisation, laveuse-sécheuse et lave-vaisselle inclus, grand balcon arrière, animaux acceptés, hydro en sus, disponible 1er oct. 2026 ; attention, la page affichait aussi 2495$ ailleurs sur l'annonce, à valider avant de contacter</t>
+          <t>Immeuble restauré de 1924, planchers de bois franc, plafonds 9 pieds, balcons avant et arrière, chats seulement, disponible août/sept. 2026 ; la page affichait des mentions de bail datées 2018-2019, à vérifier auprès du proprio avant de contacter</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/676603053/1280x960?auto=format</t>
+          <t>https://img.zumpercdn.com/222665685/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4645,27 +4649,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2, 3 chambres avec cour - Parc-Jarry (Villeray), à 4 min du métro Jarry</t>
+          <t>5½ neuf (OVILA), 3 chambres, terrasses privées - avenue Bennett (Hochelaga-Maisonneuve, près métro Pie-IX)</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Secteur Parc-Jarry (H2R 2E9), Montréal</t>
+          <t>2095, Avenue Bennett, Montréal</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -4680,27 +4684,27 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/apartments-for-rent/14724140p/3-bedroom-parc-jarry-montreal-qc</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/5-1-2-a-louer/hab-2095-avenue-bennett-1130234</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
@@ -4710,19 +4714,19 @@
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>Immeuble restauré de 1924, planchers de bois franc, plafonds 9 pieds, balcons avant et arrière, chats seulement, disponible août/sept. 2026 ; la page affichait des mentions de bail datées 2018-2019, à vérifier auprès du proprio avant de contacter</t>
+          <t>Construction neuve 2023-2024, climatisation murale, 5 électroménagers inclus, garde-robes walk-in, terrasses privées (BBQ permis), stationnement intérieur sécurisé + local vélo, ascenseur, juste en face du Marché Maisonneuve, superficie estimée entre 1050 et 1120 pi² selon l'annonce, à ~7 min du métro Pie-IX, prix à la limite haute du budget (2400$), disponibilité non précisée</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/222665685/1280x960?auto=format</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130234/4-1-2-mercier-hochelaga-maisonneuve-1600-15613083.jpg</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4732,32 +4736,32 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>5½ neuf (OVILA), 3 chambres, terrasses privées - avenue Bennett (Hochelaga-Maisonneuve, près métro Pie-IX)</t>
+          <t>4½ rénové, 2 chambres, 2 balcons - 38e Avenue (Rosemont)</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>2095, Avenue Bennett, Montréal</t>
+          <t>6180, 38e Avenue, Montréal</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -4767,7 +4771,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Pie-IX (à vérifier)</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -4777,7 +4781,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
@@ -4787,7 +4791,7 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/5-1-2-a-louer/hab-2095-avenue-bennett-1130234</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6180-38e-avenue-1129076</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
@@ -4797,19 +4801,19 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2023-2024, climatisation murale, 5 électroménagers inclus, garde-robes walk-in, terrasses privées (BBQ permis), stationnement intérieur sécurisé + local vélo, ascenseur, juste en face du Marché Maisonneuve, superficie estimée entre 1050 et 1120 pi² selon l'annonce, à ~7 min du métro Pie-IX, prix à la limite haute du budget (2400$), disponibilité non précisée</t>
+          <t>RDC, 2 grandes chambres fermées, balcon avant et arrière, garage détaché + 1 place intérieure + 2 extérieures, rangement au sous-sol, cour arrière, animaux négociables, disponible maintenant (1er septembre), distance au métro Pie-IX estimée depuis l'adresse (non confirmée par l'annonce)</t>
         </is>
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130234/4-1-2-mercier-hochelaga-maisonneuve-1600-15613083.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1129076/4-1-2-rosemont-petite-patrie-600-15587619.jpg</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -4819,7 +4823,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres, 2 balcons - 38e Avenue (Rosemont)</t>
+          <t>5½ rénové (3 chambres), 1000 pi², 2 balcons, à moins de 5 min du métro Jean-Talon - face au marché Jean-Talon</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -4829,22 +4833,22 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>6180, 38e Avenue, Montréal</t>
+          <t>192 Rue Jean-Talon E., Montréal</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -4854,44 +4858,40 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX (à vérifier)</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Logis Québec</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6180-38e-avenue-1129076</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l362224</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>RDC, 2 grandes chambres fermées, balcon avant et arrière, garage détaché + 1 place intérieure + 2 extérieures, rangement au sous-sol, cour arrière, animaux négociables, disponible maintenant (1er septembre), distance au métro Pie-IX estimée depuis l'adresse (non confirmée par l'annonce)</t>
-        </is>
-      </c>
-      <c r="Q51" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1129076/4-1-2-rosemont-petite-patrie-600-15587619.jpg</t>
-        </is>
-      </c>
+          <t>Complètement rénové, A/C mural, lave-vaisselle inclus, stationnement (permis et parcomètre) inclus, chauffage/eau chaude/électricité non inclus, animaux non admis, disponible octobre 2026, immeuble semi-commercial de 5 logements, Petite-Italie.</t>
+        </is>
+      </c>
+      <c r="Q51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -8882,7 +8882,7 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -8892,42 +8892,42 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé rénové (2 chambres), 1130 pi², 3e étage - Rosemont-La Petite-Patrie, à ~6 min du métro Beaubien</t>
+          <t>5½ (3 chambres), balcon, à 4 min du métro Joliette - Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>2356 Rue Saint-Zotique Est, Montréal, QC</t>
+          <t>n/d (Montréal, QC H1W 1G6)</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
@@ -8937,17 +8937,17 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>6 (estimé)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21588368</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-5-1-2-a-4-minutes-du-metro-joliette/1743857169</t>
         </is>
       </c>
       <c r="O98" s="5" t="inlineStr">
@@ -8957,19 +8957,19 @@
       </c>
       <c r="P98" s="6" t="inlineStr">
         <is>
-          <t>Meublé (literie et vaisselle fournies), coin bureau, aire de vie/cuisine ouverte, 3 puits de lumière, climatisation, stationnement rue, immeuble construit en 1929, disponible 1er oct. 2026, Walk Score 94, proche parc Molson, Cinéma Beaubien, écoles. Balcon non mentionné dans l'annonce.</t>
+          <t>3e étage, grande pièce commune ouverte et lumineuse, laveuse-sécheuse incluse, animaux acceptés, disponible 1er nov. 2026, bail 1 an. Superficie non précisée.</t>
         </is>
       </c>
       <c r="Q98" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1FD202DDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/df/df00680a-ce8f-4364-8e45-a7ee1cb23499?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -8979,27 +8979,27 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové (2 chambres), 950 pi², balcon couvert, accès cour - Villeray, à 3 min du métro De Castelnau</t>
+          <t>4½ (2 chambres), 980 pi², terrasse/cour - Plateau, à quelques pas du métro Laurier</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>7506 Av. Casgrain, Montréal, QC H2R 1Y8</t>
+          <t>n/d (Montréal, QC H2J 2T4)</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -9014,17 +9014,17 @@
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>De Castelnau</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M99" s="5" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/spacieux-4-a-villeray-balcon-acces-a-la-cour-march-jean-talon/1743225286</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-a-louer-dans-le-plateau-a-quelques-pas-du-metro-laurier/1743478226</t>
         </is>
       </c>
       <c r="O99" s="5" t="inlineStr">
@@ -9044,19 +9044,19 @@
       </c>
       <c r="P99" s="6" t="inlineStr">
         <is>
-          <t>Balcon couvert, accès à la cour arrière, planchers de bois franc, grande cuisine avec îlot central et évier de ferme, douche à l'italienne, internet inclus, animaux limités, disponible 9 sept. 2026, bail 1 an, option meublé/non meublé, à 2 min du parc Jarry et 5 min du marché Jean-Talon. Note : métro De Castelnau est sur la ligne bleue, pas la ligne verte.</t>
+          <t>Rez-de-chaussée, meublé, accès cour arrière avec terrasse, 5 électroménagers inclus (lave-vaisselle, laveuse-sécheuse), chats permis, non-fumeur, disponible 1er oct. 2026, bail 1 an, références exigées.</t>
         </is>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/75/75df9854-c14b-4e63-8546-4caa3de3f155?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/6e/6ed2e853-548e-4e65-bd61-886cfbe5dd9f?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Spacieux 4½ (2 chambres fermées), 950 pi², balcons avant/arrière - Rosemont/Petite-Patrie, à deux pas du métro Rosemont</t>
+          <t>5½ meublé rénové (2 chambres), 1130 pi², 3e étage - Rosemont-La Petite-Patrie, à ~6 min du métro Beaubien</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -9076,17 +9076,17 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2S 2H7)</t>
+          <t>2356 Rue Saint-Zotique Est, Montréal, QC</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -9096,32 +9096,32 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>6 (estimé)</t>
         </is>
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/spacieux-4-a-deux-pas-du-metro-rosemont/1743420224</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21588368</t>
         </is>
       </c>
       <c r="O100" s="5" t="inlineStr">
@@ -9131,19 +9131,19 @@
       </c>
       <c r="P100" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées + salon fermé, laveuse-sécheuse et lave-vaisselle inclus, meublé en option (même prix), 1er mois gratuit, 3e étage d'un 6-plex, disponible 13 sept. 2026, bail 1 an. Distance exacte au métro Rosemont non précisée ("à quelques minutes"), estimée à 5 min.</t>
+          <t>Meublé (literie et vaisselle fournies), coin bureau, aire de vie/cuisine ouverte, 3 puits de lumière, climatisation, stationnement rue, immeuble construit en 1929, disponible 1er oct. 2026, Walk Score 94, proche parc Molson, Cinéma Beaubien, écoles. Balcon non mentionné dans l'annonce.</t>
         </is>
       </c>
       <c r="Q100" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/86/86cd8da5-817c-436b-9477-0164477d1123?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1FD202DDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>5½ (2 chambres fermées), &gt;1000 pi², balcon et terrasse - Villeray (av. de Gaspé/Jarry), à 5 min du métro Jarry</t>
+          <t>4½ rénové (2 chambres), 950 pi², balcon couvert, accès cour - Villeray, à 3 min du métro De Castelnau</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Avenue de Gaspé (coin rue Jarry), Montréal, QC H2P 2J9</t>
+          <t>7506 Av. Casgrain, Montréal, QC H2R 1Y8</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -9188,17 +9188,17 @@
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>De Castelnau</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M101" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-a-louer-5-2e-etage-a-villeray/1743517904</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/spacieux-4-a-villeray-balcon-acces-a-la-cour-march-jean-talon/1743225286</t>
         </is>
       </c>
       <c r="O101" s="5" t="inlineStr">
@@ -9218,19 +9218,19 @@
       </c>
       <c r="P101" s="6" t="inlineStr">
         <is>
-          <t>2e étage d'un triplex construit en 2016, plus de 1000 pi² selon l'annonce, climatisation et échangeur d'air, laveuse-sécheuse à l'unité, rangement au sous-sol, chauffage/électricité non inclus, aucun animal, disponible 1er oct. 2026, bail 1 an. Proche du Marché Jean-Talon.</t>
+          <t>Balcon couvert, accès à la cour arrière, planchers de bois franc, grande cuisine avec îlot central et évier de ferme, douche à l'italienne, internet inclus, animaux limités, disponible 9 sept. 2026, bail 1 an, option meublé/non meublé, à 2 min du parc Jarry et 5 min du marché Jean-Talon. Note : métro De Castelnau est sur la ligne bleue, pas la ligne verte.</t>
         </is>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/12/12c6ad54-b2b6-4ed7-8b09-7cb42033e98a?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/75/75df9854-c14b-4e63-8546-4caa3de3f155?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>6 pièces (3 chambres), 1450 pi² - Rue Cartier (Rosemont/La Petite-Patrie), à 8-9 min du métro Beaubien</t>
+          <t>Spacieux 4½ (2 chambres fermées), 950 pi², balcons avant/arrière - Rosemont/Petite-Patrie, à deux pas du métro Rosemont</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -9250,32 +9250,32 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>5628, Rue Cartier, Montréal</t>
+          <t>n/d (Montréal, QC H2S 2H7)</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
@@ -9285,17 +9285,17 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>8-9 (estimé)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/11586670</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/spacieux-4-a-deux-pas-du-metro-rosemont/1743420224</t>
         </is>
       </c>
       <c r="O102" s="5" t="inlineStr">
@@ -9305,19 +9305,19 @@
       </c>
       <c r="P102" s="6" t="inlineStr">
         <is>
-          <t>Animaux non acceptés, fumeurs non acceptés, libre 10 jours après acceptation, Walk Score 94, année de construction inconnue</t>
+          <t>2 chambres fermées + salon fermé, laveuse-sécheuse et lave-vaisselle inclus, meublé en option (même prix), 1er mois gratuit, 3e étage d'un 6-plex, disponible 13 sept. 2026, bail 1 an. Distance exacte au métro Rosemont non précisée ("à quelques minutes"), estimée à 5 min.</t>
         </is>
       </c>
       <c r="Q102" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADC2C35DDDDDDDDDD1&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/86/86cd8da5-817c-436b-9477-0164477d1123?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -9327,22 +9327,22 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>4½ (2 chambres, 1000 pi²), balcon privé - Mile End/Plateau, à 10 min du métro Mont-Royal</t>
+          <t>5½ (2 chambres fermées), &gt;1000 pi², balcon et terrasse - Villeray (av. de Gaspé/Jarry), à 5 min du métro Jarry</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Secteur Mont-Royal / Saint-Laurent (adresse exacte communiquée sur demande), Montréal</t>
+          <t>Avenue de Gaspé (coin rue Jarry), Montréal, QC H2P 2J9</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-mile-end-plateau-mont-royal-for-october-1st-or-earlier/1741226751</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-a-louer-5-2e-etage-a-villeray/1743517904</t>
         </is>
       </c>
       <c r="O103" s="5" t="inlineStr">
@@ -9392,19 +9392,19 @@
       </c>
       <c r="P103" s="6" t="inlineStr">
         <is>
-          <t>Eau incluse, animaux acceptés, garde-robes dans les 2 chambres, libre 1er sept. (flexible jusqu'à début oct.), quartier très commerçant</t>
+          <t>2e étage d'un triplex construit en 2016, plus de 1000 pi² selon l'annonce, climatisation et échangeur d'air, laveuse-sécheuse à l'unité, rangement au sous-sol, chauffage/électricité non inclus, aucun animal, disponible 1er oct. 2026, bail 1 an. Proche du Marché Jean-Talon.</t>
         </is>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/48/48c69682-72d0-4f46-a048-b73d25824960?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/12/12c6ad54-b2b6-4ed7-8b09-7cb42033e98a?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Grand 6½ (3 chambres dont 1 au sous-sol), 1600 pi², semi-meublé - Rosemont/Petite-Italie, à 9 min du métro De Castelnau</t>
+          <t>6 pièces (3 chambres), 1450 pi² - Rue Cartier (Rosemont/La Petite-Patrie), à 8-9 min du métro Beaubien</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -9424,17 +9424,17 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>6725, Rue Clark, Montréal</t>
+          <t>5628, Rue Cartier, Montréal</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>De Castelnau</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>8-9 (estimé)</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/22041374</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/11586670</t>
         </is>
       </c>
       <c r="O104" s="5" t="inlineStr">
@@ -9479,19 +9479,19 @@
       </c>
       <c r="P104" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, grand sous-sol aménagé avec porte-patio et sortie extérieure, concept ouvert salon-cuisine-salle à manger, animaux acceptés, libre 3 jours après acceptation, Walk Score 100</t>
+          <t>Animaux non acceptés, fumeurs non acceptés, libre 10 jours après acceptation, Walk Score 94, année de construction inconnue</t>
         </is>
       </c>
       <c r="Q104" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA43154CDDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADC2C35DDDDDDDDDD1&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové (2 chambres, 919 pi²), terrasses avant et arrière - Plateau-Mont-Royal, à 9 min du métro Rosemont</t>
+          <t>4½ (2 chambres, 1000 pi²), balcon privé - Mile End/Plateau, à 10 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -9511,17 +9511,17 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>5559, Rue Saint-Denis, Montréal</t>
+          <t>Secteur Mont-Royal / Saint-Laurent (adresse exacte communiquée sur demande), Montréal</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr">
@@ -9546,17 +9546,17 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N105" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/22800609</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-mile-end-plateau-mont-royal-for-october-1st-or-earlier/1741226751</t>
         </is>
       </c>
       <c r="O105" s="5" t="inlineStr">
@@ -9566,19 +9566,19 @@
       </c>
       <c r="P105" s="6" t="inlineStr">
         <is>
-          <t>Cuisine rénovée, salle de bain refaite, foyer au gaz, stationnement extérieur et rangement inclus, animaux acceptés sous conditions, libre 10 jours après acceptation</t>
+          <t>Eau incluse, animaux acceptés, garde-robes dans les 2 chambres, libre 1er sept. (flexible jusqu'à début oct.), quartier très commerçant</t>
         </is>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD942B9DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/48/48c69682-72d0-4f46-a048-b73d25824960?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9588,27 +9588,27 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées dans 6½ rénové, balcon avant — rue Messier (Plateau), à 8 min du métro Frontenac (Marketplace)</t>
+          <t>Grand 6½ (3 chambres dont 1 au sous-sol), 1600 pi², semi-meublé - Rosemont/Petite-Italie, à 9 min du métro De Castelnau</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Rue Messier, Montréal, QC H2H 2J2</t>
+          <t>6725, Rue Clark, Montréal</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
@@ -9618,32 +9618,32 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>De Castelnau</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M106" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N106" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1061223113097011</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/22041374</t>
         </is>
       </c>
       <c r="O106" s="5" t="inlineStr">
@@ -9653,19 +9653,19 @@
       </c>
       <c r="P106" s="6" t="inlineStr">
         <is>
-          <t>Récemment rénové, 3 chambres fermées, balcon à l'avant, électroménagers inclus (laveuse-sécheuse, frigo, cuisinière, micro-ondes, lave-vaisselle), disponible 1er juillet, près du Parc Lafontaine et de la rue du Mont-Royal (épiceries, restaurants). Lien Facebook (connexion requise).</t>
+          <t>Semi-meublé, grand sous-sol aménagé avec porte-patio et sortie extérieure, concept ouvert salon-cuisine-salle à manger, animaux acceptés, libre 3 jours après acceptation, Walk Score 100</t>
         </is>
       </c>
       <c r="Q106" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/735625609_2065505231016426_6574529650408539097_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=E4nJjb_cVg4Q7kNvwFQwp2q&amp;_nc_oc=AdoS2U-DboFrJOuCACfN3iZAsx7mTsrap-dXy6D9Bgbb7f3JbOP-vBIYC640PMQ7DGk&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8bquEOBX4AYHloPy7y90wg&amp;_nc_ss=7f2a8&amp;oh=00_AQIGLwsoO-YRfg-zVb09X13pBE99bYA6bb__oSYv6dpxew&amp;oe=6A9BD192</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA43154CDDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -9675,27 +9675,27 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rezdechaussee (2 chambres), 895 pi2, grande terrasse - Le Giantonio, rue Saint-Hubert (Villeray), a 5 min du metro Jean-Talon</t>
+          <t>4½ rénové (2 chambres, 919 pi²), terrasses avant et arrière - Plateau-Mont-Royal, à 9 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>7400, Rue Saint-Hubert, app. 308, Montreal, QC H2R 2N3</t>
+          <t>5559, Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>919</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr">
@@ -9720,17 +9720,17 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N107" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/listings/13931011p/2-bedroom-parc-jarry-montreal-qc</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/22800609</t>
         </is>
       </c>
       <c r="O107" s="5" t="inlineStr">
@@ -9740,19 +9740,19 @@
       </c>
       <c r="P107" s="6" t="inlineStr">
         <is>
-          <t>transfert de bail 3 mois renouvelable; chiens et chats acceptes; garage interieur; terrasse privee de plus de 500 pi2; loyer prevu a 2370$ en juillet</t>
+          <t>Cuisine rénovée, salle de bain refaite, foyer au gaz, stationnement extérieur et rangement inclus, animaux acceptés sous conditions, libre 10 jours après acceptation</t>
         </is>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/478699409/1280x960?auto=format</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD942B9DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9762,32 +9762,32 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>4½ dernier étage rénové, 1000 pi², terrasse sur toit - Villeray (secteur parc Jarry / marché Jean-Talon)</t>
+          <t>3 chambres fermées dans 6½ rénové, balcon avant — rue Messier (Plateau), à 8 min du métro Frontenac (Marketplace)</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur parc Jarry / marché Jean-Talon, Montréal, QC H2P 2K8)</t>
+          <t>Rue Messier, Montréal, QC H2H 2J2</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -9797,27 +9797,27 @@
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Jarry / De Castelnau (estimé)</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N108" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/stunning-top-flr-2-bed-condo-w-terrace-garage-in-villeray/1742601711</t>
+          <t>https://www.facebook.com/marketplace/item/1061223113097011</t>
         </is>
       </c>
       <c r="O108" s="5" t="inlineStr">
@@ -9827,19 +9827,19 @@
       </c>
       <c r="P108" s="6" t="inlineStr">
         <is>
-          <t>Terrasse privée surdimensionnée sur le toit, fenêtres plafond-plancher, garage, animaux acceptés sous approbation, disponible 1er novembre 2026. Adresse exacte non précisée dans l'annonce; station de métro estimée à partir du quartier (à proximité du parc Jarry et du marché Jean-Talon).</t>
+          <t>Récemment rénové, 3 chambres fermées, balcon à l'avant, électroménagers inclus (laveuse-sécheuse, frigo, cuisinière, micro-ondes, lave-vaisselle), disponible 1er juillet, près du Parc Lafontaine et de la rue du Mont-Royal (épiceries, restaurants). Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q108" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/32/3264ba99-d383-4d4c-80fa-c34a38923adb?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/735625609_2065505231016426_6574529650408539097_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=E4nJjb_cVg4Q7kNvwFQwp2q&amp;_nc_oc=AdoS2U-DboFrJOuCACfN3iZAsx7mTsrap-dXy6D9Bgbb7f3JbOP-vBIYC640PMQ7DGk&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8bquEOBX4AYHloPy7y90wg&amp;_nc_ss=7f2a8&amp;oh=00_AQIGLwsoO-YRfg-zVb09X13pBE99bYA6bb__oSYv6dpxew&amp;oe=6A9BD192</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -9849,32 +9849,32 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres fermées), 2 balcons - avenue Gascon (Hochelaga), à 10 min des métros Préfontaine/Frontenac</t>
+          <t>4 1/2 rezdechaussee (2 chambres), 895 pi2, grande terrasse - Le Giantonio, rue Saint-Hubert (Villeray), a 5 min du metro Jean-Talon</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>n/d (avenue Gascon, Montréal, QC)</t>
+          <t>7400, Rue Saint-Hubert, app. 308, Montreal, QC H2R 2N3</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>895</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -9884,27 +9884,27 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine / Frontenac</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N109" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1034425322444723</t>
+          <t>https://www.zumper.com/listings/13931011p/2-bedroom-parc-jarry-montreal-qc</t>
         </is>
       </c>
       <c r="O109" s="5" t="inlineStr">
@@ -9914,19 +9914,19 @@
       </c>
       <c r="P109" s="6" t="inlineStr">
         <is>
-          <t>3e étage d'un immeuble de 6 logements, balcon avant et balcon arrière, électroménagers inclus (frigo, four, laveuse-sécheuse, lave-vaisselle), climatisation, stationnement gratuit dans la rue, disponible 1er juillet. Lien Facebook (connexion requise).</t>
+          <t>transfert de bail 3 mois renouvelable; chiens et chats acceptes; garage interieur; terrasse privee de plus de 500 pi2; loyer prevu a 2370$ en juillet</t>
         </is>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/724174498_986451427362791_2354216600396771595_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=A7xuOojioacQ7kNvwEpBjv9&amp;_nc_oc=Adp07rVyCTSdvON_GHUkgtkbTVkyXryWHFnSLtzm7jCgBnHmQa3GYTKbU62tjAqaTFA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=l2iYorXZG5uQ4C0wfNm3Rw&amp;_nc_ss=7f2a8&amp;oh=00_AQF7T5L1qjiWhL38C_g4OheBaQVDpLTl7mmaK7veeJmoDg&amp;oe=6A965E70</t>
+          <t>https://img.zumpercdn.com/478699409/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9936,27 +9936,27 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové (2 chambres fermées), 2 balcons - secteur rue Saint-Hubert (Rosemont/Petite-Patrie), à 7 min des métros Beaubien/Rosemont</t>
+          <t>4½ dernier étage rénové, 1000 pi², terrasse sur toit - Villeray (secteur parc Jarry / marché Jean-Talon)</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>n/d (parallèle à la rue Saint-Hubert, Montréal, QC)</t>
+          <t>n/d (secteur parc Jarry / marché Jean-Talon, Montréal, QC H2P 2K8)</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -9966,12 +9966,12 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Beaubien ou Rosemont</t>
+          <t>Jarry / De Castelnau (estimé)</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
@@ -9981,39 +9981,39 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N110" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/stunning-top-flr-2-bed-condo-w-terrace-garage-in-villeray/1742601711</t>
+        </is>
+      </c>
+      <c r="O110" s="5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M110" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N110" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/4167517746725690</t>
-        </is>
-      </c>
-      <c r="O110" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="P110" s="6" t="inlineStr">
         <is>
-          <t>3e étage d'un triplex, électroménagers inclus, jardin arrière partagé, hydro et internet aux frais du locataire, disponible 1er août 2026, quartier commerçant (rue Saint-Hubert : épiceries, boulangeries, cafés, pharmacies), proche Marché Jean-Talon et piste cyclable Bellechasse. Lien Facebook (connexion requise).</t>
+          <t>Terrasse privée surdimensionnée sur le toit, fenêtres plafond-plancher, garage, animaux acceptés sous approbation, disponible 1er novembre 2026. Adresse exacte non précisée dans l'annonce; station de métro estimée à partir du quartier (à proximité du parc Jarry et du marché Jean-Talon).</t>
         </is>
       </c>
       <c r="Q110" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741918471_996419706360866_1264760828521880651_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=101&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=lwgY2G6n6CwQ7kNvwGms63c&amp;_nc_oc=AdpwgLXJMjwm8FPxn6f3eV7FtN2-awDdlRcOA8q8ItWZD6rFwVfz6PJ8t1sJ1b52ptk&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=3mqp_MbJd1lUY84PpICqVA&amp;_nc_ss=7f2a8&amp;oh=00_AQFUZG61BB0FrytRk2B9yxhaISmm-UeSptdaDjKaD3FE9Q&amp;oe=6A90C6DC</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/32/3264ba99-d383-4d4c-80fa-c34a38923adb?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -10023,32 +10023,32 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (2 chambres), 900 pi², grand balcon arrière + toit - rue d'Iberville (Villeray), à 11 min du métro Jarry</t>
+          <t>5½ (3 chambres fermées), 2 balcons - avenue Gascon (Hochelaga), à 10 min des métros Préfontaine/Frontenac</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>7186, Rue d'Iberville, Montréal, QC</t>
+          <t>n/d (avenue Gascon, Montréal, QC)</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
@@ -10058,27 +10058,27 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Préfontaine / Frontenac</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N111" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
+          <t>https://www.facebook.com/marketplace/item/1034425322444723</t>
         </is>
       </c>
       <c r="O111" s="5" t="inlineStr">
@@ -10088,19 +10088,19 @@
       </c>
       <c r="P111" s="6" t="inlineStr">
         <is>
-          <t>2e étage d'un duplex, cuisine et salle de bain rénovées (printemps 2024), climatisation centrale, branchement laveuse-sécheuse, lave-vaisselle, ruelle verte, non-fumeur, aucun animal, disponible immédiatement, Walk Score 94.</t>
+          <t>3e étage d'un immeuble de 6 logements, balcon avant et balcon arrière, électroménagers inclus (frigo, four, laveuse-sécheuse, lave-vaisselle), climatisation, stationnement gratuit dans la rue, disponible 1er juillet. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/724174498_986451427362791_2354216600396771595_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=A7xuOojioacQ7kNvwEpBjv9&amp;_nc_oc=Adp07rVyCTSdvON_GHUkgtkbTVkyXryWHFnSLtzm7jCgBnHmQa3GYTKbU62tjAqaTFA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=l2iYorXZG5uQ4C0wfNm3Rw&amp;_nc_ss=7f2a8&amp;oh=00_AQF7T5L1qjiWhL38C_g4OheBaQVDpLTl7mmaK7veeJmoDg&amp;oe=6A965E70</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -10110,27 +10110,27 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail - 3½ rénové (2 chambres), 900 pi², 2 balcons - rue Saint-Denis, à 5 min des métros Beaubien et Rosemont (Marketplace)</t>
+          <t>4½ rénové (2 chambres fermées), 2 balcons - secteur rue Saint-Hubert (Rosemont/Petite-Patrie), à 7 min des métros Beaubien/Rosemont</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Rosemont / La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Rue Saint-Denis, Montréal, QC H2S 2R8</t>
+          <t>n/d (parallèle à la rue Saint-Hubert, Montréal, QC)</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Beaubien / Rosemont</t>
+          <t>Beaubien ou Rosemont</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M112" s="5" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="N112" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1594430635360278</t>
+          <t>https://www.facebook.com/marketplace/item/4167517746725690</t>
         </is>
       </c>
       <c r="O112" s="5" t="inlineStr">
@@ -10175,19 +10175,19 @@
       </c>
       <c r="P112" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, rénové 2023, 2 chambres séparées par portes françaises, plafonds 9 pieds, 2 balcons privés (rénovés été 2026), 3e et dernier étage. Électros inclus (cuisinière, réfrigérateur, lave-vaisselle, laveuse-sécheuse, climatisation). Chauffage électrique. Disponible 1er septembre ou 1er octobre 2026, bail existant jusqu'au 30 juin 2027 (renouvelable). Animaux acceptés. Lien Facebook (connexion requise).</t>
+          <t>3e étage d'un triplex, électroménagers inclus, jardin arrière partagé, hydro et internet aux frais du locataire, disponible 1er août 2026, quartier commerçant (rue Saint-Hubert : épiceries, boulangeries, cafés, pharmacies), proche Marché Jean-Talon et piste cyclable Bellechasse. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q112" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/781924721_10175157656315125_2373393678656261387_n.jpg?stp=c250.0.1500.1500a_dst-jpg_tt6&amp;cstp=mx1500x1500&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=smlTrHXjBewQ7kNvwGzuav8&amp;_nc_oc=Adq6D0OVuBNehdV_ceGxPNpGToNi3Apwpx6zAoSi0s06IaSYwQOIiM0J32laMCvzLLM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=l1Sy-42TMfrjsVGJoPoSEw&amp;_nc_ss=7f2a8&amp;oh=00_AQEkqJKuWjMKR1ukvmL7ZT_JTkS0N_tMdgWJqfK0_yG0HA&amp;oe=6A8E78BB</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741918471_996419706360866_1264760828521880651_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=101&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=lwgY2G6n6CwQ7kNvwGms63c&amp;_nc_oc=AdpwgLXJMjwm8FPxn6f3eV7FtN2-awDdlRcOA8q8ItWZD6rFwVfz6PJ8t1sJ1b52ptk&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=3mqp_MbJd1lUY84PpICqVA&amp;_nc_ss=7f2a8&amp;oh=00_AQFUZG61BB0FrytRk2B9yxhaISmm-UeSptdaDjKaD3FE9Q&amp;oe=6A90C6DC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -10197,27 +10197,27 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>4½ - 2 chambres, 2 salles de bain, 1400 pi², près métro Monk (Marketplace)</t>
+          <t>5½ rénové (2 chambres), 900 pi², grand balcon arrière + toit - rue d'Iberville (Villeray), à 11 min du métro Jarry</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Ville-Émard (Sud-Ouest)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>5787 Boulevard Monk, Montréal, QC H4E 3H2</t>
+          <t>7186, Rue d'Iberville, Montréal, QC</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
@@ -10227,32 +10227,32 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Monk</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>10-12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N113" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1747296433138639</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
         </is>
       </c>
       <c r="O113" s="5" t="inlineStr">
@@ -10262,19 +10262,19 @@
       </c>
       <c r="P113" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'en juin 2027 (option de renouvellement), disponible 1er septembre 2026, cuisine/salon a aire ouverte, electromenagers inclus (four, frigo, lave-vaisselle, laveuse-secheuse), stationnement dans la rue. Quartier Ville-Emard, a l'oppose de Hochelaga sur la ligne verte (extremite sud-ouest) - a evaluer selon la tolerance au trajet. Lien Facebook (connexion requise).</t>
+          <t>2e étage d'un duplex, cuisine et salle de bain rénovées (printemps 2024), climatisation centrale, branchement laveuse-sécheuse, lave-vaisselle, ruelle verte, non-fumeur, aucun animal, disponible immédiatement, Walk Score 94.</t>
         </is>
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/763119959_1360376115596175_1743883061212377860_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=T7GmmILLUT4Q7kNvwFZHa-_&amp;_nc_oc=Ado8LpOjL2dU_QC1EwTiwQR2yA-wDv5yvEJwEu21lVdHOIY8h8lXWVBCwULh2LT3vcI&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=sXY3Jdj1CztJ9pZCttdteg&amp;_nc_ss=7f2a8&amp;oh=00_AQHxAILBHiYdpR-XcXz2gH-sLhZD8F9am85nrErRNe09ZA&amp;oe=6A8E0BD4</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -10284,32 +10284,32 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, balcon - avenue Bourbonnière (Vieux-Rosemont / frontière Hochelaga)</t>
+          <t>Cession de bail - 3½ rénové (2 chambres), 900 pi², 2 balcons - rue Saint-Denis, à 5 min des métros Beaubien et Rosemont (Marketplace)</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie (Vieux-Rosemont, frontière Hochelaga-Maisonneuve)</t>
+          <t>Rosemont / La Petite-Patrie</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>5100 Avenue Bourbonnière, app. 6, Montréal, QC H1X 2M8</t>
+          <t>Rue Saint-Denis, Montréal, QC H2S 2R8</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
@@ -10319,27 +10319,27 @@
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaubien / Rosemont</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N114" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/address/5100-ave-bourbonniere-montreal-qc-h1x-2m8-can</t>
+          <t>https://www.facebook.com/marketplace/item/1594430635360278</t>
         </is>
       </c>
       <c r="O114" s="5" t="inlineStr">
@@ -10349,19 +10349,19 @@
       </c>
       <c r="P114" s="6" t="inlineStr">
         <is>
-          <t>Laveuse/sécheuse en unité incluses. Aucun animal accepté. Proche du Stade olympique.</t>
+          <t>Cession de bail, rénové 2023, 2 chambres séparées par portes françaises, plafonds 9 pieds, 2 balcons privés (rénovés été 2026), 3e et dernier étage. Électros inclus (cuisinière, réfrigérateur, lave-vaisselle, laveuse-sécheuse, climatisation). Chauffage électrique. Disponible 1er septembre ou 1er octobre 2026, bail existant jusqu'au 30 juin 2027 (renouvelable). Animaux acceptés. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q114" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/777299734/1280x960?auto=format</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/781924721_10175157656315125_2373393678656261387_n.jpg?stp=c250.0.1500.1500a_dst-jpg_tt6&amp;cstp=mx1500x1500&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=smlTrHXjBewQ7kNvwGzuav8&amp;_nc_oc=Adq6D0OVuBNehdV_ceGxPNpGToNi3Apwpx6zAoSi0s06IaSYwQOIiM0J32laMCvzLLM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=l1Sy-42TMfrjsVGJoPoSEw&amp;_nc_ss=7f2a8&amp;oh=00_AQEkqJKuWjMKR1ukvmL7ZT_JTkS0N_tMdgWJqfK0_yG0HA&amp;oe=6A8E78BB</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -10371,42 +10371,42 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Condo/appartement meublé à louer - rue De Bullion (Plateau, près Prince-Arthur)</t>
+          <t>4½ - 2 chambres, 2 salles de bain, 1400 pi², près métro Monk (Marketplace)</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Émard (Sud-Ouest)</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>3558, Rue De Bullion, Montréal</t>
+          <t>5787 Boulevard Monk, Montréal, QC H4E 3H2</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>oui (balcon privé sur cour intérieure)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Saint-Laurent</t>
+          <t>Monk</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
@@ -10416,17 +10416,17 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N115" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/12966012</t>
+          <t>https://www.facebook.com/marketplace/item/1747296433138639</t>
         </is>
       </c>
       <c r="O115" s="5" t="inlineStr">
@@ -10436,19 +10436,19 @@
       </c>
       <c r="P115" s="6" t="inlineStr">
         <is>
-          <t>Meublé, chauffage/électricité/internet inclus, animaux acceptés sous conditions, non-fumeur, disponible 1er décembre 2026.</t>
+          <t>Cession de bail jusqu'en juin 2027 (option de renouvellement), disponible 1er septembre 2026, cuisine/salon a aire ouverte, electromenagers inclus (four, frigo, lave-vaisselle, laveuse-secheuse), stationnement dans la rue. Quartier Ville-Emard, a l'oppose de Hochelaga sur la ligne verte (extremite sud-ouest) - a evaluer selon la tolerance au trajet. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q115" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA187F2ADDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/763119959_1360376115596175_1743883061212377860_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=T7GmmILLUT4Q7kNvwFZHa-_&amp;_nc_oc=Ado8LpOjL2dU_QC1EwTiwQR2yA-wDv5yvEJwEu21lVdHOIY8h8lXWVBCwULh2LT3vcI&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=sXY3Jdj1CztJ9pZCttdteg&amp;_nc_ss=7f2a8&amp;oh=00_AQHxAILBHiYdpR-XcXz2gH-sLhZD8F9am85nrErRNe09ZA&amp;oe=6A8E0BD4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -10458,27 +10458,27 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>6 1/2 avec cachet ancien, rue Mont-Royal - à 2 min à pied du métro Mont-Royal</t>
+          <t>5½ rénové, balcon - avenue Bourbonnière (Vieux-Rosemont / frontière Hochelaga)</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie (Vieux-Rosemont, frontière Hochelaga-Maisonneuve)</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>n/d (rue Mont-Royal, Montréal, QC H2J 1X1)</t>
+          <t>5100 Avenue Bourbonnière, app. 6, Montréal, QC H1X 2M8</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -10488,32 +10488,32 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M116" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N116" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-mont-royal-6-a-louer-a-2-minutes-a-pied-du-metro-mont/1741701265</t>
+          <t>https://www.zumper.com/address/5100-ave-bourbonniere-montreal-qc-h1x-2m8-can</t>
         </is>
       </c>
       <c r="O116" s="5" t="inlineStr">
@@ -10523,19 +10523,19 @@
       </c>
       <c r="P116" s="6" t="inlineStr">
         <is>
-          <t>6 1/2 avec cachet ancien, double salon (salle a manger) pouvant servir de bureau ou 2e espace fermable, buanderie et rangement inclus, animaux acceptes, non meuble, fumeur exterieur seulement, disponible 1er sept. 2026, Walk/Transit/Bike Score 10/10/10</t>
+          <t>Laveuse/sécheuse en unité incluses. Aucun animal accepté. Proche du Stade olympique.</t>
         </is>
       </c>
       <c r="Q116" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ae/ae03b0ce-4b9a-4f1e-8b34-bdb5d350ac48?rule=kijijica-960-jpg</t>
+          <t>https://img.zumpercdn.com/777299734/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -10545,27 +10545,27 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres fermées), 900 pi² - 18e Avenue (Rosemont), à 5 min du métro Pie-IX</t>
+          <t>Condo/appartement meublé à louer - rue De Bullion (Plateau, près Prince-Arthur)</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>5290, 18e Avenue, app. 2, Montréal</t>
+          <t>3558, Rue De Bullion, Montréal</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui (balcon privé sur cour intérieure)</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX (estimé)</t>
+          <t>Saint-Laurent</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M117" s="5" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="N117" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/22364038</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/12966012</t>
         </is>
       </c>
       <c r="O117" s="5" t="inlineStr">
@@ -10610,19 +10610,19 @@
       </c>
       <c r="P117" s="6" t="inlineStr">
         <is>
-          <t>Immeuble de 1959, cuisine et salle de bain rénovées, entrée laveuse-sécheuse, disponible 1er juillet 2026 (30 jours après acceptation), Walk Score 94, à proximité de la 17e Avenue déjà répertoriée</t>
+          <t>Meublé, chauffage/électricité/internet inclus, animaux acceptés sous conditions, non-fumeur, disponible 1er décembre 2026.</t>
         </is>
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA19725FDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA187F2ADDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -10632,62 +10632,62 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>4½ (2 chambres), 904 pi², grand balcon 151 pi² - chemin de la Côte-Sainte-Catherine (Outremont), à 11 min du métro Édouard-Montpetit</t>
+          <t>6 1/2 avec cachet ancien, rue Mont-Royal - à 2 min à pied du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Outremont</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>55, Chemin de la Côte-Sainte-Catherine, Montréal, QC H2V 2A5</t>
+          <t>n/d (rue Mont-Royal, Montréal, QC H2J 1X1)</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J118" s="5" t="inlineStr">
-        <is>
-          <t>Édouard-Montpetit</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr">
-        <is>
-          <t>bleue</t>
-        </is>
-      </c>
-      <c r="L118" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M118" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N118" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1026611543438786</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-mont-royal-6-a-louer-a-2-minutes-a-pied-du-metro-mont/1741701265</t>
         </is>
       </c>
       <c r="O118" s="5" t="inlineStr">
@@ -10697,19 +10697,19 @@
       </c>
       <c r="P118" s="6" t="inlineStr">
         <is>
-          <t>Hors des 4 quartiers prioritaires (secteur Outremont, près du parc Jeanne-Mance); 11e étage, piscine et sauna, disponible 31 août 2026; lien Facebook (connexion requise)</t>
+          <t>6 1/2 avec cachet ancien, double salon (salle a manger) pouvant servir de bureau ou 2e espace fermable, buanderie et rangement inclus, animaux acceptes, non meuble, fumeur exterieur seulement, disponible 1er sept. 2026, Walk/Transit/Bike Score 10/10/10</t>
         </is>
       </c>
       <c r="Q118" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/763028717_27778713158453060_4923090953497169148_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=z0pKkaHg84YQ7kNvwFCceqW&amp;_nc_oc=AdpeHA8VPvRCR6fziDXUGtwMZ8_I_boPNhjs1mrLk5oJJaTF5isgwjGWNcUMINs1on0&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=QUWVCKgQSZEZTuxprRp-TA&amp;_nc_ss=7f2a8&amp;oh=00_AQHsXcZQXfk8XVMHlEBzdbAuaZU41Ct_0WaCDW8d_EtZfw&amp;oe=6A839BE8</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ae/ae03b0ce-4b9a-4f1e-8b34-bdb5d350ac48?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové (2 chambres, 925 pi²) avec patio privé - avenue De Chateaubriand, Rosemont, à 2 min du métro Rosemont</t>
+          <t>5½ rénové (3 chambres fermées), 900 pi² - 18e Avenue (Rosemont), à 5 min du métro Pie-IX</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -10729,52 +10729,52 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>5661, Avenue De Chateaubriand, Montréal, QC H2S 0B6</t>
+          <t>5290, 18e Avenue, app. 2, Montréal</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Pie-IX (estimé)</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N119" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/address/5661-ave-de-chateaubriand-montreal-qc-h2s-0b6-can</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/22364038</t>
         </is>
       </c>
       <c r="O119" s="5" t="inlineStr">
@@ -10784,19 +10784,19 @@
       </c>
       <c r="P119" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin au dernier étage avec patio privé, 2 salles de bain, table de cuisine/frigo/lave-vaisselle/laveuse-sécheuse et stationnement inclus, vue sur le mont Royal et le Stade olympique, animaux non permis, date de disponibilité négociable.</t>
+          <t>Immeuble de 1959, cuisine et salle de bain rénovées, entrée laveuse-sécheuse, disponible 1er juillet 2026 (30 jours après acceptation), Walk Score 94, à proximité de la 17e Avenue déjà répertoriée</t>
         </is>
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/459982168/1280x960?auto=format</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA19725FDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -10806,52 +10806,52 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres, 975 pi²) semi-meublé rénové - rue Rachel Est, à 6 min du métro Frontenac (Marketplace)</t>
+          <t>4½ (2 chambres), 904 pi², grand balcon 151 pi² - chemin de la Côte-Sainte-Catherine (Outremont), à 11 min du métro Édouard-Montpetit</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Outremont</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>2473, Rue Rachel Est, Montréal, QC H2H 1R9</t>
+          <t>55, Chemin de la Côte-Sainte-Catherine, Montréal, QC H2V 2A5</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Édouard-Montpetit</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>6 (estimé)</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="N120" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/28384964421192516</t>
+          <t>https://www.facebook.com/marketplace/item/1026611543438786</t>
         </is>
       </c>
       <c r="O120" s="5" t="inlineStr">
@@ -10871,19 +10871,19 @@
       </c>
       <c r="P120" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, semi-meublé (électros inclus, meubles optionnels), wifi inclus, thermopompe (chauffage/climatisation), stationnement possible, à quelques pas du parc Baldwin, disponible janvier 2027 (rabais 100$/mois). Balcon non précisé. Lien Facebook (connexion requise).</t>
+          <t>Hors des 4 quartiers prioritaires (secteur Outremont, près du parc Jeanne-Mance); 11e étage, piscine et sauna, disponible 31 août 2026; lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q120" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-ord5-2.xx.fbcdn.net/v/t39.84726-6/729747145_1529652128704746_2446908512688911381_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LA6jZZEZ45oQ7kNvwGRnS2t&amp;_nc_oc=AdrZCuORhD3hALxRgmd10RoTq9JuIZXSg4214VZdOTXsMiakR8xw5tTQbhhgra0l8kY&amp;_nc_zt=14&amp;_nc_ht=scontent-ord5-2.xx&amp;_nc_gid=U_RbhiGiDK3yu5vaRrkfHQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHfBalX_kK8XzlY20u-FNZWV6MBFMNC2Lw_LG6TZMElxQ&amp;oe=6A7FFF35</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/763028717_27778713158453060_4923090953497169148_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=z0pKkaHg84YQ7kNvwFCceqW&amp;_nc_oc=AdpeHA8VPvRCR6fziDXUGtwMZ8_I_boPNhjs1mrLk5oJJaTF5isgwjGWNcUMINs1on0&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=QUWVCKgQSZEZTuxprRp-TA&amp;_nc_ss=7f2a8&amp;oh=00_AQHsXcZQXfk8XVMHlEBzdbAuaZU41Ct_0WaCDW8d_EtZfw&amp;oe=6A839BE8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -10893,32 +10893,32 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Grand 6½ (3 chambres) sur 2 étages avec balcon - rue Joliette, à 1 min du métro Joliette (Marketplace)</t>
+          <t>4½ rénové (2 chambres, 925 pi²) avec patio privé - avenue De Chateaubriand, Rosemont, à 2 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>2160, Rue Joliette, app. 2160, Montréal, QC H1W 3G6</t>
+          <t>5661, Avenue De Chateaubriand, Montréal, QC H2S 0B6</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>925</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -10928,27 +10928,27 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N121" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/27448354598105803</t>
+          <t>https://www.zumper.com/address/5661-ave-de-chateaubriand-montreal-qc-h2s-0b6-can</t>
         </is>
       </c>
       <c r="O121" s="5" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="P121" s="6" t="inlineStr">
         <is>
-          <t>Logement sur 2 niveaux (2e et 3e étage), belle séparation des espaces, cuisinière et frigo inclus, laveuse-sécheuse, chats acceptés, non-fumeur, disponible 1er juillet 2026. Superficie non précisée. Lien Facebook (connexion requise).</t>
+          <t>Unité de coin au dernier étage avec patio privé, 2 salles de bain, table de cuisine/frigo/lave-vaisselle/laveuse-sécheuse et stationnement inclus, vue sur le mont Royal et le Stade olympique, animaux non permis, date de disponibilité négociable.</t>
         </is>
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-ord5-1.xx.fbcdn.net/v/t39.84726-6/706781388_2020210695546568_6789588270194734204_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=7ZaeWa83n9gQ7kNvwErJKHr&amp;_nc_oc=AdqbRAE3vD-VxtsbWYHfC1EasYImUqf4qjOfiZ5xzMSizKYWZQB0dLKm9V8hbEm00EU&amp;_nc_zt=14&amp;_nc_ht=scontent-ord5-1.xx&amp;_nc_gid=hcfDg9CFnn2YrDyR7gvmZg&amp;_nc_ss=7f2a8&amp;oh=00_AQFDb0E3oqQXPs7J5-w19gSbrxjOK-TdHCbGe3cJWADFxw&amp;oe=6A8014A6</t>
+          <t>https://img.zumpercdn.com/459982168/1280x960?auto=format</t>
         </is>
       </c>
     </row>
@@ -10980,32 +10980,32 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>3+1 chambres (1200 pi²) avec sous-sol aménagé et stationnement - avenue De Lorimier, à 6 min du métro D'Iberville</t>
+          <t>5½ (3 chambres, 975 pi²) semi-meublé rénové - rue Rachel Est, à 6 min du métro Frontenac (Marketplace)</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>7183, Avenue De Lorimier, Montréal, QC</t>
+          <t>2473, Rue Rachel Est, Montréal, QC H2H 1R9</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>975</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
@@ -11015,27 +11015,27 @@
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6 (estimé)</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N122" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/19997673</t>
+          <t>https://www.facebook.com/marketplace/item/28384964421192516</t>
         </is>
       </c>
       <c r="O122" s="5" t="inlineStr">
@@ -11045,19 +11045,19 @@
       </c>
       <c r="P122" s="6" t="inlineStr">
         <is>
-          <t>Unité au rez-de-chaussée, sous-sol entièrement aménagé (salle familiale, chambre supplémentaire, rangement, buanderie), 1 place de stationnement incluse, Walk Score 97, libre 1er juillet 2026.</t>
+          <t>Entièrement rénové, semi-meublé (électros inclus, meubles optionnels), wifi inclus, thermopompe (chauffage/climatisation), stationnement possible, à quelques pas du parc Baldwin, disponible janvier 2027 (rabais 100$/mois). Balcon non précisé. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q122" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA12D770DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://scontent-ord5-2.xx.fbcdn.net/v/t39.84726-6/729747145_1529652128704746_2446908512688911381_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LA6jZZEZ45oQ7kNvwGRnS2t&amp;_nc_oc=AdrZCuORhD3hALxRgmd10RoTq9JuIZXSg4214VZdOTXsMiakR8xw5tTQbhhgra0l8kY&amp;_nc_zt=14&amp;_nc_ht=scontent-ord5-2.xx&amp;_nc_gid=U_RbhiGiDK3yu5vaRrkfHQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHfBalX_kK8XzlY20u-FNZWV6MBFMNC2Lw_LG6TZMElxQ&amp;oe=6A7FFF35</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -11067,27 +11067,27 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Grand 3 chambres (6 1/2), 1500 pi² - rue D'Iberville, à 2 min du métro D'Iberville</t>
+          <t>Grand 6½ (3 chambres) sur 2 étages avec balcon - rue Joliette, à 1 min du métro Joliette (Marketplace)</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>7243, Rue D'Iberville, Montréal</t>
+          <t>2160, Rue Joliette, app. 2160, Montréal, QC H1W 3G6</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N123" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/20850170</t>
+          <t>https://www.facebook.com/marketplace/item/27448354598105803</t>
         </is>
       </c>
       <c r="O123" s="5" t="inlineStr">
@@ -11132,19 +11132,19 @@
       </c>
       <c r="P123" s="6" t="inlineStr">
         <is>
-          <t>6.5 pieces, 1 salle de bain, laveuse-secheuse dans la salle de bain, 2e etage, 1 stationnement (allee), disponible immediatement, locataire paie chauffage et electricite</t>
+          <t>Logement sur 2 niveaux (2e et 3e étage), belle séparation des espaces, cuisinière et frigo inclus, laveuse-sécheuse, chats acceptés, non-fumeur, disponible 1er juillet 2026. Superficie non précisée. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA113E9DDDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-ord5-1.xx.fbcdn.net/v/t39.84726-6/706781388_2020210695546568_6789588270194734204_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=7ZaeWa83n9gQ7kNvwErJKHr&amp;_nc_oc=AdqbRAE3vD-VxtsbWYHfC1EasYImUqf4qjOfiZ5xzMSizKYWZQB0dLKm9V8hbEm00EU&amp;_nc_zt=14&amp;_nc_ht=scontent-ord5-1.xx&amp;_nc_gid=hcfDg9CFnn2YrDyR7gvmZg&amp;_nc_ss=7f2a8&amp;oh=00_AQFDb0E3oqQXPs7J5-w19gSbrxjOK-TdHCbGe3cJWADFxw&amp;oe=6A8014A6</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>5½ (2 chambres fermées + bureau fermé), 940 pi², balcons avant/arrière - rue St-André (Villeray), à 8 min du métro Jarry</t>
+          <t>3+1 chambres (1200 pi²) avec sous-sol aménagé et stationnement - avenue De Lorimier, à 6 min du métro D'Iberville</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -11164,52 +11164,52 @@
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>7647, Rue St-André, Montréal</t>
+          <t>7183, Avenue De Lorimier, Montréal, QC</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>8 (estime, ~655 m)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>LogisQuebec</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N124" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l356503</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/19997673</t>
         </is>
       </c>
       <c r="O124" s="5" t="inlineStr">
@@ -11219,15 +11219,19 @@
       </c>
       <c r="P124" s="6" t="inlineStr">
         <is>
-          <t>2e etage de duplex, 2 chambres fermees + bureau ferme, cuisine et salle de bain renovees, 5 electromenagers inclus (frigo/cuisiniere/lave-vaisselle/laveuse/secheuse), thermopompe murale, disponible immediatement. Jean-Talon aussi a ~819 m.</t>
-        </is>
-      </c>
-      <c r="Q124" s="5" t="inlineStr"/>
+          <t>Unité au rez-de-chaussée, sous-sol entièrement aménagé (salle familiale, chambre supplémentaire, rangement, buanderie), 1 place de stationnement incluse, Walk Score 97, libre 1er juillet 2026.</t>
+        </is>
+      </c>
+      <c r="Q124" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA12D770DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -11237,62 +11241,62 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (2 chambres fermées), 900 pi², terrasse et jardin privés - rue Parthenais (Plateau-Mont-Royal), près métro Laurier</t>
+          <t>Grand 3 chambres (6 1/2), 1500 pi² - rue D'Iberville, à 2 min du métro D'Iberville</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>Rue Parthenais (entre Gilford et Saint-Joseph), Montréal, QC H2H 2H1</t>
+          <t>7243, Rue D'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>D'Iberville</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>bleue</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I125" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J125" s="5" t="inlineStr">
-        <is>
-          <t>Laurier</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L125" s="5" t="inlineStr">
-        <is>
-          <t>n/d (estime ~5 min)</t>
-        </is>
-      </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N125" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-apartment-for-rent-plateau-mont-royal/1741275574</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/20850170</t>
         </is>
       </c>
       <c r="O125" s="5" t="inlineStr">
@@ -11302,19 +11306,19 @@
       </c>
       <c r="P125" s="6" t="inlineStr">
         <is>
-          <t>Unite au rez-de-chaussee, terrasse et jardin prives, planchers chauffants en ceramique, climatisation incluse, laveuse-secheuse et lave-vaisselle, 1 place de stationnement incluse, animaux limites, non-fumeur (a l'exterieur seulement), bail 1 an, disponible 15 septembre 2026.</t>
+          <t>6.5 pieces, 1 salle de bain, laveuse-secheuse dans la salle de bain, 2e etage, 1 stationnement (allee), disponible immediatement, locataire paie chauffage et electricite</t>
         </is>
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1b/1bc6359b-fdb1-4b4e-9109-3878085fccf4?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA113E9DDDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -11324,27 +11328,27 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>4½ (2 chambres), 900 pi², terrasse privée sur le toit 250 pi² - Little Burgundy, près métro Lionel-Groulx</t>
+          <t>5½ (2 chambres fermées + bureau fermé), 940 pi², balcons avant/arrière - rue St-André (Villeray), à 8 min du métro Jarry</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Little Burgundy (Sud-Ouest)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur rue Coursol, Little Burgundy, Montréal, QC)</t>
+          <t>7647, Rue St-André, Montréal</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>940</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -11359,27 +11363,27 @@
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Lionel-Groulx</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>verte/orange</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>n/d (à distance de marche selon l'annonce, à vérifier)</t>
+          <t>8 (estime, ~655 m)</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>LogisQuebec</t>
         </is>
       </c>
       <c r="N126" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/904662755497563</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l356503</t>
         </is>
       </c>
       <c r="O126" s="5" t="inlineStr">
@@ -11389,19 +11393,15 @@
       </c>
       <c r="P126" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, unité sur 2 étages, terrasse privée sur le toit 250 pi², stationnement privé, rangement au sous-sol, disponible 1er sept (flexible oct/nov), quartier vivant près du marché Atwater et du canal de Lachine. Lien Facebook (connexion requise).</t>
-        </is>
-      </c>
-      <c r="Q126" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/763119781_10163668641259141_4845600858709766807_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=00vCs5op-58Q7kNvwEiyGYp&amp;_nc_oc=Adrq2AN7ZvI54Evq_silgG6F7nvAHKWbfThbZYy_oUMB4KTLknk8R4uRw2QAdS7wOis&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WTNzzue3SN2xhdBOMdJYfQ&amp;_nc_ss=7f2a8&amp;oh=00_AQF-2Og5jqHllkOYZ5MxIddYDolRkrx71FIESdrtI-4MtQ&amp;oe=6A7B884A</t>
-        </is>
-      </c>
+          <t>2e etage de duplex, 2 chambres fermees + bureau ferme, cuisine et salle de bain renovees, 5 electromenagers inclus (frigo/cuisiniere/lave-vaisselle/laveuse/secheuse), thermopompe murale, disponible immediatement. Jean-Talon aussi a ~819 m.</t>
+        </is>
+      </c>
+      <c r="Q126" s="5" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -11411,27 +11411,27 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>4½ neuf (2 chambres), 970 pi², balcon privé - avenue Christophe-Colomb (Villeray), près métro Jarry</t>
+          <t>5½ rénové (2 chambres fermées), 900 pi², terrasse et jardin privés - rue Parthenais (Plateau-Mont-Royal), près métro Laurier</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>8325, Avenue Christophe-Colomb, Montréal</t>
+          <t>Rue Parthenais (entre Gilford et Saint-Joseph), Montréal, QC H2H 2H1</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
@@ -11456,17 +11456,17 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>n/d (proche selon l'annonce)</t>
+          <t>n/d (estime ~5 min)</t>
         </is>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N127" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8325-avenue-christophe-colomb-1119914</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-apartment-for-rent-plateau-mont-royal/1741275574</t>
         </is>
       </c>
       <c r="O127" s="5" t="inlineStr">
@@ -11476,19 +11476,19 @@
       </c>
       <c r="P127" s="6" t="inlineStr">
         <is>
-          <t>3e etage, construction neuve en beton, climatisation murale, electromenagers inclus, gym et terrasse dans l'immeuble, animaux acceptes, internet optionnel 45$/mois, casier de rangement inclus, disponible 1er septembre 2026.</t>
+          <t>Unite au rez-de-chaussee, terrasse et jardin prives, planchers chauffants en ceramique, climatisation incluse, laveuse-secheuse et lave-vaisselle, 1 place de stationnement incluse, animaux limites, non-fumeur (a l'exterieur seulement), bail 1 an, disponible 15 septembre 2026.</t>
         </is>
       </c>
       <c r="Q127" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202512/1119914/4-1-2-villeray-st-michel-parc-extension-600-15387152.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1b/1bc6359b-fdb1-4b4e-9109-3878085fccf4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -11498,52 +11498,52 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres fermées) - rue Stanley (Centre-Ville), proche métro McGill/Peel</t>
+          <t>4½ (2 chambres), 900 pi², terrasse privée sur le toit 250 pi² - Little Burgundy, près métro Lionel-Groulx</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Ville)</t>
+          <t>Little Burgundy (Sud-Ouest)</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>3445, Rue Stanley, Montréal, QC H3A 1S2</t>
+          <t>n/d (secteur rue Coursol, Little Burgundy, Montréal, QC)</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>McGill ou Peel (estimé)</t>
+          <t>Lionel-Groulx</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>verte/orange</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>n/d (estimé ~5-7 min)</t>
+          <t>n/d (à distance de marche selon l'annonce, à vérifier)</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="N128" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1099078819111347</t>
+          <t>https://www.facebook.com/marketplace/item/904662755497563</t>
         </is>
       </c>
       <c r="O128" s="5" t="inlineStr">
@@ -11563,19 +11563,19 @@
       </c>
       <c r="P128" s="6" t="inlineStr">
         <is>
-          <t>Chauffage et eau chaude inclus, frigo/cuisiniere/lave-vaisselle inclus, buanderie commune, proche universites McGill et Concordia, verification de credit et cote de 650+ exigees, disponible 1er septembre 2026, prix a la limite haute du budget. Quartier centre-ville, ambiance differente de Hochelaga. Lien Facebook (connexion requise).</t>
+          <t>Cession de bail, unité sur 2 étages, terrasse privée sur le toit 250 pi², stationnement privé, rangement au sous-sol, disponible 1er sept (flexible oct/nov), quartier vivant près du marché Atwater et du canal de Lachine. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q128" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/765007869_1039441669002006_4126864308132149977_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=104&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Ac4lqAU-7wgQ7kNvwHATmrB&amp;_nc_oc=AdoQhiIbdtozuD7mMBhW-tahE3fLc9_lrCr4V5BQg5KPT-OmBOfuzgC5FvEfbqZ9U2w&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WT_K7seI-W2XCrgYwGAZUg&amp;_nc_ss=7f2a8&amp;oh=00_AQGlhXodtQok8xQPTYpH6vVTynzUPKFTg_Qq77No4rqTqQ&amp;oe=6A7AC57B</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/763119781_10163668641259141_4845600858709766807_n.jpg?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=00vCs5op-58Q7kNvwEiyGYp&amp;_nc_oc=Adrq2AN7ZvI54Evq_silgG6F7nvAHKWbfThbZYy_oUMB4KTLknk8R4uRw2QAdS7wOis&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WTNzzue3SN2xhdBOMdJYfQ&amp;_nc_ss=7f2a8&amp;oh=00_AQF-2Og5jqHllkOYZ5MxIddYDolRkrx71FIESdrtI-4MtQ&amp;oe=6A7B884A</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf 2 chambres, 970 pi², balcon privé - avenue Christophe-Colomb (Villeray), près métro Jarry</t>
+          <t>4½ neuf (2 chambres), 970 pi², balcon privé - avenue Christophe-Colomb (Villeray), près métro Jarry</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>8325, Avenue Christophe-Colomb, Montréal (H2P 0C3)</t>
+          <t>8325, Avenue Christophe-Colomb, Montréal</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -11630,17 +11630,17 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>n/d (proche selon l'annonce)</t>
         </is>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N129" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-villeray_saint-michel_parc-extension-l356021</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8325-avenue-christophe-colomb-1119914</t>
         </is>
       </c>
       <c r="O129" s="5" t="inlineStr">
@@ -11650,15 +11650,19 @@
       </c>
       <c r="P129" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve en béton, climatiseur mural, gym et terrasse sur le toit dans l'immeuble, internet disponible en sus (45$/mois), animaux permis, disponible immédiatement ; aussi annoncé sur Kijiji et DuProprio (même immeuble qu'une 2e unité de 1054 pi² à 2305$).</t>
-        </is>
-      </c>
-      <c r="Q129" s="5" t="inlineStr"/>
+          <t>3e etage, construction neuve en beton, climatisation murale, electromenagers inclus, gym et terrasse dans l'immeuble, animaux acceptes, internet optionnel 45$/mois, casier de rangement inclus, disponible 1er septembre 2026.</t>
+        </is>
+      </c>
+      <c r="Q129" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202512/1119914/4-1-2-villeray-st-michel-parc-extension-600-15387152.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -11668,62 +11672,62 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres, balcon privé, 1000 pi² - boulevard Rosemont</t>
+          <t>5½ (3 chambres fermées) - rue Stanley (Centre-Ville), proche métro McGill/Peel</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Ville-Marie (Centre-Ville)</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>2041, Boulevard Rosemont, Montréal</t>
+          <t>3445, Rue Stanley, Montréal, QC H3A 1S2</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Rosemont (estimé)</t>
+          <t>McGill ou Peel (estimé)</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>n/d (estimé ~5-7 min)</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N130" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-2041-boulevard-rosemont-1123132</t>
+          <t>https://www.facebook.com/marketplace/item/1099078819111347</t>
         </is>
       </c>
       <c r="O130" s="5" t="inlineStr">
@@ -11733,19 +11737,19 @@
       </c>
       <c r="P130" s="6" t="inlineStr">
         <is>
-          <t>2e étage, cuisine à aire ouverte rénovée, climatisation murale, électroménagers en option (frais additionnels), aucun animal accepté, quartier dynamique et convivial (épiceries/restos/bars/parcs à pied), disponible immédiatement, distance métro Rosemont estimée (non confirmée par l'annonce)</t>
+          <t>Chauffage et eau chaude inclus, frigo/cuisiniere/lave-vaisselle inclus, buanderie commune, proche universites McGill et Concordia, verification de credit et cote de 650+ exigees, disponible 1er septembre 2026, prix a la limite haute du budget. Quartier centre-ville, ambiance differente de Hochelaga. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202602/1123132/4-1-2-rosemont-petite-patrie-600-15473164.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/765007869_1039441669002006_4126864308132149977_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=104&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Ac4lqAU-7wgQ7kNvwHATmrB&amp;_nc_oc=AdoQhiIbdtozuD7mMBhW-tahE3fLc9_lrCr4V5BQg5KPT-OmBOfuzgC5FvEfbqZ9U2w&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WT_K7seI-W2XCrgYwGAZUg&amp;_nc_ss=7f2a8&amp;oh=00_AQGlhXodtQok8xQPTYpH6vVTynzUPKFTg_Qq77No4rqTqQ&amp;oe=6A7AC57B</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -11755,62 +11759,62 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées, 1030 pi² - rue Joliette (Hochelaga-Maisonneuve, proche métro Joliette)</t>
+          <t>Condo neuf 2 chambres, 970 pi², balcon privé - avenue Christophe-Colomb (Villeray), près métro Jarry</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>1679 Rue Joliette, Montréal, QC</t>
+          <t>8325, Avenue Christophe-Colomb, Montréal (H2P 0C3)</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>970</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N131" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-mercier-hochelaga-maisonneuve/19180102</t>
+          <t>https://www.logisquebec.com/condo-a-louer-villeray_saint-michel_parc-extension-l356021</t>
         </is>
       </c>
       <c r="O131" s="5" t="inlineStr">
@@ -11820,19 +11824,15 @@
       </c>
       <c r="P131" s="6" t="inlineStr">
         <is>
-          <t>Construit en 1935, Walk Score 98, proximité métro, parc, piste cyclable, garderie et école secondaire, animaux acceptés sous conditions, non-fumeur, dispo 1er août 2026, balcon non mentionné dans la fiche, station de métro estimée à partir du nom de la rue</t>
-        </is>
-      </c>
-      <c r="Q131" s="5" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1B1EF9DDDDDDDDDD1&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
-        </is>
-      </c>
+          <t>Construction neuve en béton, climatiseur mural, gym et terrasse sur le toit dans l'immeuble, internet disponible en sus (45$/mois), animaux permis, disponible immédiatement ; aussi annoncé sur Kijiji et DuProprio (même immeuble qu'une 2e unité de 1054 pi² à 2305$).</t>
+        </is>
+      </c>
+      <c r="Q131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -11842,27 +11842,27 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres fermées, balcon, 950 pi² - Mile-End (Plateau), à ~10 min du métro Outremont</t>
+          <t>4½ rénové, 2 chambres, balcon privé, 1000 pi² - boulevard Rosemont</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>5970, Avenue du Parc, app. 7, Montréal</t>
+          <t>2041, Boulevard Rosemont, Montréal</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -11877,17 +11877,17 @@
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Outremont</t>
+          <t>Rosemont (estimé)</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>10 (estime, non precise par l'annonce)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="N132" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/en/rental/montreal/le-plateau-mont-royal/4-1-2-for-rent/hab-7-5970-ave-du-parc-1138366</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-2041-boulevard-rosemont-1123132</t>
         </is>
       </c>
       <c r="O132" s="5" t="inlineStr">
@@ -11907,19 +11907,19 @@
       </c>
       <c r="P132" s="6" t="inlineStr">
         <is>
-          <t>Dernier etage (3e), semi-meuble, stationnement exterieur inclus, disponible 1er septembre 2026. Secteur Mile-End (bordure Plateau/Outremont), distance au metro estimee.</t>
+          <t>2e étage, cuisine à aire ouverte rénovée, climatisation murale, électroménagers en option (frais additionnels), aucun animal accepté, quartier dynamique et convivial (épiceries/restos/bars/parcs à pied), disponible immédiatement, distance métro Rosemont estimée (non confirmée par l'annonce)</t>
         </is>
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1138366/4-1-2-plateau-mont-royal-1600-15812906.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202602/1123132/4-1-2-rosemont-petite-patrie-600-15473164.jpg</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Grand logement de 4 chambres fermées, terrasse ~1100 pi² - rue Ontario Est (Hochelaga-Maisonneuve, entre métro Pie-IX et Joliette)</t>
+          <t>3 chambres fermées, 1030 pi² - rue Joliette (Hochelaga-Maisonneuve, proche métro Joliette)</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -11939,27 +11939,27 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>3889, rue Ontario Est, Montréal</t>
+          <t>1679 Rue Joliette, Montréal, QC</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
@@ -11974,17 +11974,17 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N133" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/3191099554424215</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-mercier-hochelaga-maisonneuve/19180102</t>
         </is>
       </c>
       <c r="O133" s="5" t="inlineStr">
@@ -11994,19 +11994,19 @@
       </c>
       <c r="P133" s="6" t="inlineStr">
         <is>
-          <t>4 chambres fermées, situé au 2e étage, aucun locataire en dessous, grande terrasse ~1100 pi² (superficie intérieure non précisée), dispo 1er juillet 2026. Walk Score 98/Transit 72. Lien Facebook (connexion requise).</t>
+          <t>Construit en 1935, Walk Score 98, proximité métro, parc, piste cyclable, garderie et école secondaire, animaux acceptés sous conditions, non-fumeur, dispo 1er août 2026, balcon non mentionné dans la fiche, station de métro estimée à partir du nom de la rue</t>
         </is>
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/734367592_37516698021250688_9048995181085965231_n.jpg?stp=c0.273.1206.1206a_dst-jpg_tt6&amp;cstp=mx1206x1206&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=nR4bexDdA7kQ7kNvwETwXRu&amp;_nc_oc=Adr8b_ZPIzcfgyLtbIjdkZ5tD3NsD-JGZbJKl6RPXDVY72qwup6OtDttajaoVBxtwXs&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DKAPrnNgmI9udtZ3TamYHQ&amp;_nc_ss=7f2a8&amp;oh=00_AQB-a9NpI4qTkrXbihGbIld6aXJDIH_w-iC6HuVrESJzYg&amp;oe=6A6BCFE1</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1B1EF9DDDDDDDDDD1&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 950 pi², balcon avant + terrasse arrière privée - rue St-Joseph Est (Plateau, près parc Laurier)</t>
+          <t>4½ rénové, 2 chambres fermées, balcon, 950 pi² - Mile-End (Plateau), à ~10 min du métro Outremont</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>1570, rue St-Joseph Est, Montréal</t>
+          <t>5970, Avenue du Parc, app. 7, Montréal</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -12051,17 +12051,17 @@
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Outremont</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé, incertain)</t>
+          <t>10 (estime, non precise par l'annonce)</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="N134" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/4-1-2-a-louer/hab-1570-stjoseph-est-1119590</t>
+          <t>https://duproprio.com/en/rental/montreal/le-plateau-mont-royal/4-1-2-for-rent/hab-7-5970-ave-du-parc-1138366</t>
         </is>
       </c>
       <c r="O134" s="5" t="inlineStr">
@@ -12081,19 +12081,19 @@
       </c>
       <c r="P134" s="6" t="inlineStr">
         <is>
-          <t>Planchers de bois franc, comptoirs de granit, cuisine à îlot, disponible maintenant. Distance réelle au métro Laurier non confirmée par l'annonce, possiblement proche de la limite de 12 min - à vérifier avant de contacter.</t>
+          <t>Dernier etage (3e), semi-meuble, stationnement exterieur inclus, disponible 1er septembre 2026. Secteur Mile-End (bordure Plateau/Outremont), distance au metro estimee.</t>
         </is>
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202512/1119590/plateau-mont-royal-600-15379636.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1138366/4-1-2-plateau-mont-royal-1600-15812906.jpg</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
@@ -12103,32 +12103,32 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>2 chambres avec balcon, immeuble rénové - rue Iberville (Villeray/Parc-Ex), à 1 min du métro d'Iberville</t>
+          <t>Grand logement de 4 chambres fermées, terrasse ~1100 pi² - rue Ontario Est (Hochelaga-Maisonneuve, entre métro Pie-IX et Joliette)</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>7186, Rue Iberville, Montréal</t>
+          <t>3889, rue Ontario Est, Montréal</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
@@ -12138,27 +12138,27 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M135" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N135" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-iberville-1132385</t>
+          <t>https://www.facebook.com/marketplace/item/3191099554424215</t>
         </is>
       </c>
       <c r="O135" s="5" t="inlineStr">
@@ -12168,19 +12168,19 @@
       </c>
       <c r="P135" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové (2024), plancher chauffant salle de bain, grand balcon arrière couvert, aucun animal, Walk Score 94, disponible 1er juillet 2026</t>
+          <t>4 chambres fermées, situé au 2e étage, aucun locataire en dessous, grande terrasse ~1100 pi² (superficie intérieure non précisée), dispo 1er juillet 2026. Walk Score 98/Transit 72. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q135" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132385/villeray-st-michel-parc-extension-600-15662542.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/734367592_37516698021250688_9048995181085965231_n.jpg?stp=c0.273.1206.1206a_dst-jpg_tt6&amp;cstp=mx1206x1206&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=nR4bexDdA7kQ7kNvwETwXRu&amp;_nc_oc=Adr8b_ZPIzcfgyLtbIjdkZ5tD3NsD-JGZbJKl6RPXDVY72qwup6OtDttajaoVBxtwXs&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DKAPrnNgmI9udtZ3TamYHQ&amp;_nc_ss=7f2a8&amp;oh=00_AQB-a9NpI4qTkrXbihGbIld6aXJDIH_w-iC6HuVrESJzYg&amp;oe=6A6BCFE1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -12190,42 +12190,42 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>3 chambres (950 pi²), balcon - rue St-Viateur Est (Mile-End/Rosemont), à 9 min du métro Rosemont</t>
+          <t>4½ rénové, 950 pi², balcon avant + terrasse arrière privée - rue St-Joseph Est (Plateau, près parc Laurier)</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>81, Rue Saint-Viateur Est, Montréal</t>
+          <t>1570, rue St-Joseph Est, Montréal</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
@@ -12235,17 +12235,17 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12 (estimé, incertain)</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N136" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/address/81-rue-saint-viateur-e-montreal-qc-h2t-1a7-can</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/4-1-2-a-louer/hab-1570-stjoseph-est-1119590</t>
         </is>
       </c>
       <c r="O136" s="5" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="P136" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement rénovée, comptoirs de quartz, planchers de terrazzo/parquet restaurés, chaque chambre a son placard, animaux acceptés</t>
+          <t>Planchers de bois franc, comptoirs de granit, cuisine à îlot, disponible maintenant. Distance réelle au métro Laurier non confirmée par l'annonce, possiblement proche de la limite de 12 min - à vérifier avant de contacter.</t>
         </is>
       </c>
       <c r="Q136" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/327063905/1280x960?auto=format</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202512/1119590/plateau-mont-royal-600-15379636.jpg</t>
         </is>
       </c>
     </row>
@@ -12277,32 +12277,32 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>3 chambres avec terrasse sur cour intérieure - rue De Bullion (Plateau), à 9 min du métro Saint-Laurent</t>
+          <t>2 chambres avec balcon, immeuble rénové - rue Iberville (Villeray/Parc-Ex), à 1 min du métro d'Iberville</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>3560, Rue De Bullion, Montréal</t>
+          <t>7186, Rue Iberville, Montréal</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
@@ -12312,27 +12312,27 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Saint-Laurent</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M137" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N137" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/15238222</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-iberville-1132385</t>
         </is>
       </c>
       <c r="O137" s="5" t="inlineStr">
@@ -12342,19 +12342,19 @@
       </c>
       <c r="P137" s="6" t="inlineStr">
         <is>
-          <t>Meublé, chauffage/internet/électricité inclus, secteur Prince-Arthur/Saint-Denis, immeuble de 1845, Walk Score 100</t>
+          <t>Entièrement rénové (2024), plancher chauffant salle de bain, grand balcon arrière couvert, aucun animal, Walk Score 94, disponible 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1848FBDDDDDDDDDD2&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132385/villeray-st-michel-parc-extension-600-15662542.jpg</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -12364,22 +12364,22 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>4½ meublé de 1100 pi², 2 chambres - rue Hochelaga (Hochelaga-Maisonneuve, près métro Pie-IX)</t>
+          <t>3 chambres (950 pi²), balcon - rue St-Viateur Est (Mile-End/Rosemont), à 9 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>4229, Rue Hochelaga, app. 101, Montréal</t>
+          <t>81, Rue Saint-Viateur Est, Montréal</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
@@ -12399,27 +12399,27 @@
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N138" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/12213167</t>
+          <t>https://www.zumper.com/address/81-rue-saint-viateur-e-montreal-qc-h2t-1a7-can</t>
         </is>
       </c>
       <c r="O138" s="5" t="inlineStr">
@@ -12429,19 +12429,19 @@
       </c>
       <c r="P138" s="6" t="inlineStr">
         <is>
-          <t>Meublé, électricité et wifi inclus, animaux non acceptés, disponible 22 août 2026, à quelques minutes à pied du métro Pie-IX (limite est autorisée)</t>
+          <t>Unité de coin entièrement rénovée, comptoirs de quartz, planchers de terrazzo/parquet restaurés, chaque chambre a son placard, animaux acceptés</t>
         </is>
       </c>
       <c r="Q138" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE55732ADDDDDDDDDDB&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://img.zumpercdn.com/327063905/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -12451,32 +12451,32 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové avec balcons avant et arrière - rue Chambord (Villeray, près métro Fabre)</t>
+          <t>3 chambres avec terrasse sur cour intérieure - rue De Bullion (Plateau), à 9 min du métro Saint-Laurent</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>7572 Rue Chambord, Montréal</t>
+          <t>3560, Rue De Bullion, Montréal</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
@@ -12486,27 +12486,27 @@
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Saint-Laurent</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M139" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N139" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7572-chambord-1133371</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/15238222</t>
         </is>
       </c>
       <c r="O139" s="5" t="inlineStr">
@@ -12516,19 +12516,19 @@
       </c>
       <c r="P139" s="6" t="inlineStr">
         <is>
-          <t>Haut de duplex construit en 1950, planchers de bois franc et boiseries d'origine, semi-meublé (cuisinière, frigo, laveuse-sécheuse inclus), animaux non acceptés, un mois de crédit à la reconduction du bail, disponible maintenant/1er août</t>
+          <t>Meublé, chauffage/internet/électricité inclus, secteur Prince-Arthur/Saint-Denis, immeuble de 1845, Walk Score 100</t>
         </is>
       </c>
       <c r="Q139" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1133371/villeray-st-michel-parc-extension-600-15687060.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1848FBDDDDDDDDDD2&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -12538,27 +12538,27 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 2 chambres, 2 terrasses privées - rue Beaubien Est (Rosemont, près métro Fabre)</t>
+          <t>4½ meublé de 1100 pi², 2 chambres - rue Hochelaga (Hochelaga-Maisonneuve, près métro Pie-IX)</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>5375, Rue Beaubien Est, app. 302, Montréal</t>
+          <t>4229, Rue Hochelaga, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -12568,22 +12568,22 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="N140" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/18351984</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/12213167</t>
         </is>
       </c>
       <c r="O140" s="5" t="inlineStr">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="P140" s="6" t="inlineStr">
         <is>
-          <t>973 pi², 3e étage, deux terrasses ensoleillées privées, walk score 83, animaux acceptés avec conditions, stationnement allée + rangement extérieur, construit en 2006, non-fumeur, dispo ~15 jours après acceptation</t>
+          <t>Meublé, électricité et wifi inclus, animaux non acceptés, disponible 22 août 2026, à quelques minutes à pied du métro Pie-IX (limite est autorisée)</t>
         </is>
       </c>
       <c r="Q140" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA447553DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE55732ADDDDDDDDDDB&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, 2 balcons + terrasse sur le toit - 13e Avenue (Villeray, près métro Saint-Michel)</t>
+          <t>5½ rénové avec balcons avant et arrière - rue Chambord (Villeray, près métro Fabre)</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -12635,17 +12635,17 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>7650, 13e Avenue, app. 302, Montréal</t>
+          <t>7572 Rue Chambord, Montréal</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>940</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
@@ -12670,39 +12670,39 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M141" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N141" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7572-chambord-1133371</t>
+        </is>
+      </c>
+      <c r="O141" s="5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M141" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N141" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/9733212</t>
-        </is>
-      </c>
-      <c r="O141" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="P141" s="6" t="inlineStr">
         <is>
-          <t>1000 pi², 2 balcons + terrasse privée sur le toit (en rénovation, dispo été 2026), comptoirs de quartz, 2 garde-robes, système d'alarme, construit en 2011, animaux non acceptés, près du parc François-Perrault, dispo 1er mai 2026</t>
+          <t>Haut de duplex construit en 1950, planchers de bois franc et boiseries d'origine, semi-meublé (cuisinière, frigo, laveuse-sécheuse inclus), animaux non acceptés, un mois de crédit à la reconduction du bail, disponible maintenant/1er août</t>
         </is>
       </c>
       <c r="Q141" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE699961DDDDDDDDDD0&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1133371/villeray-st-michel-parc-extension-600-15687060.jpg</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -12712,27 +12712,27 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové 2024, balcon arrière avec toit - rue d'Iberville (Villeray), à deux pas du métro</t>
+          <t>Grand 5 1/2, 2 chambres, 2 terrasses privées - rue Beaubien Est (Rosemont, près métro Fabre)</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>7186 Rue d'Iberville, Montréal</t>
+          <t>5375, Rue Beaubien Est, app. 302, Montréal</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>973</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N142" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/18351984</t>
         </is>
       </c>
       <c r="O142" s="5" t="inlineStr">
@@ -12777,19 +12777,19 @@
       </c>
       <c r="P142" s="6" t="inlineStr">
         <is>
-          <t>Rénové au complet printemps 2024, cuisine neuve comptoirs quartz, salle de bain avec plancher chauffant, 2e étage duplex, animaux non permis, dispo immédiatement, climatisation</t>
+          <t>973 pi², 3e étage, deux terrasses ensoleillées privées, walk score 83, animaux acceptés avec conditions, stationnement allée + rangement extérieur, construit en 2006, non-fumeur, dispo ~15 jours après acceptation</t>
         </is>
       </c>
       <c r="Q142" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA447553DDDDDDDDDDC&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -12799,17 +12799,17 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
+          <t>4 1/2 rénové, 2 balcons + terrasse sur le toit - 13e Avenue (Villeray, près métro Saint-Michel)</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud/Village)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
+          <t>7650, 13e Avenue, app. 302, Montréal</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
@@ -12819,12 +12819,12 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
@@ -12834,27 +12834,27 @@
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Papineau ou Beaudry</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M143" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N143" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/9733212</t>
         </is>
       </c>
       <c r="O143" s="5" t="inlineStr">
@@ -12864,19 +12864,19 @@
       </c>
       <c r="P143" s="6" t="inlineStr">
         <is>
-          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
+          <t>1000 pi², 2 balcons + terrasse privée sur le toit (en rénovation, dispo été 2026), comptoirs de quartz, 2 garde-robes, système d'alarme, construit en 2011, animaux non acceptés, près du parc François-Perrault, dispo 1er mai 2026</t>
         </is>
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE699961DDDDDDDDDD0&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -12886,32 +12886,32 @@
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
+          <t>5½ rénové 2024, balcon arrière avec toit - rue d'Iberville (Villeray), à deux pas du métro</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>3845 rue Hochelaga (H1W 1J5)</t>
+          <t>7186 Rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
@@ -12921,27 +12921,27 @@
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N144" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
         </is>
       </c>
       <c r="O144" s="5" t="inlineStr">
@@ -12951,19 +12951,19 @@
       </c>
       <c r="P144" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
+          <t>Rénové au complet printemps 2024, cuisine neuve comptoirs quartz, salle de bain avec plancher chauffant, 2e étage duplex, animaux non permis, dispo immédiatement, climatisation</t>
         </is>
       </c>
       <c r="Q144" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -12973,32 +12973,32 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
+          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Centre-Sud/Village)</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>5048 rue Rivard (H2J 2M9)</t>
+          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I145" s="5" t="inlineStr">
@@ -13008,17 +13008,17 @@
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Papineau ou Beaudry</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M145" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="N145" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
+          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
         </is>
       </c>
       <c r="O145" s="5" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="P145" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
+          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
         </is>
       </c>
     </row>
@@ -13060,27 +13060,27 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
+          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
+          <t>3845 rue Hochelaga (H1W 1J5)</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
@@ -13090,22 +13090,22 @@
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M146" s="5" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="N146" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
+          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
         </is>
       </c>
       <c r="O146" s="5" t="inlineStr">
@@ -13125,19 +13125,19 @@
       </c>
       <c r="P146" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
+          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q146" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
@@ -13147,27 +13147,27 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>5048 rue Rivard (H2J 2M9)</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -13182,27 +13182,27 @@
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M147" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N147" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
+          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
         </is>
       </c>
       <c r="O147" s="5" t="inlineStr">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="P147" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
+          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
@@ -13244,52 +13244,52 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>8478 Rue Saint-Dominique, Montréal</t>
+          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
         <is>
-          <t>Jarry ou Crémazie</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N148" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
         </is>
       </c>
       <c r="O148" s="5" t="inlineStr">
@@ -13299,19 +13299,19 @@
       </c>
       <c r="P148" s="6" t="inlineStr">
         <is>
-          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
+          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q148" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
@@ -13321,27 +13321,27 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ (2 chambres fermées + bureau), balcon + terrasse - Hochelaga-Maisonneuve, à 10 min du métro Préfontaine</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2)</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -13356,49 +13356,49 @@
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K149" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M149" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N149" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-a-hochelaga-parking-terrasse-2-195-dispo/1739376269</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O149" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P149" s="6" t="inlineStr">
         <is>
-          <t>2e étage (dernier étage), balcon à l'avant et grande terrasse à l'arrière, hydro inclus, stationnement inclus, animaux acceptés (chiens compris), climatisé, disponible 1er août 2026, bail jusqu'en juin 2027 (cession), proche rue Ontario et Promenades Ontario. Superficie non précisée.</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q149" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -13408,27 +13408,27 @@
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 meublé, 2 chambres, 2 salles de bain, terrasse - rue Nicolet (Hochelaga), à 6 min du métro Joliette</t>
+          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>2113, Rue Nicolet, Montréal, QC H1W 3L3</t>
+          <t>8478 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -13443,49 +13443,49 @@
       </c>
       <c r="J150" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry ou Crémazie</t>
         </is>
       </c>
       <c r="K150" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M150" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N150" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambres-et-2-salles-de-bain/1742905541</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
         </is>
       </c>
       <c r="O150" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P150" s="6" t="inlineStr">
         <is>
-          <t>Totalement meuble, tous electromenagers et mobilier inclus, climatisation, internet inclus, 1 stationnement, animaux limites, disponible 1er octobre 2026, bail jusqu'au 30 sept 2027, electricite en sus (~100$/mois).</t>
+          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
         </is>
       </c>
       <c r="Q150" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/7a/7a00a15f-431e-41d1-86e4-c73116cdc2dc?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
@@ -13495,27 +13495,27 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 meublé de luxe, 2 chambres, 1050 pi² - rue Saint-Denis (Plateau), à ~8 min du métro Mont-Royal</t>
+          <t>Grand 5½ (2 chambres fermées + bureau), balcon + terrasse - Hochelaga-Maisonneuve, à 10 min du métro Préfontaine</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>4055, Rue Saint-Denis, Montréal, QC</t>
+          <t>n/d (Montréal, QC H1V 2X2)</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr">
@@ -13540,17 +13540,17 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M151" s="5" t="inlineStr">
         <is>
-          <t>logisquebec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N151" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l348152</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-a-hochelaga-parking-terrasse-2-195-dispo/1739376269</t>
         </is>
       </c>
       <c r="O151" s="5" t="inlineStr">
@@ -13560,15 +13560,19 @@
       </c>
       <c r="P151" s="6" t="inlineStr">
         <is>
-          <t>Condo meuble de prestige, coin de rue avec vues sur Saint-Denis, 2 salles de bain completes, plafonds 12 pi, internet fibre 1 Gbps, climatisation, chauffage et electricite inclus, stationnement prive, animaux acceptes, disponible immediatement.</t>
-        </is>
-      </c>
-      <c r="Q151" s="5" t="inlineStr"/>
+          <t>2e étage (dernier étage), balcon à l'avant et grande terrasse à l'arrière, hydro inclus, stationnement inclus, animaux acceptés (chiens compris), climatisé, disponible 1er août 2026, bail jusqu'en juin 2027 (cession), proche rue Ontario et Promenades Ontario. Superficie non précisée.</t>
+        </is>
+      </c>
+      <c r="Q151" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -13578,27 +13582,27 @@
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>2 chambres meublé, 1130 pi² - rue Saint-Zotique Est (Rosemont-La Petite-Patrie), à 6 min du métro Beaubien</t>
+          <t>4 1/2 meublé, 2 chambres, 2 salles de bain, terrasse - rue Nicolet (Hochelaga), à 6 min du métro Joliette</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>2356, Rue Saint-Zotique Est, Montréal</t>
+          <t>2113, Rue Nicolet, Montréal, QC H1W 3L3</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
@@ -13608,32 +13612,32 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>6 (estimé)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N152" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21588368</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambres-et-2-salles-de-bain/1742905541</t>
         </is>
       </c>
       <c r="O152" s="5" t="inlineStr">
@@ -13643,19 +13647,19 @@
       </c>
       <c r="P152" s="6" t="inlineStr">
         <is>
-          <t>Meublé avec 3 puits de lumière, climatisation, internet et chauffage inclus, idéal télétravail, disponible 1er octobre 2026, pas d'animaux mentionnés. Balcon non mentionné.</t>
+          <t>Totalement meuble, tous electromenagers et mobilier inclus, climatisation, internet inclus, 1 stationnement, animaux limites, disponible 1er octobre 2026, bail jusqu'au 30 sept 2027, electricite en sus (~100$/mois).</t>
         </is>
       </c>
       <c r="Q152" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1FD202DDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/7a/7a00a15f-431e-41d1-86e4-c73116cdc2dc?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
@@ -13665,7 +13669,7 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres), ~1076 pi² — boulevard Saint-Joseph Est (Plateau), à 10 min du métro Laurier</t>
+          <t>4 1/2 meublé de luxe, 2 chambres, 1050 pi² - rue Saint-Denis (Plateau), à ~8 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -13675,22 +13679,22 @@
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>1260A, Boulevard Saint-Joseph Est, Montréal</t>
+          <t>4055, Rue Saint-Denis, Montréal, QC</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I153" s="5" t="inlineStr">
@@ -13700,27 +13704,27 @@
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>logisquebec</t>
         </is>
       </c>
       <c r="N153" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/12989624</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l348152</t>
         </is>
       </c>
       <c r="O153" s="5" t="inlineStr">
@@ -13730,19 +13734,15 @@
       </c>
       <c r="P153" s="6" t="inlineStr">
         <is>
-          <t>Environ 100 m² (~1076 pi²), électroménagers inclus, animaux acceptés, disponible 1er septembre 2026, Walk Score 99.</t>
-        </is>
-      </c>
-      <c r="Q153" s="5" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2437FCDDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
+          <t>Condo meuble de prestige, coin de rue avec vues sur Saint-Denis, 2 salles de bain completes, plafonds 12 pi, internet fibre 1 Gbps, climatisation, chauffage et electricite inclus, stationnement prive, animaux acceptes, disponible immediatement.</t>
+        </is>
+      </c>
+      <c r="Q153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ ensoleillé (3 chambres), balcon - coin Saint-André/Bellechasse (Petite-Patrie), à 6 min du métro Beaubien</t>
+          <t>2 chambres meublé, 1130 pi² - rue Saint-Zotique Est (Rosemont-La Petite-Patrie), à 6 min du métro Beaubien</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
@@ -13762,27 +13762,27 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>n/d (coin Saint-André et Bellechasse, Montréal, QC H2S 2K4)</t>
+          <t>2356, Rue Saint-Zotique Est, Montréal</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
@@ -13797,39 +13797,39 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
+          <t>6 (estimé)</t>
+        </is>
+      </c>
+      <c r="M154" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N154" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21588368</t>
+        </is>
+      </c>
+      <c r="O154" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M154" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N154" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-appartement-5-ensoleille-rosemont-petite-patrie/1742222174</t>
-        </is>
-      </c>
-      <c r="O154" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="P154" s="6" t="inlineStr">
         <is>
-          <t>Balcon accessible depuis une chambre, four/cuisinière/lave-vaisselle/frigo/laveuse-sécheuse inclus, électricité et wifi non inclus (~100$/50$ estimés), animaux acceptés, disponible 1er oct. 2026 (dates négociables), aussi à 8 min du métro Rosemont.</t>
+          <t>Meublé avec 3 puits de lumière, climatisation, internet et chauffage inclus, idéal télétravail, disponible 1er octobre 2026, pas d'animaux mentionnés. Balcon non mentionné.</t>
         </is>
       </c>
       <c r="Q154" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c9/c94ec64e-8bbe-4c89-a24b-db48bcd3657c?rule=kijijica-640-webp</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1FD202DDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
@@ -13839,32 +13839,32 @@
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>5½ tout meublé (2 grandes chambres), 1200 pi² - rue Saint-Dominique (Villeray/Petite Italie), à 5 min des métros Castelnau/Beaubien — bail 9 mois non renouvelable</t>
+          <t>5½ (3 chambres), ~1076 pi² — boulevard Saint-Joseph Est (Plateau), à 10 min du métro Laurier</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>6723, Rue Saint-Dominique, Montréal, QC</t>
+          <t>1260A, Boulevard Saint-Joseph Est, Montréal</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I155" s="5" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Castelnau ou Beaubien</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr">
@@ -13884,17 +13884,17 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M155" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N155" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-6723-rue-saint-dominique-1114557</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/12989624</t>
         </is>
       </c>
       <c r="O155" s="5" t="inlineStr">
@@ -13904,19 +13904,19 @@
       </c>
       <c r="P155" s="6" t="inlineStr">
         <is>
-          <t>ATTENTION: bail de 9 mois non renouvelable (1er oct. 2026 au 30 juin 2027), tout meublé, électricité incluse, grande cour arrière privée avec jardin, sous-sol avec laveuse-sécheuse et rangement, rez-de-chaussée d'un triplex dans la Petite Italie.</t>
+          <t>Environ 100 m² (~1076 pi²), électroménagers inclus, animaux acceptés, disponible 1er septembre 2026, Walk Score 99.</t>
         </is>
       </c>
       <c r="Q155" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202509/1114557/5-1-2-villeray-st-michel-parc-extension-600-15245084.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2437FCDDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -13926,17 +13926,17 @@
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>5½ ensoleillé (3 chambres), balcon - Rosemont/Petite-Patrie (secteur Saint-André/Bellechasse), à 6-8 min des métros Beaubien/Rosemont</t>
+          <t>5½ tout meublé (2 grandes chambres), 1200 pi² - rue Saint-Dominique (Villeray/Petite Italie), à 5 min des métros Castelnau/Beaubien — bail 9 mois non renouvelable</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Rosemont / La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Saint-André/Bellechasse, Montréal, QC H2S 2K4)</t>
+          <t>6723, Rue Saint-Dominique, Montréal, QC</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
@@ -13946,22 +13946,22 @@
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Castelnau ou Beaubien</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr">
@@ -13971,17 +13971,17 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N156" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-appartement-5-ensoleille-rosemont-petite-patrie/1742222174</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-6723-rue-saint-dominique-1114557</t>
         </is>
       </c>
       <c r="O156" s="5" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="P156" s="6" t="inlineStr">
         <is>
-          <t>Reprise de bail recherchee pour un 5 1/2 ensoleille au 3e etage, balcon accessible depuis une chambre, laveuse-secheuse et electromenagers inclus, animaux acceptes, frais de services publics ~150$/mois en supplement, libre 1er octobre 2026, bail 1 an, meubles actuels a vendre en option, proche Plaza Saint-Hubert.</t>
+          <t>ATTENTION: bail de 9 mois non renouvelable (1er oct. 2026 au 30 juin 2027), tout meublé, électricité incluse, grande cour arrière privée avec jardin, sous-sol avec laveuse-sécheuse et rangement, rez-de-chaussée d'un triplex dans la Petite Italie.</t>
         </is>
       </c>
       <c r="Q156" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c9/c94ec64e-8bbe-4c89-a24b-db48bcd3657c?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202509/1114557/5-1-2-villeray-st-michel-parc-extension-600-15245084.jpg</t>
         </is>
       </c>
     </row>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -576,32 +576,32 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2 chambres fermées, 2 balcons, 935 pi² - rue Moreau, Hochelaga, à quelques pas du métro Préfontaine</t>
+          <t>Grand 4½ (4 chambres fermées), 8 pièces, balcon arrière - avenue Coloniale (bas du Plateau), à ~8 min du métro Saint-Laurent</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2565, Rue Moreau, Montréal</t>
+          <t>3679, Avenue Coloniale, Montréal, QC H2X 2Y6</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Saint-Laurent</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -631,22 +631,22 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-mercier-hochelaga-maisonneuve/19531960</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/23543932</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Meuble et equipe, 1 salle de bain + salle d'eau, immeuble de 1983, jardin commun amenage, dernier etage, libre 1er nov. (ou 1er dec.) 2026, Walk Score 91, a quelques pas du metro Prefontaine, cafes/restos/boutiques a proximite, animaux non precises</t>
+          <t>Logement de 8 pièces (4 chambres fermées), grand balcon à l'arrière, plafonds de 9'3", planchers de bois et boiseries foncées, chats acceptés, immeuble de 3 logements, à deux rues de l'avenue du Mont-Royal et de la rue Saint-Denis. Walk Score 97, Bike Score 100. Distance au métro Saint-Laurent estimée a partir de l'adresse (non confirmée dans l'annonce elle-même). Superficie non précisée dans l'annonce.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DACE8667DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA410287DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -5325,32 +5325,32 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Magnifique meublé RDC, 1300 pi², 3 chambres, balcon - Rosemont (location temporaire)</t>
+          <t>2 chambres fermées, 2 balcons, 935 pi² - rue Moreau, Hochelaga, à quelques pas du métro Préfontaine</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Rosemont / La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Z2, secteur Rosemont)</t>
+          <t>2565, Rue Moreau, Montréal</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>935</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -5360,27 +5360,27 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-meuble-a-louer-rdc-rosemont/1743325973</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-mercier-hochelaga-maisonneuve/19531960</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
@@ -5390,19 +5390,19 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>Meuble et equipe (literie/linge inclus), location du 1er dec. 2026 au 30 juillet 2027 puis mois par mois, chauffage/electricite/cable/internet inclus, 1 stationnement privatif inclus, animaux non acceptes, rez-de-chaussee sur deux etages, station de metro non precisee dans l'annonce</t>
+          <t>Meuble et equipe, 1 salle de bain + salle d'eau, immeuble de 1983, jardin commun amenage, dernier etage, libre 1er nov. (ou 1er dec.) 2026, Walk Score 91, a quelques pas du metro Prefontaine, cafes/restos/boutiques a proximite, animaux non precises</t>
         </is>
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9e/9eb1bea8-693d-4ba7-8848-bc70410faaed?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DACE8667DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -5412,27 +5412,27 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>1600 pi², 3 chambres + bureau, balcon avant/arrière - secteur Rosemont (Angus), entre métros St-Michel et Pie-IX</t>
+          <t>Magnifique meublé RDC, 1300 pi², 3 chambres, balcon - Rosemont (location temporaire)</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Rosemont / La Petite-Patrie</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1T 1A6, secteur Rosemont/Angus)</t>
+          <t>n/d (Montréal, QC H1Y 1Z2, secteur Rosemont)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/1600-sq-ft-3-bedroom-2-bathroom-apartment-for-rent-in-rosemont/1716389968</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-meuble-a-louer-rdc-rosemont/1743325973</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>500 pi2 additionnels au sous-sol, 2 salles de bain, porche avant + deck arriere, laveuse-secheuse avec raccordements, animaux non acceptes, disponible depuis le 15 aout 2026, desservi par autobus vers metros St-Michel et Pie-IX (distance de marche non precisee)</t>
+          <t>Meuble et equipe (literie/linge inclus), location du 1er dec. 2026 au 30 juillet 2027 puis mois par mois, chauffage/electricite/cable/internet inclus, 1 stationnement privatif inclus, animaux non acceptes, rez-de-chaussee sur deux etages, station de metro non precisee dans l'annonce</t>
         </is>
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/de/de917599-37bd-4051-bff2-ddc95cbfb94c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9e/9eb1bea8-693d-4ba7-8848-bc70410faaed?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Rénové avec parking garage privé, 3 chambres, 1100 pi², 2 balcons - 7234 Boul. Pie-IX, Rosemont</t>
+          <t>1600 pi², 3 chambres + bureau, balcon avant/arrière - secteur Rosemont (Angus), entre métros St-Michel et Pie-IX</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -5509,17 +5509,17 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>7234, Boulevard Pie-IX, Montréal</t>
+          <t>n/d (Montréal, QC H1T 1A6, secteur Rosemont/Angus)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rosemont-5-1-2-renove-avec-parking-garage-prive/1744243391</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/1600-sq-ft-3-bedroom-2-bathroom-apartment-for-rent-in-rosemont/1716389968</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>Secteur entre Villeray et Petite-Patrie, rez-de-chaussee bien isole, parking garage prive inclus, laveuse-secheuse + lave-vaisselle inclus, climatisation, animaux limites, eau incluse, disponible fin oct./1er nov. 2026, station de metro la plus proche non confirmee par l'annonce</t>
+          <t>500 pi2 additionnels au sous-sol, 2 salles de bain, porche avant + deck arriere, laveuse-secheuse avec raccordements, animaux non acceptes, disponible depuis le 15 aout 2026, desservi par autobus vers metros St-Michel et Pie-IX (distance de marche non precisee)</t>
         </is>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/ba/bab87719-1cdf-43b6-9bb3-d8691197d51e?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/de/de917599-37bd-4051-bff2-ddc95cbfb94c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ avec solarium, 3 chambres, superficie annoncée 3000 pi² (à vérifier) - secteur Rosemont</t>
+          <t>Rénové avec parking garage privé, 3 chambres, 1100 pi², 2 balcons - 7234 Boul. Pie-IX, Rosemont</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -5596,17 +5596,17 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1T 3S4, Rosemont)</t>
+          <t>7234, Boulevard Pie-IX, Montréal</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-a-louer-rosemont-montreal/1744376633</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rosemont-5-1-2-renove-avec-parking-garage-prive/1744243391</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>Superficie de 3000 pi2 annoncee, possiblement surestimee/erreur de l'annonceur - a verifier avant visite; solarium avec rideau automatique, cour arriere, chauffage et electricite inclus, garage interieur + stationnement exterieur, animaux non acceptes, disponible 1er nov. 2026, metro a proximite (non precise)</t>
+          <t>Secteur entre Villeray et Petite-Patrie, rez-de-chaussee bien isole, parking garage prive inclus, laveuse-secheuse + lave-vaisselle inclus, climatisation, animaux limites, eau incluse, disponible fin oct./1er nov. 2026, station de metro la plus proche non confirmee par l'annonce</t>
         </is>
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3d/3da1707b-3da5-4d4d-8a1b-1695b8c74df3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/ba/bab87719-1cdf-43b6-9bb3-d8691197d51e?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5673,27 +5673,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé, 3 chambres, 1100 pi², jardin/terrasse/cour arrière - aux Promenades Masson</t>
+          <t>Grand 5½ avec solarium, 3 chambres, superficie annoncée 3000 pi² (à vérifier) - secteur Rosemont</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Rosemont / La Petite-Patrie</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 2N3, Promenades Masson)</t>
+          <t>n/d (Montréal, QC H1T 3S4, Rosemont)</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-aux-promenades-masson/1744395250</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-a-louer-rosemont-montreal/1744376633</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>Meuble, rez-de-chaussee, climatisation/chauffage/electricite/eau inclus, 1 stationnement inclus, animaux acceptes, disponible 1er nov. 2026, pres de la Promenade Masson (quartier commercant), station de metro non precisee</t>
+          <t>Superficie de 3000 pi2 annoncee, possiblement surestimee/erreur de l'annonceur - a verifier avant visite; solarium avec rideau automatique, cour arriere, chauffage et electricite inclus, garage interieur + stationnement exterieur, animaux non acceptes, disponible 1er nov. 2026, metro a proximite (non precise)</t>
         </is>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5e/5e99688f-11ec-40b5-b7e3-94cc5c6eec11?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3d/3da1707b-3da5-4d4d-8a1b-1695b8c74df3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5760,32 +5760,32 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>7½ (4 chambres), 1500-1600 pi², 2 balcons, internet et stationnement inclus - 6635 20e avenue, Rosemont (près parc Étienne-Desmarteau)</t>
+          <t>5½ meublé, 3 chambres, 1100 pi², jardin/terrasse/cour arrière - aux Promenades Masson</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Rosemont / La Petite-Patrie</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>6635, 20e Avenue, Montréal</t>
+          <t>n/d (Montréal, QC H1Y 2N3, Promenades Masson)</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
@@ -5795,17 +5795,17 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>n/d (non précisé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/7-et-demi-rosemont-internet-parking-inclus-dispo-mtn/1744109211</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-aux-promenades-masson/1744395250</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>4 chambres fermees malgre le titre '7 et demi', pres du parc Etienne-Desmarteau, stationnement exterieur + internet inclus, 1 chat accepte (pas de chien), disponible depuis le 28 sept. 2026, l'annonce mentionne le metro Pie-IX comme acces transport mais la distance de marche exacte n'est pas confirmee</t>
+          <t>Meuble, rez-de-chaussee, climatisation/chauffage/electricite/eau inclus, 1 stationnement inclus, animaux acceptes, disponible 1er nov. 2026, pres de la Promenade Masson (quartier commercant), station de metro non precisee</t>
         </is>
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/3b/3b39c437-e4a0-4882-b009-c9b62a9adb6a?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5e/5e99688f-11ec-40b5-b7e3-94cc5c6eec11?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5847,32 +5847,32 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>3 grandes chambres, 1500 pi², balcon, thermopompe neuve - secteur Plateau/Mile End</t>
+          <t>7½ (4 chambres), 1500-1600 pi², 2 balcons, internet et stationnement inclus - 6635 20e avenue, Rosemont (près parc Étienne-Desmarteau)</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2V 4H4, secteur Mile End/Plateau)</t>
+          <t>6635, 20e Avenue, Montréal</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
@@ -5882,17 +5882,17 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>n/d (non précisé)</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-1-bath-apartment-in-plateau/1743229407</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/7-et-demi-rosemont-internet-parking-inclus-dispo-mtn/1744109211</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>Thermopompe neuve (chauffage/climatisation/filtration), laveuse-secheuse incluses, 1 stationnement inclus, pas de frigo inclus, animaux limites, disponible 1er oct. 2026, 2e etage, hydro non inclus, station de metro non precisee par l'annonce</t>
+          <t>4 chambres fermees malgre le titre '7 et demi', pres du parc Etienne-Desmarteau, stationnement exterieur + internet inclus, 1 chat accepte (pas de chien), disponible depuis le 28 sept. 2026, l'annonce mentionne le metro Pie-IX comme acces transport mais la distance de marche exacte n'est pas confirmee</t>
         </is>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/7e/7e22fc26-ce27-46ea-afa4-398a469d5315?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/3b/3b39c437-e4a0-4882-b009-c9b62a9adb6a?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5934,32 +5934,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail - 4½ sur 2 étages, 4 terrasses, 950 pi² - secteur Ville-Marie/Hochelaga, à 6 min du métro Frontenac</t>
+          <t>3 grandes chambres, 1500 pi², balcon, thermopompe neuve - secteur Plateau/Mile End</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur H2K 2R7, Montréal)</t>
+          <t>n/d (Montréal, QC H2V 4H4, secteur Mile End/Plateau)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -5969,17 +5969,17 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-sur-2-etages-4-terrasses-2-mois-gratuits/1741461785</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-1-bath-apartment-in-plateau/1743229407</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail avec 2 mois gratuits (loyer affiche 2150$), climatisation + echangeur d'air, 4 terrasses, chats acceptes/chiens sous approbation, disponible 1er nov. 2026, aussi a 8 min du metro Prefontaine, secteur Centre-Sud a la frontiere d'Hochelaga, adresse exacte non divulguee par l'annonce</t>
+          <t>Thermopompe neuve (chauffage/climatisation/filtration), laveuse-secheuse incluses, 1 stationnement inclus, pas de frigo inclus, animaux limites, disponible 1er oct. 2026, 2e etage, hydro non inclus, station de metro non precisee par l'annonce</t>
         </is>
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/34/34a376ec-b257-4044-8994-f129e5920e8c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/7e/7e22fc26-ce27-46ea-afa4-398a469d5315?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -6021,32 +6021,32 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 3 chambres, 1000 pi² - rue Saint-Dominique (Plateau), à quelques pas du métro Sherbrooke</t>
+          <t>Cession de bail - 4½ sur 2 étages, 4 terrasses, 950 pi² - secteur Ville-Marie/Hochelaga, à 6 min du métro Frontenac</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>3477, Rue Saint-Dominique, Montréal</t>
+          <t>n/d (secteur H2K 2R7, Montréal)</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -6056,17 +6056,17 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1744351205</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-sur-2-etages-4-terrasses-2-mois-gratuits/1741461785</t>
         </is>
       </c>
       <c r="O65" s="5" t="inlineStr">
@@ -6086,19 +6086,19 @@
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>Balcon arriere 2e etage, climatisation, eau incluse, laveuse-secheuse in-unit, proche boul. Saint-Laurent/McGill, disponible 1er juillet 2026, animaux limites</t>
+          <t>Cession de bail avec 2 mois gratuits (loyer affiche 2150$), climatisation + echangeur d'air, 4 terrasses, chats acceptes/chiens sous approbation, disponible 1er nov. 2026, aussi a 8 min du metro Prefontaine, secteur Centre-Sud a la frontiere d'Hochelaga, adresse exacte non divulguee par l'annonce</t>
         </is>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/e5/e5ab3bd1-6aab-4346-8ff2-d3f06fc00fb7?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/34/34a376ec-b257-4044-8994-f129e5920e8c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -6108,27 +6108,27 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>3 chambres renove, 1100 pi², rue Cuvillier (Hochelaga), a 4 min du metro Joliette</t>
+          <t>5½ rénové, 3 chambres, 1000 pi² - rue Saint-Dominique (Plateau), à quelques pas du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Rue Cuvillier, Montreal, QC H1W 3A8</t>
+          <t>3477, Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/newly-renovated-3-bedroom-apartment-for-rent/1744478830</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1744351205</t>
         </is>
       </c>
       <c r="O66" s="5" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>Electromenagers neufs inclus, stationnement prive, internet haute vitesse inclus, animaux a discuter, disponible 1er dec. 2026, bail 1 an. Rue Cuvillier deja representee par d'autres annonces similaires dans le meme secteur ; numero civique non precise par l'annonceur.</t>
+          <t>Balcon arriere 2e etage, climatisation, eau incluse, laveuse-secheuse in-unit, proche boul. Saint-Laurent/McGill, disponible 1er juillet 2026, animaux limites</t>
         </is>
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f2/f27476a1-d118-4727-b397-2d2a72152eca?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/e5/e5ab3bd1-6aab-4346-8ff2-d3f06fc00fb7?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -6195,17 +6195,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>4½ renove (2 chambres), 900 pi², balcons avant/arriere - rue de Bordeaux (Plateau), proche metro Mont-Royal</t>
+          <t>3 chambres renove, 1100 pi², rue Cuvillier (Hochelaga), a 4 min du metro Joliette</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Rue de Bordeaux, Montreal, QC (secteur Mont-Royal / de Bordeaux)</t>
+          <t>Rue Cuvillier, Montreal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -6215,22 +6215,22 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>oui (avant et arriere)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>10 (estime)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-plateau-transfer-de-bail-1er-novembre-1er-decembre/1740921142</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/newly-renovated-3-bedroom-apartment-for-rent/1744478830</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>Transfert de bail jusqu'au 31 juillet 2027 (renouvelable), entierement renove, semi-meuble (electromenagers inclus), climatisation, stationnement rue, disponible 1er nov. ou 1er dec. 2026. Electricite/internet non inclus. Distance au metro estimee (non precisee dans l'annonce).</t>
+          <t>Electromenagers neufs inclus, stationnement prive, internet haute vitesse inclus, animaux a discuter, disponible 1er dec. 2026, bail 1 an. Rue Cuvillier deja representee par d'autres annonces similaires dans le meme secteur ; numero civique non precise par l'annonceur.</t>
         </is>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d8/d80a2456-033c-45d7-8b17-d8ed90e2c2d7?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f2/f27476a1-d118-4727-b397-2d2a72152eca?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>4½ renove (2 chambres), 950 pi², 2 balcons - secteur De Lorimier / Parc La Fontaine (Plateau), proche metro Sherbrooke</t>
+          <t>4½ renove (2 chambres), 900 pi², balcons avant/arriere - rue de Bordeaux (Plateau), proche metro Mont-Royal</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montreal, QC H2K 4G3, secteur De Lorimier / Parc La Fontaine)</t>
+          <t>Rue de Bordeaux, Montreal, QC (secteur Mont-Royal / de Bordeaux)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui (avant et arriere)</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>11 (estime)</t>
+          <t>10 (estime)</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-4-1-2-lumineux-charmant-sur-le-plateau/1743158327</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-plateau-transfer-de-bail-1er-novembre-1er-decembre/1740921142</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, 3e et dernier etage, semi-meuble (electromenagers inclus), climatisation, petit chien accepte, disponible 6 oct. 2026. Distance au metro estimee a partir du secteur H2K (non precisee dans l'annonce).</t>
+          <t>Transfert de bail jusqu'au 31 juillet 2027 (renouvelable), entierement renove, semi-meuble (electromenagers inclus), climatisation, stationnement rue, disponible 1er nov. ou 1er dec. 2026. Electricite/internet non inclus. Distance au metro estimee (non precisee dans l'annonce).</t>
         </is>
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d1/d1079d1f-bda3-441c-8af9-24bac87a553c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d8/d80a2456-033c-45d7-8b17-d8ed90e2c2d7?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>4½ renove (2 chambres), 900 pi², balcon - Plateau-Mont-Royal (proche Mile End), metro Rosemont/Beaubien/Laurier</t>
+          <t>4½ renove (2 chambres), 950 pi², 2 balcons - secteur De Lorimier / Parc La Fontaine (Plateau), proche metro Sherbrooke</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -6379,17 +6379,17 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montreal, QC H2T 2V4)</t>
+          <t>n/d (Montreal, QC H2K 4G3, secteur De Lorimier / Parc La Fontaine)</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beautiful-apartment-available-as-of-now-plateau-mont-royal/1743509536</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-4-1-2-lumineux-charmant-sur-le-plateau/1743158327</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
@@ -6434,19 +6434,19 @@
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>Disponible immediatement, lumineux, proche commerces et cafes (secteur Mile End), animaux non admis, electromenagers inclus, laveuse-secheuse a l'unite. Station la plus proche parmi Rosemont/Beaubien/Laurier (mentionnees dans l'annonce) et distance estimees, non precisees explicitement.</t>
+          <t>Cession de bail, 3e et dernier etage, semi-meuble (electromenagers inclus), climatisation, petit chien accepte, disponible 6 oct. 2026. Distance au metro estimee a partir du secteur H2K (non precisee dans l'annonce).</t>
         </is>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/72/7218f79a-fb5b-430b-b3e7-d4eeb632b5e2?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d1/d1079d1f-bda3-441c-8af9-24bac87a553c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>5½ (2 chambres), 1050 pi², 2 balcons - rue de Bullion (Plateau), à environ 11 min du métro Sherbrooke</t>
+          <t>4½ renove (2 chambres), 900 pi², balcon - Plateau-Mont-Royal (proche Mile End), metro Rosemont/Beaubien/Laurier</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -6466,17 +6466,17 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>3986, Rue de Bullion, Montréal, QC H2W 2E4</t>
+          <t>n/d (Montreal, QC H2T 2V4)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -6501,17 +6501,17 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>11 (estimé)</t>
+          <t>11 (estime)</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/address/3986-rue-de-bullion-montreal-qc-h2w-2e4-can</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beautiful-apartment-available-as-of-now-plateau-mont-royal/1743509536</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
@@ -6521,19 +6521,19 @@
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>Chats et chiens acceptés, chauffage/électricité/eau chaude non inclus, planchers de bois franc, laveuse-sécheuse à l'unité, immeuble voisin du 3984 rue de Bullion déjà répertorié, secteur Plateau à quelques rues du boul. Saint-Laurent. Prix au plafond du budget (2400$).</t>
+          <t>Disponible immediatement, lumineux, proche commerces et cafes (secteur Mile End), animaux non admis, electromenagers inclus, laveuse-secheuse a l'unite. Station la plus proche parmi Rosemont/Beaubien/Laurier (mentionnees dans l'annonce) et distance estimees, non precisees explicitement.</t>
         </is>
       </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/837421110/1280x960?auto=format</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/72/7218f79a-fb5b-430b-b3e7-d4eeb632b5e2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -6543,42 +6543,42 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1425 pi² - rue La Fontaine, Hochelaga-Maisonneuve</t>
+          <t>5½ (2 chambres), 1050 pi², 2 balcons - rue de Bullion (Plateau), à environ 11 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>3527, Rue La Fontaine, Montréal, QC</t>
+          <t>3986, Rue de Bullion, Montréal, QC H2W 2E4</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé, 850m)</t>
+          <t>11 (estimé)</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/16826763</t>
+          <t>https://www.zumper.com/address/3986-rue-de-bullion-montreal-qc-h2w-2e4-can</t>
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
@@ -6608,19 +6608,19 @@
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
-          <t>Portes-fenetres cuisine/salon, 2 chambres avec fenetre sur 3, Walk Score 98, a 850m (environ 10 min a pied) du metro Joliette (ligne verte), pres de la Promenade Ontario (commerces, restaurants). Disponible immediatement ou 10 jours apres acceptation de la promesse de location. Balcon non precise par l'annonce. Visite libre annoncee le lundi 5 octobre 18h-19h.</t>
+          <t>Chats et chiens acceptés, chauffage/électricité/eau chaude non inclus, planchers de bois franc, laveuse-sécheuse à l'unité, immeuble voisin du 3984 rue de Bullion déjà répertorié, secteur Plateau à quelques rues du boul. Saint-Laurent. Prix au plafond du budget (2400$).</t>
         </is>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAC4E4C7DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://img.zumpercdn.com/837421110/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf 3 chambres (2 au sous-sol), 1206 pi², a quelques minutes du metro Prefontaine - Hochelaga-Maisonneuve</t>
+          <t>5½ rénové (3 chambres), 1425 pi² - rue La Fontaine, Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -6640,17 +6640,17 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>3257, Rue Sainte-Catherine Est, app. 102, Montreal</t>
+          <t>3527, Rue La Fontaine, Montréal, QC</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Prefontaine</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>5 (estime)</t>
+          <t>10 (estimé, 850m)</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-mercier-hochelaga-maisonneuve/18618728</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/16826763</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>Neuf (construction 2026), semi-meuble, 3 chambres (2 au sous-sol), lumineux, arret de bus en face, disponible 5 jours apres acceptation de la promesse de location, Walk Score 90. Balcon non mentionne dans l'annonce. Adresse a l'ouest de Pie-IX, dans Hochelaga (pas Mercier).</t>
+          <t>Portes-fenetres cuisine/salon, 2 chambres avec fenetre sur 3, Walk Score 98, a 850m (environ 10 min a pied) du metro Joliette (ligne verte), pres de la Promenade Ontario (commerces, restaurants). Disponible immediatement ou 10 jours apres acceptation de la promesse de location. Balcon non precise par l'annonce. Visite libre annoncee le lundi 5 octobre 18h-19h.</t>
         </is>
       </c>
       <c r="Q72" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA43E569DDDDDDDDDD0&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAC4E4C7DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -6717,27 +6717,27 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 6½ rénové avec énorme cour privée - rez-de-chaussée, Villeray/Saint-Michel, proche métro Saint-Michel</t>
+          <t>Condo neuf 3 chambres (2 au sous-sol), 1206 pi², a quelques minutes du metro Prefontaine - Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Villeray/Saint-Michel, Montréal, QC H2A 2A5)</t>
+          <t>3257, Rue Sainte-Catherine Est, app. 102, Montreal</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -6747,32 +6747,32 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>oui (balcon + énorme cour privée avec arbre mature)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Prefontaine</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (estime)</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-6-5-renove-avec-enorme-cour-a-villeray-st-michel/1744349548</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-mercier-hochelaga-maisonneuve/18618728</t>
         </is>
       </c>
       <c r="O73" s="5" t="inlineStr">
@@ -6782,19 +6782,19 @@
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée entièrement rénové, plancher bois franc, grande cuisine, bain séparé, véranda, garage + 3 stationnements, frigo/four/laveuse-sécheuse/lave-vaisselle inclus, aucun animal, non-fumeur, enquête de crédit requise, dispo 1er nov. 2026, bail 1 an non meublé. Secteur plus résidentiel que Hochelaga (ambiance à valider sur place), métro ligne bleue (pas verte) mais à 5 min à pied seulement.</t>
+          <t>Neuf (construction 2026), semi-meuble, 3 chambres (2 au sous-sol), lumineux, arret de bus en face, disponible 5 jours apres acceptation de la promesse de location, Walk Score 90. Balcon non mentionne dans l'annonce. Adresse a l'ouest de Pie-IX, dans Hochelaga (pas Mercier).</t>
         </is>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/7e/7e192d94-df31-42b9-8e3c-e1fa28793898?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA43E569DDDDDDDDDD0&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -6804,52 +6804,52 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Spacieux 4½ rénové (2 chambres), 950 pi², 2 balcons - La Petite-Patrie, à quelques minutes du métro Rosemont</t>
+          <t>Magnifique 6½ rénové avec énorme cour privée - rez-de-chaussée, Villeray/Saint-Michel, proche métro Saint-Michel</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray-Saint-Michel</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>n/d (La Petite-Patrie, Montréal, QC H2S 2H7)</t>
+          <t>n/d (secteur Villeray/Saint-Michel, Montréal, QC H2A 2A5)</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>oui (avant et arrière)</t>
+          <t>oui (balcon + énorme cour privée avec arbre mature)</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>5-8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/spacieux-4-a-deux-pas-du-metro-rosemont/1743420224</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-6-5-renove-avec-enorme-cour-a-villeray-st-michel/1744349548</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
-          <t>3e étage d'un sixplex sur rue calme, logement lumineux et bien aéré, eau incluse, laveuse-sécheuse et lave-vaisselle inclus, meubles disponibles au même prix si désiré, animaux limités, 1 mois gratuit jusqu'au 1er décembre, disponible 13 sept. 2026, bail 1 an. L'annonce indique le métro Rosemont « à quelques minutes » sans précision exacte.</t>
+          <t>Rez-de-chaussée entièrement rénové, plancher bois franc, grande cuisine, bain séparé, véranda, garage + 3 stationnements, frigo/four/laveuse-sécheuse/lave-vaisselle inclus, aucun animal, non-fumeur, enquête de crédit requise, dispo 1er nov. 2026, bail 1 an non meublé. Secteur plus résidentiel que Hochelaga (ambiance à valider sur place), métro ligne bleue (pas verte) mais à 5 min à pied seulement.</t>
         </is>
       </c>
       <c r="Q74" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/86/86cd8da5-817c-436b-9477-0164477d1123?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/7e/7e192d94-df31-42b9-8e3c-e1fa28793898?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -6891,27 +6891,27 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové avec sous-sol aménagé (2 chambres), 900 pi², balcon - rue Marie-Anne Est (Plateau), près des métros Mont-Royal et Saint-Laurent</t>
+          <t>Spacieux 4½ rénové (2 chambres), 950 pi², 2 balcons - La Petite-Patrie, à quelques minutes du métro Rosemont</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>172, Rue Marie-Anne Est, Montréal, QC H2W 1A5</t>
+          <t>n/d (La Petite-Patrie, Montréal, QC H2S 2H7)</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (avant et arrière)</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>7 (estimé)</t>
+          <t>5-8 (estimé)</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-basement-plateau-mont-royal-lease-transfer-1940/1743197854</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/spacieux-4-a-deux-pas-du-metro-rosemont/1743420224</t>
         </is>
       </c>
       <c r="O75" s="5" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail du 1er oct. 2026 au 30 juin 2027, 1er mois gratuit (moyenne effective ~1724$/mois sur 9 mois), rez-de-chaussée avec sous-sol aménagé (salle familiale + buanderie), chauffage électrique payé par le locataire, meublé (frigo/cuisinière/laveuse-sécheuse), aucun animal. Distance aux métros Mont-Royal et Saint-Laurent estimée à partir de l'adresse (non précisée par l'annonce).</t>
+          <t>3e étage d'un sixplex sur rue calme, logement lumineux et bien aéré, eau incluse, laveuse-sécheuse et lave-vaisselle inclus, meubles disponibles au même prix si désiré, animaux limités, 1 mois gratuit jusqu'au 1er décembre, disponible 13 sept. 2026, bail 1 an. L'annonce indique le métro Rosemont « à quelques minutes » sans précision exacte.</t>
         </is>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f5/f5072559-e474-4ba8-8085-0e99c24e576e?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/86/86cd8da5-817c-436b-9477-0164477d1123?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -6978,22 +6978,22 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Grand 4½ neuf, dernier étage (2 chambres + bureau fermé), 900 pi², 2 balcons - avenue Gascon (Centre-Sud/Plateau), à 7 min des métros Frontenac/Préfontaine</t>
+          <t>4½ rénové avec sous-sol aménagé (2 chambres), 900 pi², balcon - rue Marie-Anne Est (Plateau), près des métros Mont-Royal et Saint-Laurent</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud) / Le Plateau-Mont-Royal</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>n/d (Avenue Gascon, Montréal, QC)</t>
+          <t>172, Rue Marie-Anne Est, Montréal, QC H2W 1A5</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>Frontenac / Préfontaine</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 (estimé)</t>
         </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-neuf-dernier-etage-vue-plateau-ville-marie/1739397387</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-basement-plateau-mont-royal-lease-transfer-1940/1743197854</t>
         </is>
       </c>
       <c r="O76" s="5" t="inlineStr">
@@ -7043,19 +7043,19 @@
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové (cuisine, salle de bain, plancher, façade), 2 chambres fermées + bureau/salon fermé pouvant servir de 3e chambre, laveuse-sécheuse à l'unité, climatisation, eau et internet inclus, chats acceptés, prix promotionnel 1re année à 1900$ (régulier 2000$ - à vérifier au renouvellement), disponible 5 sept. 2026, bail 1 an. Pourrait être un autre logement du même immeuble que l'annonce avenue Gascon déjà au fichier (2553, Avenue Gascon).</t>
+          <t>Cession de bail du 1er oct. 2026 au 30 juin 2027, 1er mois gratuit (moyenne effective ~1724$/mois sur 9 mois), rez-de-chaussée avec sous-sol aménagé (salle familiale + buanderie), chauffage électrique payé par le locataire, meublé (frigo/cuisinière/laveuse-sécheuse), aucun animal. Distance aux métros Mont-Royal et Saint-Laurent estimée à partir de l'adresse (non précisée par l'annonce).</t>
         </is>
       </c>
       <c r="Q76" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9bd79cd5-6df3-4028-8b83-e706719f7804?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f5/f5072559-e474-4ba8-8085-0e99c24e576e?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -7065,32 +7065,32 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres), 1000 pi², 2 balcons - rue Jean-Talon Est, à 4-5 min des métros De Castelnau et Jean-Talon</t>
+          <t>Grand 4½ neuf, dernier étage (2 chambres + bureau fermé), 900 pi², 2 balcons - avenue Gascon (Centre-Sud/Plateau), à 7 min des métros Frontenac/Préfontaine</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie (frontière Villeray)</t>
+          <t>Ville-Marie (Centre-Sud) / Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>192, Rue Jean-Talon Est, Montréal, QC</t>
+          <t>n/d (Avenue Gascon, Montréal, QC)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -7100,27 +7100,27 @@
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>De Castelnau / Jean-Talon</t>
+          <t>Frontenac / Préfontaine</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>bleue/orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>4 (305-341 m)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l362224</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-neuf-dernier-etage-vue-plateau-ville-marie/1739397387</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
@@ -7130,10 +7130,14 @@
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
-          <t>Chauffage, eau chaude et électricité non inclus. Climatisation murale et lave-vaisselle inclus ; frigo/cuisinière/laveuse-sécheuse disponibles en sus. Stationnement (vignette + parcomètre) inclus. Animaux refusés. Balcon arrière avec vue sur le Marché Jean-Talon, second balcon accessible depuis une chambre avant. Libre immédiatement, bail minimum 12 mois.</t>
-        </is>
-      </c>
-      <c r="Q77" s="5" t="inlineStr"/>
+          <t>Entièrement rénové (cuisine, salle de bain, plancher, façade), 2 chambres fermées + bureau/salon fermé pouvant servir de 3e chambre, laveuse-sécheuse à l'unité, climatisation, eau et internet inclus, chats acceptés, prix promotionnel 1re année à 1900$ (régulier 2000$ - à vérifier au renouvellement), disponible 5 sept. 2026, bail 1 an. Pourrait être un autre logement du même immeuble que l'annonce avenue Gascon déjà au fichier (2553, Avenue Gascon).</t>
+        </is>
+      </c>
+      <c r="Q77" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9bd79cd5-6df3-4028-8b83-e706719f7804?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -7148,62 +7152,62 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové (2 chambres), 900 pi², balcon - avenue Henri-Julien (Plateau), à ~6 min du métro Mont-Royal</t>
+          <t>5½ (3 chambres), 1000 pi², 2 balcons - rue Jean-Talon Est, à 4-5 min des métros De Castelnau et Jean-Talon</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie (frontière Villeray)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Avenue Henri-Julien (coin Mont-Royal), Montréal, QC H2W 2K8</t>
+          <t>192, Rue Jean-Talon Est, Montréal, QC</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>De Castelnau / Jean-Talon</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue/orange</t>
         </is>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>6 (estimé)</t>
+          <t>4 (305-341 m)</t>
         </is>
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/2-chambres-plateau-mont-royal-libre-maintenant/1743741826</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l362224</t>
         </is>
       </c>
       <c r="O78" s="5" t="inlineStr">
@@ -7213,19 +7217,15 @@
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
-          <t>2e étage d'un quadruplex, entièrement rénové et lumineux, meublé, laveuse-sécheuse à l'unité, frigo et cuisinière inclus, douche moderne, animaux limités, libre 1er oct. 2026, bail 1 an. Distance au métro Mont-Royal (ligne verte) estimée à partir du coin Henri-Julien/Mont-Royal (non précisée par l'annonce).</t>
-        </is>
-      </c>
-      <c r="Q78" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/44/44b2c4b2-4a25-4508-ab82-068873d65185?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Chauffage, eau chaude et électricité non inclus. Climatisation murale et lave-vaisselle inclus ; frigo/cuisinière/laveuse-sécheuse disponibles en sus. Stationnement (vignette + parcomètre) inclus. Animaux refusés. Balcon arrière avec vue sur le Marché Jean-Talon, second balcon accessible depuis une chambre avant. Libre immédiatement, bail minimum 12 mois.</t>
+        </is>
+      </c>
+      <c r="Q78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -7235,32 +7235,32 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>5½ lumineux rénové, 3 chambres fermées, balcon et thermopompe - secteur Saint-Michel, à 9 min du métro Saint-Michel</t>
+          <t>4½ rénové (2 chambres), 900 pi², balcon - avenue Henri-Julien (Plateau), à ~6 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2A 2P9 (secteur Saint-Michel, près du parc St-Bernadette)</t>
+          <t>Avenue Henri-Julien (coin Mont-Royal), Montréal, QC H2W 2K8</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -7270,17 +7270,17 @@
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>6 (estimé)</t>
         </is>
       </c>
       <c r="M79" s="5" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/logement-5-1-2-lumineux-a-louer/1744132273</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/2-chambres-plateau-mont-royal-libre-maintenant/1743741826</t>
         </is>
       </c>
       <c r="O79" s="5" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
-          <t>Thermopompe murale haute performance, douche italienne, aspirateur central, laveuse-sécheuse, chauffage inclus. Pas d'animaux, non-fumeur, bail 1 an, aucun Airbnb/sous-location permis, libre 30 sept. 2026. Accès également à la nouvelle station Pie-IX (ligne bleue). Adresse exacte non précisée par l'annonceur.</t>
+          <t>2e étage d'un quadruplex, entièrement rénové et lumineux, meublé, laveuse-sécheuse à l'unité, frigo et cuisinière inclus, douche moderne, animaux limités, libre 1er oct. 2026, bail 1 an. Distance au métro Mont-Royal (ligne verte) estimée à partir du coin Henri-Julien/Mont-Royal (non précisée par l'annonce).</t>
         </is>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/af/afbf577f-8f35-4a36-82b4-0aa87f31852e?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/44/44b2c4b2-4a25-4508-ab82-068873d65185?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -7322,32 +7322,32 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové, 2 chambres fermées, terrasse privée - rue Sherbrooke Est (Plateau-Mont-Royal), proche du métro Papineau</t>
+          <t>5½ lumineux rénové, 3 chambres fermées, balcon et thermopompe - secteur Saint-Michel, à 9 min du métro Saint-Michel</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray-Saint-Michel-Parc-Extension</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>2121, Rue Sherbrooke Est, app. 102, Montréal, QC H2K 1C2</t>
+          <t>Montréal, QC H2A 2P9 (secteur Saint-Michel, près du parc St-Bernadette)</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -7357,27 +7357,27 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>Papineau</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/26877857</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/logement-5-1-2-lumineux-a-louer/1744132273</t>
         </is>
       </c>
       <c r="O80" s="5" t="inlineStr">
@@ -7387,19 +7387,19 @@
       </c>
       <c r="P80" s="6" t="inlineStr">
         <is>
-          <t>Planchers de bois franc, cuisine à aire ouverte, semi-meublé, 1 salle de bain, libre 1er déc. 2026, Walk Score 97. Distance au métro Papineau (ligne verte) estimée à partir de l'intersection Sherbrooke/Papineau (annonce ne précise pas la station exacte).</t>
+          <t>Thermopompe murale haute performance, douche italienne, aspirateur central, laveuse-sécheuse, chauffage inclus. Pas d'animaux, non-fumeur, bail 1 an, aucun Airbnb/sous-location permis, libre 30 sept. 2026. Accès également à la nouvelle station Pie-IX (ligne bleue). Adresse exacte non précisée par l'annonceur.</t>
         </is>
       </c>
       <c r="Q80" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DACD9E63DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/af/afbf577f-8f35-4a36-82b4-0aa87f31852e?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>SUPERBE 6½ Plateau-Mont-Royal, 3 chambres fermées, 2 balcons - av. de l'Hôtel-de-Ville</t>
+          <t>Condo 4½ rénové, 2 chambres fermées, terrasse privée - rue Sherbrooke Est (Plateau-Mont-Royal), proche du métro Papineau</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>4082, avenue de l'Hôtel-de-Ville, Montréal, QC H2W 2H1</t>
+          <t>2121, Rue Sherbrooke Est, app. 102, Montréal, QC H2K 1C2</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -7429,42 +7429,42 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Papineau</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-6-1-2-plateau-mont-royal/1743328232</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/26877857</t>
         </is>
       </c>
       <c r="O81" s="5" t="inlineStr">
@@ -7474,19 +7474,19 @@
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
-          <t>Maison victorienne rénovée 1890, bois franc, brique, beaucoup de rangement, laveuse/sécheuse et lave-vaisselle inclus, libre 1er oct. (négociable). Chauffage non précisé. 12 min de Mont-Royal selon l'annonce.</t>
+          <t>Planchers de bois franc, cuisine à aire ouverte, semi-meublé, 1 salle de bain, libre 1er déc. 2026, Walk Score 97. Distance au métro Papineau (ligne verte) estimée à partir de l'intersection Sherbrooke/Papineau (annonce ne précise pas la station exacte).</t>
         </is>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/8f/8f859a2b-ac80-4848-91dd-d48df583fc2c?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DACD9E63DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -7496,22 +7496,22 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1000 pi², 2 balcons, à moins de 5 min du métro Jean-Talon - face au marché Jean-Talon</t>
+          <t>SUPERBE 6½ Plateau-Mont-Royal, 3 chambres fermées, 2 balcons - av. de l'Hôtel-de-Ville</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>192 Rue Jean-Talon E., Montréal</t>
+          <t>4082, avenue de l'Hôtel-de-Ville, Montréal, QC H2W 2H1</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -7526,32 +7526,32 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>Logis Québec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N82" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l362224</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-6-1-2-plateau-mont-royal/1743328232</t>
         </is>
       </c>
       <c r="O82" s="5" t="inlineStr">
@@ -7561,15 +7561,19 @@
       </c>
       <c r="P82" s="6" t="inlineStr">
         <is>
-          <t>Complètement rénové, A/C mural, lave-vaisselle inclus, stationnement (permis et parcomètre) inclus, chauffage/eau chaude/électricité non inclus, animaux non admis, disponible octobre 2026, immeuble semi-commercial de 5 logements, Petite-Italie.</t>
-        </is>
-      </c>
-      <c r="Q82" s="5" t="inlineStr"/>
+          <t>Maison victorienne rénovée 1890, bois franc, brique, beaucoup de rangement, laveuse/sécheuse et lave-vaisselle inclus, libre 1er oct. (négociable). Chauffage non précisé. 12 min de Mont-Royal selon l'annonce.</t>
+        </is>
+      </c>
+      <c r="Q82" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/8f/8f859a2b-ac80-4848-91dd-d48df583fc2c?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -7579,7 +7583,7 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>6½ rénové (2 chambres fermées), 1000 pi², terrasse 10x10 - Rosemont/Petite-Patrie, près métro Beaubien/Rosemont</t>
+          <t>5½ rénové (3 chambres), 1000 pi², 2 balcons, à moins de 5 min du métro Jean-Talon - face au marché Jean-Talon</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -7589,12 +7593,12 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2S 2B5)</t>
+          <t>192 Rue Jean-Talon E., Montréal</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -7604,7 +7608,7 @@
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
@@ -7614,27 +7618,27 @@
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Logis Québec</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rosemont-petite-patrie-beau-6-1-2-1000pi2-92m2/1743448388</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l362224</t>
         </is>
       </c>
       <c r="O83" s="5" t="inlineStr">
@@ -7644,19 +7648,15 @@
       </c>
       <c r="P83" s="6" t="inlineStr">
         <is>
-          <t>Walk Score 10, laveuse-sécheuse et lave-vaisselle inclus, climatisé, meublé possible, eau incluse, chauffage/électricité/internet non inclus, animaux limités, disponible 1er sept. 2026, bail 1 an. Aussi à distance de marche du métro Rosemont (ligne orange). Distance exacte aux stations non précisée par l'annonce (estimée).</t>
-        </is>
-      </c>
-      <c r="Q83" s="5" t="inlineStr">
-        <is>
-          <t>/next-assets/images/not-found.jpg</t>
-        </is>
-      </c>
+          <t>Complètement rénové, A/C mural, lave-vaisselle inclus, stationnement (permis et parcomètre) inclus, chauffage/eau chaude/électricité non inclus, animaux non admis, disponible octobre 2026, immeuble semi-commercial de 5 logements, Petite-Italie.</t>
+        </is>
+      </c>
+      <c r="Q83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -7666,22 +7666,22 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½, 1000 pi², 2 chambres, balcon - rue Fabre (Parc-Laurier/Plateau), à ~8 min du métro Mont-Royal</t>
+          <t>6½ rénové (2 chambres fermées), 1000 pi², terrasse 10x10 - Rosemont/Petite-Patrie, près métro Beaubien/Rosemont</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>4557, Rue Fabre, Montréal, QC H2J 3V7</t>
+          <t>n/d (Montréal, QC H2S 2B5)</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>zumper</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/apartments-for-rent/15052052/2-bedroom-parc-laurier-montreal-qc</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rosemont-petite-patrie-beau-6-1-2-1000pi2-92m2/1743448388</t>
         </is>
       </c>
       <c r="O84" s="5" t="inlineStr">
@@ -7731,19 +7731,19 @@
       </c>
       <c r="P84" s="6" t="inlineStr">
         <is>
-          <t>Meublé, rez-de-chaussée, secteur Parc-Laurier calme, balcon exclusif + terrasse partagée, stationnement inclus, laveuse/sécheuse, animaux acceptés.</t>
+          <t>Walk Score 10, laveuse-sécheuse et lave-vaisselle inclus, climatisé, meublé possible, eau incluse, chauffage/électricité/internet non inclus, animaux limités, disponible 1er sept. 2026, bail 1 an. Aussi à distance de marche du métro Rosemont (ligne orange). Distance exacte aux stations non précisée par l'annonce (estimée).</t>
         </is>
       </c>
       <c r="Q84" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/363079520/1280x960?auto=format</t>
+          <t>/next-assets/images/not-found.jpg</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -7753,42 +7753,42 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1170 pi² — rue Sherbrooke Est (Hochelaga), à 5 min du métro Préfontaine</t>
+          <t>Condo 4½, 1000 pi², 2 chambres, balcon - rue Fabre (Parc-Laurier/Plateau), à ~8 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>3163, Rue Sherbrooke Est, Montréal, QC H1W 1B8</t>
+          <t>4557, Rue Fabre, Montréal, QC H2J 3V7</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>zumper</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/apartments-for-rent/38619713/3-bedroom-montreal-qc</t>
+          <t>https://www.zumper.com/apartments-for-rent/15052052/2-bedroom-parc-laurier-montreal-qc</t>
         </is>
       </c>
       <c r="O85" s="5" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
-          <t>Une des 3 chambres est adjacente à la salle de bain ; hydro et internet non inclus ; animaux non permis ; chauffage et date de disponibilité non précisés.</t>
+          <t>Meublé, rez-de-chaussée, secteur Parc-Laurier calme, balcon exclusif + terrasse partagée, stationnement inclus, laveuse/sécheuse, animaux acceptés.</t>
         </is>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/311160160/1280x960?auto=format</t>
+          <t>https://img.zumpercdn.com/363079520/1280x960?auto=format</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>5½ (2 chambres), 980 pi², balcon — rue Joliette (Hochelaga), près du métro Joliette (ligne verte)</t>
+          <t>5½ rénové (3 chambres), 1170 pi² — rue Sherbrooke Est (Hochelaga), à 5 min du métro Préfontaine</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -7850,32 +7850,32 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>560, Rue Joliette, Montréal, QC H1W 3E5</t>
+          <t>3163, Rue Sherbrooke Est, Montréal, QC H1W 1B8</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>n/d (estimé proche, adresse sur la même rue que la station)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M86" s="5" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/listings/61297241/2-bedroom-hochelaga-montreal-qc</t>
+          <t>https://www.zumper.com/apartments-for-rent/38619713/3-bedroom-montreal-qc</t>
         </is>
       </c>
       <c r="O86" s="5" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="P86" s="6" t="inlineStr">
         <is>
-          <t>Balcon/jardin et terrasse, chauffage central mentionné mais charges non incluses, animaux acceptés (chats et chiens), disponible 1er juin, bail 1 an, planchers de bois franc, hauts plafonds, laveuse-sécheuse. Distance exacte au métro Joliette non confirmée par l'annonce.</t>
+          <t>Une des 3 chambres est adjacente à la salle de bain ; hydro et internet non inclus ; animaux non permis ; chauffage et date de disponibilité non précisés.</t>
         </is>
       </c>
       <c r="Q86" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/836938661/1280x960?auto=format</t>
+          <t>https://img.zumpercdn.com/311160160/1280x960?auto=format</t>
         </is>
       </c>
     </row>
@@ -7927,27 +7927,27 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail — Grand 4½ meublé avec terrasse privée et jardin, près métro Préfontaine/Frontenac</t>
+          <t>5½ (2 chambres), 980 pi², balcon — rue Joliette (Hochelaga), près du métro Joliette (ligne verte)</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Centre-Sud (limitrophe Hochelaga)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2K 2S2)</t>
+          <t>560, Rue Joliette, Montréal, QC H1W 3E5</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>n/d (estimé proche, adresse sur la même rue que la station)</t>
         </is>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-4-meuble-avec-terrasse-privee-jardin/1742732549</t>
+          <t>https://www.zumper.com/listings/61297241/2-bedroom-hochelaga-montreal-qc</t>
         </is>
       </c>
       <c r="O87" s="5" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="P87" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, meublé, buanderie interne, climatisation, eau incluse ; animaux limités ; bail mensuel possible ; disponible 1er octobre 2026 ; quartier Centre-Sud/Ville-Marie (hors des 4 quartiers prioritaires mais limitrophe d'Hochelaga, à 7-8 min des stations Préfontaine et Frontenac).</t>
+          <t>Balcon/jardin et terrasse, chauffage central mentionné mais charges non incluses, animaux acceptés (chats et chiens), disponible 1er juin, bail 1 an, planchers de bois franc, hauts plafonds, laveuse-sécheuse. Distance exacte au métro Joliette non confirmée par l'annonce.</t>
         </is>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/bf/bfda5c50-a2ab-4c62-bba1-1c4c88688e17?rule=kijijica-960-jpg</t>
+          <t>https://img.zumpercdn.com/836938661/1280x960?auto=format</t>
         </is>
       </c>
     </row>
@@ -8014,27 +8014,27 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>4½ entièrement rénové avec terrasse — rue Fénelon (Villeray/Saint-Michel)</t>
+          <t>Cession de bail — Grand 4½ meublé avec terrasse privée et jardin, près métro Préfontaine/Frontenac</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Centre-Sud (limitrophe Hochelaga)</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>3611, Rue Fénelon, Montréal, QC</t>
+          <t>n/d (Montréal, QC H2K 2S2)</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -8049,27 +8049,27 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-3611-rue-fenelon-1140156</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-4-meuble-avec-terrasse-privee-jardin/1742732549</t>
         </is>
       </c>
       <c r="O88" s="5" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="P88" s="6" t="inlineStr">
         <is>
-          <t>Disponible immédiatement ; cour privée ; électroménagers neufs ; climatisation ; secteur à la limite Villeray/Saint-Michel.</t>
+          <t>Cession de bail, meublé, buanderie interne, climatisation, eau incluse ; animaux limités ; bail mensuel possible ; disponible 1er octobre 2026 ; quartier Centre-Sud/Ville-Marie (hors des 4 quartiers prioritaires mais limitrophe d'Hochelaga, à 7-8 min des stations Préfontaine et Frontenac).</t>
         </is>
       </c>
       <c r="Q88" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1140156/4-1-2-villeray-st-michel-parc-extension-1600-15853955.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/bf/bfda5c50-a2ab-4c62-bba1-1c4c88688e17?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>3 chambres neuf, balcon privé — 304 Rue Villeray (Villeray)</t>
+          <t>4½ entièrement rénové avec terrasse — rue Fénelon (Villeray/Saint-Michel)</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -8111,22 +8111,22 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>304, Rue Villeray, app. 304, Montréal, QC H2R 1G7</t>
+          <t>3611, Rue Fénelon, Montréal, QC</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>De Castelnau</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L89" s="5" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/address/304-rue-villeray-montreal-qc-h2r-1g7-can</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-3611-rue-fenelon-1140156</t>
         </is>
       </c>
       <c r="O89" s="5" t="inlineStr">
@@ -8166,19 +8166,19 @@
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
-          <t>Jamais habité (neuf) ; climatisation murale ; animaux acceptés (chats et chiens) ; assurance responsabilité 2M$ exigée ; bail 1 an ; non-fumeur.</t>
+          <t>Disponible immédiatement ; cour privée ; électroménagers neufs ; climatisation ; secteur à la limite Villeray/Saint-Michel.</t>
         </is>
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/849890701/1280x960?auto=format</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1140156/4-1-2-villeray-st-michel-parc-extension-1600-15853955.jpg</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8188,22 +8188,22 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové (2 chambres, 1000 pi²), balcon et terrasse - Hochelaga-Maisonneuve, à 4 min du métro Joliette</t>
+          <t>3 chambres neuf, balcon privé — 304 Rue Villeray (Villeray)</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur métro Joliette, Montréal, QC H1W 3J3)</t>
+          <t>304, Rue Villeray, app. 304, Montréal, QC H2R 1G7</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -8223,27 +8223,27 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>De Castelnau</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N90" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/joli-rdc-homa-metrojoliette-5-1-2-cour-thermopompe-1916-mo/1742514974</t>
+          <t>https://www.zumper.com/address/304-rue-villeray-montreal-qc-h2r-1g7-can</t>
         </is>
       </c>
       <c r="O90" s="5" t="inlineStr">
@@ -8253,19 +8253,19 @@
       </c>
       <c r="P90" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, balcon avant et terrasse arrière avec accès à la cour, thermopompe (non chauffé), animaux limités acceptés, disponible 1er octobre 2026.</t>
+          <t>Jamais habité (neuf) ; climatisation murale ; animaux acceptés (chats et chiens) ; assurance responsabilité 2M$ exigée ; bail 1 an ; non-fumeur.</t>
         </is>
       </c>
       <c r="Q90" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/46/4640cd13-3775-410a-bb1b-d31b508ce42e?rule=kijijica-960-jpg</t>
+          <t>https://img.zumpercdn.com/849890701/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Grand 6½ (3 chambres), 1400 pi², cour arrière privée avec patio - Hochelaga-Maisonneuve, à quelques pas du métro Pie-IX</t>
+          <t>5 1/2 RDC rénové (2 chambres, 1000 pi²), balcon et terrasse - Hochelaga-Maisonneuve, à 4 min du métro Joliette</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -8285,32 +8285,32 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>1629, Avenue William-David, Montréal, QC H1V 2R9</t>
+          <t>n/d (secteur métro Joliette, Montréal, QC H1W 3J3)</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M91" s="5" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="N91" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-a-louer-hochelaga-maisonneuve-2-500-mois/1742166450</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/joli-rdc-homa-metrojoliette-5-1-2-cour-thermopompe-1916-mo/1742514974</t>
         </is>
       </c>
       <c r="O91" s="5" t="inlineStr">
@@ -8340,12 +8340,12 @@
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, grande cour arrière privée avec patio et espace de rangement, salle à manger séparée, animaux limités acceptés, disponible 1er septembre 2026, bail 1 an, immeuble calme et bien entretenu.</t>
+          <t>Rez-de-chaussée, balcon avant et terrasse arrière avec accès à la cour, thermopompe (non chauffé), animaux limités acceptés, disponible 1er octobre 2026.</t>
         </is>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/e6/e6b95a29-4679-4834-bf64-51ea5e395509?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/46/4640cd13-3775-410a-bb1b-d31b508ce42e?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -8362,27 +8362,27 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>3 chambres, 1000 pi², grand balcon arrière - rue de Brébeuf (Plateau), à 12 min du métro Laurier</t>
+          <t>Grand 6½ (3 chambres), 1400 pi², cour arrière privée avec patio - Hochelaga-Maisonneuve, à quelques pas du métro Pie-IX</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>4690, Rue de Brébeuf, Montréal, QC H2J 3L3</t>
+          <t>1629, Avenue William-David, Montréal, QC H1V 2R9</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -8392,32 +8392,32 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1744638296867110</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-a-louer-hochelaga-maisonneuve-2-500-mois/1742166450</t>
         </is>
       </c>
       <c r="O92" s="5" t="inlineStr">
@@ -8427,19 +8427,19 @@
       </c>
       <c r="P92" s="6" t="inlineStr">
         <is>
-          <t>Rue tranquille près de la piste cyclable, 2 chambres doubles + 1 chambre simple séparées par des portes, grand balcon arrière avec 2 espaces de rangement, chats acceptés, locataires tranquilles seulement (références et vérification de crédit requises), disponible 1er oct. 2026, à 15 min à pied du métro Mont-Royal également. Lien Facebook (connexion requise).</t>
+          <t>Rez-de-chaussée, grande cour arrière privée avec patio et espace de rangement, salle à manger séparée, animaux limités acceptés, disponible 1er septembre 2026, bail 1 an, immeuble calme et bien entretenu.</t>
         </is>
       </c>
       <c r="Q92" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/768318721_1790315435646364_469913920099642119_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=N3cz2HWy8ssQ7kNvwGAA6Ly&amp;_nc_oc=AdpYp9k9bBGlPj2dTPmNwyPvNtOwuAkjglUEoI-FHHcnLP7oIJoSk9lv0x0SMl9Endg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=c8Qk5yqYeXWK0KeovEc67Q&amp;_nc_ss=7f2a8&amp;oh=00_AQG5pDUd79Jb3prByBPyIh5KC1DZhHItIgOlbOFc9dg8lA&amp;oe=6A927A6A</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/e6/e6b95a29-4679-4834-bf64-51ea5e395509?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -8449,27 +8449,27 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>6 1/2+ maison de ville (3 chambres), 1650 pi2 + 200 pi2 rangement - rue Sherbrooke Est (Hochelaga), a 2 min du metro Prefontaine</t>
+          <t>3 chambres, 1000 pi², grand balcon arrière - rue de Brébeuf (Plateau), à 12 min du métro Laurier</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>1-3200, Rue Sherbrooke Est, Montréal, QC</t>
+          <t>4690, Rue de Brébeuf, Montréal, QC H2J 3L3</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -8479,32 +8479,32 @@
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N93" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/6-1-2-a-louer/hab-1-3200-rue-sherbrooke-est-962958</t>
+          <t>https://www.facebook.com/marketplace/item/1744638296867110</t>
         </is>
       </c>
       <c r="O93" s="5" t="inlineStr">
@@ -8514,19 +8514,19 @@
       </c>
       <c r="P93" s="6" t="inlineStr">
         <is>
-          <t>Tout inclus (chauffage, electricite, eclairage, stationnement) et 6 electromenagers inclus (~275$/mois de valeur estimee), disponible immediatement, 1er etage, proche Parc Olympique, animaux non precises.</t>
+          <t>Rue tranquille près de la piste cyclable, 2 chambres doubles + 1 chambre simple séparées par des portes, grand balcon arrière avec 2 espaces de rangement, chats acceptés, locataires tranquilles seulement (références et vérification de crédit requises), disponible 1er oct. 2026, à 15 min à pied du métro Mont-Royal également. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202402/962958/6-1-2-mercier-hochelaga-maisonneuve-1600-14164374.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/768318721_1790315435646364_469913920099642119_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=N3cz2HWy8ssQ7kNvwGAA6Ly&amp;_nc_oc=AdpYp9k9bBGlPj2dTPmNwyPvNtOwuAkjglUEoI-FHHcnLP7oIJoSk9lv0x0SMl9Endg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=c8Qk5yqYeXWK0KeovEc67Q&amp;_nc_ss=7f2a8&amp;oh=00_AQG5pDUd79Jb3prByBPyIh5KC1DZhHItIgOlbOFc9dg8lA&amp;oe=6A927A6A</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8536,27 +8536,27 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé, balcon arrière - rue Saint-Dominique (Plateau)</t>
+          <t>6 1/2+ maison de ville (3 chambres), 1650 pi2 + 200 pi2 rangement - rue Sherbrooke Est (Hochelaga), a 2 min du metro Prefontaine</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>3477, Rue Saint-Dominique, Montréal, QC</t>
+          <t>1-3200, Rue Sherbrooke Est, Montréal, QC</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -8566,32 +8566,32 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>oui (balcon arrière au 2e étage)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
-          <t>Logis Québec</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357644</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/6-1-2-a-louer/hab-1-3200-rue-sherbrooke-est-962958</t>
         </is>
       </c>
       <c r="O94" s="5" t="inlineStr">
@@ -8601,15 +8601,19 @@
       </c>
       <c r="P94" s="6" t="inlineStr">
         <is>
-          <t>Meublé partiellement, four/frigo/laveuse-sécheuse inclus, disponible immédiatement, aucune mention d'animaux.</t>
-        </is>
-      </c>
-      <c r="Q94" s="5" t="inlineStr"/>
+          <t>Tout inclus (chauffage, electricite, eclairage, stationnement) et 6 electromenagers inclus (~275$/mois de valeur estimee), disponible immediatement, 1er etage, proche Parc Olympique, animaux non precises.</t>
+        </is>
+      </c>
+      <c r="Q94" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202402/962958/6-1-2-mercier-hochelaga-maisonneuve-1600-14164374.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -8619,79 +8623,75 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>4½ lumineux (2 chambres), 950 pi², 4 terrasses/balcons - secteur Ville-Marie/Hochelaga, à 8 min du métro Préfontaine (Marketplace)</t>
+          <t>5½ meublé, balcon arrière - rue Saint-Dominique (Plateau)</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud, près Hochelaga)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Ville-Marie, près Hochelaga, Montréal)</t>
+          <t>3477, Rue Saint-Dominique, Montréal, QC</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (balcon arrière au 2e étage)</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>Logis Québec</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357644</t>
+        </is>
+      </c>
+      <c r="O95" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M95" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N95" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1422338006376277</t>
-        </is>
-      </c>
-      <c r="O95" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="P95" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail pour mi-septembre, actif jusqu'au 30 juin 2027, appartement sur deux étages, climatisation, internet inclus, chats acceptés/chiens sous approbation du propriétaire, aussi à 6 min du métro Frontenac, à distance de marche des commerces (IGA, pharmacies). Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q95" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/761779740_1758473368932236_4735812340942361688_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=102&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4WZifLhDpYQ7kNvwEcYCr0&amp;_nc_oc=Adrcm9lL9mVuPexwf9FVuf5i3elBpCf3F7YMxklVosi_1NYXZKjg_8nIFJ_SCsrCjPg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=969Wdqd5PDnI9s8_YSJOPA&amp;_nc_ss=7f2a8&amp;oh=00_AQHKbO8ZfYSAOBsA3M9yItjJT_48d1Ejtpj3q50pS_2PjQ&amp;oe=6A8414C0</t>
-        </is>
-      </c>
+          <t>Meublé partiellement, four/frigo/laveuse-sécheuse inclus, disponible immédiatement, aucune mention d'animaux.</t>
+        </is>
+      </c>
+      <c r="Q95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -8706,42 +8706,42 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres), 1184 pi² - rue Clark (Plateau), à 2 min du métro Sherbrooke</t>
+          <t>4½ lumineux (2 chambres), 950 pi², 4 terrasses/balcons - secteur Ville-Marie/Hochelaga, à 8 min du métro Préfontaine (Marketplace)</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Centre-Sud, près Hochelaga)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>4054, Rue Clark, Montréal</t>
+          <t>n/d (secteur Ville-Marie, près Hochelaga, Montréal)</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
@@ -8751,17 +8751,17 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M96" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/27565003</t>
+          <t>https://www.facebook.com/marketplace/item/1422338006376277</t>
         </is>
       </c>
       <c r="O96" s="5" t="inlineStr">
@@ -8771,19 +8771,19 @@
       </c>
       <c r="P96" s="6" t="inlineStr">
         <is>
-          <t>Disponible 3 jours après acceptation, animaux non acceptés, Walk Score 100, coeur du Plateau-Mont-Royal, balcon non précisé dans l'annonce</t>
+          <t>Cession de bail pour mi-septembre, actif jusqu'au 30 juin 2027, appartement sur deux étages, climatisation, internet inclus, chats acceptés/chiens sous approbation du propriétaire, aussi à 6 min du métro Frontenac, à distance de marche des commerces (IGA, pharmacies). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q96" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD155D9DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/761779740_1758473368932236_4735812340942361688_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=102&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4WZifLhDpYQ7kNvwEcYCr0&amp;_nc_oc=Adrcm9lL9mVuPexwf9FVuf5i3elBpCf3F7YMxklVosi_1NYXZKjg_8nIFJ_SCsrCjPg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=969Wdqd5PDnI9s8_YSJOPA&amp;_nc_ss=7f2a8&amp;oh=00_AQHKbO8ZfYSAOBsA3M9yItjJT_48d1Ejtpj3q50pS_2PjQ&amp;oe=6A8414C0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -8793,62 +8793,62 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Grand 4½ rénové (2 chambres, 1200 pi²) avec balcon - avenue Henri-Julien, secteur Villeray, à 5 min du métro Jarry</t>
+          <t>5½ (3 chambres), 1184 pi² - rue Clark (Plateau), à 2 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>8226, Avenue Henri-Julien, Montréal, QC H2P 2J2</t>
+          <t>4054, Rue Clark, Montréal</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L97" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N97" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/listings/14837712p/2-bedroom-parc-extension-montreal-qc</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/27565003</t>
         </is>
       </c>
       <c r="O97" s="5" t="inlineStr">
@@ -8858,19 +8858,19 @@
       </c>
       <c r="P97" s="6" t="inlineStr">
         <is>
-          <t>Balcon arrière, disponible 1er août, animaux non permis, bail long terme uniquement. Secteur à la limite Villeray/Parc-Extension.</t>
+          <t>Disponible 3 jours après acceptation, animaux non acceptés, Walk Score 100, coeur du Plateau-Mont-Royal, balcon non précisé dans l'annonce</t>
         </is>
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/499382285/1280x960?auto=format</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD155D9DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -8880,27 +8880,27 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Terrasse privée sur le toit, 2 chambres + mezzanine (911 pi²) - rue Nicolet, à 12 min du métro Joliette</t>
+          <t>Grand 4½ rénové (2 chambres, 1200 pi²) avec balcon - avenue Henri-Julien, secteur Villeray, à 5 min du métro Jarry</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>578, Rue Nicolet, app. 401, Montréal, QC</t>
+          <t>8226, Avenue Henri-Julien, Montréal, QC H2P 2J2</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -8915,27 +8915,27 @@
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/24329498</t>
+          <t>https://www.zumper.com/listings/14837712p/2-bedroom-parc-extension-montreal-qc</t>
         </is>
       </c>
       <c r="O98" s="5" t="inlineStr">
@@ -8945,19 +8945,19 @@
       </c>
       <c r="P98" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve (2023), meublé, mezzanine polyvalente (bureau ou 3e chambre, non fermée) menant à la terrasse privée sur le toit, 1 stationnement + 1 rangement inclus, proche Marché Maisonneuve, non-fumeur, disponible 15 mars 2026.</t>
+          <t>Balcon arrière, disponible 1er août, animaux non permis, bail long terme uniquement. Secteur à la limite Villeray/Parc-Extension.</t>
         </is>
       </c>
       <c r="Q98" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE77B194DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://img.zumpercdn.com/499382285/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -8967,17 +8967,17 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Condo 2 chambres avec balcon (ELYA), quartier Centre-Sud - à 5 min du métro Frontenac</t>
+          <t>Terrasse privée sur le toit, 2 chambres + mezzanine (911 pi²) - rue Nicolet, à 12 min du métro Joliette</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Frontenac / de Rouen, Montréal)</t>
+          <t>578, Rue Nicolet, app. 401, Montréal, QC</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>911</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
@@ -9012,17 +9012,17 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/970016458942788</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/24329498</t>
         </is>
       </c>
       <c r="O99" s="5" t="inlineStr">
@@ -9032,19 +9032,19 @@
       </c>
       <c r="P99" s="6" t="inlineStr">
         <is>
-          <t>Condos ELYA (projet de 3 étages), partiellement meublé (mobilier chambre principale, 2e chambre et salon inclus), électroménagers inclus (frigo, cuisinière, lave-vaisselle, laveuse-sécheuse), assurance et internet exclus, Walk Score 97 / Transit Score 75 / Bike Score 98, quartier Centre-Sud adjacent à Hochelaga-Maisonneuve, disponible maintenant. Lien Facebook (connexion requise).</t>
+          <t>Construction neuve (2023), meublé, mezzanine polyvalente (bureau ou 3e chambre, non fermée) menant à la terrasse privée sur le toit, 1 stationnement + 1 rangement inclus, proche Marché Maisonneuve, non-fumeur, disponible 15 mars 2026.</t>
         </is>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-ord5-2.xx.fbcdn.net/v/t39.84726-6/680726095_813975818030704_4628638014475424705_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=DaakHU1OaocQ7kNvwEMEtaO&amp;_nc_oc=AdrsUr5TAVFF_e9NxaxSw-e62G_ASx45bZgZ3AKzGUiGAv7Y6AituyAR4PJfd2d07IM&amp;_nc_zt=14&amp;_nc_ht=scontent-ord5-2.xx&amp;_nc_gid=sttELMekqIl1QrHVrbiaqg&amp;_nc_ss=7f2a8&amp;oh=00_AQFHyumaRS4RXVFvesKyc1d5apqNp6RyNfym_4lCPOPaaQ&amp;oe=6A7EC616</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE77B194DDDDDDDDDDE&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9054,27 +9054,27 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Penthouse 1000 pi² (2 chambres), terrasse privée 300 pi² - Plateau-Mont-Royal, à 12 min du métro Mont-Royal</t>
+          <t>Condo 2 chambres avec balcon (ELYA), quartier Centre-Sud - à 5 min du métro Frontenac</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2W 1V8)</t>
+          <t>n/d (secteur Frontenac / de Rouen, Montréal)</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>944</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
@@ -9099,17 +9099,17 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-penthouse-de-1000-pc-sur-le-plateau-mont-royal/1741648116</t>
+          <t>https://www.facebook.com/marketplace/item/970016458942788</t>
         </is>
       </c>
       <c r="O100" s="5" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="P100" s="6" t="inlineStr">
         <is>
-          <t>Terrasse privée de 300 pi², climatisation centrale incluse (électricité non incluse), 1 chambre au rez + mezzanine pouvant servir de bureau/2e chambre, disponible 15 août 2026, animaux non acceptés. Distance métro estimée, proche boul. Mont-Royal.</t>
+          <t>Condos ELYA (projet de 3 étages), partiellement meublé (mobilier chambre principale, 2e chambre et salon inclus), électroménagers inclus (frigo, cuisinière, lave-vaisselle, laveuse-sécheuse), assurance et internet exclus, Walk Score 97 / Transit Score 75 / Bike Score 98, quartier Centre-Sud adjacent à Hochelaga-Maisonneuve, disponible maintenant. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q100" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/7b/7bf1684f-ed51-4bf3-b341-58feee6ed24e?rule=kijijica-640-webp</t>
+          <t>https://scontent-ord5-2.xx.fbcdn.net/v/t39.84726-6/680726095_813975818030704_4628638014475424705_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=DaakHU1OaocQ7kNvwEMEtaO&amp;_nc_oc=AdrsUr5TAVFF_e9NxaxSw-e62G_ASx45bZgZ3AKzGUiGAv7Y6AituyAR4PJfd2d07IM&amp;_nc_zt=14&amp;_nc_ht=scontent-ord5-2.xx&amp;_nc_gid=sttELMekqIl1QrHVrbiaqg&amp;_nc_ss=7f2a8&amp;oh=00_AQFHyumaRS4RXVFvesKyc1d5apqNp6RyNfym_4lCPOPaaQ&amp;oe=6A7EC616</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Superbe 5½ (3 chambres), 1000 pi², balcon arrière - rue Saint-Dominique (Plateau), à 7 min du métro Sherbrooke</t>
+          <t>Penthouse 1000 pi² (2 chambres), terrasse privée 300 pi² - Plateau-Mont-Royal, à 12 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>3477, Rue Saint-Dominique, Montréal, QC</t>
+          <t>n/d (Montréal, QC H2W 1V8)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
@@ -9176,27 +9176,27 @@
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l355865</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-penthouse-de-1000-pc-sur-le-plateau-mont-royal/1741648116</t>
         </is>
       </c>
       <c r="O101" s="5" t="inlineStr">
@@ -9206,12 +9206,12 @@
       </c>
       <c r="P101" s="6" t="inlineStr">
         <is>
-          <t>Disponible 1er juillet. Balcon arrière au 2e étage. Proche boul. St-Laurent (bars, restos, cafés, parcs). Station Saint-Laurent aussi à 543m.</t>
+          <t>Terrasse privée de 300 pi², climatisation centrale incluse (électricité non incluse), 1 chambre au rez + mezzanine pouvant servir de bureau/2e chambre, disponible 15 août 2026, animaux non acceptés. Distance métro estimée, proche boul. Mont-Royal.</t>
         </is>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>https://i.logisquebec.com/i-a-louer/112098/355865/img_6235_jpg_6a70ca268ebca.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/7b/7bf1684f-ed51-4bf3-b341-58feee6ed24e?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
@@ -9228,22 +9228,22 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Condo 2 chambres, 1000 pi², balcon donnant sur le parc - secteur Angus (Rosemont), à 10 min du métro Joliette</t>
+          <t>Superbe 5½ (3 chambres), 1000 pi², balcon arrière - rue Saint-Dominique (Plateau), à 7 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Angus, Rosemont, Montréal, QC)</t>
+          <t>3477, Rue Saint-Dominique, Montréal, QC</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
@@ -9263,27 +9263,27 @@
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1386486803577413</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l355865</t>
         </is>
       </c>
       <c r="O102" s="5" t="inlineStr">
@@ -9293,19 +9293,19 @@
       </c>
       <c r="P102" s="6" t="inlineStr">
         <is>
-          <t>Entièrement meublé (TV, lit, sofa), 2e étage, unité de coin, électroménagers inclus, non-fumeur (règlement copropriété), quartier calme et familial, épiceries/cafés/restos à pied, proche parcs Maisonneuve/Olympique et Jardin botanique, disponible 1er sept (possible août). Électricité et internet non inclus. Lien Facebook (connexion requise).</t>
+          <t>Disponible 1er juillet. Balcon arrière au 2e étage. Proche boul. St-Laurent (bars, restos, cafés, parcs). Station Saint-Laurent aussi à 543m.</t>
         </is>
       </c>
       <c r="Q102" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/731094510_1002296109281713_6152242066360649084_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=6QLJXgjkFIYQ7kNvwGbPagO&amp;_nc_oc=Ado322DjV9slwlwF-nupaVKpBMNygKtHzarhf1T24S2zx2jQt8lZkBlpLWqOiQQUSis&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WTNzzue3SN2xhdBOMdJYfQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHfrclMs6y2-89rp6RsPxYbEr8xpY2Z8YEMz64dFxq5kQ&amp;oe=6A7B8F79</t>
+          <t>https://i.logisquebec.com/i-a-louer/112098/355865/img_6235_jpg_6a70ca268ebca.jpg</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -9315,42 +9315,42 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres), 1650 pi², jardin privé avec solarium - rue Sherbrooke Est (Hochelaga), à 400 m du métro Préfontaine</t>
+          <t>Condo 2 chambres, 1000 pi², balcon donnant sur le parc - secteur Angus (Rosemont), à 10 min du métro Joliette</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>3200, Rue Sherbrooke Est, app. 1, Montréal</t>
+          <t>n/d (secteur Angus, Rosemont, Montréal, QC)</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N103" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/6-1-2-a-louer/hab-1-3200-rue-sherbrooke-est-962958</t>
+          <t>https://www.facebook.com/marketplace/item/1386486803577413</t>
         </is>
       </c>
       <c r="O103" s="5" t="inlineStr">
@@ -9380,12 +9380,12 @@
       </c>
       <c r="P103" s="6" t="inlineStr">
         <is>
-          <t>Style maison de ville semi-meublee, jardin prive 16x40 pi avec piece d'ete (pas de balcon traditionnel), 1 stationnement exterieur, 6 electromenagers inclus, tout inclus (chauffage/eau chaude/electricite ~275$/mois), disponible immediatement, a moins de 400 m de la ligne verte (station Prefontaine).</t>
+          <t>Entièrement meublé (TV, lit, sofa), 2e étage, unité de coin, électroménagers inclus, non-fumeur (règlement copropriété), quartier calme et familial, épiceries/cafés/restos à pied, proche parcs Maisonneuve/Olympique et Jardin botanique, disponible 1er sept (possible août). Électricité et internet non inclus. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202402/962958/6-1-2-mercier-hochelaga-maisonneuve-1600-14164374.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/731094510_1002296109281713_6152242066360649084_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=6QLJXgjkFIYQ7kNvwGbPagO&amp;_nc_oc=Ado322DjV9slwlwF-nupaVKpBMNygKtHzarhf1T24S2zx2jQt8lZkBlpLWqOiQQUSis&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WTNzzue3SN2xhdBOMdJYfQ&amp;_nc_ss=7f2a8&amp;oh=00_AQHfrclMs6y2-89rp6RsPxYbEr8xpY2Z8YEMz64dFxq5kQ&amp;oe=6A7B8F79</t>
         </is>
       </c>
     </row>
@@ -9402,52 +9402,52 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>6½ (2 chambres), 1100 pi², long balcon privé - rue Saint-Denis (Villeray), à 2 min du métro Jean-Talon</t>
+          <t>5½ (3 chambres), 1650 pi², jardin privé avec solarium - rue Sherbrooke Est (Hochelaga), à 400 m du métro Préfontaine</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>7248, Rue Saint-Denis, Montréal</t>
+          <t>3200, Rue Sherbrooke Est, app. 1, Montréal</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/6-1-2-a-louer/hab-7248-saint-denis-1139117</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/6-1-2-a-louer/hab-1-3200-rue-sherbrooke-est-962958</t>
         </is>
       </c>
       <c r="O104" s="5" t="inlineStr">
@@ -9467,12 +9467,12 @@
       </c>
       <c r="P104" s="6" t="inlineStr">
         <is>
-          <t>2e etage, semi-meuble, cuisine avec ilot, coin bureau et rangement, electricite en sus (~70$/mois estime), non-fumeur, aucun animal, a 50 m de la rue pietonne Castelnau et du marche Jean-Talon, dispo 15 aout 2026.</t>
+          <t>Style maison de ville semi-meublee, jardin prive 16x40 pi avec piece d'ete (pas de balcon traditionnel), 1 stationnement exterieur, 6 electromenagers inclus, tout inclus (chauffage/eau chaude/electricite ~275$/mois), disponible immediatement, a moins de 400 m de la ligne verte (station Prefontaine).</t>
         </is>
       </c>
       <c r="Q104" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139117/6-1-2-villeray-st-michel-parc-extension-1600-15829331.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202402/962958/6-1-2-mercier-hochelaga-maisonneuve-1600-14164374.jpg</t>
         </is>
       </c>
     </row>
@@ -9489,32 +9489,32 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ (3 chambres), balcon, cession de bail - secteur Ahuntsic, à 5 min du métro Crémazie</t>
+          <t>6½ (2 chambres), 1100 pi², long balcon privé - rue Saint-Denis (Villeray), à 2 min du métro Jean-Talon</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Ahuntsic</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>8906, Rue St-Denis, Montréal, QC H2M 1N6</t>
+          <t>7248, Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Crémazie</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr">
@@ -9534,17 +9534,17 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N105" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1043774935044930</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/6-1-2-a-louer/hab-7248-saint-denis-1139117</t>
         </is>
       </c>
       <c r="O105" s="5" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="P105" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail a compter du 1er septembre, grand salon lumineux ouvert sur balcon, cuisine fonctionnelle, 1 place de stationnement incluse, electromenagers inclus, quartier paisible et familial a quelques pas d'epiceries/cafes/parcs, Walk Score 95. Lien Facebook (connexion requise). Hors des quartiers prioritaires mais bien desservi.</t>
+          <t>2e etage, semi-meuble, cuisine avec ilot, coin bureau et rangement, electricite en sus (~70$/mois estime), non-fumeur, aucun animal, a 50 m de la rue pietonne Castelnau et du marche Jean-Talon, dispo 15 aout 2026.</t>
         </is>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/765929094_4303671686540544_7092219477975999300_n.jpg?stp=c0.166.1512.1512a_dst-jpg_tt6&amp;cstp=mx1512x1512&amp;ctp=s565x565&amp;_nc_cat=104&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=5zA1ILaMHyUQ7kNvwGlhpzF&amp;_nc_oc=Adp_wkHH4RyTizlXz8ekCeZcQ6uPgDyNS9jsnbH3EeF4p4ajoeDjrVmUj_uPo1NjYpk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WT_K7seI-W2XCrgYwGAZUg&amp;_nc_ss=7f2a8&amp;oh=00_AQHAShvk6WHIhCLx6nS8WAnMWsgefbY3rc_N0bq7nxLBxw&amp;oe=6A7AD9EC</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139117/6-1-2-villeray-st-michel-parc-extension-1600-15829331.jpg</t>
         </is>
       </c>
     </row>
@@ -9576,22 +9576,22 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Condo 3 chambres, balcon privé - rue Notre-Dame Ouest (Saint-Henri), près métro Lionel-Groulx</t>
+          <t>Grand 5½ (3 chambres), balcon, cession de bail - secteur Ahuntsic, à 5 min du métro Crémazie</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Saint-Henri (Sud-Ouest)</t>
+          <t>Ahuntsic</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>4230, Rue Notre-Dame O, Montréal, QC H4C 1R5</t>
+          <t>8906, Rue St-Denis, Montréal, QC H2M 1N6</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -9611,17 +9611,17 @@
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>Lionel-Groulx</t>
+          <t>Crémazie</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>verte/orange</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>n/d (estimé ~10-12 min, à vérifier)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M106" s="5" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="N106" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2188162795092330</t>
+          <t>https://www.facebook.com/marketplace/item/1043774935044930</t>
         </is>
       </c>
       <c r="O106" s="5" t="inlineStr">
@@ -9641,19 +9641,19 @@
       </c>
       <c r="P106" s="6" t="inlineStr">
         <is>
-          <t>Lumineux, aire ouverte, balcon prive, frigo/poele/lave-vaisselle/laveuse-secheuse inclus, animaux acceptes, disponible maintenant, Walk Score 98, proche marche Atwater et canal de Lachine. Lien Facebook (connexion requise).</t>
+          <t>Cession de bail a compter du 1er septembre, grand salon lumineux ouvert sur balcon, cuisine fonctionnelle, 1 place de stationnement incluse, electromenagers inclus, quartier paisible et familial a quelques pas d'epiceries/cafes/parcs, Walk Score 95. Lien Facebook (connexion requise). Hors des quartiers prioritaires mais bien desservi.</t>
         </is>
       </c>
       <c r="Q106" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.99422-6/762868506_1563096251987675_2174484908482643986_n.png?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=7TSDWMnQLsIQ7kNvwFZ_Yfz&amp;_nc_oc=Adq6wMOJh1Tm2ZESgbaHpWpOW14zPZekR642mfsuUxenoDwRb-jXrWkiIlPoLzUexWw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WT_K7seI-W2XCrgYwGAZUg&amp;_nc_ss=7f2a8&amp;oh=00_AQGJlY5Sb84pdqs191DP83chmBvp9F3K2p-JRzNpmqx_Mg&amp;oe=6A7AAF8A</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/765929094_4303671686540544_7092219477975999300_n.jpg?stp=c0.166.1512.1512a_dst-jpg_tt6&amp;cstp=mx1512x1512&amp;ctp=s565x565&amp;_nc_cat=104&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=5zA1ILaMHyUQ7kNvwGlhpzF&amp;_nc_oc=Adp_wkHH4RyTizlXz8ekCeZcQ6uPgDyNS9jsnbH3EeF4p4ajoeDjrVmUj_uPo1NjYpk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WT_K7seI-W2XCrgYwGAZUg&amp;_nc_ss=7f2a8&amp;oh=00_AQHAShvk6WHIhCLx6nS8WAnMWsgefbY3rc_N0bq7nxLBxw&amp;oe=6A7AD9EC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Grand 4½ rénové, 2 chambres, 1200 pi², 2 balcons - Saint-Henri (Marketplace)</t>
+          <t>Condo 3 chambres, balcon privé - rue Notre-Dame Ouest (Saint-Henri), près métro Lionel-Groulx</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -9673,22 +9673,22 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>n/d (face au parc Sir-George-Étienne-Cartier), Montréal</t>
+          <t>4230, Rue Notre-Dame O, Montréal, QC H4C 1R5</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -9698,49 +9698,49 @@
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>St-Henri</t>
+          <t>Lionel-Groulx</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte/orange</t>
         </is>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
+          <t>n/d (estimé ~10-12 min, à vérifier)</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N107" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2188162795092330</t>
+        </is>
+      </c>
+      <c r="O107" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M107" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N107" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/155798346069333</t>
-        </is>
-      </c>
-      <c r="O107" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="P107" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, planchers chauffants cuisine et salle de bain, eau chaude incluse (électricité non incluse), animaux acceptés sur demande, non-fumeur, disponible immédiatement, près du marché Atwater et du canal de Lachine. Lien exige une connexion Facebook.</t>
+          <t>Lumineux, aire ouverte, balcon prive, frigo/poele/lave-vaisselle/laveuse-secheuse inclus, animaux acceptes, disponible maintenant, Walk Score 98, proche marche Atwater et canal de Lachine. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-ord5-2.xx.fbcdn.net/v/t1.6435-9/137578251_10158940020512368_2403743444301173295_n.jpg?stp=c34.0.567.567a_dst-jpg_tt6&amp;cstp=mx567x567&amp;ctp=s565x565&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=39heVC1ViWkQ7kNvwFxoVHd&amp;_nc_oc=AdrSvAT2VrwzWLUQ0KajlXxpRh2m1SvPjDz1xXJRxDkYVFvlZWPk5k-j_bKA9sYFkeU&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.xx&amp;_nc_gid=2aY9pe_D1qPZRQwBRT2GtA&amp;_nc_ss=7f2a8&amp;oh=00_AQGfGTjfCY59jhPRkRpE__PuQYgQDZoKLpz6BkImhRkJew&amp;oe=6A970F3C</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.99422-6/762868506_1563096251987675_2174484908482643986_n.png?stp=c0.169.1536.1536a_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=7TSDWMnQLsIQ7kNvwFZ_Yfz&amp;_nc_oc=Adq6wMOJh1Tm2ZESgbaHpWpOW14zPZekR642mfsuUxenoDwRb-jXrWkiIlPoLzUexWw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=WT_K7seI-W2XCrgYwGAZUg&amp;_nc_ss=7f2a8&amp;oh=00_AQGJlY5Sb84pdqs191DP83chmBvp9F3K2p-JRzNpmqx_Mg&amp;oe=6A7AAF8A</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9750,27 +9750,27 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>2+1 chambres, 1286 pi², balcon privé - avenue Somerled (NDG, près métro Villa-Maria)</t>
+          <t>Grand 4½ rénové, 2 chambres, 1200 pi², 2 balcons - Saint-Henri (Marketplace)</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Notre-Dame-de-Grâce</t>
+          <t>Saint-Henri (Sud-Ouest)</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>5622, Avenue Somerled, Montréal</t>
+          <t>n/d (face au parc Sir-George-Étienne-Cartier), Montréal</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Villa-Maria</t>
+          <t>St-Henri</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>11 (estimé)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M108" s="5" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="N108" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1754611555548011</t>
+          <t>https://www.facebook.com/marketplace/item/155798346069333</t>
         </is>
       </c>
       <c r="O108" s="5" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="P108" s="6" t="inlineStr">
         <is>
-          <t>2 chambres + bureau polyvalent à l'étage, planchers de bois franc, cuisine rénovée, laveuse-sécheuse, climatiseur mural, balcon privé, à quelques pas du Village Monkland (commerces/cafés). Hors des quartiers prioritaires (NDG), ligne orange (pas verte). Preuve d'assurance et de revenu exigées, animaux non permis. Lien Facebook (connexion requise).</t>
+          <t>Entièrement rénové, planchers chauffants cuisine et salle de bain, eau chaude incluse (électricité non incluse), animaux acceptés sur demande, non-fumeur, disponible immédiatement, près du marché Atwater et du canal de Lachine. Lien exige une connexion Facebook.</t>
         </is>
       </c>
       <c r="Q108" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741906764_999333282900431_4323348310788966668_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=101&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=e7mVA1XcBRIQ7kNvwFL7uZt&amp;_nc_oc=AdqnFzyRZtxb7ka1eYUWiztJMyEoOnHjXRXo5ojOmyif9_CGvypBkMyBQytmKVgrTEA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DKAPrnNgmI9udtZ3TamYHQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAGyvXY24_iW0FUCA37EJ_3WuUlTOiALImCM8ETmYcvEw&amp;oe=6A6BCCAC</t>
+          <t>https://scontent-ord5-2.xx.fbcdn.net/v/t1.6435-9/137578251_10158940020512368_2403743444301173295_n.jpg?stp=c34.0.567.567a_dst-jpg_tt6&amp;cstp=mx567x567&amp;ctp=s565x565&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=39heVC1ViWkQ7kNvwFxoVHd&amp;_nc_oc=AdrSvAT2VrwzWLUQ0KajlXxpRh2m1SvPjDz1xXJRxDkYVFvlZWPk5k-j_bKA9sYFkeU&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.xx&amp;_nc_gid=2aY9pe_D1qPZRQwBRT2GtA&amp;_nc_ss=7f2a8&amp;oh=00_AQGfGTjfCY59jhPRkRpE__PuQYgQDZoKLpz6BkImhRkJew&amp;oe=6A970F3C</t>
         </is>
       </c>
     </row>
@@ -9837,32 +9837,32 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé, 3 chambres, 980 pi², 2 balcons - rue Fabre (Rosemont, près métro Beaubien)</t>
+          <t>2+1 chambres, 1286 pi², balcon privé - avenue Somerled (NDG, près métro Villa-Maria)</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Notre-Dame-de-Grâce</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>6334, Rue Fabre, Montréal</t>
+          <t>5622, Avenue Somerled, Montréal</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Villa-Maria</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>7 (estimé)</t>
+          <t>11 (estimé)</t>
         </is>
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N109" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-6334-rue-fabre-796253</t>
+          <t>https://www.facebook.com/marketplace/item/1754611555548011</t>
         </is>
       </c>
       <c r="O109" s="5" t="inlineStr">
@@ -9902,19 +9902,19 @@
       </c>
       <c r="P109" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, chauffage et électroménagers inclus, dernier étage, deux petits balcons, animaux acceptés, disponible immédiatement. Distance exacte au métro Beaubien non confirmée par l'annonce (estimée à partir de l'adresse).</t>
+          <t>2 chambres + bureau polyvalent à l'étage, planchers de bois franc, cuisine rénovée, laveuse-sécheuse, climatiseur mural, balcon privé, à quelques pas du Village Monkland (commerces/cafés). Hors des quartiers prioritaires (NDG), ligne orange (pas verte). Preuve d'assurance et de revenu exigées, animaux non permis. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201804/796253/5-1-2-rosemont-petite-patrie-1600-8635638.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741906764_999333282900431_4323348310788966668_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=101&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=e7mVA1XcBRIQ7kNvwFL7uZt&amp;_nc_oc=AdqnFzyRZtxb7ka1eYUWiztJMyEoOnHjXRXo5ojOmyif9_CGvypBkMyBQytmKVgrTEA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DKAPrnNgmI9udtZ3TamYHQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAGyvXY24_iW0FUCA37EJ_3WuUlTOiALImCM8ETmYcvEw&amp;oe=6A6BCCAC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9924,32 +9924,32 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>4½ neuf (OVILA), 2 chambres, terrasses privées, 800-1050 pi² - avenue Bennett (Hochelaga-Maisonneuve, près métro Pie-IX)</t>
+          <t>5½ meublé, 3 chambres, 980 pi², 2 balcons - rue Fabre (Rosemont, près métro Beaubien)</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>2095, Avenue Bennett, Montréal</t>
+          <t>6334, Rue Fabre, Montréal</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="N110" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-2095-avenue-bennett-1130232</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-6334-rue-fabre-796253</t>
         </is>
       </c>
       <c r="O110" s="5" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="P110" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2023-2024 (même immeuble OVILA que le 5½ déjà répertorié), superficie variable 800-1050 pi² selon l'unité, terrasses privées (BBQ permis), 5 électroménagers inclus, climatisation murale, stationnement intérieur sécurisé + local vélo, ascenseur, juste en face du Marché Maisonneuve, disponibilité non précisée</t>
+          <t>Semi-meublé, chauffage et électroménagers inclus, dernier étage, deux petits balcons, animaux acceptés, disponible immédiatement. Distance exacte au métro Beaubien non confirmée par l'annonce (estimée à partir de l'adresse).</t>
         </is>
       </c>
       <c r="Q110" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130232/3-1-2-mercier-hochelaga-maisonneuve-1600-15613061.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201804/796253/5-1-2-rosemont-petite-patrie-1600-8635638.jpg</t>
         </is>
       </c>
     </row>
@@ -10011,27 +10011,27 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>6½ lumineux, 2 chambres (+ 3e possible), balcon privé - Plateau, à 10 min du métro Mont-Royal</t>
+          <t>4½ neuf (OVILA), 2 chambres, terrasses privées, 800-1050 pi² - avenue Bennett (Hochelaga-Maisonneuve, près métro Pie-IX)</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur avenue Mont-Royal, Montréal)</t>
+          <t>2095, Avenue Bennett, Montréal</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
@@ -10041,12 +10041,12 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>oui (grand balcon privé)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7 (estimé)</t>
         </is>
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N111" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/973452448907992</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-2095-avenue-bennett-1130232</t>
         </is>
       </c>
       <c r="O111" s="5" t="inlineStr">
@@ -10076,12 +10076,12 @@
       </c>
       <c r="P111" s="6" t="inlineStr">
         <is>
-          <t>Possibilité de 3e chambre sans fenêtre, à 3 min de l'avenue Mont-Royal et ses commerces, réfrigérateur/cuisinière/lave-vaisselle non inclus, dispo 1er juillet, lien exige une connexion Facebook</t>
+          <t>Construction neuve 2023-2024 (même immeuble OVILA que le 5½ déjà répertorié), superficie variable 800-1050 pi² selon l'unité, terrasses privées (BBQ permis), 5 électroménagers inclus, climatisation murale, stationnement intérieur sécurisé + local vélo, ascenseur, juste en face du Marché Maisonneuve, disponibilité non précisée</t>
         </is>
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/722412619_1617305450011741_6846067607866144954_n.jpg?stp=c0.169.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=i88TCt10YGMQ7kNvwEnUsao&amp;_nc_oc=AdrvLp-lCdA5ACif3RiqpRsnZSFYYbio12l9aPpcJgaEV6yKGgapKeozdS-BwYw-o4k&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fvFLeV7qKVviv4IuubP9nA&amp;_nc_ss=7f2a8&amp;oh=00_AQAd5veOG2wwylzp4NkrAahwV01Fgfi6q3HfSwQ0p9yT_w&amp;oe=6A6A6CB2</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130232/3-1-2-mercier-hochelaga-maisonneuve-1600-15613061.jpg</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres fermées, balcon - Plateau (boul. Saint-Laurent)</t>
+          <t>6½ lumineux, 2 chambres (+ 3e possible), balcon privé - Plateau, à 10 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>4655, Boulevard Saint-Laurent, Montréal</t>
+          <t>n/d (secteur avenue Mont-Royal, Montréal)</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (grand balcon privé)</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal (à vérifier)</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>11 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M112" s="5" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="N112" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1310293694593951</t>
+          <t>https://www.facebook.com/marketplace/item/973452448907992</t>
         </is>
       </c>
       <c r="O112" s="5" t="inlineStr">
@@ -10163,19 +10163,19 @@
       </c>
       <c r="P112" s="6" t="inlineStr">
         <is>
-          <t>Cuisine rénovée avec 5 électroménagers inclus (cuisinière, réfrigérateur, lave-vaisselle, laveuse, sécheuse), proche universités et espaces verts, enquête de crédit et références requises, lien exige une connexion Facebook</t>
+          <t>Possibilité de 3e chambre sans fenêtre, à 3 min de l'avenue Mont-Royal et ses commerces, réfrigérateur/cuisinière/lave-vaisselle non inclus, dispo 1er juillet, lien exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q112" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/749286191_10234373342255525_9092352675603353029_n.jpg?stp=c106.0.428.428a_dst-jpg_tt6&amp;cstp=mx428x428&amp;ctp=s428x428&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=ic73Tw0-fv0Q7kNvwFNI03n&amp;_nc_oc=AdoRe9nP95ciefPsFjp2Cz9dDFg9ClCwxaH95PBTgjuHGcE-LLH8Zj-Pkys_8IC0dFw&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fvFLeV7qKVviv4IuubP9nA&amp;_nc_ss=7f2a8&amp;oh=00_AQAUDDqQ7V8ap6HixCq0L7v792rJEBP5hErOYq_FI48LzQ&amp;oe=6A6A7D85</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/722412619_1617305450011741_6846067607866144954_n.jpg?stp=c0.169.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=i88TCt10YGMQ7kNvwEnUsao&amp;_nc_oc=AdrvLp-lCdA5ACif3RiqpRsnZSFYYbio12l9aPpcJgaEV6yKGgapKeozdS-BwYw-o4k&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fvFLeV7qKVviv4IuubP9nA&amp;_nc_ss=7f2a8&amp;oh=00_AQAd5veOG2wwylzp4NkrAahwV01Fgfi6q3HfSwQ0p9yT_w&amp;oe=6A6A6CB2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -10185,27 +10185,27 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, terrasse et jardin privés, 900 pi² - Hochelaga-Maisonneuve, entre métro Joliette et Pie-IX</t>
+          <t>4½ rénové, 2 chambres fermées, balcon - Plateau (boul. Saint-Laurent)</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>1693, Avenue Bourbonnière, Montréal, QC H1W 3N5</t>
+          <t>4655, Boulevard Saint-Laurent, Montréal</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
@@ -10230,32 +10230,32 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
+          <t>11 (estimé)</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N113" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1310293694593951</t>
+        </is>
+      </c>
+      <c r="O113" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M113" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N113" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1034802492591491</t>
-        </is>
-      </c>
-      <c r="O113" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="P113" s="6" t="inlineStr">
         <is>
-          <t>Disponible immédiatement, rez-de-chaussée, terrasse et jardin privatifs, cuisine à aire ouverte rénovée, 2 chambres fermées (dont une sans fenêtre), quartier vivant (Promenade Ontario et Place Simon-Valois à quelques pas, épicerie Metro à 1 min, boulangerie Arhoma à 3 min), lien exige une connexion Facebook</t>
+          <t>Cuisine rénovée avec 5 électroménagers inclus (cuisinière, réfrigérateur, lave-vaisselle, laveuse, sécheuse), proche universités et espaces verts, enquête de crédit et références requises, lien exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/753150552_1751825949398830_7748096224825680064_n.jpg?stp=c0.131.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=txNuAhu_pLcQ7kNvwHiiRz0&amp;_nc_oc=Adq4Y8hUGt7t-fn9-xMzOJvF0XnAxulDS6h6MJ1-H-KzkyPCGVe0wKms14Y_Cv6WhBg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=B5o1L6DOFl7nDR-4qOZp8w&amp;_nc_ss=7f2a8&amp;oh=00_AQDrCMy7mTtG81cVO5z7qMXz4EH2WeIi2mo0WvZTs_F2eg&amp;oe=6A69ACB2</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/749286191_10234373342255525_9092352675603353029_n.jpg?stp=c106.0.428.428a_dst-jpg_tt6&amp;cstp=mx428x428&amp;ctp=s428x428&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=ic73Tw0-fv0Q7kNvwFNI03n&amp;_nc_oc=AdoRe9nP95ciefPsFjp2Cz9dDFg9ClCwxaH95PBTgjuHGcE-LLH8Zj-Pkys_8IC0dFw&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fvFLeV7qKVviv4IuubP9nA&amp;_nc_ss=7f2a8&amp;oh=00_AQAUDDqQ7V8ap6HixCq0L7v792rJEBP5hErOYq_FI48LzQ&amp;oe=6A6A7D85</t>
         </is>
       </c>
     </row>
@@ -10272,27 +10272,27 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>4½ lumineux ~1000 pi², 2 chambres, à 2 min du métro Berri-UQAM - Ville-Marie (Village)</t>
+          <t>4½ rénové, terrasse et jardin privés, 900 pi² - Hochelaga-Maisonneuve, entre métro Joliette et Pie-IX</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud/Village)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Rue St-Christophe, Montréal, QC H2L 3W5</t>
+          <t>1693, Avenue Bourbonnière, Montréal, QC H1W 3N5</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>Berri-UQAM</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M114" s="5" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="N114" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1751858266169561</t>
+          <t>https://www.facebook.com/marketplace/item/1034802492591491</t>
         </is>
       </c>
       <c r="O114" s="5" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="P114" s="6" t="inlineStr">
         <is>
-          <t>Appartement traversant au 2e étage, climatisation murale, chauffage individuel, cuisine équipée (laveuse-sécheuse, four, lave-vaisselle inclus), terrasses, IGA (Place Dupuis) à 2 min, hydro et internet en sus, disponible 2026-07-31, lien exige une connexion Facebook</t>
+          <t>Disponible immédiatement, rez-de-chaussée, terrasse et jardin privatifs, cuisine à aire ouverte rénovée, 2 chambres fermées (dont une sans fenêtre), quartier vivant (Promenade Ontario et Place Simon-Valois à quelques pas, épicerie Metro à 1 min, boulangerie Arhoma à 3 min), lien exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q114" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/745314157_4506616636283141_3078788711921915710_n.jpg?stp=c210.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=v9K3UGzkcsEQ7kNvwERCe40&amp;_nc_oc=Adq52vl1YHgj2RMkHyNT0S_0Vl2aVMc6rxpiAPilcaq2j13AUN-pcICWqlsACnEP_pM&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=B5o1L6DOFl7nDR-4qOZp8w&amp;_nc_ss=7f2a8&amp;oh=00_AQDa9_6CM7_wxQCzlfSVLvzBKNIKKamC-XDLllZx_H39MA&amp;oe=6A69AB7F</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/753150552_1751825949398830_7748096224825680064_n.jpg?stp=c0.131.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=txNuAhu_pLcQ7kNvwHiiRz0&amp;_nc_oc=Adq4Y8hUGt7t-fn9-xMzOJvF0XnAxulDS6h6MJ1-H-KzkyPCGVe0wKms14Y_Cv6WhBg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=B5o1L6DOFl7nDR-4qOZp8w&amp;_nc_ss=7f2a8&amp;oh=00_AQDrCMy7mTtG81cVO5z7qMXz4EH2WeIi2mo0WvZTs_F2eg&amp;oe=6A69ACB2</t>
         </is>
       </c>
     </row>
@@ -10359,22 +10359,22 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ de 1000 pi² rénové, entrée privée, 2 chambres fermées - Parc Angus (Rosemont), 900m du métro Joliette</t>
+          <t>4½ lumineux ~1000 pi², 2 chambres, à 2 min du métro Berri-UQAM - Ville-Marie (Village)</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Ville-Marie (Centre-Sud/Village)</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>4295, Rue Moïse-Picard, Montréal</t>
+          <t>Rue St-Christophe, Montréal, QC H2L 3W5</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Berri-UQAM</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M115" s="5" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="N115" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1326176662918618</t>
+          <t>https://www.facebook.com/marketplace/item/1751858266169561</t>
         </is>
       </c>
       <c r="O115" s="5" t="inlineStr">
@@ -10424,19 +10424,19 @@
       </c>
       <c r="P115" s="6" t="inlineStr">
         <is>
-          <t>Condo entièrement rénové, entrée privée, 2 grandes chambres fermées + coin bureau, 2 balcons dont 1 grande terrasse, plancher chauffant salle de bain, thermopompe, situé dans les Shops Angus, disponible 31 juillet, lien exige une connexion Facebook</t>
+          <t>Appartement traversant au 2e étage, climatisation murale, chauffage individuel, cuisine équipée (laveuse-sécheuse, four, lave-vaisselle inclus), terrasses, IGA (Place Dupuis) à 2 min, hydro et internet en sus, disponible 2026-07-31, lien exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q115" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/746502992_1028593923434855_1315585068431478383_n.jpg?stp=c0.133.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NP6TLDhnpIcQ7kNvwGeEfBB&amp;_nc_oc=AdpOse6UOfV704_DU5qcUb8vc3t1c1r2QKlkwuG-vgXxMK0tksSPCnO45ydv_nMMlsE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=2IPC_R3iEO52q4kqKBqevQ&amp;_nc_ss=7f2a8&amp;oh=00_AQCq9I6GwYWVyjtri2el3bYacFYyqLRS34hHZzP65cH1zQ&amp;oe=6A6930CE</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/745314157_4506616636283141_3078788711921915710_n.jpg?stp=c210.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=v9K3UGzkcsEQ7kNvwERCe40&amp;_nc_oc=Adq52vl1YHgj2RMkHyNT0S_0Vl2aVMc6rxpiAPilcaq2j13AUN-pcICWqlsACnEP_pM&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=B5o1L6DOFl7nDR-4qOZp8w&amp;_nc_ss=7f2a8&amp;oh=00_AQDa9_6CM7_wxQCzlfSVLvzBKNIKKamC-XDLllZx_H39MA&amp;oe=6A69AB7F</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -10446,22 +10446,22 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>5½ de 3 chambres avec balcon - rue Saint-Dominique (Plateau-Mont-Royal, près métro Sherbrooke)</t>
+          <t>Condo 4½ de 1000 pi² rénové, entrée privée, 2 chambres fermées - Parc Angus (Rosemont), 900m du métro Joliette</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>3477 Rue Saint-Dominique, Montréal</t>
+          <t>4295, Rue Moïse-Picard, Montréal</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
@@ -10481,27 +10481,27 @@
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M116" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N116" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l353533</t>
+          <t>https://www.facebook.com/marketplace/item/1326176662918618</t>
         </is>
       </c>
       <c r="O116" s="5" t="inlineStr">
@@ -10511,15 +10511,19 @@
       </c>
       <c r="P116" s="6" t="inlineStr">
         <is>
-          <t>Balcon arrière, disponible 1er juillet, prix exactement au plafond du budget (2400$)</t>
-        </is>
-      </c>
-      <c r="Q116" s="5" t="inlineStr"/>
+          <t>Condo entièrement rénové, entrée privée, 2 grandes chambres fermées + coin bureau, 2 balcons dont 1 grande terrasse, plancher chauffant salle de bain, thermopompe, situé dans les Shops Angus, disponible 31 juillet, lien exige une connexion Facebook</t>
+        </is>
+      </c>
+      <c r="Q116" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/746502992_1028593923434855_1315585068431478383_n.jpg?stp=c0.133.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NP6TLDhnpIcQ7kNvwGeEfBB&amp;_nc_oc=AdpOse6UOfV704_DU5qcUb8vc3t1c1r2QKlkwuG-vgXxMK0tksSPCnO45ydv_nMMlsE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=2IPC_R3iEO52q4kqKBqevQ&amp;_nc_ss=7f2a8&amp;oh=00_AQCq9I6GwYWVyjtri2el3bYacFYyqLRS34hHZzP65cH1zQ&amp;oe=6A6930CE</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -10529,17 +10533,17 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>6½ lumineux, 2 chambres + bureau, 1125 pi² - rue Chambord (Rosemont), près métro Beaubien</t>
+          <t>5½ de 3 chambres avec balcon - rue Saint-Dominique (Plateau-Mont-Royal, près métro Sherbrooke)</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>6565 Rue Chambord, Montréal</t>
+          <t>3477 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -10549,22 +10553,22 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>oui (avant et arrière)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
@@ -10574,17 +10578,17 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M117" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N117" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/6-1-2-a-louer/hab-6565-chambord-1132276</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l353533</t>
         </is>
       </c>
       <c r="O117" s="5" t="inlineStr">
@@ -10594,19 +10598,15 @@
       </c>
       <c r="P117" s="6" t="inlineStr">
         <is>
-          <t>3e étage d'un triplex, dispo immédiatement (1er juillet), non-fumeurs, pas d'animaux, prix à la limite haute du budget</t>
-        </is>
-      </c>
-      <c r="Q117" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132276/6-1-2-rosemont-petite-patrie-600-15660148.jpg</t>
-        </is>
-      </c>
+          <t>Balcon arrière, disponible 1er juillet, prix exactement au plafond du budget (2400$)</t>
+        </is>
+      </c>
+      <c r="Q117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -10616,27 +10616,27 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (2 chambres + bureau fermé), balcon arrière - rue Saint-Denis (Villeray)</t>
+          <t>6½ lumineux, 2 chambres + bureau, 1125 pi² - rue Chambord (Rosemont), près métro Beaubien</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>8360 Rue Saint-Denis, Montréal</t>
+          <t>6565 Rue Chambord, Montréal</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (avant et arrière)</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M118" s="5" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="N118" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-8360-st-denis-1132893</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/6-1-2-a-louer/hab-6565-chambord-1132276</t>
         </is>
       </c>
       <c r="O118" s="5" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="P118" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové 2024, électroménagers haut de gamme, walk-in, porte-patio, balcon arrière sur ruelle tranquille, dispo 1er sept. 2026, 2e étage</t>
+          <t>3e étage d'un triplex, dispo immédiatement (1er juillet), non-fumeurs, pas d'animaux, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q118" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132893/5-1-2-villeray-st-michel-parc-extension-600-15673596.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132276/6-1-2-rosemont-petite-patrie-600-15660148.jpg</t>
         </is>
       </c>
     </row>
@@ -10703,32 +10703,32 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
+          <t>5½ rénové (2 chambres + bureau fermé), balcon arrière - rue Saint-Denis (Villeray)</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>4224 Rue de Bellechasse, Montréal</t>
+          <t>8360 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
@@ -10738,27 +10738,27 @@
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Fabre (à vérifier)</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>2 (estimé)</t>
         </is>
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N119" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-8360-st-denis-1132893</t>
         </is>
       </c>
       <c r="O119" s="5" t="inlineStr">
@@ -10768,19 +10768,19 @@
       </c>
       <c r="P119" s="6" t="inlineStr">
         <is>
-          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
+          <t>Entièrement rénové 2024, électroménagers haut de gamme, walk-in, porte-patio, balcon arrière sur ruelle tranquille, dispo 1er sept. 2026, 2e étage</t>
         </is>
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132893/5-1-2-villeray-st-michel-parc-extension-600-15673596.jpg</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -10790,32 +10790,32 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
+          <t>4224 Rue de Bellechasse, Montréal</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
@@ -10825,27 +10825,27 @@
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Joliette/Pie-IX</t>
+          <t>Fabre (à vérifier)</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N120" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
         </is>
       </c>
       <c r="O120" s="5" t="inlineStr">
@@ -10855,19 +10855,19 @@
       </c>
       <c r="P120" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q120" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -10877,27 +10877,27 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N121" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O121" s="5" t="inlineStr">
@@ -10942,10 +10942,14 @@
       </c>
       <c r="P121" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q121" s="5" t="inlineStr"/>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+        </is>
+      </c>
+      <c r="Q121" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -10960,22 +10964,22 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -10995,7 +10999,7 @@
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
@@ -11015,7 +11019,7 @@
       </c>
       <c r="N122" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O122" s="5" t="inlineStr">
@@ -11025,7 +11029,7 @@
       </c>
       <c r="P122" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
         </is>
       </c>
       <c r="Q122" s="5" t="inlineStr"/>
@@ -11033,7 +11037,7 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -11043,42 +11047,42 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
@@ -11088,17 +11092,17 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N123" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O123" s="5" t="inlineStr">
@@ -11108,19 +11112,15 @@
       </c>
       <c r="P123" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q123" s="5" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -11130,27 +11130,27 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>3 chambres (5½), 1005 pi², 2 balcons - secteur Rosemont-Petite-Patrie</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Rosemont / La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1T 1H8, Rosemont-Petite-Patrie)</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -11160,54 +11160,54 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N124" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-5-5-a-louer-dans-rosemont-petite-patrie/1744531044</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O124" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P124" s="6" t="inlineStr">
         <is>
-          <t>Cuisine et salle de bain neuves, planchers sables/vernis, laveuse-secheuse in-unit, petit animal tranquille possiblement tolere, disponible 15 oct. 2026, station de metro non precisee par l'annonce</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q124" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/db/db4c19e3-57ea-4dc1-b36e-afa035401891?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -11217,32 +11217,32 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>4½ unite de coin (2 chambres), 980 pi², balcon - coin Villeray et Chambord (Villeray), proche metro De Castelnau</t>
+          <t>3 chambres (5½), 1005 pi², 2 balcons - secteur Rosemont-Petite-Patrie</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont / La Petite-Patrie</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>n/d (coin rue Villeray et rue Chambord, Montreal, QC)</t>
+          <t>n/d (Montréal, QC H1T 1H8, Rosemont-Petite-Patrie)</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -11252,17 +11252,17 @@
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>De Castelnau</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>10 (estime)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M125" s="5" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="N125" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer-4-1-2-coin-villeray-et-chambord-montreal/1744362598</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-5-5-a-louer-dans-rosemont-petite-patrie/1744531044</t>
         </is>
       </c>
       <c r="O125" s="5" t="inlineStr">
@@ -11282,19 +11282,19 @@
       </c>
       <c r="P125" s="6" t="inlineStr">
         <is>
-          <t>Unite de coin lumineuse, chauffage/hydro/eau inclus, thermopompe (chauffage+climatisation), laveuse-secheuse/lave-vaisselle/frigo/cuisiniere inclus, rangement au sous-sol, bail a terme fixe jusqu'au 30 juin 2028, verification de credit requise. Station de metro et distance estimees a partir de l'intersection (non precisees dans l'annonce).</t>
+          <t>Cuisine et salle de bain neuves, planchers sables/vernis, laveuse-secheuse in-unit, petit animal tranquille possiblement tolere, disponible 15 oct. 2026, station de metro non precisee par l'annonce</t>
         </is>
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/aa/aa1d2521-b516-4bc7-a6ff-d9d756abfde9?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/db/db4c19e3-57ea-4dc1-b36e-afa035401891?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -11304,42 +11304,42 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>6½ rénové (3 chambres), 1600 pi², cour arrière privée - rue Saint-Hubert (Villeray), à 10 min du métro Jarry</t>
+          <t>4½ unite de coin (2 chambres), 980 pi², balcon - coin Villeray et Chambord (Villeray), proche metro De Castelnau</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>8413, Rue Saint-Hubert, Montréal, QC</t>
+          <t>n/d (coin rue Villeray et rue Chambord, Montreal, QC)</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>De Castelnau</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estime)</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="N126" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-cour-arriere-privee-villeray-electros-inclus/1744379988</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer-4-1-2-coin-villeray-et-chambord-montreal/1744362598</t>
         </is>
       </c>
       <c r="O126" s="5" t="inlineStr">
@@ -11369,12 +11369,12 @@
       </c>
       <c r="P126" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée + sous-sol, 5 électroménagers neufs inclus (lave-vaisselle, frigo/congélateur, laveuse-sécheuse à l'unité), cour arrière privée (pas de balcon), 1 chat accepté (chiens refusés), bail 12 mois renouvelable, disponible 1er oct. 2026, bus 30 à 2 min, proche épicerie/pharmacie. Propriétaire professionnel (Devloc Immobilier).</t>
+          <t>Unite de coin lumineuse, chauffage/hydro/eau inclus, thermopompe (chauffage+climatisation), laveuse-secheuse/lave-vaisselle/frigo/cuisiniere inclus, rangement au sous-sol, bail a terme fixe jusqu'au 30 juin 2028, verification de credit requise. Station de metro et distance estimees a partir de l'intersection (non precisees dans l'annonce).</t>
         </is>
       </c>
       <c r="Q126" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/fa/fa88dfaa-c4bc-49f5-bfd5-884ae35b5b87?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/aa/aa1d2521-b516-4bc7-a6ff-d9d756abfde9?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1200 pi² - rue Saint-Denis (Villeray), proche métro Jarry</t>
+          <t>6½ rénové (3 chambres), 1600 pi², cour arrière privée - rue Saint-Hubert (Villeray), à 10 min du métro Jarry</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -11401,17 +11401,17 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur rue Saint-Denis, Montréal, QC H2R 2E9)</t>
+          <t>8413, Rue Saint-Hubert, Montréal, QC</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -11421,12 +11421,12 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Jarry (estimé)</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>10-12 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M127" s="5" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="N127" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/bright-renovated-3-bedroom-villeray-saint-denis-montreal/1744205540</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-cour-arriere-privee-villeray-electros-inclus/1744379988</t>
         </is>
       </c>
       <c r="O127" s="5" t="inlineStr">
@@ -11456,19 +11456,19 @@
       </c>
       <c r="P127" s="6" t="inlineStr">
         <is>
-          <t>Duplex/triplex, 2 salles de bain, 2 salons et 2 cuisines, planchers de bois franc, électroménagers inox (frigo, cuisinière, lave-vaisselle), laveuse-sécheuse à l'unité, wifi inclus, électricité non incluse, chauffage non électrique (type non précisé), animaux étudiés sur demande, disponible dès maintenant (annonce datée 30 sept. 2026). Adresse exacte et balcon non précisés par l'annonce ; station de métro Jarry estimée à partir du secteur Saint-Denis/Villeray (à confirmer).</t>
+          <t>Rez-de-chaussée + sous-sol, 5 électroménagers neufs inclus (lave-vaisselle, frigo/congélateur, laveuse-sécheuse à l'unité), cour arrière privée (pas de balcon), 1 chat accepté (chiens refusés), bail 12 mois renouvelable, disponible 1er oct. 2026, bus 30 à 2 min, proche épicerie/pharmacie. Propriétaire professionnel (Devloc Immobilier).</t>
         </is>
       </c>
       <c r="Q127" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3f/3f43b849-82ae-4f6d-b8f4-b39f8a0a6f6f?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/fa/fa88dfaa-c4bc-49f5-bfd5-884ae35b5b87?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -11478,27 +11478,27 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres fermées + pièce additionnelle), grande cuisine, balcon avant et terrasse arrière - secteur Mile-Ex, entre les métros Beaubien et Rosemont</t>
+          <t>5½ rénové (3 chambres), 1200 pi² - rue Saint-Denis (Villeray), proche métro Jarry</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie (secteur Mile-Ex)</t>
+          <t>Villeray-Saint-Michel-Parc-Extension</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>n/d (Avenue de l'Esplanade, secteur Mile-Ex, Montréal, QC H2V 4L5)</t>
+          <t>n/d (secteur rue Saint-Denis, Montréal, QC H2R 2E9)</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -11508,22 +11508,22 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>oui (balcon avant + terrasse arrière + cour)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>Beaubien ou Rosemont (à confirmer)</t>
+          <t>Jarry (estimé)</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>10-12 (estimé, à vérifier)</t>
+          <t>10-12 (estimé)</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="N128" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-mile-ex/1744015089</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/bright-renovated-3-bedroom-villeray-saint-denis-montreal/1744205540</t>
         </is>
       </c>
       <c r="O128" s="5" t="inlineStr">
@@ -11543,12 +11543,12 @@
       </c>
       <c r="P128" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, chauffage et eau chaude inclus (électricité ~70$/mois), 3 chambres fermées + 4e pièce sans fenêtre (bureau/salon), grande cuisine, lave-vaisselle/frigo/cuisinière/laveuse inclus, climatisation, 1 stationnement inclus, animaux limités, disponible 1er nov. 2026, bail 1 an. Secteur Mile-Ex entre Rosemont et Petite-Italie ; distance exacte au métro non précisée par l'annonce, à vérifier sur place.</t>
+          <t>Duplex/triplex, 2 salles de bain, 2 salons et 2 cuisines, planchers de bois franc, électroménagers inox (frigo, cuisinière, lave-vaisselle), laveuse-sécheuse à l'unité, wifi inclus, électricité non incluse, chauffage non électrique (type non précisé), animaux étudiés sur demande, disponible dès maintenant (annonce datée 30 sept. 2026). Adresse exacte et balcon non précisés par l'annonce ; station de métro Jarry estimée à partir du secteur Saint-Denis/Villeray (à confirmer).</t>
         </is>
       </c>
       <c r="Q128" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/48/4875e800-c3d2-40b9-a1e0-b8cc1835b4fb?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3f/3f43b849-82ae-4f6d-b8f4-b39f8a0a6f6f?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -11565,52 +11565,52 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail - 4½ (2 chambres, 2 sdb), 1000 pi², terrasse et cour - Villeray, à deux pas du métro Jarry</t>
+          <t>5½ (3 chambres fermées + pièce additionnelle), grande cuisine, balcon avant et terrasse arrière - secteur Mile-Ex, entre les métros Beaubien et Rosemont</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension</t>
+          <t>Rosemont-La Petite-Patrie (secteur Mile-Ex)</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Parc Jarry, Montréal, QC H2T 2V2)</t>
+          <t>n/d (Avenue de l'Esplanade, secteur Mile-Ex, Montréal, QC H2V 4L5)</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>oui (grande terrasse + cour)</t>
+          <t>oui (balcon avant + terrasse arrière + cour)</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Beaubien ou Rosemont (à confirmer)</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>10-12 (estimé, à vérifier)</t>
         </is>
       </c>
       <c r="M129" s="5" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="N129" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/lease-transfer-spacious-2-bed-2-bath-in-villeray/1744270943</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-mile-ex/1744015089</t>
         </is>
       </c>
       <c r="O129" s="5" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="P129" s="6" t="inlineStr">
         <is>
-          <t>2 chambres, 2 salles de bain, rez-de-chaussée avec grande terrasse et cour, à quelques pas du parc Jarry et du métro Jarry (ligne orange). Frigo/cuisinière/lave-vaisselle inclus, branchements laveuse-sécheuse, chauffage et électricité non inclus, animaux acceptés, non-fumeur, cession de bail dès le 1er déc. 2025 jusqu'au 1er mai 2026 puis renouvelable.</t>
+          <t>Cession de bail, chauffage et eau chaude inclus (électricité ~70$/mois), 3 chambres fermées + 4e pièce sans fenêtre (bureau/salon), grande cuisine, lave-vaisselle/frigo/cuisinière/laveuse inclus, climatisation, 1 stationnement inclus, animaux limités, disponible 1er nov. 2026, bail 1 an. Secteur Mile-Ex entre Rosemont et Petite-Italie ; distance exacte au métro non précisée par l'annonce, à vérifier sur place.</t>
         </is>
       </c>
       <c r="Q129" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0f/0ff407fb-b934-41df-b29f-2dbe4379a94d?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/48/4875e800-c3d2-40b9-a1e0-b8cc1835b4fb?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Beau 6½ (4 chambres fermées), 1200 pi², climatisation - secteur Villeray/Rosemont, à 9 min du métro Fabre</t>
+          <t>Cession de bail - 4½ (2 chambres, 2 sdb), 1000 pi², terrasse et cour - Villeray, à deux pas du métro Jarry</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -11662,42 +11662,42 @@
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur métro Fabre, Villeray/Rosemont, Montréal, QC)</t>
+          <t>n/d (secteur Parc Jarry, Montréal, QC H2T 2V2)</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui (grande terrasse + cour)</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="N130" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-4cac-metro-fabre-villeray-rosemont/1743964018</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/lease-transfer-spacious-2-bed-2-bath-in-villeray/1744270943</t>
         </is>
       </c>
       <c r="O130" s="5" t="inlineStr">
@@ -11717,19 +11717,19 @@
       </c>
       <c r="P130" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, pas de stationnement, animaux limités aux chats, non-fumeur (intérieur et extérieur), cannabis interdit, bail 1 an, secteur très calme, Walk Score 10/Transit Score 10, proche d'une station BIXI. Disponible 1er oct. 2026. Présence d'un balcon non précisée par l'annonce.</t>
+          <t>2 chambres, 2 salles de bain, rez-de-chaussée avec grande terrasse et cour, à quelques pas du parc Jarry et du métro Jarry (ligne orange). Frigo/cuisinière/lave-vaisselle inclus, branchements laveuse-sécheuse, chauffage et électricité non inclus, animaux acceptés, non-fumeur, cession de bail dès le 1er déc. 2025 jusqu'au 1er mai 2026 puis renouvelable.</t>
         </is>
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/b1/b1c97521-30fd-418c-973c-f0c5a0823131?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0f/0ff407fb-b934-41df-b29f-2dbe4379a94d?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové, 2 chambres fermées, grande terrasse privée - rue Saint-Hubert (Villeray), à quelques pas du métro Jean-Talon</t>
+          <t>Beau 6½ (4 chambres fermées), 1200 pi², climatisation - secteur Villeray/Rosemont, à 9 min du métro Fabre</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -11749,52 +11749,52 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>7250, Rue Saint-Hubert, app. 305, Montréal, QC</t>
+          <t>n/d (secteur métro Fabre, Villeray/Rosemont, Montréal, QC)</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>7 (estimé)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N131" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/21269608</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-4cac-metro-fabre-villeray-rosemont/1743964018</t>
         </is>
       </c>
       <c r="O131" s="5" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="P131" s="6" t="inlineStr">
         <is>
-          <t>2 salles de bain complètes, 1 place de stationnement garage, rangement inclus, cuisine moderne aire ouverte, Walk Score 99, libre 1er déc. 2026. Métro Jean-Talon (lignes orange et bleue) à quelques pas selon l'annonce.</t>
+          <t>Climatisation incluse, pas de stationnement, animaux limités aux chats, non-fumeur (intérieur et extérieur), cannabis interdit, bail 1 an, secteur très calme, Walk Score 10/Transit Score 10, proche d'une station BIXI. Disponible 1er oct. 2026. Présence d'un balcon non précisée par l'annonce.</t>
         </is>
       </c>
       <c r="Q131" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2F2347DDDDDDDDDDE&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/b1/b1c97521-30fd-418c-973c-f0c5a0823131?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>5½, 2 chambres fermées + atelier, 2 balcons - rue Saint-Denis (Villeray), près des métros Jean-Talon et Jarry</t>
+          <t>Condo 4½ rénové, 2 chambres fermées, grande terrasse privée - rue Saint-Hubert (Villeray), à quelques pas du métro Jean-Talon</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Rue Saint-Denis, Montréal, QC H2R 2E9</t>
+          <t>7250, Rue Saint-Hubert, app. 305, Montréal, QC</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -11856,32 +11856,32 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>7 (estimé)</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N132" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-2-chambres-a-villeray/1744171535</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/21269608</t>
         </is>
       </c>
       <c r="O132" s="5" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="P132" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées + atelier/bureau (configuration a confirmer), salle de bain renovee 2022, electromenagers neufs 2022 (frigo, lave-vaisselle), laveuse-secheuse a l'unite, coin double salon, hydro a la charge du locataire, animaux acceptes, disponible 1er oct. 2026, bail 1 an, secteur commercant anime de Villeray. Adresse exacte non precisee par l'annonceur (secteur rue Saint-Denis, code postal H2R 2E9) ; station de metro et distance estimees a partir de ce secteur.</t>
+          <t>2 salles de bain complètes, 1 place de stationnement garage, rangement inclus, cuisine moderne aire ouverte, Walk Score 99, libre 1er déc. 2026. Métro Jean-Talon (lignes orange et bleue) à quelques pas selon l'annonce.</t>
         </is>
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1f/1f4aaa78-98b6-4cbe-b7a1-bc73c5f5c864?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2F2347DDDDDDDDDDE&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Grand condo 3 chambres fermées, 1615 pi² - 12e Avenue (Villeray/Saint-Michel), à 5 min du métro Saint-Michel</t>
+          <t>5½, 2 chambres fermées + atelier, 2 balcons - rue Saint-Denis (Villeray), près des métros Jean-Talon et Jarry</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -11923,52 +11923,52 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>7105, 12e Avenue, app. 3, Montréal, QC</t>
+          <t>Rue Saint-Denis, Montréal, QC H2R 2E9</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N133" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/22967692</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-2-chambres-a-villeray/1744171535</t>
         </is>
       </c>
       <c r="O133" s="5" t="inlineStr">
@@ -11978,12 +11978,12 @@
       </c>
       <c r="P133" s="6" t="inlineStr">
         <is>
-          <t>9 pieces au total, 1 salle de bain + 1 salle d'eau, construit en 1969, Walk Score 94, non-fumeur, disponible 5 jours apres acceptation de la promesse de location. Balcon non precise dans l'annonce. Distance au metro Saint-Michel (ligne bleue) estimee a 5 min de marche a partir de l'adresse.</t>
+          <t>2 chambres fermées + atelier/bureau (configuration a confirmer), salle de bain renovee 2022, electromenagers neufs 2022 (frigo, lave-vaisselle), laveuse-secheuse a l'unite, coin double salon, hydro a la charge du locataire, animaux acceptes, disponible 1er oct. 2026, bail 1 an, secteur commercant anime de Villeray. Adresse exacte non precisee par l'annonceur (secteur rue Saint-Denis, code postal H2R 2E9) ; station de metro et distance estimees a partir de ce secteur.</t>
         </is>
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE623092DDDDDDDDDD1&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1f/1f4aaa78-98b6-4cbe-b7a1-bc73c5f5c864?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -576,258 +576,258 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Grand 6½, 2 chambres + bureau, jardin privé clôturé - rue Cuvillier (Hochelaga-Maisonneuve), à qqs minutes du métro Joliette</t>
+          <t>5½ rénové, 3 chambres fermées, 1250 pi², balcon - rue Saint-Louis (Plateau-Mont-Royal), face au parc Jeanne-Mance</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Rue Saint-Louis, Montréal, QC H2W 2N4</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>10-12 (estimé, à vérifier)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-emplacement-parfait/1736891738</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Chauffé et eau chaude inclus, laveuse-sécheuse et lave-vaisselle inclus, animaux acceptés, face au parc Jeanne-Mance, libre 1er oct. 2026. ATTENTION : loyer promotionnel la 1re année (2195$), remonte à 2645$/mois au renouvellement - à vérifier avant de visiter.</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/58/58ff440f-a1b5-47e0-ad60-2ce9c09ef345?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Rare grand logement, 3 chambres fermées + 2 bureaux, 1200 pi², balcon - rue Gauthier (Plateau/De Lorimier), à ~8 min du métro Papineau</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>2184, Rue Gauthier, Montréal</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Papineau</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rare-large-plateau-3-bedrooms-2-office-spaces/1742864871</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>Grand solarium/balcon arriere prive, 2 salles de bain, eau chaude incluse, laveuse-secheuse in-unit, proche avenue du Mont-Royal (cafes/restos/epiceries/boulangeries), disponible 31 oct. 2026, animaux limites, distance au metro estimee (non confirmee par l'annonce elle-meme)</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/dd/dde6421b-1352-4e19-b7af-361e4ec0cd82?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>3 chambres fermées meublé, 1200 pi², balcon - HOMA, à 1 min du métro Pie-IX</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
           <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2265, Rue Cuvillier, Montréal</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H1V 2E7)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Pie-IX</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>5 (estimé)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rare-:-grand-6-jardin-prive-chiens-et-chats-acceptes-metr/1744540259</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Jardin privé clôturé, chiens et chats acceptés (max 2), internet haute vitesse inclus, chauffage et eau chaude inclus (électricité en sus), libre 8 oct. 2026, bail jusqu'au 30 juin 2027</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a3/a3ed511f-7786-47a1-98b6-1bd8ee837d8a?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>5½ sur 2 étages, 2 chambres + bureau, balcon privé - rue Saint-André (Rosemont), à 3 min du métro Beaubien</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>6790, Rue Saint-André, app. 101, Montréal</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Beaubien</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/11517731</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>Style maisonette sur 2 étages, 2 salles de bain complètes, bureau séparé (utilisable comme 3e chambre), climatisation murale, animaux non acceptés, fumeurs non acceptés, Walk Score 99, libre 1er sept. 2026</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADA3CF3DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>3 chambres fermées, 900 pi², directement face au métro Pie-IX - boulevard Pie-IX (Hochelaga-Maisonneuve)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2645, Boulevard Pie-IX, app. 1, Montréal</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Pie-IX</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/12105558</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Rénové, semi-meublé, électroménagers neufs, thermopompe murale, wifi et eau chaude inclus, stationnement extérieur optionnel 100$/mois, animaux acceptés sous conditions, disponible immédiatement</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DACE479EDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-fully-furnished-in-homa/1744496516</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>Meuble avec bureau dedie, toutes charges incluses (chauffage, hydro, eau), climatisation, stationnement prive inclus, laveuse-secheuse a l'unite, animaux acceptes, bail mensuel possible, disponible immediatement.</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/25/25ed6e06-9846-40bd-9f5b-c75dfb9fa5b3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Rare grand logement, 3 chambres fermées + 2 bureaux, 1200 pi², balcon - rue Gauthier (Plateau/De Lorimier), à ~8 min du métro Papineau</t>
+          <t>5½ rénové (3 chambres fermées), 1250 pi², balcon, chauffé et eau chaude inclus - Plateau (secteur Saint-Louis), face au parc Jeanne-Mance</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -847,17 +847,17 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>2184, Rue Gauthier, Montréal</t>
+          <t>n/d (Montréal, QC H2W 2N4)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Papineau</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rare-large-plateau-3-bedrooms-2-office-spaces/1742864871</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-emplacement-parfait/1736891738</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
@@ -902,19 +902,19 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>Grand solarium/balcon arriere prive, 2 salles de bain, eau chaude incluse, laveuse-secheuse in-unit, proche avenue du Mont-Royal (cafes/restos/epiceries/boulangeries), disponible 31 oct. 2026, animaux limites, distance au metro estimee (non confirmee par l'annonce elle-meme)</t>
+          <t>Prix promotionnel 1re année (2245$/mois), prix régulier 2645$/mois par la suite - à vérifier au renouvellement. Duplex/triplex, entrée privée, face au parc Jeanne-Mance et vue sur le Mont-Royal, laveuse-sécheuse et lave-vaisselle inclus, frigo/congélateur inclus, chauffage et eau chaude inclus, animaux acceptés, fumeur extérieur seulement, disponible 1er oct. 2026, bail 1 an. Walk Score 10, Transit Score 10. Station non précisée par l'annonce, Sherbrooke (ligne verte) estimée à ~12 min.</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/dd/dde6421b-1352-4e19-b7af-361e4ec0cd82?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/58/58ff440f-a1b5-47e0-ad60-2ce9c09ef345?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées meublé, 1200 pi², balcon - HOMA, à 1 min du métro Pie-IX</t>
+          <t>Grand 6½ rénové (4 chambres fermées), 1200 pi², balcon et grande cour - Hochelaga-Maisonneuve, à 6 min du métro Joliette</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2E7)</t>
+          <t>n/d (Montréal, QC H1W 1C7)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-fully-furnished-in-homa/1744496516</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-renove-4-chambres-homa/1743249113</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
@@ -989,19 +989,19 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Meuble avec bureau dedie, toutes charges incluses (chauffage, hydro, eau), climatisation, stationnement prive inclus, laveuse-secheuse a l'unite, animaux acceptes, bail mensuel possible, disponible immediatement.</t>
+          <t>Entièrement rénové, cuisine et salon séparés, laveuse-sécheuse (branchements), frigo/congélateur inclus, grande cour arrière, stationnement disponible, animaux acceptés, hydro non inclus, non-fumeur (extérieur permis), disponible 9 sept. 2026, bail 1 an.</t>
         </is>
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/25/25ed6e06-9846-40bd-9f5b-c75dfb9fa5b3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/95/957701f8-3728-48b2-8c06-e6ce352b8efb?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres fermées), 1250 pi², balcon, chauffé et eau chaude inclus - Plateau (secteur Saint-Louis), face au parc Jeanne-Mance</t>
+          <t>5½ sur deux étages, 3 chambres, 2 balcons - rue Napoléon (Plateau), à ~8-9 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2W 2N4)</t>
+          <t>106, Rue Napoléon, Montréal</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>8-9 (estimé)</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>logisquebec</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-emplacement-parfait/1736891738</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l358813</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
@@ -1076,19 +1076,15 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>Prix promotionnel 1re année (2245$/mois), prix régulier 2645$/mois par la suite - à vérifier au renouvellement. Duplex/triplex, entrée privée, face au parc Jeanne-Mance et vue sur le Mont-Royal, laveuse-sécheuse et lave-vaisselle inclus, frigo/congélateur inclus, chauffage et eau chaude inclus, animaux acceptés, fumeur extérieur seulement, disponible 1er oct. 2026, bail 1 an. Walk Score 10, Transit Score 10. Station non précisée par l'annonce, Sherbrooke (ligne verte) estimée à ~12 min.</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/58/58ff440f-a1b5-47e0-ad60-2ce9c09ef345?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ sur deux étages, 2 balcons, secteur Plateau proche métro Sherbrooke (ligne verte, ~676 m).</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1098,7 +1094,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Grand 6½ rénové (4 chambres fermées), 1200 pi², balcon et grande cour - Hochelaga-Maisonneuve, à 6 min du métro Joliette</t>
+          <t>5½ rénové (3 chambres), 1100 pi², grand balcon arrière privé - rue La Fontaine (Hochelaga), à 5 min du métro Pie-IX</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1108,7 +1104,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 1C7)</t>
+          <t>4602, Rue La Fontaine, Montréal, QC</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1118,12 +1114,12 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1133,7 +1129,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1143,17 +1139,17 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-renove-4-chambres-homa/1743249113</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22900247</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
@@ -1163,19 +1159,19 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, cuisine et salon séparés, laveuse-sécheuse (branchements), frigo/congélateur inclus, grande cour arrière, stationnement disponible, animaux acceptés, hydro non inclus, non-fumeur (extérieur permis), disponible 9 sept. 2026, bail 1 an.</t>
+          <t>Entièrement rénové, thermopompe, cuisine et salle de bain refaites, 1 mois gratuit en promotion, animaux à discuter, disponible immédiatement, Walk Score 94.</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/95/957701f8-3728-48b2-8c06-e6ce352b8efb?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F87A3DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1185,7 +1181,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>5½ sur deux étages, 3 chambres, 2 balcons - rue Napoléon (Plateau), à ~8-9 min du métro Sherbrooke</t>
+          <t>5½ rénové (3 chambres), 1100 pi², balcon - rue de Bullion (Plateau), à 11 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1195,12 +1191,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>106, Rue Napoléon, Montréal</t>
+          <t>3984, Rue de Bullion, Montréal, QC H2W 2E4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1230,17 +1226,17 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>8-9 (estimé)</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>logisquebec</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l358813</t>
+          <t>https://www.zumper.com/address/3984-rue-de-bullion-montreal-qc-h2w-2e4-can</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
@@ -1250,15 +1246,19 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>5½ sur deux étages, 2 balcons, secteur Plateau proche métro Sherbrooke (ligne verte, ~676 m).</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr"/>
+          <t>Plafonds de 9,5 pieds, plancher de bois franc récemment repeint, laveuse-sécheuse et électroménagers inclus, animaux acceptés, électricité/chauffage/eau non inclus, bail 1 an, à 3 rues du boul. Saint-Laurent.</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>https://img.zumpercdn.com/895146226/1280x960?dpr=1&amp;fit=crop&amp;h=542&amp;q=76&amp;w=991</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1268,27 +1268,27 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1100 pi², grand balcon arrière privé - rue La Fontaine (Hochelaga), à 5 min du métro Pie-IX</t>
+          <t>5½ rénové, 3 chambres, près métro Pie-IX (Rosemont)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>4602, Rue La Fontaine, Montréal, QC</t>
+          <t>4419, Avenue Charlemagne, Montréal</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22900247</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l355773</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -1333,19 +1333,15 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, thermopompe, cuisine et salle de bain refaites, 1 mois gratuit en promotion, animaux à discuter, disponible immédiatement, Walk Score 94.</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F87A3DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
+          <t>Récemment rénové, non meublé, proche du Parc Maisonneuve et du Jardin botanique, disponible 1er juillet 2026.</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1355,22 +1351,22 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1100 pi², balcon - rue de Bullion (Plateau), à 11 min du métro Sherbrooke</t>
+          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>3984, Rue de Bullion, Montréal, QC H2W 2E4</t>
+          <t>Près du parc Lalancette (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1390,7 +1386,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1400,17 +1396,17 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/address/3984-rue-de-bullion-montreal-qc-h2w-2e4-can</t>
+          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -1420,19 +1416,19 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Plafonds de 9,5 pieds, plancher de bois franc récemment repeint, laveuse-sécheuse et électroménagers inclus, animaux acceptés, électricité/chauffage/eau non inclus, bail 1 an, à 3 rues du boul. Saint-Laurent.</t>
+          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/895146226/1280x960?dpr=1&amp;fit=crop&amp;h=542&amp;q=76&amp;w=991</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1442,27 +1438,27 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 3 chambres, près métro Pie-IX (Rosemont)</t>
+          <t>Cession de bail - Grand 5½ de 1700 pi², balcon, garage inclus, a ~6 min du metro Laurier - Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>4419, Avenue Charlemagne, Montréal</t>
+          <t>Avenue Laurier Est (Montreal, QC H2L 3M7)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1477,45 +1473,49 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6 (estime)</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l355773</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/location-appartement-1700pi2-5-1-2-garage-inclus-plateau/1743833147</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Récemment rénové, non meublé, proche du Parc Maisonneuve et du Jardin botanique, disponible 1er juillet 2026.</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr"/>
+          <t>Cession de bail, 3 grandes chambres fermees, balcon inclus, garage ferme gratuit, grand sous-sol chauffe pour rangement, entree independante, chauffage au gaz, electromenagers inclus (cuisiniere, frigo, lave-vaisselle, laveuse, secheuse), animaux limites, disponible 1er dec. 2026, bail 1 an requis.</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/88/88e3586c-3218-4aa4-b913-57f910f11d5e?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1525,42 +1525,42 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
+          <t>Cession de bail - 5½ (2 chambres fermées), 1200 pi², grande cour arrière avec jardin et terrasse, stationnement privé inclus - secteur Chabot/Rosemont/des Carrières, proche métro Rosemont</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Près du parc Lalancette (adresse exacte n/d)</t>
+          <t>n/d (secteur Chabot/Rosemont/des Carrières, Montréal, QC H2G 2S7)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (jardin + grande terrasse)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1570,39 +1570,39 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8-10 (estimé)</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-2-chambres-rosemont-jardin-stationnement/1744312413</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
+          <t>Cession de bail dès 1er nov. 2026, grande cour arrière privée avec jardin et grande terrasse, stationnement privé inclus, électroménagers inclus, climatisation, remise extérieure, rangement vélo, cuisine rénovée, loyer 2340$ + environ 200$/mois d'électricité estimée, chats acceptés (petits chiens à discuter avec propriétaire), proche métro Rosemont (ligne verte) et plusieurs lignes d'autobus ; distance exacte non précisée par l'annonce.</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2c/2cbf05b8-a8f5-4168-85ce-bd54d4fd4c0e?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1612,27 +1612,27 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail - Grand 5½ de 1700 pi², balcon, garage inclus, a ~6 min du metro Laurier - Plateau-Mont-Royal</t>
+          <t>Haut de duplex rénové (3 chambres), 1100 pi², balcon - secteur La Petite-Patrie, proche « métro Fabre » (non officiel)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Avenue Laurier Est (Montreal, QC H2L 3M7)</t>
+          <t>n/d (secteur La Petite-Patrie, Montréal, QC H2G 2P9)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Fabre (station non officielle, à vérifier)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>6 (estime)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/location-appartement-1700pi2-5-1-2-garage-inclus-plateau/1743833147</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/haut-de-duplex/1743595578</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -1677,19 +1677,19 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, 3 grandes chambres fermees, balcon inclus, garage ferme gratuit, grand sous-sol chauffe pour rangement, entree independante, chauffage au gaz, electromenagers inclus (cuisiniere, frigo, lave-vaisselle, laveuse, secheuse), animaux limites, disponible 1er dec. 2026, bail 1 an requis.</t>
+          <t>Haut de duplex entièrement rénové, planchers de bois avec boiseries de chêne, lave-vaisselle et frigo/congélateur inclus, climatisation, chauffage et électricité inclus dans le loyer, non-fumeur à l'intérieur, aucun animal, libre 24 sept. 2026, bail 1 an. L'annonce mentionne un « métro Fabre » qui n'existe pas (comme pour d'autres fiches du secteur) ; distance estimée à partir du quartier La Petite-Patrie, à confirmer.</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/88/88e3586c-3218-4aa4-b913-57f910f11d5e?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/18/18749eaf-b75e-4198-85b4-10a2dfe07a36?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail - 5½ (2 chambres fermées), 1200 pi², grande cour arrière avec jardin et terrasse, stationnement privé inclus - secteur Chabot/Rosemont/des Carrières, proche métro Rosemont</t>
+          <t>5½ avec garage, 3 chambres fermées, 2 balcons - boulevard Pie-IX (Rosemont/Villeray), à 12 min du métro Saint-Michel</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1709,52 +1709,52 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Chabot/Rosemont/des Carrières, Montréal, QC H2G 2S7)</t>
+          <t>7238, Boulevard Pie-IX, Montréal, QC</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>oui (jardin + grande terrasse)</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>8-10 (estimé)</t>
+          <t>12 (estimé, 980 m)</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuebec</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-2-chambres-rosemont-jardin-stationnement/1744312413</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l363372</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -1764,19 +1764,15 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail dès 1er nov. 2026, grande cour arrière privée avec jardin et grande terrasse, stationnement privé inclus, électroménagers inclus, climatisation, remise extérieure, rangement vélo, cuisine rénovée, loyer 2340$ + environ 200$/mois d'électricité estimée, chats acceptés (petits chiens à discuter avec propriétaire), proche métro Rosemont (ligne verte) et plusieurs lignes d'autobus ; distance exacte non précisée par l'annonce.</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2c/2cbf05b8-a8f5-4168-85ce-bd54d4fd4c0e?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Garage privé inclus, rez-de-chaussée bien isolé, électroménagers inclus (cuisinière, frigo, laveuse-sécheuse), disponible immédiatement. Situé entre Villeray et Petite-Patrie, près de Jean-Talon Est. Chauffage et électricité non inclus.</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1786,7 +1782,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Haut de duplex rénové (3 chambres), 1100 pi², balcon - secteur La Petite-Patrie, proche « métro Fabre » (non officiel)</t>
+          <t>5½ rénové, 3 chambres fermées, grand balcon - avenue Louis-Hébert (Rosemont/Petite-Patrie), à 10 min du métro Beaubien</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1796,17 +1792,17 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur La Petite-Patrie, Montréal, QC H2G 2P9)</t>
+          <t>5838, Avenue Louis-Hébert, Montréal, QC H2G 2G2</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1821,12 +1817,12 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Fabre (station non officielle, à vérifier)</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1841,7 +1837,7 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/haut-de-duplex/1743595578</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-rosemont-gem-spacious-3-bedroom-fully-equipped/1742621981</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -1851,19 +1847,19 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Haut de duplex entièrement rénové, planchers de bois avec boiseries de chêne, lave-vaisselle et frigo/congélateur inclus, climatisation, chauffage et électricité inclus dans le loyer, non-fumeur à l'intérieur, aucun animal, libre 24 sept. 2026, bail 1 an. L'annonce mentionne un « métro Fabre » qui n'existe pas (comme pour d'autres fiches du secteur) ; distance estimée à partir du quartier La Petite-Patrie, à confirmer.</t>
+          <t>2 thermopompes (chauffage+clim), laveuse-sécheuse et électroménagers neufs (four, lave-vaisselle, frigo XL), wifi et eau inclus, animaux limités, disponible 1er sept. 2026, bail 1 an avec sous-location/cession possible, pharmacie/épicerie/café à 2 min à pied, ruelle verte adjacente. Distance au métro Beaubien (ligne verte) estimée à 10 min de marche (769 m).</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/18/18749eaf-b75e-4198-85b4-10a2dfe07a36?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3a/3a0782e0-8e3f-45d2-837e-7359b10b34d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1873,22 +1869,22 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>5½ avec garage, 3 chambres fermées, 2 balcons - boulevard Pie-IX (Rosemont/Villeray), à 12 min du métro Saint-Michel</t>
+          <t>Grand 4 1/2 lumineux, 1100 pi², balcon + rooftop privatif - Centre-Sud</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>7238, Boulevard Pie-IX, Montréal, QC</t>
+          <t>n/d (secteur avenue de Lorimier / rue Ontario, Montréal, QC H2K 3X1)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1898,37 +1894,37 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé, 980 m)</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>LogisQuebec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-rosemont_la-petite-patrie-l363372</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-lumineux/1744143048</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -1938,15 +1934,19 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Garage privé inclus, rez-de-chaussée bien isolé, électroménagers inclus (cuisinière, frigo, laveuse-sécheuse), disponible immédiatement. Situé entre Villeray et Petite-Patrie, près de Jean-Talon Est. Chauffage et électricité non inclus.</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="inlineStr"/>
+          <t>Balcon + rooftop privatif, laveuse/sécheuse intégrées, lave-vaisselle et réfrigérateur inclus, eau incluse, animaux acceptés, bail 1 an. Adresse exacte non précisée dans l'annonce (seul le code postal est donné) ; station de métro et distance estimées à partir de ce secteur.</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/11/114f80ab-055b-478f-887d-b3648a7716dd?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 3 chambres fermées, grand balcon - avenue Louis-Hébert (Rosemont/Petite-Patrie), à 10 min du métro Beaubien</t>
+          <t>Grand 5 1/2, 3 chambres, 1200 pi², balcon avant et arrière - secteur Parc-Jarry</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Jarry)</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>5838, Avenue Louis-Hébert, Montréal, QC H2G 2G2</t>
+          <t>n/d (secteur rue Marquette, Parc-Jarry, Montréal, QC H2E 2C8)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-rosemont-gem-spacious-3-bedroom-fully-equipped/1742621981</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1743217472</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -2021,19 +2021,19 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>2 thermopompes (chauffage+clim), laveuse-sécheuse et électroménagers neufs (four, lave-vaisselle, frigo XL), wifi et eau inclus, animaux limités, disponible 1er sept. 2026, bail 1 an avec sous-location/cession possible, pharmacie/épicerie/café à 2 min à pied, ruelle verte adjacente. Distance au métro Beaubien (ligne verte) estimée à 10 min de marche (769 m).</t>
+          <t>Balcon avant et arrière, climatisation, sécurité/concierge 24h, animaux non admis sauf chats, bail 1 an. L'annonce mentionne un 'métro Fabre' qui n'existe pas : le secteur (rue Marquette, Parc-Jarry) est en réalité à distance de marche de la station Jarry (ligne orange), retenue ici en estimation.</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3a/3a0782e0-8e3f-45d2-837e-7359b10b34d8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/ba98470a-66af-4439-89d7-a03111a24476?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2043,22 +2043,22 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Grand 4 1/2 lumineux, 1100 pi², balcon + rooftop privatif - Centre-Sud</t>
+          <t>4½ rez-de-chaussée avec garage, 2 chambres, 1100 pi², balcon - rue Dézéry (Hochelaga), à 3-5 min du métro Préfontaine</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur avenue de Lorimier / rue Ontario, Montréal, QC H2K 3X1)</t>
+          <t>2098, Rue Dézéry, Montréal, QC H1W 2S2</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-lumineux/1744143048</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/spacious-ground-floor-4-with-garage-in-hochelaga/1744003883</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2108,19 +2108,19 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>Balcon + rooftop privatif, laveuse/sécheuse intégrées, lave-vaisselle et réfrigérateur inclus, eau incluse, animaux acceptés, bail 1 an. Adresse exacte non précisée dans l'annonce (seul le code postal est donné) ; station de métro et distance estimées à partir de ce secteur.</t>
+          <t>Rez-de-chaussée, 1 garage inclus, laveuse-sécheuse à l'unité, cuisine avec îlot, planchers de bois, briques et poutres apparentes, climatisation, option d'achat des électroménagers, animaux limités acceptés, non meublé, bail 1 an, rue résidentielle calme, disponible 1er déc. 2026, à proximité des stations Préfontaine et Joliette (ligne verte). Chauffage non précisé dans l'annonce.</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/11/114f80ab-055b-478f-887d-b3648a7716dd?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/f4/f459c2bd-a442-4b8e-a10e-f394f280e33e?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2130,27 +2130,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres, 1200 pi², balcon avant et arrière - secteur Parc-Jarry</t>
+          <t>5½ rénové, 3 chambres, 1100 pi², 2 balcons - av. De Châteaubriand (Petite-Patrie), à 5 min du métro Jean-Talon (Marketplace)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Jarry)</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur rue Marquette, Parc-Jarry, Montréal, QC H2E 2C8)</t>
+          <t>6911, Avenue De Châteaubriand, Montréal, QC H2S 2N9</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2160,32 +2160,32 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1743217472</t>
+          <t>https://www.facebook.com/marketplace/item/4692029684455917</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2195,19 +2195,15 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Balcon avant et arrière, climatisation, sécurité/concierge 24h, animaux non admis sauf chats, bail 1 an. L'annonce mentionne un 'métro Fabre' qui n'existe pas : le secteur (rue Marquette, Parc-Jarry) est en réalité à distance de marche de la station Jarry (ligne orange), retenue ici en estimation.</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/ba98470a-66af-4439-89d7-a03111a24476?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Rez-de-chaussée, plancher bois franc, entrée laveuse/sécheuse, lave-vaisselle. Métro Jean-Talon à 350 m, marché Jean-Talon à 450 m, Plaza St-Hubert adjacente, face à un parc. Non chauffé, non éclairé. Libre immédiatement. Lien Facebook (connexion requise).</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2217,22 +2213,22 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>4½ rez-de-chaussée avec garage, 2 chambres, 1100 pi², balcon - rue Dézéry (Hochelaga), à 3-5 min du métro Préfontaine</t>
+          <t>5½ rénové, 3 chambres, 1100 pi², terrasse privée - av. De Châteaubriand (Petite-Patrie), à 5 min du métro Jean-Talon (Marketplace)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2098, Rue Dézéry, Montréal, QC H1W 2S2</t>
+          <t>6909, Avenue De Châteaubriand, Montréal, QC H2S 2N9</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2242,37 +2238,37 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (terrasse privée)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/spacious-ground-floor-4-with-garage-in-hochelaga/1744003883</t>
+          <t>https://www.facebook.com/marketplace/item/1965931567448549</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -2282,14 +2278,10 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, 1 garage inclus, laveuse-sécheuse à l'unité, cuisine avec îlot, planchers de bois, briques et poutres apparentes, climatisation, option d'achat des électroménagers, animaux limités acceptés, non meublé, bail 1 an, rue résidentielle calme, disponible 1er déc. 2026, à proximité des stations Préfontaine et Joliette (ligne verte). Chauffage non précisé dans l'annonce.</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/f4/f459c2bd-a442-4b8e-a10e-f394f280e33e?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Même immeuble et même propriétaire que le 6911. Rez-de-chaussée, sous-sol de rangement, stationnement inclus selon une 2e annonce du même logement (item 910103881888546, libre 1er oct.). Lien Facebook (connexion requise).</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2304,7 +2296,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 3 chambres, 1100 pi², 2 balcons - av. De Châteaubriand (Petite-Patrie), à 5 min du métro Jean-Talon (Marketplace)</t>
+          <t>5½, 3 chambres, 1250 pi², grande terrasse - av. Christophe-Colomb (Rosemont), près du métro Rosemont (Marketplace)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2314,17 +2306,17 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>6911, Avenue De Châteaubriand, Montréal, QC H2S 2N9</t>
+          <t>5726, Avenue Christophe-Colomb, Montréal, QC H2S 2G1</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2334,22 +2326,22 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui (grande terrasse/balcon privé)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7 (estimé)</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -2359,7 +2351,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/4692029684455917</t>
+          <t>https://www.facebook.com/marketplace/item/2322777655136518</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2369,7 +2361,7 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, plancher bois franc, entrée laveuse/sécheuse, lave-vaisselle. Métro Jean-Talon à 350 m, marché Jean-Talon à 450 m, Plaza St-Hubert adjacente, face à un parc. Non chauffé, non éclairé. Libre immédiatement. Lien Facebook (connexion requise).</t>
+          <t>Planchers de bois, fraîchement peint, cuisine avec beaucoup de rangement, bain/douche. Disponible maintenant. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr"/>
@@ -2387,52 +2379,52 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 3 chambres, 1100 pi², terrasse privée - av. De Châteaubriand (Petite-Patrie), à 5 min du métro Jean-Talon (Marketplace)</t>
+          <t>Grand logement 4 chambres, 2 sdb, 1800 pi², 2 balcons - rue Bélanger, près du métro Fabre (Marketplace)</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie (limite Villeray)</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>6909, Avenue De Châteaubriand, Montréal, QC H2S 2N9</t>
+          <t>2302, Rue Bélanger, Montréal, QC H2G 1C8</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>oui (terrasse privée)</t>
+          <t>oui (2 balcons)</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -2442,7 +2434,7 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1965931567448549</t>
+          <t>https://www.facebook.com/marketplace/item/2476229422857514</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2452,7 +2444,7 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Même immeuble et même propriétaire que le 6911. Rez-de-chaussée, sous-sol de rangement, stationnement inclus selon une 2e annonce du même logement (item 910103881888546, libre 1er oct.). Lien Facebook (connexion requise).</t>
+          <t>Inclus : frigo, four, laveuse/sécheuse, climatisation, eau chaude. Stationnement disponible. Animaux acceptés. Disponible 30 sept. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q23" s="5" t="inlineStr"/>
@@ -2470,27 +2462,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>5½, 3 chambres, 1250 pi², grande terrasse - av. Christophe-Colomb (Rosemont), près du métro Rosemont (Marketplace)</t>
+          <t>Grand 5½ (3 chambres), 1700 pi², balcon, garage inclus - avenue Laurier Est (Plateau), cession de bail</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>5726, Avenue Christophe-Colomb, Montréal, QC H2S 2G1</t>
+          <t>Avenue Laurier Est, Montréal, QC H2L 3M7</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2500,12 +2492,12 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>oui (grande terrasse/balcon privé)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -2515,17 +2507,17 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>7 (estimé)</t>
+          <t>12 (estimé, à vérifier)</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2322777655136518</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/location-appartement-5-1-2-1700pi2-garage-inclus-plateau/1743833147</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2535,15 +2527,19 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Planchers de bois, fraîchement peint, cuisine avec beaucoup de rangement, bain/douche. Disponible maintenant. Lien Facebook (connexion requise).</t>
-        </is>
-      </c>
-      <c r="Q24" s="5" t="inlineStr"/>
+          <t>Cession de bail, libre 1er déc.; chauffage au gaz; garage, lave-vaisselle, laveuse-sécheuse; distance au métro à vérifier (Laurier ou Papineau)</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/88/88e3586c-3218-4aa4-b913-57f910f11d5e?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2553,62 +2549,62 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Grand logement 4 chambres, 2 sdb, 1800 pi², 2 balcons - rue Bélanger, près du métro Fabre (Marketplace)</t>
+          <t>5½ (3 chambres fermées), 920 pi², balcon - secteur Ateliers Angus (Rosemont), à 10 min du métro Préfontaine</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie (limite Villeray)</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2302, Rue Bélanger, Montréal, QC H2G 1C8</t>
+          <t>n/d (secteur Ateliers Angus, Montréal, QC H1X 2H3)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>oui (2 balcons)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2476229422857514</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-a-louer-3-chambres-shop-angus-montreal/1743567611</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2618,15 +2614,19 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Inclus : frigo, four, laveuse/sécheuse, climatisation, eau chaude. Stationnement disponible. Animaux acceptés. Disponible 30 sept. Lien Facebook (connexion requise).</t>
-        </is>
-      </c>
-      <c r="Q25" s="5" t="inlineStr"/>
+          <t>Plancher bois sur dalle béton avec isolation phonique, climatisation, locker disponible, animaux limités, libre 4 octobre, quartier vivant proche commerces et parcs.</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c2/c2ddd2a9-e29a-4342-bd11-8edefeef5b45?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -2636,27 +2636,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ (3 chambres), 1700 pi², balcon, garage inclus - avenue Laurier Est (Plateau), cession de bail</t>
+          <t>Grand 5½ (3 chambres), 1200 pi², 2 balcons - Villeray/Rosemont, à 10 min du métro Fabre</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Avenue Laurier Est, Montréal, QC H2L 3M7</t>
+          <t>n/d (Montréal, QC H2E 2C8)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé, à vérifier)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/location-appartement-5-1-2-1700pi2-garage-inclus-plateau/1743833147</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1743217472</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, libre 1er déc.; chauffage au gaz; garage, lave-vaisselle, laveuse-sécheuse; distance au métro à vérifier (Laurier ou Papineau)</t>
+          <t>Immeuble sécurisé avec concierge 24h, climatisation incluse, accès laveuse-sécheuse, animaux limités (chats seulement), chauffage non inclus, disponible 12 sept. 2026, bail 1 an. Walk Score 8/10, Transit Score 9/10.</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/88/88e3586c-3218-4aa4-b913-57f910f11d5e?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/ba98470a-66af-4439-89d7-a03111a24476?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2723,27 +2723,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres fermées), 920 pi², balcon - secteur Ateliers Angus (Rosemont), à 10 min du métro Préfontaine</t>
+          <t>Grand 5 1/2 Plateau-Mont-Royal, près du parc Laurier</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Ateliers Angus, Montréal, QC H1X 2H3)</t>
+          <t>5483, Rue Cartier, Montréal</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-a-louer-3-chambres-shop-angus-montreal/1743567611</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-plateau-disponible-des-maintenant/1742926253</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2788,19 +2788,19 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>Plancher bois sur dalle béton avec isolation phonique, climatisation, locker disponible, animaux limités, libre 4 octobre, quartier vivant proche commerces et parcs.</t>
+          <t>Libre immédiatement, 3 balcons (avant, arrière, latéral), remise et BBQ inclus, bail 1 an, animaux acceptés sous conditions, station BIXI à 2 min</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c2/c2ddd2a9-e29a-4342-bd11-8edefeef5b45?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a1/a156df4e-a074-4098-9f9f-fa7b1b73bbed?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ (3 chambres), 1200 pi², 2 balcons - Villeray/Rosemont, à 10 min du métro Fabre</t>
+          <t>5½ rénové, 1200 pi², 3 chambres, balcon - rue Villeray, à ~10 min du métro De Castelnau</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2E 2C8)</t>
+          <t>3007, Rue Villeray, Montréal</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>De Castelnau</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1743217472</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/16587333</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
@@ -2875,19 +2875,19 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Immeuble sécurisé avec concierge 24h, climatisation incluse, accès laveuse-sécheuse, animaux limités (chats seulement), chauffage non inclus, disponible 12 sept. 2026, bail 1 an. Walk Score 8/10, Transit Score 9/10.</t>
+          <t>Climatisation incluse, cour clôturée, balcon neuf, Walk Score 92, disponible 5 jours après acceptation. Chauffage/animaux/meublé non précisés.</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/ba98470a-66af-4439-89d7-a03111a24476?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2CC3A0DDDDDDDDDD2&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2897,27 +2897,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 Plateau-Mont-Royal, près du parc Laurier</t>
+          <t>5 1/2 rénové, 3 chambres, grande cour privée - rue Cuvillier (Hochelaga), à 5 min du métro Joliette</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>5483, Rue Cartier, Montréal</t>
+          <t>Rue Cuvillier, Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-plateau-disponible-des-maintenant/1742926253</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-in-hochelaga-internet-included-pet-friendly/1742899363</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
@@ -2962,19 +2962,19 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Libre immédiatement, 3 balcons (avant, arrière, latéral), remise et BBQ inclus, bail 1 an, animaux acceptés sous conditions, station BIXI à 2 min</t>
+          <t>Internet et électroménagers inclus (frigo, cuisinière, lave-vaisselle, laveuse-sécheuse), immense cour privée, chauffé à l'eau chaude incluse, animaux acceptés (chiens et chats), disponible 1er septembre 2026, bail 1 an.</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a1/a156df4e-a074-4098-9f9f-fa7b1b73bbed?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/dc/dc0af1fd-4be5-4589-b759-26be54d04e13?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2984,32 +2984,32 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 1200 pi², 3 chambres, balcon - rue Villeray, à ~10 min du métro De Castelnau</t>
+          <t>2 chambres rénové + bureau, 1233 pi², 2 balcons privés (vue rue et cour) - rue Beaudry (Plateau/Village), à 5 min des métros Beaudry et Sherbrooke (Marketplace)</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>3007, Rue Villeray, Montréal</t>
+          <t>2096, Rue Beaudry, Montréal, QC H2L 3G3</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -3019,27 +3019,27 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>De Castelnau</t>
+          <t>Beaudry</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/16587333</t>
+          <t>https://www.facebook.com/marketplace/item/1013235751248159</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
@@ -3049,19 +3049,19 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, cour clôturée, balcon neuf, Walk Score 92, disponible 5 jours après acceptation. Chauffage/animaux/meublé non précisés.</t>
+          <t>Triplex historique (1910), 3e étage, planchers de bois franc, cuisine électros inox, salle de bain avec plancher chauffant, 2 balcons privés, BBQ permis, non meublé, pas d'animaux, à deux pas du Parc Lafontaine et des rues St-Denis/Mont-Royal. Lien Facebook (connexion requise).</t>
         </is>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA2CC3A0DDDDDDDDDD2&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/708034371_1980439032561863_4399292961270502724_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=seOsuJ82OCgQ7kNvwHJQAF_&amp;_nc_oc=AdpIcN9dvrhSjH3cUUKe-1NoCXjdRPWkLEJHM1iRX0uSNM82UoGBmceDQc6ivHVJc0o&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=23FdRsoQlpiB5o1uD2RUxQ&amp;_nc_ss=7f2a8&amp;oh=00_AQE_v7UCx6SSbwxfLxWa52ow8tBnENPnwu6_KHRlOAjZ_w&amp;oe=6A91F461</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 3 chambres, grande cour privée - rue Cuvillier (Hochelaga), à 5 min du métro Joliette</t>
+          <t>5½ rénové (2 chambres), 1160 pi², 2 terrasses, stationnement inclus - rue Bossuet (Hochelaga), à ~10-12 min des métros Préfontaine/Joliette</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -3081,32 +3081,32 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Rue Cuvillier, Montréal, QC H1W 3A8</t>
+          <t>2502, Rue Bossuet, app. 305, Montréal, QC</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (2 terrasses)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Préfontaine ou Joliette (à confirmer)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10-12 (estimé)</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-in-hochelaga-internet-included-pet-friendly/1742899363</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22273952</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
@@ -3136,19 +3136,19 @@
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Internet et électroménagers inclus (frigo, cuisinière, lave-vaisselle, laveuse-sécheuse), immense cour privée, chauffé à l'eau chaude incluse, animaux acceptés (chiens et chats), disponible 1er septembre 2026, bail 1 an.</t>
+          <t>Dernier étage (construction 2004), meublé et équipé, 1 place de stationnement garage incluse, animaux non acceptés, non-fumeur, Walk Score 84, disponible 5 jours après acceptation du bail, jusqu'en mai 2027.</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/dc/dc0af1fd-4be5-4589-b759-26be54d04e13?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1D8268DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3158,32 +3158,32 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2 chambres rénové + bureau, 1233 pi², 2 balcons privés (vue rue et cour) - rue Beaudry (Plateau/Village), à 5 min des métros Beaudry et Sherbrooke (Marketplace)</t>
+          <t>5½ meublé, 3 chambres fermées, 1200 pi², terrasse arrière - rue Saint-Dominique (Mile-End/Plateau), à 10 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Le Plateau-Mont-Royal (Mile-End)</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2096, Rue Beaudry, Montréal, QC H2L 3G3</t>
+          <t>5561, Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -3193,27 +3193,27 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Beaudry</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1013235751248159</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5561-rue-saint-dominique-1139770</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Triplex historique (1910), 3e étage, planchers de bois franc, cuisine électros inox, salle de bain avec plancher chauffant, 2 balcons privés, BBQ permis, non meublé, pas d'animaux, à deux pas du Parc Lafontaine et des rues St-Denis/Mont-Royal. Lien Facebook (connexion requise).</t>
+          <t>Entièrement meublé et équipé (peut être loué non meublé), rez-de-chaussée, belle salle de bain avec laveuse-sécheuse, grand espace ouvert salon/salle à manger avec mur de brique, petite terrasse arrière, WiFi inclus, situé entre Mile-End et Plateau, disponible immédiatement</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/708034371_1980439032561863_4399292961270502724_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=seOsuJ82OCgQ7kNvwHJQAF_&amp;_nc_oc=AdpIcN9dvrhSjH3cUUKe-1NoCXjdRPWkLEJHM1iRX0uSNM82UoGBmceDQc6ivHVJc0o&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=23FdRsoQlpiB5o1uD2RUxQ&amp;_nc_ss=7f2a8&amp;oh=00_AQE_v7UCx6SSbwxfLxWa52ow8tBnENPnwu6_KHRlOAjZ_w&amp;oe=6A91F461</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139770/5-1-2-plateau-mont-royal-1600-15844601.jpg</t>
         </is>
       </c>
     </row>
@@ -3245,62 +3245,62 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (2 chambres), 1160 pi², 2 terrasses, stationnement inclus - rue Bossuet (Hochelaga), à ~10-12 min des métros Préfontaine/Joliette</t>
+          <t>5½, 3 chambres fermées, 1100 pi², accès terrasse - rue Saint-Dominique (Mile-End/Plateau), à 10 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal (Mile-End)</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>2502, Rue Bossuet, app. 305, Montréal, QC</t>
+          <t>5571, Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>oui (2 terrasses)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine ou Joliette (à confirmer)</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>10-12 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22273952</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5571-rue-saint-dominique-1139764</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
@@ -3310,19 +3310,19 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage (construction 2004), meublé et équipé, 1 place de stationnement garage incluse, animaux non acceptés, non-fumeur, Walk Score 84, disponible 5 jours après acceptation du bail, jusqu'en mai 2027.</t>
+          <t>Rez-de-chaussée, 3 chambres lumineuses avec rangement, accès à une petite terrasse pour BBQ + rangement, à quelques pas du boulevard Saint-Laurent, coeur du Mile-End, tous électros inclus, disponible immédiatement</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1D8268DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139764/plateau-mont-royal-1600-15844509.jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -3332,32 +3332,32 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé, 3 chambres fermées, 1200 pi², terrasse arrière - rue Saint-Dominique (Mile-End/Plateau), à 10 min du métro Rosemont</t>
+          <t>5½ meublé (2 chambres + bureau), terrasse privée + balcon - rue Rachel Est (Plateau) (Marketplace)</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal (Mile-End)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>5561, Rue Saint-Dominique, Montréal</t>
+          <t>1952, Rue Rachel Est, Montréal (H2H 1P7)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Papineau (à vérifier)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5561-rue-saint-dominique-1139770</t>
+          <t>https://www.facebook.com/marketplace/item/2292527024853183</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3397,19 +3397,19 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Entièrement meublé et équipé (peut être loué non meublé), rez-de-chaussée, belle salle de bain avec laveuse-sécheuse, grand espace ouvert salon/salle à manger avec mur de brique, petite terrasse arrière, WiFi inclus, situé entre Mile-End et Plateau, disponible immédiatement</t>
+          <t>Meublé tout inclus (chauffage, électricité, internet), dernier étage, 2 chambres fermées dont une avec balcon privé, terrasse privée additionnelle, disponible 1er oct. 2026, animaux refusés, près du Parc La Fontaine et des commerces du Plateau. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139770/5-1-2-plateau-mont-royal-1600-15844601.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/761611239_1396606412369389_589761538047184410_n.jpg?stp=c106.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=ByqmxtV-qr8Q7kNvwHv7fu1&amp;_nc_oc=Adqs88FQ5PCbjl9_ccROEdYgjrDJgwYGaQdpr82zVt8nSiGqfRrTTxeuF3rWdT2I8lQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=GNvZuYTYNEtOQRxhL_vEyQ&amp;_nc_ss=7f2a8&amp;oh=00_AQEV1OaYCcEikcQP70OW1e4Cl8IrZ927IG4qBoDioL_qlg&amp;oe=6A8A9DFD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -3419,17 +3419,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>5½, 3 chambres fermées, 1100 pi², accès terrasse - rue Saint-Dominique (Mile-End/Plateau), à 10 min du métro Rosemont</t>
+          <t>5 1/2 meuble (3 chambres), petite terrasse arriere - rue Saint-Dominique (Mile-End/Plateau), a 6 min du metro Rosemont</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal (Mile-End)</t>
+          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>5571, Rue Saint-Dominique, Montréal</t>
+          <t>5561, Rue Saint-Dominique, Montréal, QC</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -3464,17 +3464,17 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>logisquebec</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5571-rue-saint-dominique-1139764</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357976</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
@@ -3484,19 +3484,15 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, 3 chambres lumineuses avec rangement, accès à une petite terrasse pour BBQ + rangement, à quelques pas du boulevard Saint-Laurent, coeur du Mile-End, tous électros inclus, disponible immédiatement</t>
-        </is>
-      </c>
-      <c r="Q35" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202608/1139764/plateau-mont-royal-1600-15844509.jpg</t>
-        </is>
-      </c>
+          <t>Rez-de-chaussee, entierement meuble et equipe (louable non meuble), WiFi inclus, disponible immediatement, superficie annoncee jusqu'a 1200 pi2, chauffage non precise.</t>
+        </is>
+      </c>
+      <c r="Q35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -3506,7 +3502,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé (2 chambres + bureau), terrasse privée + balcon - rue Rachel Est (Plateau) (Marketplace)</t>
+          <t>5½ rénové (3 chambres), 1000 pi², balcon arrière - rue Saint-Dominique (Plateau-Mont-Royal), à 10 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -3516,22 +3512,22 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>1952, Rue Rachel Est, Montréal (H2H 1P7)</t>
+          <t>3477, Rue Saint-Dominique, Montréal, QC</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -3541,7 +3537,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Papineau (à vérifier)</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -3551,17 +3547,17 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2292527024853183</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-3477-rue-saint-dominique-1130024</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
@@ -3571,19 +3567,19 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Meublé tout inclus (chauffage, électricité, internet), dernier étage, 2 chambres fermées dont une avec balcon privé, terrasse privée additionnelle, disponible 1er oct. 2026, animaux refusés, près du Parc La Fontaine et des commerces du Plateau. Lien Facebook (connexion requise)</t>
+          <t>2e étage, électroménagers inclus (four, frigo, laveuse-sécheuse), à distance de marche du boul. Saint-Laurent, bars/restaurants/parcs, disponible 19 août 2026, politique animaux non précisée.</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/761611239_1396606412369389_589761538047184410_n.jpg?stp=c106.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=ByqmxtV-qr8Q7kNvwHv7fu1&amp;_nc_oc=Adqs88FQ5PCbjl9_ccROEdYgjrDJgwYGaQdpr82zVt8nSiGqfRrTTxeuF3rWdT2I8lQ&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=GNvZuYTYNEtOQRxhL_vEyQ&amp;_nc_ss=7f2a8&amp;oh=00_AQEV1OaYCcEikcQP70OW1e4Cl8IrZ927IG4qBoDioL_qlg&amp;oe=6A8A9DFD</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130024/plateau-mont-royal-600-15608538.jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3593,7 +3589,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meuble (3 chambres), petite terrasse arriere - rue Saint-Dominique (Mile-End/Plateau), a 6 min du metro Rosemont</t>
+          <t>5½ rénové, petite terrasse - rue Saint-Dominique (Plateau, limite Mile-End)</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -3603,7 +3599,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>5561, Rue Saint-Dominique, Montréal, QC</t>
+          <t>5571 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -3623,7 +3619,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (terrasse + rangement)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -3643,12 +3639,12 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>logisquebec</t>
+          <t>Logis Québec</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357976</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357647</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
@@ -3658,7 +3654,7 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussee, entierement meuble et equipe (louable non meuble), WiFi inclus, disponible immediatement, superficie annoncee jusqu'a 1200 pi2, chauffage non precise.</t>
+          <t>Disponible immédiatement. Même immeuble déjà repéré au 5561/5571 à 2075$ précédemment; nouvelle fiche à prix réduit.</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr"/>
@@ -3666,7 +3662,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -3676,27 +3672,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1000 pi², balcon arrière - rue Saint-Dominique (Plateau-Mont-Royal), à 10 min du métro Sherbrooke</t>
+          <t>5½ (3 chambres, 1250 pi²) avec balcon, plancher flottant neuf - rue Léonard-De Vinci, Villeray/Saint-Michel, à 11 min du métro Saint-Michel</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Saint-Michel/Villeray</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>3477, Rue Saint-Dominique, Montréal, QC</t>
+          <t>rue Léonard-De Vinci, entre 17e et 18e avenue, Montréal, QC H2A 2N9</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -3711,27 +3707,27 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-3477-rue-saint-dominique-1130024</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-dans-villeray-a-louer-pour-septembre/1741798163</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -3741,19 +3737,19 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>2e étage, électroménagers inclus (four, frigo, laveuse-sécheuse), à distance de marche du boul. Saint-Laurent, bars/restaurants/parcs, disponible 19 août 2026, politique animaux non précisée.</t>
+          <t>2e étage, plancher flottant neuf, aucun animal, non-fumeur, bail 1 an, disponible 1er septembre 2026.</t>
         </is>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130024/plateau-mont-royal-600-15608538.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5df5accb-8187-4cb7-a711-ee6ae12ae898?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -3763,7 +3759,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, petite terrasse - rue Saint-Dominique (Plateau, limite Mile-End)</t>
+          <t>5½ (3 chambres, 1100 pi²) meublé, mur de brique - rue Saint-Dominique, Plateau-Mont-Royal (limite Mile-End), à 6 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -3773,12 +3769,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>5571 Rue Saint-Dominique, Montréal</t>
+          <t>5561 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -3793,7 +3789,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>oui (terrasse + rangement)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -3813,12 +3809,12 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Logis Québec</t>
+          <t>Logisquebec</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357647</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357139</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
@@ -3828,10 +3824,14 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>Disponible immédiatement. Même immeuble déjà repéré au 5561/5571 à 2075$ précédemment; nouvelle fiche à prix réduit.</t>
-        </is>
-      </c>
-      <c r="Q39" s="5" t="inlineStr"/>
+          <t>Meublé et équipé, wifi inclus, disponible immédiatement, mur de brique apparent, salon/salle à manger ouvert.</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>https://i.logisquebec.com/i-a-louer/112098/357139/img_5778_jpg_6a7b438a91d83.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3846,27 +3846,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres, 1250 pi²) avec balcon, plancher flottant neuf - rue Léonard-De Vinci, Villeray/Saint-Michel, à 11 min du métro Saint-Michel</t>
+          <t>5½ (3 chambres, 1100 pi²) rez-de-chaussée avec terrasse - rue Saint-Dominique, Plateau-Mont-Royal (limite Mile-End), à 6 min du métro Rosemont</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel/Villeray</t>
+          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>rue Léonard-De Vinci, entre 17e et 18e avenue, Montréal, QC H2A 2N9</t>
+          <t>5571 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -3881,27 +3881,27 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Logisquebec</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-dans-villeray-a-louer-pour-septembre/1741798163</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357134</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
@@ -3911,19 +3911,19 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>2e étage, plancher flottant neuf, aucun animal, non-fumeur, bail 1 an, disponible 1er septembre 2026.</t>
+          <t>Rez-de-chaussée, accès à une petite terrasse (BBQ + rangement), tous électroménagers inclus, disponible immédiatement. Unité voisine de celle du 5561 Saint-Dominique (même secteur).</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5df5accb-8187-4cb7-a711-ee6ae12ae898?rule=kijijica-960-jpg</t>
+          <t>https://i.logisquebec.com/i-a-louer/112098/357134/758427288_10174783720475263_3825985666760897901_n_jpg_6a7b3e3cb1ac5.jpg</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3933,32 +3933,32 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres, 1100 pi²) meublé, mur de brique - rue Saint-Dominique, Plateau-Mont-Royal (limite Mile-End), à 6 min du métro Rosemont</t>
+          <t>Penthouse 2 étages (2 chambres, 1372-1400 pi²) avec 2 balcons - boul. Pie-IX, Hochelaga-Maisonneuve, à 10 min du métro Pie-IX</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>5561 Rue Saint-Dominique, Montréal</t>
+          <t>1859, Boulevard Pie-IX, Montréal, QC H1V 2C7</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -3968,27 +3968,27 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Logisquebec</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357139</t>
+          <t>https://www.zumper.com/listings/773677p/2-bedroom-maisonneuve-montreal-qc</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
@@ -3998,19 +3998,19 @@
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>Meublé et équipé, wifi inclus, disponible immédiatement, mur de brique apparent, salon/salle à manger ouvert.</t>
+          <t>Penthouse d'angle sur deux étages (1372 à 1400 pi² selon la fiche), 2 balcons privés dont un sur cour, non meublé, laveuse-sécheuse et lave-vaisselle inclus, stationnement inclus, aucun animal, chauffage/eau/électricité/internet non inclus, secteur Maisonneuve (pas Mercier), à la limite ouest de Pie-IX autorisée.</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>https://i.logisquebec.com/i-a-louer/112098/357139/img_5778_jpg_6a7b438a91d83.jpg</t>
+          <t>https://img.zumpercdn.com/491722127/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4020,27 +4020,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>5½ (3 chambres, 1100 pi²) rez-de-chaussée avec terrasse - rue Saint-Dominique, Plateau-Mont-Royal (limite Mile-End), à 6 min du métro Rosemont</t>
+          <t>5½ rénové (3 chambres), 1000 pi², grand balcon arrière privé - avenue Aird (Hochelaga), à 6 min du métro Pie-IX</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal (limite Mile-End)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>5571 Rue Saint-Dominique, Montréal</t>
+          <t>1692, Avenue Aird, Montréal, QC</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Logisquebec</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-le-plateau-mont-royal-l357134</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22918210</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
@@ -4085,19 +4085,19 @@
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, accès à une petite terrasse (BBQ + rangement), tous électroménagers inclus, disponible immédiatement. Unité voisine de celle du 5561 Saint-Dominique (même secteur).</t>
+          <t>Entièrement rénové, thermopompe incluse, 1 mois gratuit en promotion, animaux à discuter, disponible immédiatement, Walk Score 94.</t>
         </is>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>https://i.logisquebec.com/i-a-louer/112098/357134/758427288_10174783720475263_3825985666760897901_n_jpg_6a7b3e3cb1ac5.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE581B7BDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -4107,54 +4107,54 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Penthouse 2 étages (2 chambres, 1372-1400 pi²) avec 2 balcons - boul. Pie-IX, Hochelaga-Maisonneuve, à 10 min du métro Pie-IX</t>
+          <t>5½ entièrement rénové (3 chambres), 1000 pi², balcon - rue de la Visitation (Centre-Sud), à 2 min du métro Beaudry</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Ville-Marie (Sainte-Marie/Centre-Sud)</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>1859, Boulevard Pie-IX, Montréal, QC H1V 2C7</t>
+          <t>1576, Rue de la Visitation, Montréal, QC H2L 3C1</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Beaudry</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>Pie-IX</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
           <t>Zumper</t>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/listings/773677p/2-bedroom-maisonneuve-montreal-qc</t>
+          <t>https://www.zumper.com/apartment-buildings/p1126251/1568-1576-rue-de-la-visitation-sainte-marie-montreal-qc</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -4172,19 +4172,19 @@
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>Penthouse d'angle sur deux étages (1372 à 1400 pi² selon la fiche), 2 balcons privés dont un sur cour, non meublé, laveuse-sécheuse et lave-vaisselle inclus, stationnement inclus, aucun animal, chauffage/eau/électricité/internet non inclus, secteur Maisonneuve (pas Mercier), à la limite ouest de Pie-IX autorisée.</t>
+          <t>3 chambres fermées avec garde-robe et fenêtre, plancher de bois franc, laveuse-sécheuse, frigo et cuisinière inclus, chauffage électrique (~85$/mois), disponibilité 1er juillet/août/septembre selon l'unité.</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/491722127/1280x960?auto=format</t>
+          <t>https://img.zumpercdn.com/829563647/1280x960?dpr=1&amp;fit=crop&amp;h=542&amp;q=76&amp;w=991</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (3 chambres), 1000 pi², grand balcon arrière privé - avenue Aird (Hochelaga), à 6 min du métro Pie-IX</t>
+          <t>Grand 5½ (3 chambres), 1400 pi², 2 balcons (avant/arrière) - secteur Parc-Jarry (Villeray), près métro Jean-Talon</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>1692, Avenue Aird, Montréal, QC</t>
+          <t>n/d (secteur Parc-Jarry, Montréal, QC H2R 2E9)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -4229,27 +4229,27 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Jean-Talon</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>n/d (courte marche selon l'annonce)</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/22918210</t>
+          <t>https://www.zumper.com/apartments-for-rent/9730117p/3-bedroom-parc-jarry-montreal-qc</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
@@ -4259,19 +4259,19 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, thermopompe incluse, 1 mois gratuit en promotion, animaux à discuter, disponible immédiatement, Walk Score 94.</t>
+          <t>Chats acceptés (chiens refusés), proche marché Jean-Talon et Petite Italie ; la date de disponibilité affichée par la fiche (avril/mai) semble périmée, à valider auprès du proprio avant de contacter.</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE581B7BDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://img.zumpercdn.com/404533906/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -4281,27 +4281,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>5½ entièrement rénové (3 chambres), 1000 pi², balcon - rue de la Visitation (Centre-Sud), à 2 min du métro Beaudry</t>
+          <t>Spacieux 5½ (3 chambres, 2 salles de bain), garage - 20e Avenue (Rosemont, secteur Saint-Michel)</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Sainte-Marie/Centre-Sud)</t>
+          <t>Rosemont-La Petite-Patrie (secteur Saint-Michel)</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>1576, Rue de la Visitation, Montréal, QC H2L 3C1</t>
+          <t>6940, 20e Avenue, app. 201, Montréal</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -4316,27 +4316,27 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Beaudry</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/apartment-buildings/p1126251/1568-1576-rue-de-la-visitation-sainte-marie-montreal-qc</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/17444358</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
@@ -4346,19 +4346,19 @@
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées avec garde-robe et fenêtre, plancher de bois franc, laveuse-sécheuse, frigo et cuisinière inclus, chauffage électrique (~85$/mois), disponibilité 1er juillet/août/septembre selon l'unité.</t>
+          <t>Construit en 2016, cuisine ouverte équipée, garage intérieur + casier (150$/mois en sus), aucun animal ni fumeur accepté, disponible 10 jours après acceptation de la promesse de location.</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/829563647/1280x960?dpr=1&amp;fit=crop&amp;h=542&amp;q=76&amp;w=991</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE9F5F13DDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ (3 chambres), 1400 pi², 2 balcons (avant/arrière) - secteur Parc-Jarry (Villeray), près métro Jean-Talon</t>
+          <t>Grand logement 5½ sur deux niveaux, 3 chambres (2 au sous-sol), terrasse privée, +1300 pi² - rue Villeray</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Parc-Jarry, Montréal, QC H2R 2E9)</t>
+          <t>1180, Rue Villeray, Montréal, QC</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Jarry (estimé)</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>n/d (courte marche selon l'annonce)</t>
+          <t>n/d (estimé, non précisé par l'annonce)</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/apartments-for-rent/9730117p/3-bedroom-parc-jarry-montreal-qc</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/28201368</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
@@ -4433,19 +4433,19 @@
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>Chats acceptés (chiens refusés), proche marché Jean-Talon et Petite Italie ; la date de disponibilité affichée par la fiche (avril/mai) semble périmée, à valider auprès du proprio avant de contacter.</t>
+          <t>Sur deux niveaux, 2 chambres au sous-sol, 2 salles de bain, terrasse privée accessible depuis le salon, climatisation, chats acceptés (chiens refusés), disponible 1er juillet 2026, vérification de crédit exigée. Walk Score 97. Distance exacte au métro non précisée par l'annonce.</t>
         </is>
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/404533906/1280x960?auto=format</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA12F7C2DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -4455,32 +4455,32 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Spacieux 5½ (3 chambres, 2 salles de bain), garage - 20e Avenue (Rosemont, secteur Saint-Michel)</t>
+          <t>5½ rénové, 2 chambres fermées, 1129 pi², balcons avant/arrière - rue Cartier (Plateau-Mont-Royal, près métro Laurier)</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie (secteur Saint-Michel)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>6940, 20e Avenue, app. 201, Montréal</t>
+          <t>5228, Rue Cartier, Montréal</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -4490,17 +4490,17 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé, à vérifier)</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/17444358</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/27220680</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
@@ -4520,19 +4520,19 @@
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>Construit en 2016, cuisine ouverte équipée, garage intérieur + casier (150$/mois en sus), aucun animal ni fumeur accepté, disponible 10 jours après acceptation de la promesse de location.</t>
+          <t>2e étage d'un triplex de 1910, planchers de bois franc, salle de bain rénovée, une chambre avec grand lit double, coin lavage en cuisine, rue Cartier paisible, proche cafés/restos/parcs, animaux acceptés sous conditions, non-fumeur, dispo 1er juillet 2026, Walk Score 97 (distance exacte au métro Laurier non précisée par l'annonce)</t>
         </is>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE9F5F13DDDDDDDDDDA&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADBB74ADDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4542,27 +4542,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Grand logement 5½ sur deux niveaux, 3 chambres (2 au sous-sol), terrasse privée, +1300 pi² - rue Villeray</t>
+          <t>7½ rénové, 3 chambres, terrasse arrière - Village, près métros Beaudry/Papineau</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Ville-Marie (Village/Centre-Sud)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>1180, Rue Villeray, Montréal, QC</t>
+          <t>n/d (Rue Sainte-Catherine Est, secteur Village, Montréal)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -4572,32 +4572,32 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (terrasse arrière)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Jarry (estimé)</t>
+          <t>Beaudry ou Papineau</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>n/d (estimé, non précisé par l'annonce)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-villeray-saint-michel-parc-extension/28201368</t>
+          <t>https://www.facebook.com/marketplace/item/1667192434430051</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
@@ -4607,19 +4607,19 @@
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>Sur deux niveaux, 2 chambres au sous-sol, 2 salles de bain, terrasse privée accessible depuis le salon, climatisation, chats acceptés (chiens refusés), disponible 1er juillet 2026, vérification de crédit exigée. Walk Score 97. Distance exacte au métro non précisée par l'annonce.</t>
+          <t>Terrasse arrière, planchers bois franc, boiserie style centenaire, climatisation murale, près pont Jacques-Cartier et nombreux restos/cafés, lien exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA12F7C2DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/692069772_26712358195041265_6975725434404613474_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=K4QVlYLlbQQQ7kNvwE0KbUC&amp;_nc_oc=Adrk3RVHHBi5OgoT14PLqzSx6d01I7y8L2T47es6h11qi8YHvRoE9bE1E0Q_zayt4sA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=AakSf6B1WC1yfj4w57lVGA&amp;_nc_ss=7f2a8&amp;oh=00_AQCYGPel-1aXi7quArIAJzfowcbz2xzXa35Ilq-Fz-dWhw&amp;oe=6A6A7855</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4629,27 +4629,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové, 2 chambres fermées, 1129 pi², balcons avant/arrière - rue Cartier (Plateau-Mont-Royal, près métro Laurier)</t>
+          <t>Grand 5½ de 1240 pi² avec 2 balcons privés - rue de la Visitation (Centre-Sud), à 2 min du métro Beaudry</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Centre-Sud</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>5228, Rue Cartier, Montréal</t>
+          <t>1433, Rue de la Visitation, Montréal</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Beaudry</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé, à vérifier)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/27220680</t>
+          <t>https://www.facebook.com/marketplace/item/1675910780361896</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
@@ -4694,19 +4694,19 @@
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>2e étage d'un triplex de 1910, planchers de bois franc, salle de bain rénovée, une chambre avec grand lit double, coin lavage en cuisine, rue Cartier paisible, proche cafés/restos/parcs, animaux acceptés sous conditions, non-fumeur, dispo 1er juillet 2026, Walk Score 97 (distance exacte au métro Laurier non précisée par l'annonce)</t>
+          <t>2 chambres fermées + 1 chambre ouverte, grande cuisine moderne avec îlot central, salle de bain rénovée avec espace laveuse/sécheuse, lien exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADBB74ADDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/747978141_10167419432889256_7838070296744630358_n.jpg?stp=c273.0.652.652a_dst-jpg_tt6&amp;cstp=mx652x652&amp;ctp=s565x565&amp;_nc_cat=102&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=1BHIBLZMut0Q7kNvwGcjJKY&amp;_nc_oc=AdqL6QD8fVTD7q3J4l5WBnexTjWzHzx5_JFODaqPJQYjJbX5CNPnTI7QmCUqQifrkxQ&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=I01Huqn8cRYQWCF5daV0fw&amp;_nc_ss=7f2a8&amp;oh=00_AQCmBZgaUJOgbf9TtDkOp05R878cvx5VZPmstj6q8E25Kg&amp;oe=6A686D2B</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4716,27 +4716,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>7½ rénové, 3 chambres, terrasse arrière - Village, près métros Beaudry/Papineau</t>
+          <t>Grand 5 1/2, 3 chambres - avenue St-Germain (Hochelaga), à 10 min du métro Préfontaine</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Village/Centre-Sud)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>n/d (Rue Sainte-Catherine Est, secteur Village, Montréal)</t>
+          <t>1921 Rue St-Germain, Montréal (H1W 2T5)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>oui (terrasse arrière)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Beaudry ou Papineau</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1667192434430051</t>
+          <t>https://www.zumper.com/listings/20844079p/3-bedroom-hochelaga-montreal-qc</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>Terrasse arrière, planchers bois franc, boiserie style centenaire, climatisation murale, près pont Jacques-Cartier et nombreux restos/cafés, lien exige une connexion Facebook</t>
+          <t>Entièrement rénové, concept ouvert, climatisation, laveuse-sécheuse et lave-vaisselle inclus, grand balcon arrière, animaux acceptés, hydro en sus, disponible 1er oct. 2026 ; attention, la page affichait aussi 2495$ ailleurs sur l'annonce, à valider avant de contacter</t>
         </is>
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/692069772_26712358195041265_6975725434404613474_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=K4QVlYLlbQQQ7kNvwE0KbUC&amp;_nc_oc=Adrk3RVHHBi5OgoT14PLqzSx6d01I7y8L2T47es6h11qi8YHvRoE9bE1E0Q_zayt4sA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=AakSf6B1WC1yfj4w57lVGA&amp;_nc_ss=7f2a8&amp;oh=00_AQCYGPel-1aXi7quArIAJzfowcbz2xzXa35Ilq-Fz-dWhw&amp;oe=6A6A7855</t>
+          <t>https://img.zumpercdn.com/676603053/1280x960?auto=format</t>
         </is>
       </c>
     </row>
@@ -4803,32 +4803,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ de 1240 pi² avec 2 balcons privés - rue de la Visitation (Centre-Sud), à 2 min du métro Beaudry</t>
+          <t>Grand 6 1/2, 3 chambres avec cour - Parc-Jarry (Villeray), à 4 min du métro Jarry</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Centre-Sud</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>1433, Rue de la Visitation, Montréal</t>
+          <t>Secteur Parc-Jarry (H2R 2E9), Montréal</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -4838,27 +4838,27 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Beaudry</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Zumper</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1675910780361896</t>
+          <t>https://www.zumper.com/apartments-for-rent/14724140p/3-bedroom-parc-jarry-montreal-qc</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
@@ -4868,19 +4868,19 @@
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées + 1 chambre ouverte, grande cuisine moderne avec îlot central, salle de bain rénovée avec espace laveuse/sécheuse, lien exige une connexion Facebook</t>
+          <t>Immeuble restauré de 1924, planchers de bois franc, plafonds 9 pieds, balcons avant et arrière, chats seulement, disponible août/sept. 2026 ; la page affichait des mentions de bail datées 2018-2019, à vérifier auprès du proprio avant de contacter</t>
         </is>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/747978141_10167419432889256_7838070296744630358_n.jpg?stp=c273.0.652.652a_dst-jpg_tt6&amp;cstp=mx652x652&amp;ctp=s565x565&amp;_nc_cat=102&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=1BHIBLZMut0Q7kNvwGcjJKY&amp;_nc_oc=AdqL6QD8fVTD7q3J4l5WBnexTjWzHzx5_JFODaqPJQYjJbX5CNPnTI7QmCUqQifrkxQ&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=I01Huqn8cRYQWCF5daV0fw&amp;_nc_ss=7f2a8&amp;oh=00_AQCmBZgaUJOgbf9TtDkOp05R878cvx5VZPmstj6q8E25Kg&amp;oe=6A686D2B</t>
+          <t>https://img.zumpercdn.com/222665685/1280x960?auto=format</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres - avenue St-Germain (Hochelaga), à 10 min du métro Préfontaine</t>
+          <t>5½ neuf (OVILA), 3 chambres, terrasses privées - avenue Bennett (Hochelaga-Maisonneuve, près métro Pie-IX)</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -4900,17 +4900,17 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>1921 Rue St-Germain, Montréal (H1W 2T5)</t>
+          <t>2095, Avenue Bennett, Montréal</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/listings/20844079p/3-bedroom-hochelaga-montreal-qc</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/5-1-2-a-louer/hab-2095-avenue-bennett-1130234</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
@@ -4955,19 +4955,19 @@
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, concept ouvert, climatisation, laveuse-sécheuse et lave-vaisselle inclus, grand balcon arrière, animaux acceptés, hydro en sus, disponible 1er oct. 2026 ; attention, la page affichait aussi 2495$ ailleurs sur l'annonce, à valider avant de contacter</t>
+          <t>Construction neuve 2023-2024, climatisation murale, 5 électroménagers inclus, garde-robes walk-in, terrasses privées (BBQ permis), stationnement intérieur sécurisé + local vélo, ascenseur, juste en face du Marché Maisonneuve, superficie estimée entre 1050 et 1120 pi² selon l'annonce, à ~7 min du métro Pie-IX, prix à la limite haute du budget (2400$), disponibilité non précisée</t>
         </is>
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/676603053/1280x960?auto=format</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130234/4-1-2-mercier-hochelaga-maisonneuve-1600-15613083.jpg</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -4977,32 +4977,32 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2, 3 chambres avec cour - Parc-Jarry (Villeray), à 4 min du métro Jarry</t>
+          <t>4½ rénové, 2 chambres, 2 balcons - 38e Avenue (Rosemont)</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Secteur Parc-Jarry (H2R 2E9), Montréal</t>
+          <t>6180, 38e Avenue, Montréal</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -5012,27 +5012,27 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Pie-IX (à vérifier)</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>Zumper</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>https://www.zumper.com/apartments-for-rent/14724140p/3-bedroom-parc-jarry-montreal-qc</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6180-38e-avenue-1129076</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
@@ -5042,19 +5042,19 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>Immeuble restauré de 1924, planchers de bois franc, plafonds 9 pieds, balcons avant et arrière, chats seulement, disponible août/sept. 2026 ; la page affichait des mentions de bail datées 2018-2019, à vérifier auprès du proprio avant de contacter</t>
+          <t>RDC, 2 grandes chambres fermées, balcon avant et arrière, garage détaché + 1 place intérieure + 2 extérieures, rangement au sous-sol, cour arrière, animaux négociables, disponible maintenant (1er septembre), distance au métro Pie-IX estimée depuis l'adresse (non confirmée par l'annonce)</t>
         </is>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>https://img.zumpercdn.com/222665685/1280x960?auto=format</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1129076/4-1-2-rosemont-petite-patrie-600-15587619.jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>5½ neuf (OVILA), 3 chambres, terrasses privées - avenue Bennett (Hochelaga-Maisonneuve, près métro Pie-IX)</t>
+          <t>Grand 6½, 2 chambres + bureau, jardin privé clôturé - rue Cuvillier (Hochelaga-Maisonneuve), à qqs minutes du métro Joliette</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>2095, Avenue Bennett, Montréal</t>
+          <t>2265, Rue Cuvillier, Montréal</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -5109,39 +5109,39 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/5-1-2-a-louer/hab-2095-avenue-bennett-1130234</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/rare-:-grand-6-jardin-prive-chiens-et-chats-acceptes-metr/1744540259</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2023-2024, climatisation murale, 5 électroménagers inclus, garde-robes walk-in, terrasses privées (BBQ permis), stationnement intérieur sécurisé + local vélo, ascenseur, juste en face du Marché Maisonneuve, superficie estimée entre 1050 et 1120 pi² selon l'annonce, à ~7 min du métro Pie-IX, prix à la limite haute du budget (2400$), disponibilité non précisée</t>
+          <t>Jardin privé clôturé, chiens et chats acceptés (max 2), internet haute vitesse inclus, chauffage et eau chaude inclus (électricité en sus), libre 8 oct. 2026, bail jusqu'au 30 juin 2027</t>
         </is>
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1130234/4-1-2-mercier-hochelaga-maisonneuve-1600-15613083.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a3/a3ed511f-7786-47a1-98b6-1bd8ee837d8a?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres, 2 balcons - 38e Avenue (Rosemont)</t>
+          <t>5½ sur 2 étages, 2 chambres + bureau, balcon privé - rue Saint-André (Rosemont), à 3 min du métro Beaubien</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -5161,17 +5161,17 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>6180, 38e Avenue, Montréal</t>
+          <t>6790, Rue Saint-André, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -5186,42 +5186,42 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX (à vérifier)</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6180-38e-avenue-1129076</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/11517731</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>RDC, 2 grandes chambres fermées, balcon avant et arrière, garage détaché + 1 place intérieure + 2 extérieures, rangement au sous-sol, cour arrière, animaux négociables, disponible maintenant (1er septembre), distance au métro Pie-IX estimée depuis l'adresse (non confirmée par l'annonce)</t>
+          <t>Style maisonette sur 2 étages, 2 salles de bain complètes, bureau séparé (utilisable comme 3e chambre), climatisation murale, animaux non acceptés, fumeurs non acceptés, Walk Score 99, libre 1er sept. 2026</t>
         </is>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202604/1129076/4-1-2-rosemont-petite-patrie-600-15587619.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADA3CF3DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -10960,42 +10960,42 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N122" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O122" s="5" t="inlineStr">
@@ -11025,15 +11025,19 @@
       </c>
       <c r="P122" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q122" s="5" t="inlineStr"/>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q122" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -11043,7 +11047,7 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>3 chambres fermées, 900 pi², directement face au métro Pie-IX - boulevard Pie-IX (Hochelaga-Maisonneuve)</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -11053,17 +11057,17 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>2645, Boulevard Pie-IX, app. 1, Montréal</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -11073,7 +11077,7 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
@@ -11088,7 +11092,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M123" s="5" t="inlineStr">
@@ -11098,22 +11102,22 @@
       </c>
       <c r="N123" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/12105558</t>
         </is>
       </c>
       <c r="O123" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P123" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>Rénové, semi-meublé, électroménagers neufs, thermopompe murale, wifi et eau chaude inclus, stationnement extérieur optionnel 100$/mois, animaux acceptés sous conditions, disponible immédiatement</t>
         </is>
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DACE479EDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
